--- a/docs/鍵盤設計規格_方音符號輸入_台語音標編碼.xlsx
+++ b/docs/鍵盤設計規格_方音符號輸入_台語音標編碼.xlsx
@@ -8,37 +8,38 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81EBDEA-08F6-448A-BF5A-A7363F56F37B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{483B5F2C-798F-44C0-86C5-9BFFB7B64E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-195" windowWidth="38640" windowHeight="15720" xr2:uid="{6D6F034E-466E-416C-B3CC-1F7937B8DE3D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6D6F034E-466E-416C-B3CC-1F7937B8DE3D}"/>
   </bookViews>
   <sheets>
     <sheet name="xlit對映工具" sheetId="1" r:id="rId1"/>
     <sheet name="韻母列表" sheetId="4" r:id="rId2"/>
-    <sheet name="韻母列表 (2)" sheetId="5" r:id="rId3"/>
-    <sheet name="聲調符號" sheetId="3" r:id="rId4"/>
-    <sheet name="RIME設定【台語音標】" sheetId="2" r:id="rId5"/>
+    <sheet name="韻母列表 (陽聲韻轉換)" sheetId="5" r:id="rId3"/>
+    <sheet name="韻母列表 (3)" sheetId="6" r:id="rId4"/>
+    <sheet name="聲調符號" sheetId="3" r:id="rId5"/>
+    <sheet name="RIME設定【台語音標】" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RIME設定【台語音標】!$BR$4:$BT$59</definedName>
-    <definedName name="_xlnm.Criteria" localSheetId="4">RIME設定【台語音標】!$CQ$1:$CQ$2</definedName>
-    <definedName name="_xlnm.Extract" localSheetId="4">RIME設定【台語音標】!$CR$4:$CV$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">RIME設定【台語音標】!$BR$4:$BT$59</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="5">RIME設定【台語音標】!$CQ$1:$CQ$2</definedName>
+    <definedName name="_xlnm.Extract" localSheetId="5">RIME設定【台語音標】!$CR$4:$CV$4</definedName>
     <definedName name="十五音韻母">#REF!</definedName>
     <definedName name="十五音韻母對照表">#REF!</definedName>
-    <definedName name="方音符號" localSheetId="4">#REF!</definedName>
+    <definedName name="方音符號" localSheetId="5">#REF!</definedName>
     <definedName name="方音符號">#REF!</definedName>
     <definedName name="台羅韻母八音反切">#REF!</definedName>
     <definedName name="白話字韻母八音反切">#REF!</definedName>
-    <definedName name="字典編碼" localSheetId="4">#REF!</definedName>
+    <definedName name="字典編碼" localSheetId="5">#REF!</definedName>
     <definedName name="字典編碼">#REF!</definedName>
     <definedName name="注音符號">#REF!</definedName>
     <definedName name="注音編碼">#REF!</definedName>
-    <definedName name="拼音字母" localSheetId="4">#REF!</definedName>
+    <definedName name="拼音字母" localSheetId="5">#REF!</definedName>
     <definedName name="拼音字母">#REF!</definedName>
     <definedName name="閩拼韻母八音反切">#REF!</definedName>
     <definedName name="聲母碼">#REF!</definedName>
     <definedName name="聲母碼表">#REF!</definedName>
-    <definedName name="鍵盤位置" localSheetId="4">#REF!</definedName>
+    <definedName name="鍵盤位置" localSheetId="5">#REF!</definedName>
     <definedName name="鍵盤位置">#REF!</definedName>
     <definedName name="鍵盤按鍵">#REF!</definedName>
     <definedName name="韻母對照表">#REF!</definedName>
@@ -46,6 +47,7 @@
     <definedName name="顯示注音輸入">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -88,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="514">
   <si>
     <t>algebra:</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1889,6 +1891,93 @@
   </si>
   <si>
     <t>[48]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>aG</t>
+  </si>
+  <si>
+    <t>iG</t>
+  </si>
+  <si>
+    <t>iaG</t>
+  </si>
+  <si>
+    <t>ioG</t>
+  </si>
+  <si>
+    <t>oG</t>
+  </si>
+  <si>
+    <t>irG</t>
+  </si>
+  <si>
+    <t>eG</t>
+  </si>
+  <si>
+    <t>uaG</t>
+  </si>
+  <si>
+    <t>aN</t>
+  </si>
+  <si>
+    <t>iaN</t>
+  </si>
+  <si>
+    <t>uN</t>
+  </si>
+  <si>
+    <t>uaN</t>
+  </si>
+  <si>
+    <t>aM</t>
+  </si>
+  <si>
+    <t>iM</t>
+  </si>
+  <si>
+    <t>iaM</t>
+  </si>
+  <si>
+    <t>oM</t>
+  </si>
+  <si>
+    <t>irM</t>
+  </si>
+  <si>
+    <t>陽声韻</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>入場韻</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>([12357])</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>in</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>iN</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>陽韻韻組</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>irn</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RIME Script</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>字長</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2030,6 +2119,7 @@
       <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="SimSun"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="20"/>
@@ -2634,7 +2724,7 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="31">
+  <fills count="32">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2812,6 +2902,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAECF0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3085,7 +3181,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="255">
+  <cellXfs count="259">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3723,6 +3819,23 @@
     <xf numFmtId="0" fontId="108" fillId="29" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="105" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="108" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="107" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3750,20 +3863,11 @@
     <xf numFmtId="0" fontId="107" fillId="30" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="108" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="108" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4146,7 +4250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14158527-94DC-4FED-8C0E-3D91F976F89A}">
-  <dimension ref="A1:BP61"/>
+  <dimension ref="A1:BP62"/>
   <sheetFormatPr defaultRowHeight="25.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.3984375" style="1" customWidth="1"/>
@@ -5233,132 +5337,301 @@
       </c>
     </row>
     <row r="7" spans="1:68">
-      <c r="AR7" s="220" t="s">
+      <c r="C7" s="257"/>
+      <c r="D7" s="257"/>
+      <c r="E7" s="257"/>
+      <c r="F7" s="257"/>
+      <c r="G7" s="257"/>
+      <c r="H7" s="257"/>
+      <c r="I7" s="257"/>
+      <c r="J7" s="257"/>
+      <c r="K7" s="257"/>
+      <c r="L7" s="257"/>
+      <c r="M7" s="257"/>
+      <c r="N7" s="257"/>
+      <c r="O7" s="257"/>
+      <c r="P7" s="257"/>
+      <c r="Q7" s="257"/>
+      <c r="R7" s="257"/>
+      <c r="S7" s="257"/>
+      <c r="T7" s="257"/>
+      <c r="U7" s="257"/>
+      <c r="V7" s="257"/>
+      <c r="W7" s="257"/>
+      <c r="X7" s="257"/>
+      <c r="Y7" s="257"/>
+      <c r="Z7" s="257"/>
+      <c r="AA7" s="257"/>
+      <c r="AB7" s="257"/>
+      <c r="AC7" s="257"/>
+      <c r="AD7" s="257"/>
+      <c r="AE7" s="257"/>
+      <c r="AF7" s="257"/>
+      <c r="AG7" s="257"/>
+      <c r="AH7" s="257"/>
+      <c r="AI7" s="257"/>
+      <c r="AJ7" s="257"/>
+      <c r="AK7" s="257"/>
+      <c r="AL7" s="257"/>
+      <c r="AM7" s="257"/>
+      <c r="AN7" s="257"/>
+      <c r="AO7" s="257"/>
+      <c r="AP7" s="257"/>
+      <c r="AQ7" s="257"/>
+      <c r="AR7" s="257"/>
+      <c r="AS7" s="257"/>
+      <c r="AT7" s="257"/>
+      <c r="AU7" s="257"/>
+      <c r="AV7" s="257"/>
+      <c r="AW7" s="257"/>
+      <c r="AX7" s="257"/>
+      <c r="AY7" s="257"/>
+      <c r="AZ7" s="257"/>
+      <c r="BA7" s="257"/>
+      <c r="BB7" s="257"/>
+      <c r="BC7" s="257"/>
+      <c r="BD7" s="257"/>
+      <c r="BE7" s="257"/>
+      <c r="BF7" s="257"/>
+      <c r="BG7" s="257"/>
+      <c r="BH7" s="257"/>
+      <c r="BI7" s="257"/>
+      <c r="BJ7" s="257"/>
+      <c r="BL7" s="221">
+        <v>6</v>
+      </c>
+      <c r="BM7" s="221" t="str">
+        <v>t</v>
+      </c>
+      <c r="BN7" s="221" t="str">
+        <v>t</v>
+      </c>
+      <c r="BO7" s="221" t="str">
+        <v>2</v>
+      </c>
+      <c r="BP7" s="221" t="str">
+        <v>ㄉ</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="C8" s="258" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("""", C5:AY5, AZ5:BH5, """")</f>
+        <v>"!1qas2wxEedGYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7N"</v>
+      </c>
+      <c r="D8" s="257"/>
+      <c r="E8" s="257"/>
+      <c r="F8" s="257"/>
+      <c r="G8" s="257"/>
+      <c r="H8" s="257"/>
+      <c r="I8" s="257"/>
+      <c r="J8" s="257"/>
+      <c r="K8" s="257"/>
+      <c r="L8" s="257"/>
+      <c r="M8" s="257"/>
+      <c r="N8" s="257"/>
+      <c r="O8" s="257"/>
+      <c r="P8" s="257"/>
+      <c r="Q8" s="257"/>
+      <c r="R8" s="257"/>
+      <c r="S8" s="257"/>
+      <c r="T8" s="257"/>
+      <c r="U8" s="257"/>
+      <c r="V8" s="257"/>
+      <c r="W8" s="257"/>
+      <c r="X8" s="257"/>
+      <c r="Y8" s="257"/>
+      <c r="Z8" s="257"/>
+      <c r="AA8" s="257"/>
+      <c r="AB8" s="257"/>
+      <c r="AC8" s="257"/>
+      <c r="AD8" s="257"/>
+      <c r="AE8" s="257"/>
+      <c r="AF8" s="257"/>
+      <c r="AG8" s="257"/>
+      <c r="AH8" s="257"/>
+      <c r="AI8" s="257"/>
+      <c r="AJ8" s="257"/>
+      <c r="AK8" s="257"/>
+      <c r="AL8" s="257"/>
+      <c r="AM8" s="257"/>
+      <c r="AN8" s="257"/>
+      <c r="AO8" s="257"/>
+      <c r="AP8" s="257"/>
+      <c r="AQ8" s="257"/>
+      <c r="AR8" s="257"/>
+      <c r="AS8" s="257"/>
+      <c r="AT8" s="257"/>
+      <c r="AU8" s="257"/>
+      <c r="AV8" s="257"/>
+      <c r="AW8" s="257"/>
+      <c r="AX8" s="257"/>
+      <c r="AY8" s="257"/>
+      <c r="AZ8" s="257"/>
+      <c r="BA8" s="257"/>
+      <c r="BB8" s="257"/>
+      <c r="BC8" s="257"/>
+      <c r="BD8" s="257"/>
+      <c r="BE8" s="257"/>
+      <c r="BF8" s="257"/>
+      <c r="BG8" s="257"/>
+      <c r="BH8" s="257"/>
+      <c r="BI8" s="257"/>
+      <c r="BJ8" s="257"/>
+      <c r="BL8" s="221">
+        <v>7</v>
+      </c>
+      <c r="BM8" s="221" t="str">
+        <v>th</v>
+      </c>
+      <c r="BN8" s="221" t="str">
+        <v>T</v>
+      </c>
+      <c r="BO8" s="221" t="str">
+        <v>w</v>
+      </c>
+      <c r="BP8" s="221" t="str">
+        <v>ㄊ</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68">
+      <c r="C9" s="1" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("""",C5:AY5, """")</f>
+        <v>"!1qas2wxEedGYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"</v>
+      </c>
+      <c r="D9" s="257"/>
+      <c r="E9" s="257"/>
+      <c r="F9" s="257"/>
+      <c r="G9" s="257"/>
+      <c r="H9" s="257"/>
+      <c r="I9" s="257"/>
+      <c r="J9" s="257"/>
+      <c r="K9" s="257"/>
+      <c r="L9" s="257"/>
+      <c r="M9" s="257"/>
+      <c r="N9" s="257"/>
+      <c r="O9" s="257"/>
+      <c r="P9" s="257"/>
+      <c r="Q9" s="257"/>
+      <c r="R9" s="257"/>
+      <c r="S9" s="257"/>
+      <c r="T9" s="257"/>
+      <c r="U9" s="257"/>
+      <c r="V9" s="257"/>
+      <c r="W9" s="257"/>
+      <c r="X9" s="257"/>
+      <c r="Y9" s="257"/>
+      <c r="Z9" s="257"/>
+      <c r="AA9" s="257"/>
+      <c r="AB9" s="257"/>
+      <c r="AC9" s="257"/>
+      <c r="AD9" s="257"/>
+      <c r="AE9" s="257"/>
+      <c r="AF9" s="257"/>
+      <c r="AG9" s="257"/>
+      <c r="AH9" s="257"/>
+      <c r="AI9" s="257"/>
+      <c r="AJ9" s="257"/>
+      <c r="AK9" s="257"/>
+      <c r="AL9" s="257"/>
+      <c r="AM9" s="257"/>
+      <c r="AN9" s="257"/>
+      <c r="AO9" s="257"/>
+      <c r="AP9" s="257"/>
+      <c r="AQ9" s="257"/>
+      <c r="AR9" s="257"/>
+      <c r="AS9" s="257"/>
+      <c r="AT9" s="257"/>
+      <c r="AU9" s="257"/>
+      <c r="AV9" s="257"/>
+      <c r="AW9" s="257"/>
+      <c r="AX9" s="257"/>
+      <c r="AY9" s="257"/>
+      <c r="AZ9" s="257"/>
+      <c r="BA9" s="257"/>
+      <c r="BB9" s="257"/>
+      <c r="BC9" s="257"/>
+      <c r="BD9" s="257"/>
+      <c r="BE9" s="257"/>
+      <c r="BF9" s="257"/>
+      <c r="BG9" s="257"/>
+      <c r="BH9" s="257"/>
+      <c r="BI9" s="257"/>
+      <c r="BJ9" s="257"/>
+      <c r="BL9" s="221">
+        <v>8</v>
+      </c>
+      <c r="BM9" s="221" t="str">
+        <v>l</v>
+      </c>
+      <c r="BN9" s="221" t="str">
+        <v>l</v>
+      </c>
+      <c r="BO9" s="221" t="str">
+        <v>x</v>
+      </c>
+      <c r="BP9" s="221" t="str">
+        <v>ㄌ</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
+      <c r="AR10" s="220" t="s">
         <v>283</v>
       </c>
-      <c r="AS7" s="1" t="s">
+      <c r="AS10" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="AV7" s="1" t="str">
+      <c r="AV10" s="1" t="str">
         <f xml:space="preserve"> _xlfn.UNICHAR(HEX2DEC(RIGHT("U+207F",4)))</f>
         <v>ⁿ</v>
       </c>
-      <c r="BL7" s="221">
-        <v>6</v>
-      </c>
-      <c r="BM7" s="221" t="str">
-        <v>t</v>
-      </c>
-      <c r="BN7" s="221" t="str">
-        <v>t</v>
-      </c>
-      <c r="BO7" s="221" t="str">
-        <v>2</v>
-      </c>
-      <c r="BP7" s="221" t="str">
-        <v>ㄉ</v>
+      <c r="BL10" s="221">
+        <v>9</v>
+      </c>
+      <c r="BM10" s="221" t="str">
+        <v>ㆣ</v>
+      </c>
+      <c r="BN10" s="221" t="str">
+        <v>g</v>
+      </c>
+      <c r="BO10" s="221" t="str">
+        <v>E</v>
+      </c>
+      <c r="BP10" s="221" t="str">
+        <v>ㆣ</v>
       </c>
     </row>
-    <row r="8" spans="1:68">
-      <c r="A8" s="1" t="s">
+    <row r="11" spans="1:68">
+      <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="BL8" s="221">
-        <v>7</v>
-      </c>
-      <c r="BM8" s="221" t="str">
-        <v>th</v>
-      </c>
-      <c r="BN8" s="223" t="str">
-        <v>T</v>
-      </c>
-      <c r="BO8" s="221" t="str">
-        <v>w</v>
-      </c>
-      <c r="BP8" s="221" t="str">
-        <v>ㄊ</v>
+      <c r="BL11" s="221">
+        <v>10</v>
+      </c>
+      <c r="BM11" s="221" t="str">
+        <v>k</v>
+      </c>
+      <c r="BN11" s="223" t="str">
+        <v>k</v>
+      </c>
+      <c r="BO11" s="221" t="str">
+        <v>e</v>
+      </c>
+      <c r="BP11" s="221" t="str">
+        <v>ㄍ</v>
       </c>
     </row>
-    <row r="9" spans="1:68" outlineLevel="1">
-      <c r="B9" s="1" t="str">
+    <row r="12" spans="1:68" outlineLevel="1">
+      <c r="B12" s="1" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - xlit|", C4:BH4, "|", C5:BH5, "|")</f>
         <v xml:space="preserve">    - xlit|bpPmntTlgkKŋjzcshJZCSaiwueOəMNGRFQVIUY@AWHdfqrvxy17325840L|!1qas2wxEedGYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7N|</v>
       </c>
-      <c r="BL9" s="221">
-        <v>8</v>
-      </c>
-      <c r="BM9" s="221" t="str">
-        <v>l</v>
-      </c>
-      <c r="BN9" s="221" t="str">
-        <v>l</v>
-      </c>
-      <c r="BO9" s="221" t="str">
-        <v>x</v>
-      </c>
-      <c r="BP9" s="221" t="str">
-        <v>ㄌ</v>
-      </c>
-    </row>
-    <row r="10" spans="1:68" outlineLevel="1">
-      <c r="B10" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="BL10" s="221">
-        <v>9</v>
-      </c>
-      <c r="BM10" s="221" t="str">
-        <v>ㆣ</v>
-      </c>
-      <c r="BN10" s="221" t="str">
-        <v>g</v>
-      </c>
-      <c r="BO10" s="221" t="str">
-        <v>E</v>
-      </c>
-      <c r="BP10" s="221" t="str">
-        <v>ㆣ</v>
-      </c>
-    </row>
-    <row r="11" spans="1:68" outlineLevel="1">
-      <c r="A11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="1">
-        <f xml:space="preserve"> SEARCH("|", $B$9)</f>
-        <v>11</v>
-      </c>
-      <c r="BL11" s="221">
-        <v>10</v>
-      </c>
-      <c r="BM11" s="221" t="str">
-        <v>k</v>
-      </c>
-      <c r="BN11" s="221" t="str">
-        <v>k</v>
-      </c>
-      <c r="BO11" s="221" t="str">
-        <v>e</v>
-      </c>
-      <c r="BP11" s="221" t="str">
-        <v>ㄍ</v>
-      </c>
-    </row>
-    <row r="12" spans="1:68" outlineLevel="1">
-      <c r="A12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="1">
-        <f xml:space="preserve"> SEARCH("|", $B$9, B11+1)</f>
-        <v>70</v>
-      </c>
       <c r="BL12" s="221">
         <v>11</v>
       </c>
       <c r="BM12" s="221" t="str">
         <v>kh</v>
       </c>
-      <c r="BN12" s="223" t="str">
+      <c r="BN12" s="221" t="str">
         <v>K</v>
       </c>
       <c r="BO12" s="221" t="str">
@@ -5369,12 +5642,8 @@
       </c>
     </row>
     <row r="13" spans="1:68" outlineLevel="1">
-      <c r="A13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="1">
-        <f xml:space="preserve"> SEARCH("|", $B$9, B12+1)</f>
-        <v>129</v>
+      <c r="B13" s="2" t="s">
+        <v>286</v>
       </c>
       <c r="BL13" s="221">
         <v>12</v>
@@ -5382,7 +5651,7 @@
       <c r="BM13" s="221" t="str">
         <v>ng</v>
       </c>
-      <c r="BN13" s="223" t="str">
+      <c r="BN13" s="221" t="str">
         <v>ŋ</v>
       </c>
       <c r="BO13" s="221" t="str">
@@ -5393,13 +5662,20 @@
       </c>
     </row>
     <row r="14" spans="1:68" outlineLevel="1">
+      <c r="A14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="1">
+        <f xml:space="preserve"> SEARCH("|", $B$12)</f>
+        <v>11</v>
+      </c>
       <c r="BL14" s="221">
         <v>13</v>
       </c>
       <c r="BM14" s="221" t="str">
         <v>j</v>
       </c>
-      <c r="BN14" s="223" t="str">
+      <c r="BN14" s="221" t="str">
         <v>j</v>
       </c>
       <c r="BO14" s="221" t="str">
@@ -5411,15 +5687,11 @@
     </row>
     <row r="15" spans="1:68" outlineLevel="1">
       <c r="A15" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B15" s="1">
-        <f xml:space="preserve"> LEN(C15)</f>
-        <v>58</v>
-      </c>
-      <c r="C15" s="1" t="str">
-        <f xml:space="preserve"> MID($B$9,B11+1, (B12-B11-1))</f>
-        <v>bpPmntTlgkKŋjzcshJZCSaiwueOəMNGRFQVIUY@AWHdfqrvxy17325840L</v>
+        <f xml:space="preserve"> SEARCH("|", $B$12, B14+1)</f>
+        <v>70</v>
       </c>
       <c r="BL15" s="221">
         <v>14</v>
@@ -5439,15 +5711,11 @@
     </row>
     <row r="16" spans="1:68" outlineLevel="1">
       <c r="A16" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B16" s="1">
-        <f xml:space="preserve"> LEN(C16)</f>
-        <v>58</v>
-      </c>
-      <c r="C16" s="1" t="str">
-        <f xml:space="preserve"> MID($B$9,B12+1, (B13-B12-1))</f>
-        <v>!1qas2wxEedGYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7N</v>
+        <f xml:space="preserve"> SEARCH("|", $B$12, B15+1)</f>
+        <v>129</v>
       </c>
       <c r="BL16" s="221">
         <v>15</v>
@@ -5465,7 +5733,7 @@
         <v>ㄘ</v>
       </c>
     </row>
-    <row r="17" spans="1:68">
+    <row r="17" spans="1:68" outlineLevel="1">
       <c r="BL17" s="221">
         <v>16</v>
       </c>
@@ -5482,801 +5750,580 @@
         <v>ㄙ</v>
       </c>
     </row>
-    <row r="18" spans="1:68">
-      <c r="C18" s="3">
+    <row r="18" spans="1:68" outlineLevel="1">
+      <c r="A18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="1">
+        <f xml:space="preserve"> LEN(C18)</f>
+        <v>58</v>
+      </c>
+      <c r="C18" s="1" t="str">
+        <f xml:space="preserve"> MID($B$12,B14+1, (B15-B14-1))</f>
+        <v>bpPmntTlgkKŋjzcshJZCSaiwueOəMNGRFQVIUY@AWHdfqrvxy17325840L</v>
+      </c>
+      <c r="BL18" s="221">
+        <v>17</v>
+      </c>
+      <c r="BM18" s="221" t="str">
+        <v>h</v>
+      </c>
+      <c r="BN18" s="223" t="str">
+        <v>h</v>
+      </c>
+      <c r="BO18" s="221" t="str">
+        <v>c</v>
+      </c>
+      <c r="BP18" s="221" t="str">
+        <v>ㄏ</v>
+      </c>
+    </row>
+    <row r="19" spans="1:68" outlineLevel="1">
+      <c r="A19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1">
+        <f xml:space="preserve"> LEN(C19)</f>
+        <v>58</v>
+      </c>
+      <c r="C19" s="1" t="str">
+        <f xml:space="preserve"> MID($B$12,B15+1, (B16-B15-1))</f>
+        <v>!1qas2wxEedGYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7N</v>
+      </c>
+      <c r="BL19" s="221">
+        <v>18</v>
+      </c>
+      <c r="BM19" s="221" t="str">
+        <v>j(i)</v>
+      </c>
+      <c r="BN19" s="223" t="str">
+        <v>J</v>
+      </c>
+      <c r="BO19" s="221" t="str">
+        <v>R</v>
+      </c>
+      <c r="BP19" s="221" t="str">
+        <v>ㆢ</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68">
+      <c r="BL20" s="221">
+        <v>19</v>
+      </c>
+      <c r="BM20" s="221" t="str">
+        <v>z(i)</v>
+      </c>
+      <c r="BN20" s="223" t="str">
+        <v>Z</v>
+      </c>
+      <c r="BO20" s="221" t="str">
+        <v>r</v>
+      </c>
+      <c r="BP20" s="221" t="str">
+        <v>ㄐ</v>
+      </c>
+    </row>
+    <row r="21" spans="1:68">
+      <c r="C21" s="3">
         <f xml:space="preserve"> COLUMN() -2</f>
         <v>1</v>
       </c>
-      <c r="D18" s="3">
-        <f t="shared" ref="D18:BJ18" si="1" xml:space="preserve"> COLUMN() -2</f>
+      <c r="D21" s="3">
+        <f t="shared" ref="D21:BJ21" si="1" xml:space="preserve"> COLUMN() -2</f>
         <v>2</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E21" s="3">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F21" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G21" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H21" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I21" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J21" s="3">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K21" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L21" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M21" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N21" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O21" s="3">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P21" s="3">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q21" s="3">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R21" s="3">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S21" s="3">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="T18" s="3">
+      <c r="T21" s="3">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U21" s="3">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="V18" s="3">
+      <c r="V21" s="3">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="W18" s="3">
+      <c r="W21" s="3">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="X18" s="3">
+      <c r="X21" s="3">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Y21" s="3">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="Z21" s="3">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AA21" s="3">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AB21" s="3">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AC21" s="3">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AD21" s="3">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AE21" s="3">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AF21" s="3">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AG21" s="3">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AH21" s="3">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AI21" s="3">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AJ21" s="3">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AK21" s="3">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AL21" s="3">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AM21" s="3">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AN21" s="3">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AO21" s="3">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AP21" s="3">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="AQ18" s="3">
+      <c r="AQ21" s="3">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="AR18" s="3">
+      <c r="AR21" s="3">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="AS18" s="3">
+      <c r="AS21" s="3">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
-      <c r="AT18" s="3">
+      <c r="AT21" s="3">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="AU18" s="3">
+      <c r="AU21" s="3">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="AV18" s="3">
+      <c r="AV21" s="3">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="AW18" s="3">
+      <c r="AW21" s="3">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
-      <c r="AX18" s="3">
+      <c r="AX21" s="3">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="AY18" s="3">
+      <c r="AY21" s="3">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="AZ18" s="3">
+      <c r="AZ21" s="3">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="BA18" s="3">
+      <c r="BA21" s="3">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="BB18" s="3">
+      <c r="BB21" s="3">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="BC18" s="3">
+      <c r="BC21" s="3">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="BD18" s="3">
+      <c r="BD21" s="3">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="BE18" s="3">
+      <c r="BE21" s="3">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
-      <c r="BF18" s="3">
+      <c r="BF21" s="3">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="BG18" s="3">
+      <c r="BG21" s="3">
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
-      <c r="BH18" s="3">
+      <c r="BH21" s="3">
         <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="BI18" s="3">
+      <c r="BI21" s="3">
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
-      <c r="BJ18" s="3">
+      <c r="BJ21" s="3">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="BL18" s="221">
-        <v>17</v>
-      </c>
-      <c r="BM18" s="221" t="str">
-        <v>h</v>
-      </c>
-      <c r="BN18" s="223" t="str">
-        <v>h</v>
-      </c>
-      <c r="BO18" s="221" t="str">
-        <v>c</v>
-      </c>
-      <c r="BP18" s="221" t="str">
-        <v>ㄏ</v>
+      <c r="BL21" s="221">
+        <v>20</v>
+      </c>
+      <c r="BM21" s="221" t="str">
+        <v>c(i)</v>
+      </c>
+      <c r="BN21" s="223" t="str">
+        <v>C</v>
+      </c>
+      <c r="BO21" s="221" t="str">
+        <v>f</v>
+      </c>
+      <c r="BP21" s="221" t="str">
+        <v>ㄑ</v>
       </c>
     </row>
-    <row r="19" spans="1:68">
-      <c r="A19" s="4" t="s">
+    <row r="22" spans="1:68">
+      <c r="A22" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="5" t="str">
-        <f xml:space="preserve"> MID($C$15,C$18,1)</f>
+      <c r="C22" s="5" t="str">
+        <f xml:space="preserve"> MID($C$18,C$21,1)</f>
         <v>b</v>
       </c>
-      <c r="D19" s="5" t="str">
-        <f t="shared" ref="D19:BJ19" si="2" xml:space="preserve"> MID($C$15,D$18,1)</f>
+      <c r="D22" s="5" t="str">
+        <f t="shared" ref="D22:BJ22" si="2" xml:space="preserve"> MID($C$18,D$21,1)</f>
         <v>p</v>
       </c>
-      <c r="E19" s="5" t="str">
+      <c r="E22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>P</v>
       </c>
-      <c r="F19" s="5" t="str">
+      <c r="F22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>m</v>
       </c>
-      <c r="G19" s="5" t="str">
+      <c r="G22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>n</v>
       </c>
-      <c r="H19" s="5" t="str">
+      <c r="H22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>t</v>
       </c>
-      <c r="I19" s="5" t="str">
+      <c r="I22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>T</v>
       </c>
-      <c r="J19" s="5" t="str">
+      <c r="J22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>l</v>
       </c>
-      <c r="K19" s="5" t="str">
+      <c r="K22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>g</v>
       </c>
-      <c r="L19" s="5" t="str">
+      <c r="L22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>k</v>
       </c>
-      <c r="M19" s="5" t="str">
+      <c r="M22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>K</v>
       </c>
-      <c r="N19" s="5" t="str">
+      <c r="N22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>ŋ</v>
       </c>
-      <c r="O19" s="5" t="str">
+      <c r="O22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>j</v>
       </c>
-      <c r="P19" s="5" t="str">
+      <c r="P22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>z</v>
       </c>
-      <c r="Q19" s="5" t="str">
+      <c r="Q22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>c</v>
       </c>
-      <c r="R19" s="5" t="str">
+      <c r="R22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>s</v>
       </c>
-      <c r="S19" s="5" t="str">
+      <c r="S22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>h</v>
       </c>
-      <c r="T19" s="5" t="str">
+      <c r="T22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>J</v>
       </c>
-      <c r="U19" s="5" t="str">
+      <c r="U22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>Z</v>
       </c>
-      <c r="V19" s="5" t="str">
+      <c r="V22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>C</v>
       </c>
-      <c r="W19" s="5" t="str">
+      <c r="W22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>S</v>
       </c>
-      <c r="X19" s="5" t="str">
+      <c r="X22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>a</v>
       </c>
-      <c r="Y19" s="5" t="str">
+      <c r="Y22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>i</v>
       </c>
-      <c r="Z19" s="5" t="str">
+      <c r="Z22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>w</v>
       </c>
-      <c r="AA19" s="5" t="str">
+      <c r="AA22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>u</v>
       </c>
-      <c r="AB19" s="5" t="str">
+      <c r="AB22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>e</v>
       </c>
-      <c r="AC19" s="5" t="str">
+      <c r="AC22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>O</v>
       </c>
-      <c r="AD19" s="5" t="str">
+      <c r="AD22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>ə</v>
       </c>
-      <c r="AE19" s="5" t="str">
+      <c r="AE22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
-      <c r="AF19" s="5" t="str">
+      <c r="AF22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>N</v>
       </c>
-      <c r="AG19" s="5" t="str">
+      <c r="AG22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>G</v>
       </c>
-      <c r="AH19" s="5" t="str">
+      <c r="AH22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>R</v>
       </c>
-      <c r="AI19" s="5" t="str">
+      <c r="AI22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>F</v>
       </c>
-      <c r="AJ19" s="5" t="str">
+      <c r="AJ22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>Q</v>
       </c>
-      <c r="AK19" s="5" t="str">
+      <c r="AK22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>V</v>
       </c>
-      <c r="AL19" s="5" t="str">
+      <c r="AL22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>I</v>
       </c>
-      <c r="AM19" s="5" t="str">
+      <c r="AM22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>U</v>
       </c>
-      <c r="AN19" s="5" t="str">
+      <c r="AN22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>Y</v>
       </c>
-      <c r="AO19" s="5" t="str">
+      <c r="AO22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>@</v>
       </c>
-      <c r="AP19" s="5" t="str">
+      <c r="AP22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>A</v>
       </c>
-      <c r="AQ19" s="5" t="str">
+      <c r="AQ22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>W</v>
       </c>
-      <c r="AR19" s="5" t="str">
+      <c r="AR22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>H</v>
       </c>
-      <c r="AS19" s="5" t="str">
+      <c r="AS22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>d</v>
       </c>
-      <c r="AT19" s="5" t="str">
+      <c r="AT22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>f</v>
       </c>
-      <c r="AU19" s="5" t="str">
+      <c r="AU22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>q</v>
       </c>
-      <c r="AV19" s="5" t="str">
+      <c r="AV22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>r</v>
       </c>
-      <c r="AW19" s="5" t="str">
+      <c r="AW22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>v</v>
       </c>
-      <c r="AX19" s="5" t="str">
+      <c r="AX22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>x</v>
       </c>
-      <c r="AY19" s="5" t="str">
+      <c r="AY22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>y</v>
       </c>
-      <c r="AZ19" s="5" t="str">
+      <c r="AZ22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="BA19" s="5" t="str">
+      <c r="BA22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="BB19" s="5" t="str">
+      <c r="BB22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="BC19" s="5" t="str">
+      <c r="BC22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="BD19" s="5" t="str">
+      <c r="BD22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="BE19" s="5" t="str">
+      <c r="BE22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="BF19" s="5" t="str">
+      <c r="BF22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="BG19" s="5" t="str">
+      <c r="BG22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BH19" s="5" t="str">
+      <c r="BH22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>L</v>
       </c>
-      <c r="BI19" s="5" t="str">
+      <c r="BI22" s="5" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="BJ19" s="5" t="str">
+      <c r="BJ22" s="5" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="BL19" s="221">
-        <v>18</v>
-      </c>
-      <c r="BM19" s="221" t="str">
-        <v>j(i)</v>
-      </c>
-      <c r="BN19" s="223" t="str">
-        <v>J</v>
-      </c>
-      <c r="BO19" s="221" t="str">
-        <v>R</v>
-      </c>
-      <c r="BP19" s="221" t="str">
-        <v>ㆢ</v>
-      </c>
-    </row>
-    <row r="20" spans="1:68">
-      <c r="A20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="6" t="str">
-        <f xml:space="preserve"> MID($C$16,C$18,1)</f>
-        <v>!</v>
-      </c>
-      <c r="D20" s="6" t="str">
-        <f t="shared" ref="D20:BJ20" si="3" xml:space="preserve"> MID($C$16,D$18,1)</f>
-        <v>1</v>
-      </c>
-      <c r="E20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>q</v>
-      </c>
-      <c r="F20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>a</v>
-      </c>
-      <c r="G20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>s</v>
-      </c>
-      <c r="H20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="I20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>w</v>
-      </c>
-      <c r="J20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>x</v>
-      </c>
-      <c r="K20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>E</v>
-      </c>
-      <c r="L20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>e</v>
-      </c>
-      <c r="M20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>d</v>
-      </c>
-      <c r="N20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>G</v>
-      </c>
-      <c r="O20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>Y</v>
-      </c>
-      <c r="P20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>y</v>
-      </c>
-      <c r="Q20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>h</v>
-      </c>
-      <c r="R20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>n</v>
-      </c>
-      <c r="S20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>c</v>
-      </c>
-      <c r="T20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>R</v>
-      </c>
-      <c r="U20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>r</v>
-      </c>
-      <c r="V20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>f</v>
-      </c>
-      <c r="W20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>v</v>
-      </c>
-      <c r="X20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="Y20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>u</v>
-      </c>
-      <c r="Z20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>K</v>
-      </c>
-      <c r="AA20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>j</v>
-      </c>
-      <c r="AB20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>,</v>
-      </c>
-      <c r="AC20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>i</v>
-      </c>
-      <c r="AD20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>k</v>
-      </c>
-      <c r="AE20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>m</v>
-      </c>
-      <c r="AF20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>p</v>
-      </c>
-      <c r="AG20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>/</v>
-      </c>
-      <c r="AH20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>b</v>
-      </c>
-      <c r="AI20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>t</v>
-      </c>
-      <c r="AJ20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>g</v>
-      </c>
-      <c r="AK20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>z</v>
-      </c>
-      <c r="AL20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
-      <c r="AM20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>l</v>
-      </c>
-      <c r="AN20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>M</v>
-      </c>
-      <c r="AO20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AP20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>;</v>
-      </c>
-      <c r="AQ20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>O</v>
-      </c>
-      <c r="AR20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>o</v>
-      </c>
-      <c r="AS20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>*</v>
-      </c>
-      <c r="AT20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>U</v>
-      </c>
-      <c r="AU20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>J</v>
-      </c>
-      <c r="AV20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>&lt;</v>
-      </c>
-      <c r="AW20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>I</v>
-      </c>
-      <c r="AX20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>(</v>
-      </c>
-      <c r="AY20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>L</v>
-      </c>
-      <c r="AZ20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>:</v>
-      </c>
-      <c r="BA20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="BB20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="BC20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="BD20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="BE20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>]</v>
-      </c>
-      <c r="BF20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>[</v>
-      </c>
-      <c r="BG20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
-      <c r="BH20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>N</v>
-      </c>
-      <c r="BI20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="BJ20" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="BL20" s="221">
-        <v>19</v>
-      </c>
-      <c r="BM20" s="221" t="str">
-        <v>z(i)</v>
-      </c>
-      <c r="BN20" s="223" t="str">
-        <v>Z</v>
-      </c>
-      <c r="BO20" s="221" t="str">
-        <v>r</v>
-      </c>
-      <c r="BP20" s="221" t="str">
-        <v>ㄐ</v>
-      </c>
-    </row>
-    <row r="21" spans="1:68">
-      <c r="BL21" s="221">
-        <v>20</v>
-      </c>
-      <c r="BM21" s="221" t="str">
-        <v>c(i)</v>
-      </c>
-      <c r="BN21" s="223" t="str">
-        <v>C</v>
-      </c>
-      <c r="BO21" s="221" t="str">
-        <v>f</v>
-      </c>
-      <c r="BP21" s="221" t="str">
-        <v>ㄑ</v>
-      </c>
-    </row>
-    <row r="22" spans="1:68">
       <c r="BL22" s="221">
         <v>21</v>
       </c>
@@ -6295,7 +6342,247 @@
     </row>
     <row r="23" spans="1:68">
       <c r="A23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="6" t="str">
+        <f xml:space="preserve"> MID($C$19,C$21,1)</f>
+        <v>!</v>
+      </c>
+      <c r="D23" s="6" t="str">
+        <f t="shared" ref="D23:BJ23" si="3" xml:space="preserve"> MID($C$19,D$21,1)</f>
+        <v>1</v>
+      </c>
+      <c r="E23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>q</v>
+      </c>
+      <c r="F23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>a</v>
+      </c>
+      <c r="G23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>s</v>
+      </c>
+      <c r="H23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="I23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>w</v>
+      </c>
+      <c r="J23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>x</v>
+      </c>
+      <c r="K23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>E</v>
+      </c>
+      <c r="L23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>e</v>
+      </c>
+      <c r="M23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>d</v>
+      </c>
+      <c r="N23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>G</v>
+      </c>
+      <c r="O23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>Y</v>
+      </c>
+      <c r="P23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>y</v>
+      </c>
+      <c r="Q23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>h</v>
+      </c>
+      <c r="R23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>n</v>
+      </c>
+      <c r="S23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>c</v>
+      </c>
+      <c r="T23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>R</v>
+      </c>
+      <c r="U23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>r</v>
+      </c>
+      <c r="V23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>f</v>
+      </c>
+      <c r="W23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>v</v>
+      </c>
+      <c r="X23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="Y23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>u</v>
+      </c>
+      <c r="Z23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>K</v>
+      </c>
+      <c r="AA23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>j</v>
+      </c>
+      <c r="AB23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>,</v>
+      </c>
+      <c r="AC23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>i</v>
+      </c>
+      <c r="AD23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>k</v>
+      </c>
+      <c r="AE23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>m</v>
+      </c>
+      <c r="AF23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>p</v>
+      </c>
+      <c r="AG23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>/</v>
+      </c>
+      <c r="AH23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>b</v>
+      </c>
+      <c r="AI23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>t</v>
+      </c>
+      <c r="AJ23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>g</v>
+      </c>
+      <c r="AK23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>z</v>
+      </c>
+      <c r="AL23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="AM23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>l</v>
+      </c>
+      <c r="AN23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>M</v>
+      </c>
+      <c r="AO23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AP23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>;</v>
+      </c>
+      <c r="AQ23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>O</v>
+      </c>
+      <c r="AR23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>o</v>
+      </c>
+      <c r="AS23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>*</v>
+      </c>
+      <c r="AT23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>U</v>
+      </c>
+      <c r="AU23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>J</v>
+      </c>
+      <c r="AV23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>&lt;</v>
+      </c>
+      <c r="AW23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>I</v>
+      </c>
+      <c r="AX23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>(</v>
+      </c>
+      <c r="AY23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>L</v>
+      </c>
+      <c r="AZ23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>:</v>
+      </c>
+      <c r="BA23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="BB23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="BC23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="BD23" s="6" t="str">
+        <f t="shared" si="3"/>
         <v>6</v>
+      </c>
+      <c r="BE23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>]</v>
+      </c>
+      <c r="BF23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>[</v>
+      </c>
+      <c r="BG23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="BH23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>N</v>
+      </c>
+      <c r="BI23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="BJ23" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="BL23" s="221">
         <v>22</v>
@@ -6303,7 +6590,7 @@
       <c r="BM23" s="221" t="str">
         <v>a</v>
       </c>
-      <c r="BN23" s="221" t="str">
+      <c r="BN23" s="223" t="str">
         <v>a</v>
       </c>
       <c r="BO23" s="221" t="str">
@@ -6313,76 +6600,65 @@
         <v>ㄚ</v>
       </c>
     </row>
-    <row r="24" spans="1:68" outlineLevel="1">
-      <c r="B24" s="1" t="str">
+    <row r="24" spans="1:68">
+      <c r="BL24" s="221">
+        <v>23</v>
+      </c>
+      <c r="BM24" s="221" t="str">
+        <v>i</v>
+      </c>
+      <c r="BN24" s="223" t="str">
+        <v>i</v>
+      </c>
+      <c r="BO24" s="221" t="str">
+        <v>u</v>
+      </c>
+      <c r="BP24" s="221" t="str">
+        <v>ㄧ</v>
+      </c>
+    </row>
+    <row r="25" spans="1:68">
+      <c r="BL25" s="221">
+        <v>24</v>
+      </c>
+      <c r="BM25" s="221" t="str">
+        <v>ir</v>
+      </c>
+      <c r="BN25" s="223" t="str">
+        <v>w</v>
+      </c>
+      <c r="BO25" s="221" t="str">
+        <v>K</v>
+      </c>
+      <c r="BP25" s="221" t="str">
+        <v>ㆨ</v>
+      </c>
+    </row>
+    <row r="26" spans="1:68">
+      <c r="A26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="BL26" s="221">
+        <v>25</v>
+      </c>
+      <c r="BM26" s="221" t="str">
+        <v>u</v>
+      </c>
+      <c r="BN26" s="221" t="str">
+        <v>u</v>
+      </c>
+      <c r="BO26" s="221" t="str">
+        <v>j</v>
+      </c>
+      <c r="BP26" s="221" t="str">
+        <v>ㄨ</v>
+      </c>
+    </row>
+    <row r="27" spans="1:68" outlineLevel="1">
+      <c r="B27" s="1" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - xlit|", C5:BH5, "|", C6:BH6, "|")</f>
         <v xml:space="preserve">    - xlit|!1qas2wxEedGYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7N|ㆠㄅㄆㄇㄋㄉㄊㄌㆣㄍㄎㄫㆡㄗㄘㄙㄏㆢㄐㄑㄒㄚㄧㆨㄨㆤㆦㄜㆬㄣㆭㆴㆵㆻㆷㄞㄠㆰㄢㄤㆱㆲㆩㆪㆫㆥㆧㆮㆯ一七三二五八四入ㄥ|</v>
       </c>
-      <c r="BL24" s="221">
-        <v>23</v>
-      </c>
-      <c r="BM24" s="221" t="str">
-        <v>i</v>
-      </c>
-      <c r="BN24" s="221" t="str">
-        <v>i</v>
-      </c>
-      <c r="BO24" s="221" t="str">
-        <v>u</v>
-      </c>
-      <c r="BP24" s="221" t="str">
-        <v>ㄧ</v>
-      </c>
-    </row>
-    <row r="25" spans="1:68" outlineLevel="1">
-      <c r="BL25" s="221">
-        <v>24</v>
-      </c>
-      <c r="BM25" s="221" t="str">
-        <v>ir</v>
-      </c>
-      <c r="BN25" s="221" t="str">
-        <v>w</v>
-      </c>
-      <c r="BO25" s="221" t="str">
-        <v>K</v>
-      </c>
-      <c r="BP25" s="221" t="str">
-        <v>ㆨ</v>
-      </c>
-    </row>
-    <row r="26" spans="1:68" outlineLevel="1">
-      <c r="A26" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="1">
-        <f xml:space="preserve"> SEARCH("|", $B$24)</f>
-        <v>11</v>
-      </c>
-      <c r="BL26" s="221">
-        <v>25</v>
-      </c>
-      <c r="BM26" s="221" t="str">
-        <v>u</v>
-      </c>
-      <c r="BN26" s="221" t="str">
-        <v>u</v>
-      </c>
-      <c r="BO26" s="221" t="str">
-        <v>j</v>
-      </c>
-      <c r="BP26" s="221" t="str">
-        <v>ㄨ</v>
-      </c>
-    </row>
-    <row r="27" spans="1:68" outlineLevel="1">
-      <c r="A27" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="1">
-        <f xml:space="preserve"> SEARCH("|", $B$24, B26+1)</f>
-        <v>70</v>
-      </c>
       <c r="BL27" s="221">
         <v>26</v>
       </c>
@@ -6400,13 +6676,6 @@
       </c>
     </row>
     <row r="28" spans="1:68" outlineLevel="1">
-      <c r="A28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="1">
-        <f xml:space="preserve"> SEARCH("|", $B$24, B27+1)</f>
-        <v>129</v>
-      </c>
       <c r="BL28" s="221">
         <v>27</v>
       </c>
@@ -6424,6 +6693,13 @@
       </c>
     </row>
     <row r="29" spans="1:68" outlineLevel="1">
+      <c r="A29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="1">
+        <f xml:space="preserve"> SEARCH("|", $B$27)</f>
+        <v>11</v>
+      </c>
       <c r="BL29" s="221">
         <v>28</v>
       </c>
@@ -6442,15 +6718,11 @@
     </row>
     <row r="30" spans="1:68" outlineLevel="1">
       <c r="A30" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B30" s="1">
-        <f xml:space="preserve"> LEN(C30)</f>
-        <v>58</v>
-      </c>
-      <c r="C30" s="1" t="str">
-        <f xml:space="preserve"> MID($B$24,B26+1, (B27-B26-1))</f>
-        <v>!1qas2wxEedGYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7N</v>
+        <f xml:space="preserve"> SEARCH("|", $B$27, B29+1)</f>
+        <v>70</v>
       </c>
       <c r="BL30" s="221">
         <v>29</v>
@@ -6470,15 +6742,11 @@
     </row>
     <row r="31" spans="1:68" outlineLevel="1">
       <c r="A31" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B31" s="1">
-        <f xml:space="preserve"> LEN(C31)</f>
-        <v>58</v>
-      </c>
-      <c r="C31" s="1" t="str">
-        <f xml:space="preserve"> MID($B$24,B27+1, (B28-B27-1))</f>
-        <v>ㆠㄅㄆㄇㄋㄉㄊㄌㆣㄍㄎㄫㆡㄗㄘㄙㄏㆢㄐㄑㄒㄚㄧㆨㄨㆤㆦㄜㆬㄣㆭㆴㆵㆻㆷㄞㄠㆰㄢㄤㆱㆲㆩㆪㆫㆥㆧㆮㆯ一七三二五八四入ㄥ</v>
+        <f xml:space="preserve"> SEARCH("|", $B$27, B30+1)</f>
+        <v>129</v>
       </c>
       <c r="BL31" s="221">
         <v>30</v>
@@ -6496,7 +6764,7 @@
         <v>ㄣ</v>
       </c>
     </row>
-    <row r="32" spans="1:68">
+    <row r="32" spans="1:68" outlineLevel="1">
       <c r="BL32" s="221">
         <v>31</v>
       </c>
@@ -6513,1085 +6781,1107 @@
         <v>ㆭ</v>
       </c>
     </row>
-    <row r="33" spans="1:68">
-      <c r="C33" s="3">
+    <row r="33" spans="1:68" outlineLevel="1">
+      <c r="A33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="1">
+        <f xml:space="preserve"> LEN(C33)</f>
+        <v>58</v>
+      </c>
+      <c r="C33" s="1" t="str">
+        <f xml:space="preserve"> MID($B$27,B29+1, (B30-B29-1))</f>
+        <v>!1qas2wxEedGYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7N</v>
+      </c>
+      <c r="BL33" s="221">
+        <v>32</v>
+      </c>
+      <c r="BM33" s="221" t="str">
+        <v>-p</v>
+      </c>
+      <c r="BN33" s="221" t="str">
+        <v>R</v>
+      </c>
+      <c r="BO33" s="221" t="str">
+        <v>b</v>
+      </c>
+      <c r="BP33" s="221" t="str">
+        <v>ㆴ</v>
+      </c>
+    </row>
+    <row r="34" spans="1:68" outlineLevel="1">
+      <c r="A34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="1">
+        <f xml:space="preserve"> LEN(C34)</f>
+        <v>58</v>
+      </c>
+      <c r="C34" s="1" t="str">
+        <f xml:space="preserve"> MID($B$27,B30+1, (B31-B30-1))</f>
+        <v>ㆠㄅㄆㄇㄋㄉㄊㄌㆣㄍㄎㄫㆡㄗㄘㄙㄏㆢㄐㄑㄒㄚㄧㆨㄨㆤㆦㄜㆬㄣㆭㆴㆵㆻㆷㄞㄠㆰㄢㄤㆱㆲㆩㆪㆫㆥㆧㆮㆯ一七三二五八四入ㄥ</v>
+      </c>
+      <c r="BL34" s="221">
+        <v>33</v>
+      </c>
+      <c r="BM34" s="221" t="str">
+        <v>-t</v>
+      </c>
+      <c r="BN34" s="221" t="str">
+        <v>F</v>
+      </c>
+      <c r="BO34" s="221" t="str">
+        <v>t</v>
+      </c>
+      <c r="BP34" s="221" t="str">
+        <v>ㆵ</v>
+      </c>
+    </row>
+    <row r="35" spans="1:68">
+      <c r="BL35" s="221">
+        <v>34</v>
+      </c>
+      <c r="BM35" s="221" t="str">
+        <v>-k</v>
+      </c>
+      <c r="BN35" s="221" t="str">
+        <v>Q</v>
+      </c>
+      <c r="BO35" s="221" t="str">
+        <v>g</v>
+      </c>
+      <c r="BP35" s="221" t="str">
+        <v>ㆻ</v>
+      </c>
+    </row>
+    <row r="36" spans="1:68">
+      <c r="C36" s="3">
         <f xml:space="preserve"> COLUMN() -2</f>
         <v>1</v>
       </c>
-      <c r="D33" s="3">
-        <f t="shared" ref="D33:BJ33" si="4" xml:space="preserve"> COLUMN() -2</f>
+      <c r="D36" s="3">
+        <f t="shared" ref="D36:BJ36" si="4" xml:space="preserve"> COLUMN() -2</f>
         <v>2</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E36" s="3">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F36" s="3">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G36" s="3">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H36" s="3">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="I33" s="3">
+      <c r="I36" s="3">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="J33" s="3">
+      <c r="J36" s="3">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K36" s="3">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L36" s="3">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M36" s="3">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="N33" s="3">
+      <c r="N36" s="3">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O36" s="3">
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="P33" s="3">
+      <c r="P36" s="3">
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q36" s="3">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="R33" s="3">
+      <c r="R36" s="3">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="S33" s="3">
+      <c r="S36" s="3">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="T33" s="3">
+      <c r="T36" s="3">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="U33" s="3">
+      <c r="U36" s="3">
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="V33" s="3">
+      <c r="V36" s="3">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="W33" s="3">
+      <c r="W36" s="3">
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="X33" s="3">
+      <c r="X36" s="3">
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Y36" s="3">
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="Z36" s="3">
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AA36" s="3">
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AB36" s="3">
         <f t="shared" si="4"/>
         <v>26</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AC36" s="3">
         <f t="shared" si="4"/>
         <v>27</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AD36" s="3">
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AE36" s="3">
         <f t="shared" si="4"/>
         <v>29</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AF36" s="3">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AG36" s="3">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AH36" s="3">
         <f t="shared" si="4"/>
         <v>32</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AI36" s="3">
         <f t="shared" si="4"/>
         <v>33</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AJ36" s="3">
         <f t="shared" si="4"/>
         <v>34</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AK36" s="3">
         <f t="shared" si="4"/>
         <v>35</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AL36" s="3">
         <f t="shared" si="4"/>
         <v>36</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AM36" s="3">
         <f t="shared" si="4"/>
         <v>37</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AN36" s="3">
         <f t="shared" si="4"/>
         <v>38</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AO36" s="3">
         <f t="shared" si="4"/>
         <v>39</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AP36" s="3">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="AQ33" s="3">
+      <c r="AQ36" s="3">
         <f t="shared" si="4"/>
         <v>41</v>
       </c>
-      <c r="AR33" s="3">
+      <c r="AR36" s="3">
         <f t="shared" si="4"/>
         <v>42</v>
       </c>
-      <c r="AS33" s="3">
+      <c r="AS36" s="3">
         <f t="shared" si="4"/>
         <v>43</v>
       </c>
-      <c r="AT33" s="3">
+      <c r="AT36" s="3">
         <f t="shared" si="4"/>
         <v>44</v>
       </c>
-      <c r="AU33" s="3">
+      <c r="AU36" s="3">
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
-      <c r="AV33" s="3">
+      <c r="AV36" s="3">
         <f t="shared" si="4"/>
         <v>46</v>
       </c>
-      <c r="AW33" s="3">
+      <c r="AW36" s="3">
         <f t="shared" si="4"/>
         <v>47</v>
       </c>
-      <c r="AX33" s="3">
+      <c r="AX36" s="3">
         <f t="shared" si="4"/>
         <v>48</v>
       </c>
-      <c r="AY33" s="3">
+      <c r="AY36" s="3">
         <f t="shared" si="4"/>
         <v>49</v>
       </c>
-      <c r="AZ33" s="3">
+      <c r="AZ36" s="3">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="BA33" s="3">
+      <c r="BA36" s="3">
         <f t="shared" si="4"/>
         <v>51</v>
       </c>
-      <c r="BB33" s="3">
+      <c r="BB36" s="3">
         <f t="shared" si="4"/>
         <v>52</v>
       </c>
-      <c r="BC33" s="3">
+      <c r="BC36" s="3">
         <f t="shared" si="4"/>
         <v>53</v>
       </c>
-      <c r="BD33" s="3">
+      <c r="BD36" s="3">
         <f t="shared" si="4"/>
         <v>54</v>
       </c>
-      <c r="BE33" s="3">
+      <c r="BE36" s="3">
         <f t="shared" si="4"/>
         <v>55</v>
       </c>
-      <c r="BF33" s="3">
+      <c r="BF36" s="3">
         <f t="shared" si="4"/>
         <v>56</v>
       </c>
-      <c r="BG33" s="3">
+      <c r="BG36" s="3">
         <f t="shared" si="4"/>
         <v>57</v>
       </c>
-      <c r="BH33" s="3">
+      <c r="BH36" s="3">
         <f t="shared" si="4"/>
         <v>58</v>
       </c>
-      <c r="BI33" s="3">
+      <c r="BI36" s="3">
         <f t="shared" si="4"/>
         <v>59</v>
       </c>
-      <c r="BJ33" s="3">
+      <c r="BJ36" s="3">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="BL33" s="221">
-        <v>32</v>
-      </c>
-      <c r="BM33" s="221" t="str">
-        <v>-p</v>
-      </c>
-      <c r="BN33" s="221" t="str">
-        <v>R</v>
-      </c>
-      <c r="BO33" s="221" t="str">
+      <c r="BL36" s="221">
+        <v>35</v>
+      </c>
+      <c r="BM36" s="221" t="str">
+        <v>-h</v>
+      </c>
+      <c r="BN36" s="221" t="str">
+        <v>V</v>
+      </c>
+      <c r="BO36" s="221" t="str">
+        <v>z</v>
+      </c>
+      <c r="BP36" s="221" t="str">
+        <v>ㆷ</v>
+      </c>
+    </row>
+    <row r="37" spans="1:68">
+      <c r="A37" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" s="5" t="str">
+        <f>C22</f>
         <v>b</v>
       </c>
-      <c r="BP33" s="221" t="str">
-        <v>ㆴ</v>
-      </c>
-    </row>
-    <row r="34" spans="1:68">
-      <c r="A34" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="5" t="str">
-        <f>C19</f>
-        <v>b</v>
-      </c>
-      <c r="D34" s="5" t="str">
-        <f t="shared" ref="D34:BH34" si="5">D19</f>
+      <c r="D37" s="5" t="str">
+        <f t="shared" ref="D37:BH37" si="5">D22</f>
         <v>p</v>
       </c>
-      <c r="E34" s="5" t="str">
+      <c r="E37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>P</v>
       </c>
-      <c r="F34" s="5" t="str">
+      <c r="F37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>m</v>
       </c>
-      <c r="G34" s="5" t="str">
+      <c r="G37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>n</v>
       </c>
-      <c r="H34" s="5" t="str">
+      <c r="H37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>t</v>
       </c>
-      <c r="I34" s="5" t="str">
+      <c r="I37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>T</v>
       </c>
-      <c r="J34" s="5" t="str">
+      <c r="J37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>l</v>
       </c>
-      <c r="K34" s="5" t="str">
+      <c r="K37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>g</v>
       </c>
-      <c r="L34" s="5" t="str">
+      <c r="L37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>k</v>
       </c>
-      <c r="M34" s="5" t="str">
+      <c r="M37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>K</v>
       </c>
-      <c r="N34" s="5" t="str">
+      <c r="N37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>ŋ</v>
       </c>
-      <c r="O34" s="5" t="str">
+      <c r="O37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>j</v>
       </c>
-      <c r="P34" s="5" t="str">
+      <c r="P37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>z</v>
       </c>
-      <c r="Q34" s="5" t="str">
+      <c r="Q37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>c</v>
       </c>
-      <c r="R34" s="5" t="str">
+      <c r="R37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>s</v>
       </c>
-      <c r="S34" s="5" t="str">
+      <c r="S37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>h</v>
       </c>
-      <c r="T34" s="5" t="str">
+      <c r="T37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>J</v>
       </c>
-      <c r="U34" s="5" t="str">
+      <c r="U37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>Z</v>
       </c>
-      <c r="V34" s="5" t="str">
+      <c r="V37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>C</v>
       </c>
-      <c r="W34" s="5" t="str">
+      <c r="W37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>S</v>
       </c>
-      <c r="X34" s="5" t="str">
+      <c r="X37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>a</v>
       </c>
-      <c r="Y34" s="5" t="str">
+      <c r="Y37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>i</v>
       </c>
-      <c r="Z34" s="5" t="str">
+      <c r="Z37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>w</v>
       </c>
-      <c r="AA34" s="5" t="str">
+      <c r="AA37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>u</v>
       </c>
-      <c r="AB34" s="5" t="str">
+      <c r="AB37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>e</v>
       </c>
-      <c r="AC34" s="5" t="str">
+      <c r="AC37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>O</v>
       </c>
-      <c r="AD34" s="5" t="str">
+      <c r="AD37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>ə</v>
       </c>
-      <c r="AE34" s="5" t="str">
+      <c r="AE37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>M</v>
       </c>
-      <c r="AF34" s="5" t="str">
+      <c r="AF37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>N</v>
       </c>
-      <c r="AG34" s="5" t="str">
+      <c r="AG37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>G</v>
       </c>
-      <c r="AH34" s="5" t="str">
+      <c r="AH37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>R</v>
       </c>
-      <c r="AI34" s="5" t="str">
+      <c r="AI37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>F</v>
       </c>
-      <c r="AJ34" s="5" t="str">
+      <c r="AJ37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>Q</v>
       </c>
-      <c r="AK34" s="5" t="str">
+      <c r="AK37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>V</v>
       </c>
-      <c r="AL34" s="5" t="str">
+      <c r="AL37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>I</v>
       </c>
-      <c r="AM34" s="5" t="str">
+      <c r="AM37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>U</v>
       </c>
-      <c r="AN34" s="5" t="str">
+      <c r="AN37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>Y</v>
       </c>
-      <c r="AO34" s="5" t="str">
+      <c r="AO37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>@</v>
       </c>
-      <c r="AP34" s="5" t="str">
+      <c r="AP37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>A</v>
       </c>
-      <c r="AQ34" s="5" t="str">
+      <c r="AQ37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>W</v>
       </c>
-      <c r="AR34" s="5" t="str">
+      <c r="AR37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>H</v>
       </c>
-      <c r="AS34" s="5" t="str">
+      <c r="AS37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>d</v>
       </c>
-      <c r="AT34" s="5" t="str">
+      <c r="AT37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>f</v>
       </c>
-      <c r="AU34" s="5" t="str">
+      <c r="AU37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>q</v>
       </c>
-      <c r="AV34" s="5" t="str">
+      <c r="AV37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>r</v>
       </c>
-      <c r="AW34" s="5" t="str">
+      <c r="AW37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>v</v>
       </c>
-      <c r="AX34" s="5" t="str">
+      <c r="AX37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>x</v>
       </c>
-      <c r="AY34" s="5" t="str">
+      <c r="AY37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>y</v>
       </c>
-      <c r="AZ34" s="5" t="str">
+      <c r="AZ37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="BA34" s="5" t="str">
+      <c r="BA37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="BB34" s="5" t="str">
+      <c r="BB37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="BC34" s="5" t="str">
+      <c r="BC37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="BD34" s="5" t="str">
+      <c r="BD37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="BE34" s="5" t="str">
+      <c r="BE37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="BF34" s="5" t="str">
+      <c r="BF37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="BG34" s="5" t="str">
+      <c r="BG37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BH34" s="5" t="str">
+      <c r="BH37" s="5" t="str">
         <f t="shared" si="5"/>
         <v>L</v>
       </c>
-      <c r="BI34" s="5" t="str">
-        <f xml:space="preserve"> _xlfn.XLOOKUP(BI35, $C$20:$BJ$20,$C$19:$BJ$19, "")</f>
+      <c r="BI37" s="5" t="str">
+        <f xml:space="preserve"> _xlfn.XLOOKUP(BI38, $C$23:$BJ$23,$C$22:$BJ$22, "")</f>
         <v/>
       </c>
-      <c r="BJ34" s="5" t="str">
-        <f xml:space="preserve"> _xlfn.XLOOKUP(BJ35, $C$20:$BJ$20,$C$19:$BJ$19, "")</f>
+      <c r="BJ37" s="5" t="str">
+        <f xml:space="preserve"> _xlfn.XLOOKUP(BJ38, $C$23:$BJ$23,$C$22:$BJ$22, "")</f>
         <v/>
       </c>
-      <c r="BL34" s="221">
-        <v>33</v>
-      </c>
-      <c r="BM34" s="221" t="str">
-        <v>-t</v>
-      </c>
-      <c r="BN34" s="221" t="str">
-        <v>F</v>
-      </c>
-      <c r="BO34" s="221" t="str">
-        <v>t</v>
-      </c>
-      <c r="BP34" s="221" t="str">
-        <v>ㆵ</v>
+      <c r="BL37" s="221">
+        <v>36</v>
+      </c>
+      <c r="BM37" s="221" t="str">
+        <v>ai</v>
+      </c>
+      <c r="BN37" s="221" t="str">
+        <v>I</v>
+      </c>
+      <c r="BO37" s="221" t="str">
+        <v>9</v>
+      </c>
+      <c r="BP37" s="221" t="str">
+        <v>ㄞ</v>
       </c>
     </row>
-    <row r="35" spans="1:68">
-      <c r="A35" s="1" t="s">
+    <row r="38" spans="1:68">
+      <c r="A38" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="6" t="str">
-        <f t="shared" ref="C35:BJ35" si="6" xml:space="preserve"> MID($C$30,C$33,1)</f>
+      <c r="C38" s="6" t="str">
+        <f t="shared" ref="C38:BJ38" si="6" xml:space="preserve"> MID($C$33,C$36,1)</f>
         <v>!</v>
       </c>
-      <c r="D35" s="6" t="str">
+      <c r="D38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="E35" s="6" t="str">
+      <c r="E38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>q</v>
       </c>
-      <c r="F35" s="6" t="str">
+      <c r="F38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>a</v>
       </c>
-      <c r="G35" s="6" t="str">
+      <c r="G38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>s</v>
       </c>
-      <c r="H35" s="6" t="str">
+      <c r="H38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="I35" s="6" t="str">
+      <c r="I38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>w</v>
       </c>
-      <c r="J35" s="6" t="str">
+      <c r="J38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>x</v>
       </c>
-      <c r="K35" s="6" t="str">
+      <c r="K38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>E</v>
       </c>
-      <c r="L35" s="6" t="str">
+      <c r="L38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>e</v>
       </c>
-      <c r="M35" s="6" t="str">
+      <c r="M38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>d</v>
       </c>
-      <c r="N35" s="6" t="str">
+      <c r="N38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>G</v>
       </c>
-      <c r="O35" s="6" t="str">
+      <c r="O38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>Y</v>
       </c>
-      <c r="P35" s="6" t="str">
+      <c r="P38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>y</v>
       </c>
-      <c r="Q35" s="6" t="str">
+      <c r="Q38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>h</v>
       </c>
-      <c r="R35" s="6" t="str">
+      <c r="R38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>n</v>
       </c>
-      <c r="S35" s="6" t="str">
+      <c r="S38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>c</v>
       </c>
-      <c r="T35" s="6" t="str">
+      <c r="T38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>R</v>
       </c>
-      <c r="U35" s="6" t="str">
+      <c r="U38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>r</v>
       </c>
-      <c r="V35" s="6" t="str">
+      <c r="V38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>f</v>
       </c>
-      <c r="W35" s="6" t="str">
+      <c r="W38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>v</v>
       </c>
-      <c r="X35" s="6" t="str">
+      <c r="X38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="Y35" s="6" t="str">
+      <c r="Y38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>u</v>
       </c>
-      <c r="Z35" s="6" t="str">
+      <c r="Z38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>K</v>
       </c>
-      <c r="AA35" s="6" t="str">
+      <c r="AA38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>j</v>
       </c>
-      <c r="AB35" s="6" t="str">
+      <c r="AB38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>,</v>
       </c>
-      <c r="AC35" s="6" t="str">
+      <c r="AC38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>i</v>
       </c>
-      <c r="AD35" s="6" t="str">
+      <c r="AD38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>k</v>
       </c>
-      <c r="AE35" s="6" t="str">
+      <c r="AE38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>m</v>
       </c>
-      <c r="AF35" s="6" t="str">
+      <c r="AF38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>p</v>
       </c>
-      <c r="AG35" s="6" t="str">
+      <c r="AG38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>/</v>
       </c>
-      <c r="AH35" s="6" t="str">
+      <c r="AH38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>b</v>
       </c>
-      <c r="AI35" s="6" t="str">
+      <c r="AI38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>t</v>
       </c>
-      <c r="AJ35" s="6" t="str">
+      <c r="AJ38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>g</v>
       </c>
-      <c r="AK35" s="6" t="str">
+      <c r="AK38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>z</v>
       </c>
-      <c r="AL35" s="6" t="str">
+      <c r="AL38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="AM35" s="6" t="str">
+      <c r="AM38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>l</v>
       </c>
-      <c r="AN35" s="6" t="str">
+      <c r="AN38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>M</v>
       </c>
-      <c r="AO35" s="6" t="str">
+      <c r="AO38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AP35" s="6" t="str">
+      <c r="AP38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>;</v>
       </c>
-      <c r="AQ35" s="6" t="str">
+      <c r="AQ38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>O</v>
       </c>
-      <c r="AR35" s="6" t="str">
+      <c r="AR38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>o</v>
       </c>
-      <c r="AS35" s="6" t="str">
+      <c r="AS38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>*</v>
       </c>
-      <c r="AT35" s="6" t="str">
+      <c r="AT38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>U</v>
       </c>
-      <c r="AU35" s="6" t="str">
+      <c r="AU38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>J</v>
       </c>
-      <c r="AV35" s="6" t="str">
+      <c r="AV38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>&lt;</v>
       </c>
-      <c r="AW35" s="6" t="str">
+      <c r="AW38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>I</v>
       </c>
-      <c r="AX35" s="6" t="str">
+      <c r="AX38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>(</v>
       </c>
-      <c r="AY35" s="6" t="str">
+      <c r="AY38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>L</v>
       </c>
-      <c r="AZ35" s="6" t="str">
+      <c r="AZ38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>:</v>
       </c>
-      <c r="BA35" s="6" t="str">
+      <c r="BA38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="BB35" s="6" t="str">
+      <c r="BB38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="BC35" s="6" t="str">
+      <c r="BC38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="BD35" s="6" t="str">
+      <c r="BD38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="BE35" s="6" t="str">
+      <c r="BE38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>]</v>
       </c>
-      <c r="BF35" s="6" t="str">
+      <c r="BF38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>[</v>
       </c>
-      <c r="BG35" s="6" t="str">
+      <c r="BG38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="BH35" s="6" t="str">
+      <c r="BH38" s="6" t="str">
         <f t="shared" si="6"/>
         <v>N</v>
       </c>
-      <c r="BI35" s="6" t="str">
+      <c r="BI38" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BJ35" s="6" t="str">
+      <c r="BJ38" s="6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BL35" s="221">
-        <v>34</v>
-      </c>
-      <c r="BM35" s="221" t="str">
-        <v>-k</v>
-      </c>
-      <c r="BN35" s="221" t="str">
-        <v>Q</v>
-      </c>
-      <c r="BO35" s="221" t="str">
-        <v>g</v>
-      </c>
-      <c r="BP35" s="221" t="str">
-        <v>ㆻ</v>
+      <c r="BL38" s="221">
+        <v>37</v>
+      </c>
+      <c r="BM38" s="221" t="str">
+        <v>au</v>
+      </c>
+      <c r="BN38" s="221" t="str">
+        <v>U</v>
+      </c>
+      <c r="BO38" s="221" t="str">
+        <v>l</v>
+      </c>
+      <c r="BP38" s="221" t="str">
+        <v>ㄠ</v>
       </c>
     </row>
-    <row r="36" spans="1:68">
-      <c r="A36" s="1" t="s">
+    <row r="39" spans="1:68">
+      <c r="A39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="8" t="str">
-        <f t="shared" ref="C36:BJ36" si="7" xml:space="preserve"> MID($C$31,C$33,1)</f>
+      <c r="C39" s="8" t="str">
+        <f t="shared" ref="C39:BJ39" si="7" xml:space="preserve"> MID($C$34,C$36,1)</f>
         <v>ㆠ</v>
       </c>
-      <c r="D36" s="8" t="str">
+      <c r="D39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄅ</v>
       </c>
-      <c r="E36" s="8" t="str">
+      <c r="E39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄆ</v>
       </c>
-      <c r="F36" s="8" t="str">
+      <c r="F39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄇ</v>
       </c>
-      <c r="G36" s="8" t="str">
+      <c r="G39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄋ</v>
       </c>
-      <c r="H36" s="8" t="str">
+      <c r="H39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄉ</v>
       </c>
-      <c r="I36" s="8" t="str">
+      <c r="I39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄊ</v>
       </c>
-      <c r="J36" s="8" t="str">
+      <c r="J39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄌ</v>
       </c>
-      <c r="K36" s="8" t="str">
+      <c r="K39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆣ</v>
       </c>
-      <c r="L36" s="8" t="str">
+      <c r="L39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄍ</v>
       </c>
-      <c r="M36" s="8" t="str">
+      <c r="M39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄎ</v>
       </c>
-      <c r="N36" s="8" t="str">
+      <c r="N39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄫ</v>
       </c>
-      <c r="O36" s="8" t="str">
+      <c r="O39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆡ</v>
       </c>
-      <c r="P36" s="8" t="str">
+      <c r="P39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄗ</v>
       </c>
-      <c r="Q36" s="8" t="str">
+      <c r="Q39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄘ</v>
       </c>
-      <c r="R36" s="8" t="str">
+      <c r="R39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄙ</v>
       </c>
-      <c r="S36" s="8" t="str">
+      <c r="S39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄏ</v>
       </c>
-      <c r="T36" s="8" t="str">
+      <c r="T39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆢ</v>
       </c>
-      <c r="U36" s="8" t="str">
+      <c r="U39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄐ</v>
       </c>
-      <c r="V36" s="8" t="str">
+      <c r="V39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄑ</v>
       </c>
-      <c r="W36" s="8" t="str">
+      <c r="W39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄒ</v>
       </c>
-      <c r="X36" s="8" t="str">
+      <c r="X39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄚ</v>
       </c>
-      <c r="Y36" s="8" t="str">
+      <c r="Y39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄧ</v>
       </c>
-      <c r="Z36" s="8" t="str">
+      <c r="Z39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆨ</v>
       </c>
-      <c r="AA36" s="8" t="str">
+      <c r="AA39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄨ</v>
       </c>
-      <c r="AB36" s="8" t="str">
+      <c r="AB39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆤ</v>
       </c>
-      <c r="AC36" s="8" t="str">
+      <c r="AC39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆦ</v>
       </c>
-      <c r="AD36" s="8" t="str">
+      <c r="AD39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄜ</v>
       </c>
-      <c r="AE36" s="8" t="str">
+      <c r="AE39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆬ</v>
       </c>
-      <c r="AF36" s="8" t="str">
+      <c r="AF39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄣ</v>
       </c>
-      <c r="AG36" s="8" t="str">
+      <c r="AG39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆭ</v>
       </c>
-      <c r="AH36" s="8" t="str">
+      <c r="AH39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆴ</v>
       </c>
-      <c r="AI36" s="8" t="str">
+      <c r="AI39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆵ</v>
       </c>
-      <c r="AJ36" s="8" t="str">
+      <c r="AJ39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆻ</v>
       </c>
-      <c r="AK36" s="8" t="str">
+      <c r="AK39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆷ</v>
       </c>
-      <c r="AL36" s="8" t="str">
+      <c r="AL39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄞ</v>
       </c>
-      <c r="AM36" s="8" t="str">
+      <c r="AM39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄠ</v>
       </c>
-      <c r="AN36" s="8" t="str">
+      <c r="AN39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆰ</v>
       </c>
-      <c r="AO36" s="8" t="str">
+      <c r="AO39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄢ</v>
       </c>
-      <c r="AP36" s="8" t="str">
+      <c r="AP39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄤ</v>
       </c>
-      <c r="AQ36" s="8" t="str">
+      <c r="AQ39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆱ</v>
       </c>
-      <c r="AR36" s="8" t="str">
+      <c r="AR39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆲ</v>
       </c>
-      <c r="AS36" s="8" t="str">
+      <c r="AS39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆩ</v>
       </c>
-      <c r="AT36" s="8" t="str">
+      <c r="AT39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆪ</v>
       </c>
-      <c r="AU36" s="8" t="str">
+      <c r="AU39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆫ</v>
       </c>
-      <c r="AV36" s="8" t="str">
+      <c r="AV39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆥ</v>
       </c>
-      <c r="AW36" s="8" t="str">
+      <c r="AW39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆧ</v>
       </c>
-      <c r="AX36" s="8" t="str">
+      <c r="AX39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆮ</v>
       </c>
-      <c r="AY36" s="8" t="str">
+      <c r="AY39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㆯ</v>
       </c>
-      <c r="AZ36" s="8" t="str">
+      <c r="AZ39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>一</v>
       </c>
-      <c r="BA36" s="8" t="str">
+      <c r="BA39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>七</v>
       </c>
-      <c r="BB36" s="8" t="str">
+      <c r="BB39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>三</v>
       </c>
-      <c r="BC36" s="8" t="str">
+      <c r="BC39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>二</v>
       </c>
-      <c r="BD36" s="8" t="str">
+      <c r="BD39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>五</v>
       </c>
-      <c r="BE36" s="8" t="str">
+      <c r="BE39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>八</v>
       </c>
-      <c r="BF36" s="8" t="str">
+      <c r="BF39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>四</v>
       </c>
-      <c r="BG36" s="8" t="str">
+      <c r="BG39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>入</v>
       </c>
-      <c r="BH36" s="8" t="str">
+      <c r="BH39" s="8" t="str">
         <f t="shared" si="7"/>
         <v>ㄥ</v>
       </c>
-      <c r="BI36" s="8" t="str">
+      <c r="BI39" s="8" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="BJ36" s="8" t="str">
+      <c r="BJ39" s="8" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="BL36" s="221">
-        <v>35</v>
-      </c>
-      <c r="BM36" s="221" t="str">
-        <v>-h</v>
-      </c>
-      <c r="BN36" s="221" t="str">
-        <v>V</v>
-      </c>
-      <c r="BO36" s="221" t="str">
-        <v>z</v>
-      </c>
-      <c r="BP36" s="221" t="str">
-        <v>ㆷ</v>
-      </c>
-    </row>
-    <row r="37" spans="1:68">
-      <c r="BL37" s="221">
-        <v>36</v>
-      </c>
-      <c r="BM37" s="221" t="str">
-        <v>ai</v>
-      </c>
-      <c r="BN37" s="223" t="str">
-        <v>I</v>
-      </c>
-      <c r="BO37" s="221" t="str">
-        <v>9</v>
-      </c>
-      <c r="BP37" s="221" t="str">
-        <v>ㄞ</v>
-      </c>
-    </row>
-    <row r="38" spans="1:68">
-      <c r="BL38" s="221">
-        <v>37</v>
-      </c>
-      <c r="BM38" s="221" t="str">
-        <v>au</v>
-      </c>
-      <c r="BN38" s="223" t="str">
-        <v>U</v>
-      </c>
-      <c r="BO38" s="221" t="str">
-        <v>l</v>
-      </c>
-      <c r="BP38" s="221" t="str">
-        <v>ㄠ</v>
-      </c>
-    </row>
-    <row r="39" spans="1:68">
       <c r="BL39" s="221">
         <v>38</v>
       </c>
       <c r="BM39" s="221" t="str">
         <v>am</v>
       </c>
-      <c r="BN39" s="223" t="str">
+      <c r="BN39" s="221" t="str">
         <v>Y</v>
       </c>
       <c r="BO39" s="221" t="str">
@@ -7795,7 +8085,7 @@
       <c r="BM51" s="221">
         <v>1</v>
       </c>
-      <c r="BN51" s="221">
+      <c r="BN51" s="223">
         <v>1</v>
       </c>
       <c r="BO51" s="221" t="str">
@@ -7812,7 +8102,7 @@
       <c r="BM52" s="221">
         <v>7</v>
       </c>
-      <c r="BN52" s="221">
+      <c r="BN52" s="223">
         <v>7</v>
       </c>
       <c r="BO52" s="221">
@@ -7829,7 +8119,7 @@
       <c r="BM53" s="221">
         <v>3</v>
       </c>
-      <c r="BN53" s="221">
+      <c r="BN53" s="223">
         <v>3</v>
       </c>
       <c r="BO53" s="221">
@@ -7942,38 +8232,45 @@
       </c>
     </row>
     <row r="60" spans="64:68">
-      <c r="BL60" s="1">
+      <c r="BL60" s="221">
         <v>59</v>
       </c>
-      <c r="BM60" s="1" t="str">
+      <c r="BM60" s="221" t="str">
         <v/>
       </c>
-      <c r="BN60" s="1" t="str">
+      <c r="BN60" s="221" t="str">
         <v/>
       </c>
-      <c r="BO60" s="1" t="str">
+      <c r="BO60" s="221" t="str">
         <v/>
       </c>
-      <c r="BP60" s="1" t="str">
+      <c r="BP60" s="221" t="str">
         <v/>
       </c>
     </row>
     <row r="61" spans="64:68">
-      <c r="BL61" s="1">
+      <c r="BL61" s="221">
         <v>60</v>
       </c>
-      <c r="BM61" s="1">
+      <c r="BM61" s="221">
         <v>0</v>
       </c>
-      <c r="BN61" s="1">
+      <c r="BN61" s="221">
         <v>0</v>
       </c>
-      <c r="BO61" s="1">
+      <c r="BO61" s="221">
         <v>0</v>
       </c>
-      <c r="BP61" s="1">
+      <c r="BP61" s="221">
         <v>0</v>
       </c>
+    </row>
+    <row r="62" spans="64:68">
+      <c r="BL62" s="221"/>
+      <c r="BM62" s="221"/>
+      <c r="BN62" s="221"/>
+      <c r="BO62" s="221"/>
+      <c r="BP62" s="221"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -7986,50 +8283,50 @@
   <dimension ref="B1:Y28"/>
   <sheetFormatPr defaultRowHeight="21.75"/>
   <cols>
-    <col min="15" max="16" width="8.796875" style="251"/>
-    <col min="17" max="18" width="15" style="251" customWidth="1"/>
-    <col min="19" max="19" width="47.296875" style="251" customWidth="1"/>
-    <col min="20" max="25" width="8.796875" style="251"/>
+    <col min="15" max="16" width="8.796875" style="239"/>
+    <col min="17" max="18" width="15" style="239" customWidth="1"/>
+    <col min="19" max="19" width="47.296875" style="239" customWidth="1"/>
+    <col min="20" max="25" width="8.796875" style="239"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:19" ht="22.5" thickBot="1"/>
     <row r="2" spans="2:19" ht="24" thickBot="1">
-      <c r="B2" s="239" t="s">
+      <c r="B2" s="248" t="s">
         <v>333</v>
       </c>
-      <c r="C2" s="241" t="s">
+      <c r="C2" s="250" t="s">
         <v>334</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="245" t="s">
+      <c r="D2" s="251"/>
+      <c r="E2" s="254" t="s">
         <v>335</v>
       </c>
-      <c r="F2" s="246"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="245" t="s">
+      <c r="F2" s="255"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="254" t="s">
         <v>336</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="247"/>
-      <c r="O2" s="251" t="s">
+      <c r="I2" s="255"/>
+      <c r="J2" s="255"/>
+      <c r="K2" s="255"/>
+      <c r="L2" s="256"/>
+      <c r="O2" s="239" t="s">
         <v>485</v>
       </c>
-      <c r="P2" s="251" t="s">
+      <c r="P2" s="239" t="s">
         <v>486</v>
       </c>
-      <c r="Q2" s="254">
+      <c r="Q2" s="242">
         <v>0</v>
       </c>
-      <c r="R2" s="254" t="s">
+      <c r="R2" s="242" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="3" spans="2:19" ht="24" thickBot="1">
-      <c r="B3" s="240"/>
-      <c r="C3" s="243"/>
-      <c r="D3" s="244"/>
+      <c r="B3" s="249"/>
+      <c r="C3" s="252"/>
+      <c r="D3" s="253"/>
       <c r="E3" s="237" t="s">
         <v>337</v>
       </c>
@@ -8048,25 +8345,25 @@
       <c r="J3" s="237" t="s">
         <v>342</v>
       </c>
-      <c r="K3" s="245" t="s">
+      <c r="K3" s="254" t="s">
         <v>343</v>
       </c>
-      <c r="L3" s="247"/>
-      <c r="O3" s="251" t="s">
+      <c r="L3" s="256"/>
+      <c r="O3" s="239" t="s">
         <v>279</v>
       </c>
-      <c r="P3" s="251" t="s">
+      <c r="P3" s="239" t="s">
         <v>455</v>
       </c>
-      <c r="Q3" s="251" t="str">
-        <f>_xlfn.CONCAT(O3,$Q$2)</f>
+      <c r="Q3" s="239" t="str">
+        <f t="shared" ref="Q3:Q19" si="0">_xlfn.CONCAT(O3,$Q$2)</f>
         <v>ang0</v>
       </c>
-      <c r="R3" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P3,$R$2)</f>
+      <c r="R3" s="239" t="str">
+        <f t="shared" ref="R3:R19" si="1" xml:space="preserve"> _xlfn.CONCAT(P3,$R$2)</f>
         <v>ak[48]</v>
       </c>
-      <c r="S3" s="251" t="str">
+      <c r="S3" s="239" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - derive/", Q3, "/", R3, "/    # " &amp; R3, "入 = ", P3, "[48]")</f>
         <v xml:space="preserve">    - derive/ang0/ak[48]/    # ak[48]入 = ak[48]</v>
       </c>
@@ -8105,22 +8402,22 @@
       <c r="L4" s="238" t="s">
         <v>349</v>
       </c>
-      <c r="O4" s="251" t="s">
+      <c r="O4" s="239" t="s">
         <v>278</v>
       </c>
-      <c r="P4" s="251" t="s">
+      <c r="P4" s="239" t="s">
         <v>456</v>
       </c>
-      <c r="Q4" s="251" t="str">
-        <f>_xlfn.CONCAT(O4,$Q$2)</f>
+      <c r="Q4" s="239" t="str">
+        <f t="shared" si="0"/>
         <v>an0</v>
       </c>
-      <c r="R4" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P4,$R$2)</f>
+      <c r="R4" s="239" t="str">
+        <f t="shared" si="1"/>
         <v>at[48]</v>
       </c>
-      <c r="S4" s="251" t="str">
-        <f t="shared" ref="S4:S19" si="0" xml:space="preserve"> _xlfn.CONCAT("    - derive/", Q4, "/", R4, "/    # " &amp; R4, "入 = ", P4, "[48]")</f>
+      <c r="S4" s="239" t="str">
+        <f t="shared" ref="S4:S19" si="2" xml:space="preserve"> _xlfn.CONCAT("    - derive/", Q4, "/", R4, "/    # " &amp; R4, "入 = ", P4, "[48]")</f>
         <v xml:space="preserve">    - derive/an0/at[48]/    # at[48]入 = at[48]</v>
       </c>
     </row>
@@ -8146,22 +8443,22 @@
       <c r="L5" s="238" t="s">
         <v>352</v>
       </c>
-      <c r="O5" s="251" t="s">
+      <c r="O5" s="239" t="s">
         <v>277</v>
       </c>
-      <c r="P5" s="251" t="s">
+      <c r="P5" s="239" t="s">
         <v>454</v>
       </c>
-      <c r="Q5" s="251" t="str">
-        <f>_xlfn.CONCAT(O5,$Q$2)</f>
+      <c r="Q5" s="239" t="str">
+        <f t="shared" si="0"/>
         <v>am0</v>
       </c>
-      <c r="R5" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P5,$R$2)</f>
+      <c r="R5" s="239" t="str">
+        <f t="shared" si="1"/>
         <v>ap[48]</v>
       </c>
-      <c r="S5" s="251" t="str">
-        <f t="shared" si="0"/>
+      <c r="S5" s="239" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/am0/ap[48]/    # ap[48]入 = ap[48]</v>
       </c>
     </row>
@@ -8185,22 +8482,22 @@
       <c r="L6" s="238" t="s">
         <v>355</v>
       </c>
-      <c r="O6" s="251" t="s">
+      <c r="O6" s="239" t="s">
         <v>462</v>
       </c>
-      <c r="P6" s="251" t="s">
+      <c r="P6" s="239" t="s">
         <v>459</v>
       </c>
-      <c r="Q6" s="251" t="str">
-        <f>_xlfn.CONCAT(O6,$Q$2)</f>
+      <c r="Q6" s="239" t="str">
+        <f t="shared" si="0"/>
         <v>ing0</v>
       </c>
-      <c r="R6" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P6,$R$2)</f>
+      <c r="R6" s="239" t="str">
+        <f t="shared" si="1"/>
         <v>ik[48]</v>
       </c>
-      <c r="S6" s="251" t="str">
-        <f t="shared" si="0"/>
+      <c r="S6" s="239" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/ing0/ik[48]/    # ik[48]入 = ik[48]</v>
       </c>
     </row>
@@ -8226,22 +8523,22 @@
         <v>360</v>
       </c>
       <c r="L7" s="238"/>
-      <c r="O7" s="251" t="s">
+      <c r="O7" s="239" t="s">
         <v>462</v>
       </c>
-      <c r="P7" s="251" t="s">
+      <c r="P7" s="239" t="s">
         <v>460</v>
       </c>
-      <c r="Q7" s="251" t="str">
-        <f>_xlfn.CONCAT(O7,$Q$2)</f>
+      <c r="Q7" s="239" t="str">
+        <f t="shared" si="0"/>
         <v>ing0</v>
       </c>
-      <c r="R7" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P7,$R$2)</f>
+      <c r="R7" s="239" t="str">
+        <f t="shared" si="1"/>
         <v>it[48]</v>
       </c>
-      <c r="S7" s="251" t="str">
-        <f t="shared" si="0"/>
+      <c r="S7" s="239" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/ing0/it[48]/    # it[48]入 = it[48]</v>
       </c>
     </row>
@@ -8267,22 +8564,22 @@
       <c r="L8" s="238" t="s">
         <v>363</v>
       </c>
-      <c r="O8" s="251" t="s">
+      <c r="O8" s="239" t="s">
         <v>463</v>
       </c>
-      <c r="P8" s="251" t="s">
+      <c r="P8" s="239" t="s">
         <v>461</v>
       </c>
-      <c r="Q8" s="251" t="str">
-        <f>_xlfn.CONCAT(O8,$Q$2)</f>
+      <c r="Q8" s="239" t="str">
+        <f t="shared" si="0"/>
         <v>im0</v>
       </c>
-      <c r="R8" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P8,$R$2)</f>
+      <c r="R8" s="239" t="str">
+        <f t="shared" si="1"/>
         <v>ip[48]</v>
       </c>
-      <c r="S8" s="251" t="str">
-        <f t="shared" si="0"/>
+      <c r="S8" s="239" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/im0/ip[48]/    # ip[48]入 = ip[48]</v>
       </c>
     </row>
@@ -8320,22 +8617,22 @@
       <c r="L9" s="238" t="s">
         <v>372</v>
       </c>
-      <c r="O9" s="251" t="s">
+      <c r="O9" s="239" t="s">
         <v>465</v>
       </c>
-      <c r="P9" s="251" t="s">
+      <c r="P9" s="239" t="s">
         <v>464</v>
       </c>
-      <c r="Q9" s="251" t="str">
-        <f>_xlfn.CONCAT(O9,$Q$2)</f>
+      <c r="Q9" s="239" t="str">
+        <f t="shared" si="0"/>
         <v>iang0</v>
       </c>
-      <c r="R9" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P9,$R$2)</f>
+      <c r="R9" s="239" t="str">
+        <f t="shared" si="1"/>
         <v>iak[48]</v>
       </c>
-      <c r="S9" s="251" t="str">
-        <f t="shared" si="0"/>
+      <c r="S9" s="239" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/iang0/iak[48]/    # iak[48]入 = iak[48]</v>
       </c>
     </row>
@@ -8373,22 +8670,22 @@
       <c r="L10" s="238" t="s">
         <v>383</v>
       </c>
-      <c r="O10" s="251" t="s">
+      <c r="O10" s="239" t="s">
         <v>468</v>
       </c>
-      <c r="P10" s="251" t="s">
+      <c r="P10" s="239" t="s">
         <v>466</v>
       </c>
-      <c r="Q10" s="251" t="str">
-        <f>_xlfn.CONCAT(O10,$Q$2)</f>
+      <c r="Q10" s="239" t="str">
+        <f t="shared" si="0"/>
         <v>ian0</v>
       </c>
-      <c r="R10" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P10,$R$2)</f>
+      <c r="R10" s="239" t="str">
+        <f t="shared" si="1"/>
         <v>iat[48]</v>
       </c>
-      <c r="S10" s="251" t="str">
-        <f t="shared" si="0"/>
+      <c r="S10" s="239" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/ian0/iat[48]/    # iat[48]入 = iat[48]</v>
       </c>
     </row>
@@ -8412,22 +8709,22 @@
         <v>387</v>
       </c>
       <c r="L11" s="238"/>
-      <c r="O11" s="251" t="s">
+      <c r="O11" s="239" t="s">
         <v>469</v>
       </c>
-      <c r="P11" s="251" t="s">
+      <c r="P11" s="239" t="s">
         <v>467</v>
       </c>
-      <c r="Q11" s="251" t="str">
-        <f>_xlfn.CONCAT(O11,$Q$2)</f>
+      <c r="Q11" s="239" t="str">
+        <f t="shared" si="0"/>
         <v>iam0</v>
       </c>
-      <c r="R11" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P11,$R$2)</f>
+      <c r="R11" s="239" t="str">
+        <f t="shared" si="1"/>
         <v>iap[48]</v>
       </c>
-      <c r="S11" s="251" t="str">
-        <f t="shared" si="0"/>
+      <c r="S11" s="239" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/iam0/iap[48]/    # iap[48]入 = iap[48]</v>
       </c>
     </row>
@@ -8449,22 +8746,22 @@
         <v>390</v>
       </c>
       <c r="L12" s="238"/>
-      <c r="O12" s="251" t="s">
+      <c r="O12" s="239" t="s">
         <v>471</v>
       </c>
-      <c r="P12" s="251" t="s">
+      <c r="P12" s="239" t="s">
         <v>470</v>
       </c>
-      <c r="Q12" s="251" t="str">
-        <f>_xlfn.CONCAT(O12,$Q$2)</f>
+      <c r="Q12" s="239" t="str">
+        <f t="shared" si="0"/>
         <v>iong0</v>
       </c>
-      <c r="R12" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P12,$R$2)</f>
+      <c r="R12" s="239" t="str">
+        <f t="shared" si="1"/>
         <v>iok[48]</v>
       </c>
-      <c r="S12" s="251" t="str">
-        <f t="shared" si="0"/>
+      <c r="S12" s="239" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/iong0/iok[48]/    # iok[48]入 = iok[48]</v>
       </c>
     </row>
@@ -8492,22 +8789,22 @@
         <v>396</v>
       </c>
       <c r="L13" s="238"/>
-      <c r="O13" s="251" t="s">
+      <c r="O13" s="239" t="s">
         <v>281</v>
       </c>
-      <c r="P13" s="251" t="s">
+      <c r="P13" s="239" t="s">
         <v>472</v>
       </c>
-      <c r="Q13" s="251" t="str">
-        <f>_xlfn.CONCAT(O13,$Q$2)</f>
+      <c r="Q13" s="239" t="str">
+        <f t="shared" si="0"/>
         <v>ong0</v>
       </c>
-      <c r="R13" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P13,$R$2)</f>
+      <c r="R13" s="239" t="str">
+        <f t="shared" si="1"/>
         <v>ok[48]</v>
       </c>
-      <c r="S13" s="251" t="str">
-        <f t="shared" si="0"/>
+      <c r="S13" s="239" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/ong0/ok[48]/    # ok[48]入 = ok[48]</v>
       </c>
     </row>
@@ -8533,22 +8830,22 @@
       <c r="L14" s="238" t="s">
         <v>401</v>
       </c>
-      <c r="O14" s="251" t="s">
+      <c r="O14" s="239" t="s">
         <v>280</v>
       </c>
-      <c r="P14" s="251" t="s">
+      <c r="P14" s="239" t="s">
         <v>473</v>
       </c>
-      <c r="Q14" s="251" t="str">
-        <f>_xlfn.CONCAT(O14,$Q$2)</f>
+      <c r="Q14" s="239" t="str">
+        <f t="shared" si="0"/>
         <v>om0</v>
       </c>
-      <c r="R14" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P14,$R$2)</f>
+      <c r="R14" s="239" t="str">
+        <f t="shared" si="1"/>
         <v>op[48]</v>
       </c>
-      <c r="S14" s="251" t="str">
-        <f t="shared" si="0"/>
+      <c r="S14" s="239" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/om0/op[48]/    # op[48]入 = op[48]</v>
       </c>
     </row>
@@ -8570,22 +8867,22 @@
         <v>404</v>
       </c>
       <c r="L15" s="238"/>
-      <c r="O15" s="251" t="s">
+      <c r="O15" s="239" t="s">
         <v>477</v>
       </c>
-      <c r="P15" s="251" t="s">
+      <c r="P15" s="239" t="s">
         <v>474</v>
       </c>
-      <c r="Q15" s="251" t="str">
-        <f>_xlfn.CONCAT(O15,$Q$2)</f>
+      <c r="Q15" s="239" t="str">
+        <f t="shared" si="0"/>
         <v>irng0</v>
       </c>
-      <c r="R15" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P15,$R$2)</f>
+      <c r="R15" s="239" t="str">
+        <f t="shared" si="1"/>
         <v>irk[48]</v>
       </c>
-      <c r="S15" s="251" t="str">
-        <f t="shared" si="0"/>
+      <c r="S15" s="239" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/irng0/irk[48]/    # irk[48]入 = irk[48]</v>
       </c>
     </row>
@@ -8607,22 +8904,22 @@
         <v>406</v>
       </c>
       <c r="L16" s="238"/>
-      <c r="O16" s="251" t="s">
+      <c r="O16" s="239" t="s">
         <v>477</v>
       </c>
-      <c r="P16" s="251" t="s">
+      <c r="P16" s="239" t="s">
         <v>475</v>
       </c>
-      <c r="Q16" s="251" t="str">
-        <f>_xlfn.CONCAT(O16,$Q$2)</f>
+      <c r="Q16" s="239" t="str">
+        <f t="shared" si="0"/>
         <v>irng0</v>
       </c>
-      <c r="R16" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P16,$R$2)</f>
+      <c r="R16" s="239" t="str">
+        <f t="shared" si="1"/>
         <v>irt[48]</v>
       </c>
-      <c r="S16" s="251" t="str">
-        <f t="shared" si="0"/>
+      <c r="S16" s="239" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/irng0/irt[48]/    # irt[48]入 = irt[48]</v>
       </c>
     </row>
@@ -8656,22 +8953,22 @@
       <c r="L17" s="238" t="s">
         <v>412</v>
       </c>
-      <c r="O17" s="251" t="s">
+      <c r="O17" s="239" t="s">
         <v>478</v>
       </c>
-      <c r="P17" s="251" t="s">
+      <c r="P17" s="239" t="s">
         <v>476</v>
       </c>
-      <c r="Q17" s="251" t="str">
-        <f>_xlfn.CONCAT(O17,$Q$2)</f>
+      <c r="Q17" s="239" t="str">
+        <f t="shared" si="0"/>
         <v>irm0</v>
       </c>
-      <c r="R17" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P17,$R$2)</f>
+      <c r="R17" s="239" t="str">
+        <f t="shared" si="1"/>
         <v>irp[48]</v>
       </c>
-      <c r="S17" s="251" t="str">
-        <f t="shared" si="0"/>
+      <c r="S17" s="239" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/irm0/irp[48]/    # irp[48]入 = irp[48]</v>
       </c>
     </row>
@@ -8705,22 +9002,22 @@
         <v>420</v>
       </c>
       <c r="L18" s="238"/>
-      <c r="O18" s="251" t="s">
+      <c r="O18" s="239" t="s">
         <v>480</v>
       </c>
-      <c r="P18" s="251" t="s">
+      <c r="P18" s="239" t="s">
         <v>479</v>
       </c>
-      <c r="Q18" s="251" t="str">
-        <f>_xlfn.CONCAT(O18,$Q$2)</f>
+      <c r="Q18" s="239" t="str">
+        <f t="shared" si="0"/>
         <v>un0</v>
       </c>
-      <c r="R18" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P18,$R$2)</f>
+      <c r="R18" s="239" t="str">
+        <f t="shared" si="1"/>
         <v>ut[48]</v>
       </c>
-      <c r="S18" s="251" t="str">
-        <f t="shared" si="0"/>
+      <c r="S18" s="239" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/un0/ut[48]/    # ut[48]入 = ut[48]</v>
       </c>
     </row>
@@ -8746,22 +9043,22 @@
         <v>424</v>
       </c>
       <c r="L19" s="238"/>
-      <c r="O19" s="251" t="s">
+      <c r="O19" s="239" t="s">
         <v>482</v>
       </c>
-      <c r="P19" s="251" t="s">
+      <c r="P19" s="239" t="s">
         <v>481</v>
       </c>
-      <c r="Q19" s="251" t="str">
-        <f>_xlfn.CONCAT(O19,$Q$2)</f>
+      <c r="Q19" s="239" t="str">
+        <f t="shared" si="0"/>
         <v>uan0</v>
       </c>
-      <c r="R19" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(P19,$R$2)</f>
+      <c r="R19" s="239" t="str">
+        <f t="shared" si="1"/>
         <v>uat[48]</v>
       </c>
-      <c r="S19" s="251" t="str">
-        <f t="shared" si="0"/>
+      <c r="S19" s="239" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/uan0/uat[48]/    # uat[48]入 = uat[48]</v>
       </c>
     </row>
@@ -8829,21 +9126,21 @@
         <v>437</v>
       </c>
       <c r="L22" s="238"/>
-      <c r="O22" s="252" t="s">
+      <c r="O22" s="240" t="s">
         <v>458</v>
       </c>
-      <c r="P22" s="252" t="s">
+      <c r="P22" s="240" t="s">
         <v>457</v>
       </c>
-      <c r="Q22" s="252" t="str">
+      <c r="Q22" s="240" t="str">
         <f>_xlfn.CONCAT(O22,$Q$2)</f>
         <v>eng0</v>
       </c>
-      <c r="R22" s="252" t="str">
+      <c r="R22" s="240" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(P22,$R$2)</f>
         <v>ek[48]</v>
       </c>
-      <c r="S22" s="252" t="str">
+      <c r="S22" s="240" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - xform/", R22, "/", Q22, "/    # " &amp; O22, "入 = ", P22, "[48]")</f>
         <v xml:space="preserve">    - xform/ek[48]/eng0/    # eng入 = ek[48]</v>
       </c>
@@ -8866,25 +9163,25 @@
         <v>440</v>
       </c>
       <c r="L23" s="238"/>
-      <c r="O23" s="251" t="s">
+      <c r="O23" s="239" t="s">
         <v>483</v>
       </c>
-      <c r="P23" s="253" t="s">
+      <c r="P23" s="241" t="s">
         <v>484</v>
       </c>
-      <c r="Q23" s="251" t="str">
+      <c r="Q23" s="239" t="str">
         <f>_xlfn.CONCAT(O23,$Q$2)</f>
         <v>uang0</v>
       </c>
-      <c r="R23" s="251" t="str">
+      <c r="R23" s="239" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(P23,$R$2)</f>
         <v>uak[48]</v>
       </c>
-      <c r="S23" s="251" t="str">
+      <c r="S23" s="239" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - xform/", R23, "/", Q23, "/    # " &amp; O23, "入 = ", P23, "[48]")</f>
         <v xml:space="preserve">    - xform/uak[48]/uang0/    # uang入 = uak[48]</v>
       </c>
-      <c r="T23" s="252"/>
+      <c r="T23" s="240"/>
     </row>
     <row r="24" spans="2:20" ht="24" thickBot="1">
       <c r="B24" s="237" t="s">
@@ -8943,57 +9240,57 @@
       <c r="B27" s="237" t="s">
         <v>448</v>
       </c>
-      <c r="C27" s="248" t="s">
+      <c r="C27" s="245" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="249"/>
-      <c r="E27" s="248" t="s">
+      <c r="D27" s="246"/>
+      <c r="E27" s="245" t="s">
         <v>449</v>
       </c>
-      <c r="F27" s="250"/>
-      <c r="G27" s="250"/>
-      <c r="H27" s="250"/>
-      <c r="I27" s="250"/>
-      <c r="J27" s="249"/>
-      <c r="K27" s="248" t="s">
+      <c r="F27" s="247"/>
+      <c r="G27" s="247"/>
+      <c r="H27" s="247"/>
+      <c r="I27" s="247"/>
+      <c r="J27" s="246"/>
+      <c r="K27" s="245" t="s">
         <v>450</v>
       </c>
-      <c r="L27" s="249"/>
+      <c r="L27" s="246"/>
     </row>
     <row r="28" spans="2:20" ht="24" thickBot="1">
       <c r="B28" s="237" t="s">
         <v>451</v>
       </c>
-      <c r="C28" s="248" t="s">
+      <c r="C28" s="245" t="s">
         <v>452</v>
       </c>
-      <c r="D28" s="249"/>
-      <c r="E28" s="248" t="s">
+      <c r="D28" s="246"/>
+      <c r="E28" s="245" t="s">
         <v>449</v>
       </c>
-      <c r="F28" s="250"/>
-      <c r="G28" s="250"/>
-      <c r="H28" s="250"/>
-      <c r="I28" s="250"/>
-      <c r="J28" s="249"/>
-      <c r="K28" s="248" t="s">
+      <c r="F28" s="247"/>
+      <c r="G28" s="247"/>
+      <c r="H28" s="247"/>
+      <c r="I28" s="247"/>
+      <c r="J28" s="246"/>
+      <c r="K28" s="245" t="s">
         <v>453</v>
       </c>
-      <c r="L28" s="249"/>
+      <c r="L28" s="246"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="K3:L3"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="E27:J27"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:J28"/>
     <mergeCell ref="K28:L28"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:D3"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9002,48 +9299,43 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A576E6A5-6E98-4E7F-8993-972F5CA6ECFB}">
-  <dimension ref="B1:Y28"/>
+  <dimension ref="B1:Z28"/>
   <sheetFormatPr defaultRowHeight="21.75"/>
   <cols>
-    <col min="15" max="16" width="8.796875" style="251"/>
-    <col min="17" max="18" width="15" style="251" customWidth="1"/>
-    <col min="19" max="19" width="47.296875" style="251" customWidth="1"/>
-    <col min="20" max="25" width="8.796875" style="251"/>
+    <col min="1" max="1" width="2.8984375" customWidth="1"/>
+    <col min="15" max="15" width="6" customWidth="1"/>
+    <col min="16" max="17" width="7.796875" style="239" customWidth="1"/>
+    <col min="18" max="19" width="14.69921875" style="239" customWidth="1"/>
+    <col min="20" max="20" width="65.09765625" style="239" customWidth="1"/>
+    <col min="21" max="26" width="8.796875" style="239"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="22.5" thickBot="1"/>
-    <row r="2" spans="2:19" ht="24" thickBot="1">
-      <c r="B2" s="239" t="s">
+    <row r="1" spans="2:20" ht="22.5" thickBot="1"/>
+    <row r="2" spans="2:20" ht="24" thickBot="1">
+      <c r="B2" s="248" t="s">
         <v>333</v>
       </c>
-      <c r="C2" s="241" t="s">
+      <c r="C2" s="250" t="s">
         <v>334</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="245" t="s">
+      <c r="D2" s="251"/>
+      <c r="E2" s="254" t="s">
         <v>335</v>
       </c>
-      <c r="F2" s="246"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="245" t="s">
+      <c r="F2" s="255"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="254" t="s">
         <v>336</v>
       </c>
-      <c r="I2" s="246"/>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="247"/>
-      <c r="Q2" s="251" t="str">
-        <f xml:space="preserve"> "([48])"</f>
-        <v>([48])</v>
-      </c>
-      <c r="R2" s="251">
-        <v>0</v>
-      </c>
+      <c r="I2" s="255"/>
+      <c r="J2" s="255"/>
+      <c r="K2" s="255"/>
+      <c r="L2" s="256"/>
     </row>
-    <row r="3" spans="2:19" ht="24" thickBot="1">
-      <c r="B3" s="240"/>
-      <c r="C3" s="243"/>
-      <c r="D3" s="244"/>
+    <row r="3" spans="2:20" ht="24" thickBot="1">
+      <c r="B3" s="249"/>
+      <c r="C3" s="252"/>
+      <c r="D3" s="253"/>
       <c r="E3" s="237" t="s">
         <v>337</v>
       </c>
@@ -9062,30 +9354,34 @@
       <c r="J3" s="237" t="s">
         <v>342</v>
       </c>
-      <c r="K3" s="245" t="s">
+      <c r="K3" s="254" t="s">
         <v>343</v>
       </c>
-      <c r="L3" s="247"/>
-      <c r="O3" s="251" t="s">
-        <v>455</v>
-      </c>
-      <c r="P3" s="251" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q3" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(O3,$Q$2)</f>
-        <v>ak([48])</v>
-      </c>
-      <c r="R3" s="251" t="str">
-        <f>_xlfn.CONCAT(P3,$R$2)</f>
-        <v>ang0</v>
-      </c>
-      <c r="S3" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - derive/", Q3, "/", R3, "/    # " &amp; P3, "入 = ", O3, "[48]")</f>
-        <v xml:space="preserve">    - derive/ak([48])/ang0/    # ang入 = ak[48]</v>
+      <c r="L3" s="256"/>
+      <c r="N3" s="243" t="s">
+        <v>510</v>
+      </c>
+      <c r="O3" s="243" t="s">
+        <v>513</v>
+      </c>
+      <c r="P3" s="244" t="s">
+        <v>506</v>
+      </c>
+      <c r="Q3" s="244" t="s">
+        <v>505</v>
+      </c>
+      <c r="R3" s="244" t="s">
+        <v>507</v>
+      </c>
+      <c r="S3" s="244" t="str">
+        <f xml:space="preserve"> "$1"</f>
+        <v>$1</v>
+      </c>
+      <c r="T3" s="244" t="s">
+        <v>512</v>
       </c>
     </row>
-    <row r="4" spans="2:19" ht="24" thickBot="1">
+    <row r="4" spans="2:20" ht="24" thickBot="1">
       <c r="B4" s="237" t="s">
         <v>344</v>
       </c>
@@ -9119,26 +9415,33 @@
       <c r="L4" s="238" t="s">
         <v>349</v>
       </c>
-      <c r="O4" s="251" t="s">
-        <v>456</v>
-      </c>
-      <c r="P4" s="251" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q4" s="251" t="str">
-        <f t="shared" ref="Q4:Q19" si="0" xml:space="preserve"> _xlfn.CONCAT(O4,$Q$2)</f>
-        <v>at([48])</v>
-      </c>
-      <c r="R4" s="251" t="str">
-        <f t="shared" ref="R4:R19" si="1">_xlfn.CONCAT(P4,$R$2)</f>
-        <v>an0</v>
-      </c>
-      <c r="S4" s="251" t="str">
-        <f t="shared" ref="S4:S19" si="2" xml:space="preserve"> _xlfn.CONCAT("    - derive/", Q4, "/", R4, "/    # " &amp; P4, "入 = ", O4, "[48]")</f>
-        <v xml:space="preserve">    - derive/at([48])/an0/    # an入 = at[48]</v>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <f t="shared" ref="O4:O20" si="0" xml:space="preserve"> LEN(P4)</f>
+        <v>4</v>
+      </c>
+      <c r="P4" s="239" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q4" s="239" t="s">
+        <v>490</v>
+      </c>
+      <c r="R4" s="239" t="str">
+        <f>_xlfn.CONCAT(P4,$R$3)</f>
+        <v>iang([12357])</v>
+      </c>
+      <c r="S4" s="239" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Q4,$S$3)</f>
+        <v>iaG$1</v>
+      </c>
+      <c r="T4" s="239" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - derive/", R4, "/", S4, "/    # " &amp; Q4, "入 = ", P4, "[48]")</f>
+        <v xml:space="preserve">    - derive/iang([12357])/iaG$1/    # iaG入 = iang[48]</v>
       </c>
     </row>
-    <row r="5" spans="2:19" ht="24" thickBot="1">
+    <row r="5" spans="2:20" ht="24" thickBot="1">
       <c r="B5" s="237" t="s">
         <v>350</v>
       </c>
@@ -9160,26 +9463,33 @@
       <c r="L5" s="238" t="s">
         <v>352</v>
       </c>
-      <c r="O5" s="251" t="s">
-        <v>454</v>
-      </c>
-      <c r="P5" s="251" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q5" s="251" t="str">
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
         <f t="shared" si="0"/>
-        <v>ap([48])</v>
-      </c>
-      <c r="R5" s="251" t="str">
-        <f t="shared" si="1"/>
-        <v>am0</v>
-      </c>
-      <c r="S5" s="251" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    - derive/ap([48])/am0/    # am入 = ap[48]</v>
+        <v>4</v>
+      </c>
+      <c r="P5" s="239" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q5" s="239" t="s">
+        <v>491</v>
+      </c>
+      <c r="R5" s="239" t="str">
+        <f t="shared" ref="R5:R20" si="1">_xlfn.CONCAT(P5,$R$3)</f>
+        <v>iong([12357])</v>
+      </c>
+      <c r="S5" s="239" t="str">
+        <f t="shared" ref="S5:S20" si="2" xml:space="preserve"> _xlfn.CONCAT(Q5,$S$3)</f>
+        <v>ioG$1</v>
+      </c>
+      <c r="T5" s="239" t="str">
+        <f t="shared" ref="T5:T20" si="3" xml:space="preserve"> _xlfn.CONCAT("    - derive/", R5, "/", S5, "/    # " &amp; Q5, "入 = ", P5, "[48]")</f>
+        <v xml:space="preserve">    - derive/iong([12357])/ioG$1/    # ioG入 = iong[48]</v>
       </c>
     </row>
-    <row r="6" spans="2:19" ht="24" thickBot="1">
+    <row r="6" spans="2:20" ht="24" thickBot="1">
       <c r="B6" s="237" t="s">
         <v>353</v>
       </c>
@@ -9199,26 +9509,33 @@
       <c r="L6" s="238" t="s">
         <v>355</v>
       </c>
-      <c r="O6" s="251" t="s">
-        <v>459</v>
-      </c>
-      <c r="P6" s="251" t="s">
-        <v>462</v>
-      </c>
-      <c r="Q6" s="251" t="str">
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
         <f t="shared" si="0"/>
-        <v>ik([48])</v>
-      </c>
-      <c r="R6" s="251" t="str">
+        <v>4</v>
+      </c>
+      <c r="P6" s="239" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q6" s="239" t="s">
+        <v>493</v>
+      </c>
+      <c r="R6" s="239" t="str">
         <f t="shared" si="1"/>
-        <v>ing0</v>
-      </c>
-      <c r="S6" s="251" t="str">
+        <v>irng([12357])</v>
+      </c>
+      <c r="S6" s="239" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    - derive/ik([48])/ing0/    # ing入 = ik[48]</v>
+        <v>irG$1</v>
+      </c>
+      <c r="T6" s="239" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - derive/irng([12357])/irG$1/    # irG入 = irng[48]</v>
       </c>
     </row>
-    <row r="7" spans="2:19" ht="24" thickBot="1">
+    <row r="7" spans="2:20" ht="24" thickBot="1">
       <c r="B7" s="237" t="s">
         <v>356</v>
       </c>
@@ -9240,26 +9557,33 @@
         <v>360</v>
       </c>
       <c r="L7" s="238"/>
-      <c r="O7" s="251" t="s">
-        <v>460</v>
-      </c>
-      <c r="P7" s="251" t="s">
-        <v>462</v>
-      </c>
-      <c r="Q7" s="251" t="str">
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
         <f t="shared" si="0"/>
-        <v>it([48])</v>
-      </c>
-      <c r="R7" s="251" t="str">
+        <v>3</v>
+      </c>
+      <c r="P7" s="239" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q7" s="239" t="s">
+        <v>488</v>
+      </c>
+      <c r="R7" s="239" t="str">
         <f t="shared" si="1"/>
-        <v>ing0</v>
-      </c>
-      <c r="S7" s="251" t="str">
+        <v>ang([12357])</v>
+      </c>
+      <c r="S7" s="239" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    - derive/it([48])/ing0/    # ing入 = it[48]</v>
+        <v>aG$1</v>
+      </c>
+      <c r="T7" s="239" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - derive/ang([12357])/aG$1/    # aG入 = ang[48]</v>
       </c>
     </row>
-    <row r="8" spans="2:19" ht="24" thickBot="1">
+    <row r="8" spans="2:20" ht="24" thickBot="1">
       <c r="B8" s="237" t="s">
         <v>361</v>
       </c>
@@ -9281,26 +9605,33 @@
       <c r="L8" s="238" t="s">
         <v>363</v>
       </c>
-      <c r="O8" s="251" t="s">
-        <v>461</v>
-      </c>
-      <c r="P8" s="251" t="s">
-        <v>463</v>
-      </c>
-      <c r="Q8" s="251" t="str">
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
         <f t="shared" si="0"/>
-        <v>ip([48])</v>
-      </c>
-      <c r="R8" s="251" t="str">
+        <v>3</v>
+      </c>
+      <c r="P8" s="239" t="s">
+        <v>462</v>
+      </c>
+      <c r="Q8" s="239" t="s">
+        <v>489</v>
+      </c>
+      <c r="R8" s="239" t="str">
         <f t="shared" si="1"/>
-        <v>im0</v>
-      </c>
-      <c r="S8" s="251" t="str">
+        <v>ing([12357])</v>
+      </c>
+      <c r="S8" s="239" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    - derive/ip([48])/im0/    # im入 = ip[48]</v>
+        <v>iG$1</v>
+      </c>
+      <c r="T8" s="239" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - derive/ing([12357])/iG$1/    # iG入 = ing[48]</v>
       </c>
     </row>
-    <row r="9" spans="2:19" ht="24" thickBot="1">
+    <row r="9" spans="2:20" ht="24" thickBot="1">
       <c r="B9" s="237" t="s">
         <v>364</v>
       </c>
@@ -9334,26 +9665,33 @@
       <c r="L9" s="238" t="s">
         <v>372</v>
       </c>
-      <c r="O9" s="251" t="s">
-        <v>464</v>
-      </c>
-      <c r="P9" s="251" t="s">
-        <v>465</v>
-      </c>
-      <c r="Q9" s="251" t="str">
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
         <f t="shared" si="0"/>
-        <v>iak([48])</v>
-      </c>
-      <c r="R9" s="251" t="str">
+        <v>3</v>
+      </c>
+      <c r="P9" s="239" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q9" s="239" t="s">
+        <v>492</v>
+      </c>
+      <c r="R9" s="239" t="str">
         <f t="shared" si="1"/>
-        <v>iang0</v>
-      </c>
-      <c r="S9" s="251" t="str">
+        <v>ong([12357])</v>
+      </c>
+      <c r="S9" s="239" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    - derive/iak([48])/iang0/    # iang入 = iak[48]</v>
+        <v>oG$1</v>
+      </c>
+      <c r="T9" s="239" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - derive/ong([12357])/oG$1/    # oG入 = ong[48]</v>
       </c>
     </row>
-    <row r="10" spans="2:19" ht="24" thickBot="1">
+    <row r="10" spans="2:20" ht="24" thickBot="1">
       <c r="B10" s="237" t="s">
         <v>373</v>
       </c>
@@ -9387,26 +9725,33 @@
       <c r="L10" s="238" t="s">
         <v>383</v>
       </c>
-      <c r="O10" s="251" t="s">
-        <v>466</v>
-      </c>
-      <c r="P10" s="251" t="s">
+      <c r="N10">
+        <v>2</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P10" s="239" t="s">
         <v>468</v>
       </c>
-      <c r="Q10" s="251" t="str">
-        <f t="shared" si="0"/>
-        <v>iat([48])</v>
-      </c>
-      <c r="R10" s="251" t="str">
+      <c r="Q10" s="239" t="s">
+        <v>497</v>
+      </c>
+      <c r="R10" s="239" t="str">
         <f t="shared" si="1"/>
-        <v>ian0</v>
-      </c>
-      <c r="S10" s="251" t="str">
+        <v>ian([12357])</v>
+      </c>
+      <c r="S10" s="239" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    - derive/iat([48])/ian0/    # ian入 = iat[48]</v>
+        <v>iaN$1</v>
+      </c>
+      <c r="T10" s="239" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - derive/ian([12357])/iaN$1/    # iaN入 = ian[48]</v>
       </c>
     </row>
-    <row r="11" spans="2:19" ht="24" thickBot="1">
+    <row r="11" spans="2:20" ht="24" thickBot="1">
       <c r="B11" s="237" t="s">
         <v>384</v>
       </c>
@@ -9426,26 +9771,33 @@
         <v>387</v>
       </c>
       <c r="L11" s="238"/>
-      <c r="O11" s="251" t="s">
-        <v>467</v>
-      </c>
-      <c r="P11" s="251" t="s">
-        <v>469</v>
-      </c>
-      <c r="Q11" s="251" t="str">
+      <c r="N11">
+        <v>2</v>
+      </c>
+      <c r="O11">
         <f t="shared" si="0"/>
-        <v>iap([48])</v>
-      </c>
-      <c r="R11" s="251" t="str">
+        <v>3</v>
+      </c>
+      <c r="P11" s="239" t="s">
+        <v>511</v>
+      </c>
+      <c r="Q11" s="239" t="s">
+        <v>493</v>
+      </c>
+      <c r="R11" s="239" t="str">
         <f t="shared" si="1"/>
-        <v>iam0</v>
-      </c>
-      <c r="S11" s="251" t="str">
+        <v>irn([12357])</v>
+      </c>
+      <c r="S11" s="239" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    - derive/iap([48])/iam0/    # iam入 = iap[48]</v>
+        <v>irG$1</v>
+      </c>
+      <c r="T11" s="239" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - derive/irn([12357])/irG$1/    # irG入 = irn[48]</v>
       </c>
     </row>
-    <row r="12" spans="2:19" ht="24" thickBot="1">
+    <row r="12" spans="2:20" ht="24" thickBot="1">
       <c r="B12" s="237" t="s">
         <v>388</v>
       </c>
@@ -9463,26 +9815,33 @@
         <v>390</v>
       </c>
       <c r="L12" s="238"/>
-      <c r="O12" s="251" t="s">
-        <v>470</v>
-      </c>
-      <c r="P12" s="251" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q12" s="251" t="str">
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12">
         <f t="shared" si="0"/>
-        <v>iok([48])</v>
-      </c>
-      <c r="R12" s="251" t="str">
+        <v>3</v>
+      </c>
+      <c r="P12" s="239" t="s">
+        <v>482</v>
+      </c>
+      <c r="Q12" s="239" t="s">
+        <v>499</v>
+      </c>
+      <c r="R12" s="239" t="str">
         <f t="shared" si="1"/>
-        <v>iong0</v>
-      </c>
-      <c r="S12" s="251" t="str">
+        <v>uan([12357])</v>
+      </c>
+      <c r="S12" s="239" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    - derive/iok([48])/iong0/    # iong入 = iok[48]</v>
+        <v>uaN$1</v>
+      </c>
+      <c r="T12" s="239" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - derive/uan([12357])/uaN$1/    # uaN入 = uan[48]</v>
       </c>
     </row>
-    <row r="13" spans="2:19" ht="24" thickBot="1">
+    <row r="13" spans="2:20" ht="24" thickBot="1">
       <c r="B13" s="237" t="s">
         <v>391</v>
       </c>
@@ -9506,26 +9865,33 @@
         <v>396</v>
       </c>
       <c r="L13" s="238"/>
-      <c r="O13" s="251" t="s">
-        <v>472</v>
-      </c>
-      <c r="P13" s="251" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q13" s="251" t="str">
+      <c r="N13">
+        <v>2</v>
+      </c>
+      <c r="O13">
         <f t="shared" si="0"/>
-        <v>ok([48])</v>
-      </c>
-      <c r="R13" s="251" t="str">
+        <v>2</v>
+      </c>
+      <c r="P13" s="239" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q13" s="239" t="s">
+        <v>496</v>
+      </c>
+      <c r="R13" s="239" t="str">
         <f t="shared" si="1"/>
-        <v>ong0</v>
-      </c>
-      <c r="S13" s="251" t="str">
+        <v>an([12357])</v>
+      </c>
+      <c r="S13" s="239" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    - derive/ok([48])/ong0/    # ong入 = ok[48]</v>
+        <v>aN$1</v>
+      </c>
+      <c r="T13" s="239" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - derive/an([12357])/aN$1/    # aN入 = an[48]</v>
       </c>
     </row>
-    <row r="14" spans="2:19" ht="24" thickBot="1">
+    <row r="14" spans="2:20" ht="24" thickBot="1">
       <c r="B14" s="237" t="s">
         <v>397</v>
       </c>
@@ -9547,26 +9913,33 @@
       <c r="L14" s="238" t="s">
         <v>401</v>
       </c>
-      <c r="O14" s="251" t="s">
-        <v>473</v>
-      </c>
-      <c r="P14" s="251" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q14" s="251" t="str">
+      <c r="N14">
+        <v>2</v>
+      </c>
+      <c r="O14">
         <f t="shared" si="0"/>
-        <v>op([48])</v>
-      </c>
-      <c r="R14" s="251" t="str">
+        <v>2</v>
+      </c>
+      <c r="P14" s="239" t="s">
+        <v>508</v>
+      </c>
+      <c r="Q14" s="239" t="s">
+        <v>509</v>
+      </c>
+      <c r="R14" s="239" t="str">
         <f t="shared" si="1"/>
-        <v>om0</v>
-      </c>
-      <c r="S14" s="251" t="str">
+        <v>in([12357])</v>
+      </c>
+      <c r="S14" s="239" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    - derive/op([48])/om0/    # om入 = op[48]</v>
+        <v>iN$1</v>
+      </c>
+      <c r="T14" s="239" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - derive/in([12357])/iN$1/    # iN入 = in[48]</v>
       </c>
     </row>
-    <row r="15" spans="2:19" ht="24" thickBot="1">
+    <row r="15" spans="2:20" ht="24" thickBot="1">
       <c r="B15" s="237" t="s">
         <v>402</v>
       </c>
@@ -9584,26 +9957,33 @@
         <v>404</v>
       </c>
       <c r="L15" s="238"/>
-      <c r="O15" s="251" t="s">
-        <v>474</v>
-      </c>
-      <c r="P15" s="251" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q15" s="251" t="str">
+      <c r="N15">
+        <v>2</v>
+      </c>
+      <c r="O15">
         <f t="shared" si="0"/>
-        <v>irk([48])</v>
-      </c>
-      <c r="R15" s="251" t="str">
+        <v>2</v>
+      </c>
+      <c r="P15" s="239" t="s">
+        <v>480</v>
+      </c>
+      <c r="Q15" s="239" t="s">
+        <v>498</v>
+      </c>
+      <c r="R15" s="239" t="str">
         <f t="shared" si="1"/>
-        <v>irng0</v>
-      </c>
-      <c r="S15" s="251" t="str">
+        <v>un([12357])</v>
+      </c>
+      <c r="S15" s="239" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    - derive/irk([48])/irng0/    # irng入 = irk[48]</v>
+        <v>uN$1</v>
+      </c>
+      <c r="T15" s="239" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - derive/un([12357])/uN$1/    # uN入 = un[48]</v>
       </c>
     </row>
-    <row r="16" spans="2:19" ht="24" thickBot="1">
+    <row r="16" spans="2:20" ht="24" thickBot="1">
       <c r="B16" s="237" t="s">
         <v>405</v>
       </c>
@@ -9621,26 +10001,33 @@
         <v>406</v>
       </c>
       <c r="L16" s="238"/>
-      <c r="O16" s="251" t="s">
-        <v>475</v>
-      </c>
-      <c r="P16" s="251" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q16" s="251" t="str">
+      <c r="N16">
+        <v>3</v>
+      </c>
+      <c r="O16">
         <f t="shared" si="0"/>
-        <v>irt([48])</v>
-      </c>
-      <c r="R16" s="251" t="str">
+        <v>3</v>
+      </c>
+      <c r="P16" s="239" t="s">
+        <v>469</v>
+      </c>
+      <c r="Q16" s="239" t="s">
+        <v>502</v>
+      </c>
+      <c r="R16" s="239" t="str">
         <f t="shared" si="1"/>
-        <v>irng0</v>
-      </c>
-      <c r="S16" s="251" t="str">
+        <v>iam([12357])</v>
+      </c>
+      <c r="S16" s="239" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    - derive/irt([48])/irng0/    # irng入 = irt[48]</v>
+        <v>iaM$1</v>
+      </c>
+      <c r="T16" s="239" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - derive/iam([12357])/iaM$1/    # iaM入 = iam[48]</v>
       </c>
     </row>
-    <row r="17" spans="2:20" ht="24" thickBot="1">
+    <row r="17" spans="2:21" ht="24" thickBot="1">
       <c r="B17" s="237" t="s">
         <v>407</v>
       </c>
@@ -9670,26 +10057,33 @@
       <c r="L17" s="238" t="s">
         <v>412</v>
       </c>
-      <c r="O17" s="251" t="s">
-        <v>476</v>
-      </c>
-      <c r="P17" s="251" t="s">
+      <c r="N17">
+        <v>3</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P17" s="239" t="s">
         <v>478</v>
       </c>
-      <c r="Q17" s="251" t="str">
-        <f t="shared" si="0"/>
-        <v>irp([48])</v>
-      </c>
-      <c r="R17" s="251" t="str">
+      <c r="Q17" s="239" t="s">
+        <v>504</v>
+      </c>
+      <c r="R17" s="239" t="str">
         <f t="shared" si="1"/>
-        <v>irm0</v>
-      </c>
-      <c r="S17" s="251" t="str">
+        <v>irm([12357])</v>
+      </c>
+      <c r="S17" s="239" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    - derive/irp([48])/irm0/    # irm入 = irp[48]</v>
+        <v>irM$1</v>
+      </c>
+      <c r="T17" s="239" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - derive/irm([12357])/irM$1/    # irM入 = irm[48]</v>
       </c>
     </row>
-    <row r="18" spans="2:20" ht="24" thickBot="1">
+    <row r="18" spans="2:21" ht="24" thickBot="1">
       <c r="B18" s="237" t="s">
         <v>413</v>
       </c>
@@ -9719,26 +10113,33 @@
         <v>420</v>
       </c>
       <c r="L18" s="238"/>
-      <c r="O18" s="251" t="s">
-        <v>479</v>
-      </c>
-      <c r="P18" s="251" t="s">
-        <v>480</v>
-      </c>
-      <c r="Q18" s="251" t="str">
+      <c r="N18">
+        <v>3</v>
+      </c>
+      <c r="O18">
         <f t="shared" si="0"/>
-        <v>ut([48])</v>
-      </c>
-      <c r="R18" s="251" t="str">
+        <v>2</v>
+      </c>
+      <c r="P18" s="239" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q18" s="239" t="s">
+        <v>500</v>
+      </c>
+      <c r="R18" s="239" t="str">
         <f t="shared" si="1"/>
-        <v>un0</v>
-      </c>
-      <c r="S18" s="251" t="str">
+        <v>am([12357])</v>
+      </c>
+      <c r="S18" s="239" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    - derive/ut([48])/un0/    # un入 = ut[48]</v>
+        <v>aM$1</v>
+      </c>
+      <c r="T18" s="239" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - derive/am([12357])/aM$1/    # aM入 = am[48]</v>
       </c>
     </row>
-    <row r="19" spans="2:20" ht="24" thickBot="1">
+    <row r="19" spans="2:21" ht="24" thickBot="1">
       <c r="B19" s="237" t="s">
         <v>421</v>
       </c>
@@ -9760,26 +10161,33 @@
         <v>424</v>
       </c>
       <c r="L19" s="238"/>
-      <c r="O19" s="251" t="s">
-        <v>481</v>
-      </c>
-      <c r="P19" s="251" t="s">
-        <v>482</v>
-      </c>
-      <c r="Q19" s="251" t="str">
+      <c r="N19">
+        <v>3</v>
+      </c>
+      <c r="O19">
         <f t="shared" si="0"/>
-        <v>uat([48])</v>
-      </c>
-      <c r="R19" s="251" t="str">
+        <v>2</v>
+      </c>
+      <c r="P19" s="239" t="s">
+        <v>463</v>
+      </c>
+      <c r="Q19" s="239" t="s">
+        <v>501</v>
+      </c>
+      <c r="R19" s="239" t="str">
         <f t="shared" si="1"/>
-        <v>uan0</v>
-      </c>
-      <c r="S19" s="251" t="str">
+        <v>im([12357])</v>
+      </c>
+      <c r="S19" s="239" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    - derive/uat([48])/uan0/    # uan入 = uat[48]</v>
+        <v>iM$1</v>
+      </c>
+      <c r="T19" s="239" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - derive/im([12357])/iM$1/    # iM入 = im[48]</v>
       </c>
     </row>
-    <row r="20" spans="2:20" ht="24" thickBot="1">
+    <row r="20" spans="2:21" ht="24" thickBot="1">
       <c r="B20" s="237" t="s">
         <v>425</v>
       </c>
@@ -9805,8 +10213,33 @@
         <v>431</v>
       </c>
       <c r="L20" s="238"/>
+      <c r="N20">
+        <v>3</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="P20" s="239" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q20" s="239" t="s">
+        <v>503</v>
+      </c>
+      <c r="R20" s="239" t="str">
+        <f t="shared" si="1"/>
+        <v>om([12357])</v>
+      </c>
+      <c r="S20" s="239" t="str">
+        <f t="shared" si="2"/>
+        <v>oM$1</v>
+      </c>
+      <c r="T20" s="239" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">    - derive/om([12357])/oM$1/    # oM入 = om[48]</v>
+      </c>
     </row>
-    <row r="21" spans="2:20" ht="24" thickBot="1">
+    <row r="21" spans="2:21" ht="24" thickBot="1">
       <c r="B21" s="237" t="s">
         <v>432</v>
       </c>
@@ -9825,7 +10258,7 @@
       <c r="K21" s="238"/>
       <c r="L21" s="238"/>
     </row>
-    <row r="22" spans="2:20" ht="24" thickBot="1">
+    <row r="22" spans="2:21" ht="24" thickBot="1">
       <c r="B22" s="237" t="s">
         <v>435</v>
       </c>
@@ -9843,26 +10276,26 @@
         <v>437</v>
       </c>
       <c r="L22" s="238"/>
-      <c r="O22" s="252" t="s">
+      <c r="P22" s="240" t="s">
         <v>457</v>
       </c>
-      <c r="P22" s="252" t="s">
-        <v>458</v>
-      </c>
-      <c r="Q22" s="252" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(O22,$Q$2)</f>
-        <v>ek([48])</v>
-      </c>
-      <c r="R22" s="252" t="str">
-        <f>_xlfn.CONCAT(P22,$R$2)</f>
-        <v>eng0</v>
-      </c>
-      <c r="S22" s="252" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/", Q22, "/", R22, "/    # " &amp; P22, "入 = ", O22, "[48]")</f>
-        <v xml:space="preserve">    - xform/ek([48])/eng0/    # eng入 = ek[48]</v>
+      <c r="Q22" s="240" t="s">
+        <v>494</v>
+      </c>
+      <c r="R22" s="240" t="str">
+        <f>_xlfn.CONCAT(Q22,$R$3)</f>
+        <v>eG([12357])</v>
+      </c>
+      <c r="S22" s="240" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(P22,$S$3)</f>
+        <v>ek$1</v>
+      </c>
+      <c r="T22" s="240" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/", S22, "/", R22, "/    # " &amp; Q22, "入 = ", P22, "[48]")</f>
+        <v xml:space="preserve">    - xform/ek$1/eG([12357])/    # eG入 = ek[48]</v>
       </c>
     </row>
-    <row r="23" spans="2:20" ht="24" thickBot="1">
+    <row r="23" spans="2:21" ht="24" thickBot="1">
       <c r="B23" s="237" t="s">
         <v>438</v>
       </c>
@@ -9880,27 +10313,27 @@
         <v>440</v>
       </c>
       <c r="L23" s="238"/>
-      <c r="O23" s="253" t="s">
+      <c r="P23" s="241" t="s">
         <v>484</v>
       </c>
-      <c r="P23" s="251" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q23" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT(O23,$Q$2)</f>
-        <v>uak([48])</v>
-      </c>
-      <c r="R23" s="251" t="str">
-        <f>_xlfn.CONCAT(P23,$R$2)</f>
-        <v>uang0</v>
-      </c>
-      <c r="S23" s="251" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/", Q23, "/", R23, "/    # " &amp; P23, "入 = ", O23, "[48]")</f>
-        <v xml:space="preserve">    - xform/uak([48])/uang0/    # uang入 = uak[48]</v>
-      </c>
-      <c r="T23" s="252"/>
+      <c r="Q23" s="239" t="s">
+        <v>495</v>
+      </c>
+      <c r="R23" s="239" t="str">
+        <f>_xlfn.CONCAT(Q23,$R$3)</f>
+        <v>uaG([12357])</v>
+      </c>
+      <c r="S23" s="239" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(P23,$S$3)</f>
+        <v>uak$1</v>
+      </c>
+      <c r="T23" s="239" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/", S23, "/", R23, "/    # " &amp; Q23, "入 = ", P23, "[48]")</f>
+        <v xml:space="preserve">    - xform/uak$1/uaG([12357])/    # uaG入 = uak[48]</v>
+      </c>
+      <c r="U23" s="240"/>
     </row>
-    <row r="24" spans="2:20" ht="24" thickBot="1">
+    <row r="24" spans="2:21" ht="24" thickBot="1">
       <c r="B24" s="237" t="s">
         <v>441</v>
       </c>
@@ -9917,7 +10350,7 @@
       <c r="K24" s="238"/>
       <c r="L24" s="238"/>
     </row>
-    <row r="25" spans="2:20" ht="24" thickBot="1">
+    <row r="25" spans="2:21" ht="24" thickBot="1">
       <c r="B25" s="237" t="s">
         <v>443</v>
       </c>
@@ -9934,7 +10367,7 @@
       <c r="K25" s="238"/>
       <c r="L25" s="238"/>
     </row>
-    <row r="26" spans="2:20" ht="24" thickBot="1">
+    <row r="26" spans="2:21" ht="24" thickBot="1">
       <c r="B26" s="237" t="s">
         <v>445</v>
       </c>
@@ -9953,47 +10386,1066 @@
       </c>
       <c r="L26" s="238"/>
     </row>
-    <row r="27" spans="2:20" ht="24" thickBot="1">
+    <row r="27" spans="2:21" ht="24" thickBot="1">
       <c r="B27" s="237" t="s">
         <v>448</v>
       </c>
-      <c r="C27" s="248" t="s">
+      <c r="C27" s="245" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="249"/>
-      <c r="E27" s="248" t="s">
+      <c r="D27" s="246"/>
+      <c r="E27" s="245" t="s">
         <v>449</v>
       </c>
-      <c r="F27" s="250"/>
-      <c r="G27" s="250"/>
-      <c r="H27" s="250"/>
-      <c r="I27" s="250"/>
-      <c r="J27" s="249"/>
-      <c r="K27" s="248" t="s">
+      <c r="F27" s="247"/>
+      <c r="G27" s="247"/>
+      <c r="H27" s="247"/>
+      <c r="I27" s="247"/>
+      <c r="J27" s="246"/>
+      <c r="K27" s="245" t="s">
         <v>450</v>
       </c>
-      <c r="L27" s="249"/>
+      <c r="L27" s="246"/>
     </row>
-    <row r="28" spans="2:20" ht="24" thickBot="1">
+    <row r="28" spans="2:21" ht="24" thickBot="1">
       <c r="B28" s="237" t="s">
         <v>451</v>
       </c>
-      <c r="C28" s="248" t="s">
+      <c r="C28" s="245" t="s">
         <v>452</v>
       </c>
-      <c r="D28" s="249"/>
-      <c r="E28" s="248" t="s">
+      <c r="D28" s="246"/>
+      <c r="E28" s="245" t="s">
         <v>449</v>
       </c>
-      <c r="F28" s="250"/>
-      <c r="G28" s="250"/>
-      <c r="H28" s="250"/>
-      <c r="I28" s="250"/>
-      <c r="J28" s="249"/>
-      <c r="K28" s="248" t="s">
+      <c r="F28" s="247"/>
+      <c r="G28" s="247"/>
+      <c r="H28" s="247"/>
+      <c r="I28" s="247"/>
+      <c r="J28" s="246"/>
+      <c r="K28" s="245" t="s">
         <v>453</v>
       </c>
-      <c r="L28" s="249"/>
+      <c r="L28" s="246"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N4:T20">
+    <sortCondition ref="N4:N20"/>
+    <sortCondition descending="1" ref="O4:O20"/>
+  </sortState>
+  <mergeCells count="11">
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:J28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:J27"/>
+    <mergeCell ref="K27:L27"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ED0EFA4-32E9-4AEC-A6ED-2DBF7A08ED31}">
+  <dimension ref="B1:X28"/>
+  <sheetFormatPr defaultRowHeight="21.75"/>
+  <cols>
+    <col min="1" max="1" width="2.8984375" customWidth="1"/>
+    <col min="14" max="15" width="6.8984375" style="239" customWidth="1"/>
+    <col min="16" max="17" width="13.09765625" style="239" customWidth="1"/>
+    <col min="18" max="18" width="47.296875" style="239" customWidth="1"/>
+    <col min="19" max="24" width="8.796875" style="239"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:18" ht="22.5" thickBot="1"/>
+    <row r="2" spans="2:18" ht="24" thickBot="1">
+      <c r="B2" s="248" t="s">
+        <v>333</v>
+      </c>
+      <c r="C2" s="250" t="s">
+        <v>334</v>
+      </c>
+      <c r="D2" s="251"/>
+      <c r="E2" s="254" t="s">
+        <v>335</v>
+      </c>
+      <c r="F2" s="255"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="254" t="s">
+        <v>336</v>
+      </c>
+      <c r="I2" s="255"/>
+      <c r="J2" s="255"/>
+      <c r="K2" s="255"/>
+      <c r="L2" s="256"/>
+      <c r="P2" s="239" t="str">
+        <f xml:space="preserve"> "([48])"</f>
+        <v>([48])</v>
+      </c>
+      <c r="Q2" s="239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18" ht="24" thickBot="1">
+      <c r="B3" s="249"/>
+      <c r="C3" s="252"/>
+      <c r="D3" s="253"/>
+      <c r="E3" s="237" t="s">
+        <v>337</v>
+      </c>
+      <c r="F3" s="237" t="s">
+        <v>338</v>
+      </c>
+      <c r="G3" s="237" t="s">
+        <v>339</v>
+      </c>
+      <c r="H3" s="237" t="s">
+        <v>340</v>
+      </c>
+      <c r="I3" s="237" t="s">
+        <v>341</v>
+      </c>
+      <c r="J3" s="237" t="s">
+        <v>342</v>
+      </c>
+      <c r="K3" s="254" t="s">
+        <v>343</v>
+      </c>
+      <c r="L3" s="256"/>
+      <c r="N3" s="239" t="s">
+        <v>455</v>
+      </c>
+      <c r="O3" s="239" t="s">
+        <v>279</v>
+      </c>
+      <c r="P3" s="239" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(N3,$P$2)</f>
+        <v>ak([48])</v>
+      </c>
+      <c r="Q3" s="239" t="str">
+        <f>_xlfn.CONCAT(O3,$Q$2)</f>
+        <v>ang0</v>
+      </c>
+      <c r="R3" s="239" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - derive/", P3, "/", Q3, "/    # " &amp; O3, "入 = ", N3, "[48]")</f>
+        <v xml:space="preserve">    - derive/ak([48])/ang0/    # ang入 = ak[48]</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" ht="24" thickBot="1">
+      <c r="B4" s="237" t="s">
+        <v>344</v>
+      </c>
+      <c r="C4" s="238" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="238" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="238" t="s">
+        <v>162</v>
+      </c>
+      <c r="F4" s="238" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="238" t="s">
+        <v>148</v>
+      </c>
+      <c r="H4" s="238" t="s">
+        <v>345</v>
+      </c>
+      <c r="I4" s="238" t="s">
+        <v>346</v>
+      </c>
+      <c r="J4" s="238" t="s">
+        <v>347</v>
+      </c>
+      <c r="K4" s="238" t="s">
+        <v>348</v>
+      </c>
+      <c r="L4" s="238" t="s">
+        <v>349</v>
+      </c>
+      <c r="N4" s="239" t="s">
+        <v>456</v>
+      </c>
+      <c r="O4" s="239" t="s">
+        <v>278</v>
+      </c>
+      <c r="P4" s="239" t="str">
+        <f t="shared" ref="P4:P19" si="0" xml:space="preserve"> _xlfn.CONCAT(N4,$P$2)</f>
+        <v>at([48])</v>
+      </c>
+      <c r="Q4" s="239" t="str">
+        <f t="shared" ref="Q4:Q19" si="1">_xlfn.CONCAT(O4,$Q$2)</f>
+        <v>an0</v>
+      </c>
+      <c r="R4" s="239" t="str">
+        <f t="shared" ref="R4:R19" si="2" xml:space="preserve"> _xlfn.CONCAT("    - derive/", P4, "/", Q4, "/    # " &amp; O4, "入 = ", N4, "[48]")</f>
+        <v xml:space="preserve">    - derive/at([48])/an0/    # an入 = at[48]</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" ht="24" thickBot="1">
+      <c r="B5" s="237" t="s">
+        <v>350</v>
+      </c>
+      <c r="C5" s="238" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="238" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="238"/>
+      <c r="F5" s="238"/>
+      <c r="G5" s="238"/>
+      <c r="H5" s="238"/>
+      <c r="I5" s="238"/>
+      <c r="J5" s="238"/>
+      <c r="K5" s="238" t="s">
+        <v>351</v>
+      </c>
+      <c r="L5" s="238" t="s">
+        <v>352</v>
+      </c>
+      <c r="N5" s="239" t="s">
+        <v>454</v>
+      </c>
+      <c r="O5" s="239" t="s">
+        <v>277</v>
+      </c>
+      <c r="P5" s="239" t="str">
+        <f t="shared" si="0"/>
+        <v>ap([48])</v>
+      </c>
+      <c r="Q5" s="239" t="str">
+        <f t="shared" si="1"/>
+        <v>am0</v>
+      </c>
+      <c r="R5" s="239" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    - derive/ap([48])/am0/    # am入 = ap[48]</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" ht="24" thickBot="1">
+      <c r="B6" s="237" t="s">
+        <v>353</v>
+      </c>
+      <c r="C6" s="238" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="238"/>
+      <c r="E6" s="238"/>
+      <c r="F6" s="238"/>
+      <c r="G6" s="238"/>
+      <c r="H6" s="238"/>
+      <c r="I6" s="238"/>
+      <c r="J6" s="238"/>
+      <c r="K6" s="238" t="s">
+        <v>354</v>
+      </c>
+      <c r="L6" s="238" t="s">
+        <v>355</v>
+      </c>
+      <c r="N6" s="239" t="s">
+        <v>459</v>
+      </c>
+      <c r="O6" s="239" t="s">
+        <v>462</v>
+      </c>
+      <c r="P6" s="239" t="str">
+        <f t="shared" si="0"/>
+        <v>ik([48])</v>
+      </c>
+      <c r="Q6" s="239" t="str">
+        <f t="shared" si="1"/>
+        <v>ing0</v>
+      </c>
+      <c r="R6" s="239" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    - derive/ik([48])/ing0/    # ing入 = ik[48]</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" ht="24" thickBot="1">
+      <c r="B7" s="237" t="s">
+        <v>356</v>
+      </c>
+      <c r="C7" s="238" t="s">
+        <v>357</v>
+      </c>
+      <c r="D7" s="238"/>
+      <c r="E7" s="238"/>
+      <c r="F7" s="238"/>
+      <c r="G7" s="238" t="s">
+        <v>358</v>
+      </c>
+      <c r="H7" s="238"/>
+      <c r="I7" s="238"/>
+      <c r="J7" s="238" t="s">
+        <v>359</v>
+      </c>
+      <c r="K7" s="238" t="s">
+        <v>360</v>
+      </c>
+      <c r="L7" s="238"/>
+      <c r="N7" s="239" t="s">
+        <v>460</v>
+      </c>
+      <c r="O7" s="239" t="s">
+        <v>462</v>
+      </c>
+      <c r="P7" s="239" t="str">
+        <f t="shared" si="0"/>
+        <v>it([48])</v>
+      </c>
+      <c r="Q7" s="239" t="str">
+        <f t="shared" si="1"/>
+        <v>ing0</v>
+      </c>
+      <c r="R7" s="239" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    - derive/it([48])/ing0/    # ing入 = it[48]</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" ht="24" thickBot="1">
+      <c r="B8" s="237" t="s">
+        <v>361</v>
+      </c>
+      <c r="C8" s="238" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="238" t="s">
+        <v>164</v>
+      </c>
+      <c r="E8" s="238"/>
+      <c r="F8" s="238"/>
+      <c r="G8" s="238"/>
+      <c r="H8" s="238"/>
+      <c r="I8" s="238"/>
+      <c r="J8" s="238"/>
+      <c r="K8" s="238" t="s">
+        <v>362</v>
+      </c>
+      <c r="L8" s="238" t="s">
+        <v>363</v>
+      </c>
+      <c r="N8" s="239" t="s">
+        <v>461</v>
+      </c>
+      <c r="O8" s="239" t="s">
+        <v>463</v>
+      </c>
+      <c r="P8" s="239" t="str">
+        <f t="shared" si="0"/>
+        <v>ip([48])</v>
+      </c>
+      <c r="Q8" s="239" t="str">
+        <f t="shared" si="1"/>
+        <v>im0</v>
+      </c>
+      <c r="R8" s="239" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    - derive/ip([48])/im0/    # im入 = ip[48]</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" ht="24" thickBot="1">
+      <c r="B9" s="237" t="s">
+        <v>364</v>
+      </c>
+      <c r="C9" s="238" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="238" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="238" t="s">
+        <v>365</v>
+      </c>
+      <c r="F9" s="238" t="s">
+        <v>366</v>
+      </c>
+      <c r="G9" s="238" t="s">
+        <v>367</v>
+      </c>
+      <c r="H9" s="238" t="s">
+        <v>368</v>
+      </c>
+      <c r="I9" s="238" t="s">
+        <v>369</v>
+      </c>
+      <c r="J9" s="238" t="s">
+        <v>370</v>
+      </c>
+      <c r="K9" s="238" t="s">
+        <v>371</v>
+      </c>
+      <c r="L9" s="238" t="s">
+        <v>372</v>
+      </c>
+      <c r="N9" s="239" t="s">
+        <v>464</v>
+      </c>
+      <c r="O9" s="239" t="s">
+        <v>465</v>
+      </c>
+      <c r="P9" s="239" t="str">
+        <f t="shared" si="0"/>
+        <v>iak([48])</v>
+      </c>
+      <c r="Q9" s="239" t="str">
+        <f t="shared" si="1"/>
+        <v>iang0</v>
+      </c>
+      <c r="R9" s="239" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    - derive/iak([48])/iang0/    # iang入 = iak[48]</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" ht="24" thickBot="1">
+      <c r="B10" s="237" t="s">
+        <v>373</v>
+      </c>
+      <c r="C10" s="238" t="s">
+        <v>374</v>
+      </c>
+      <c r="D10" s="238" t="s">
+        <v>375</v>
+      </c>
+      <c r="E10" s="238" t="s">
+        <v>376</v>
+      </c>
+      <c r="F10" s="238" t="s">
+        <v>377</v>
+      </c>
+      <c r="G10" s="238" t="s">
+        <v>378</v>
+      </c>
+      <c r="H10" s="238" t="s">
+        <v>379</v>
+      </c>
+      <c r="I10" s="238" t="s">
+        <v>380</v>
+      </c>
+      <c r="J10" s="238" t="s">
+        <v>381</v>
+      </c>
+      <c r="K10" s="238" t="s">
+        <v>382</v>
+      </c>
+      <c r="L10" s="238" t="s">
+        <v>383</v>
+      </c>
+      <c r="N10" s="239" t="s">
+        <v>466</v>
+      </c>
+      <c r="O10" s="239" t="s">
+        <v>468</v>
+      </c>
+      <c r="P10" s="239" t="str">
+        <f t="shared" si="0"/>
+        <v>iat([48])</v>
+      </c>
+      <c r="Q10" s="239" t="str">
+        <f t="shared" si="1"/>
+        <v>ian0</v>
+      </c>
+      <c r="R10" s="239" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    - derive/iat([48])/ian0/    # ian入 = iat[48]</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" ht="24" thickBot="1">
+      <c r="B11" s="237" t="s">
+        <v>384</v>
+      </c>
+      <c r="C11" s="238" t="s">
+        <v>385</v>
+      </c>
+      <c r="D11" s="238" t="s">
+        <v>386</v>
+      </c>
+      <c r="E11" s="238"/>
+      <c r="F11" s="238"/>
+      <c r="G11" s="238"/>
+      <c r="H11" s="238"/>
+      <c r="I11" s="238"/>
+      <c r="J11" s="238"/>
+      <c r="K11" s="238" t="s">
+        <v>387</v>
+      </c>
+      <c r="L11" s="238"/>
+      <c r="N11" s="239" t="s">
+        <v>467</v>
+      </c>
+      <c r="O11" s="239" t="s">
+        <v>469</v>
+      </c>
+      <c r="P11" s="239" t="str">
+        <f t="shared" si="0"/>
+        <v>iap([48])</v>
+      </c>
+      <c r="Q11" s="239" t="str">
+        <f t="shared" si="1"/>
+        <v>iam0</v>
+      </c>
+      <c r="R11" s="239" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    - derive/iap([48])/iam0/    # iam入 = iap[48]</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" ht="24" thickBot="1">
+      <c r="B12" s="237" t="s">
+        <v>388</v>
+      </c>
+      <c r="C12" s="238" t="s">
+        <v>389</v>
+      </c>
+      <c r="D12" s="238"/>
+      <c r="E12" s="238"/>
+      <c r="F12" s="238"/>
+      <c r="G12" s="238"/>
+      <c r="H12" s="238"/>
+      <c r="I12" s="238"/>
+      <c r="J12" s="238"/>
+      <c r="K12" s="238" t="s">
+        <v>390</v>
+      </c>
+      <c r="L12" s="238"/>
+      <c r="N12" s="239" t="s">
+        <v>470</v>
+      </c>
+      <c r="O12" s="239" t="s">
+        <v>471</v>
+      </c>
+      <c r="P12" s="239" t="str">
+        <f t="shared" si="0"/>
+        <v>iok([48])</v>
+      </c>
+      <c r="Q12" s="239" t="str">
+        <f t="shared" si="1"/>
+        <v>iong0</v>
+      </c>
+      <c r="R12" s="239" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    - derive/iok([48])/iong0/    # iong入 = iok[48]</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" ht="24" thickBot="1">
+      <c r="B13" s="237" t="s">
+        <v>391</v>
+      </c>
+      <c r="C13" s="238" t="s">
+        <v>392</v>
+      </c>
+      <c r="D13" s="238" t="s">
+        <v>393</v>
+      </c>
+      <c r="E13" s="238"/>
+      <c r="F13" s="238"/>
+      <c r="G13" s="238" t="s">
+        <v>394</v>
+      </c>
+      <c r="H13" s="238"/>
+      <c r="I13" s="238"/>
+      <c r="J13" s="238" t="s">
+        <v>395</v>
+      </c>
+      <c r="K13" s="238" t="s">
+        <v>396</v>
+      </c>
+      <c r="L13" s="238"/>
+      <c r="N13" s="239" t="s">
+        <v>472</v>
+      </c>
+      <c r="O13" s="239" t="s">
+        <v>281</v>
+      </c>
+      <c r="P13" s="239" t="str">
+        <f t="shared" si="0"/>
+        <v>ok([48])</v>
+      </c>
+      <c r="Q13" s="239" t="str">
+        <f t="shared" si="1"/>
+        <v>ong0</v>
+      </c>
+      <c r="R13" s="239" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    - derive/ok([48])/ong0/    # ong入 = ok[48]</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" ht="24" thickBot="1">
+      <c r="B14" s="237" t="s">
+        <v>397</v>
+      </c>
+      <c r="C14" s="238" t="s">
+        <v>398</v>
+      </c>
+      <c r="D14" s="238" t="s">
+        <v>399</v>
+      </c>
+      <c r="E14" s="238"/>
+      <c r="F14" s="238"/>
+      <c r="G14" s="238"/>
+      <c r="H14" s="238"/>
+      <c r="I14" s="238"/>
+      <c r="J14" s="238"/>
+      <c r="K14" s="238" t="s">
+        <v>400</v>
+      </c>
+      <c r="L14" s="238" t="s">
+        <v>401</v>
+      </c>
+      <c r="N14" s="239" t="s">
+        <v>473</v>
+      </c>
+      <c r="O14" s="239" t="s">
+        <v>280</v>
+      </c>
+      <c r="P14" s="239" t="str">
+        <f t="shared" si="0"/>
+        <v>op([48])</v>
+      </c>
+      <c r="Q14" s="239" t="str">
+        <f t="shared" si="1"/>
+        <v>om0</v>
+      </c>
+      <c r="R14" s="239" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    - derive/op([48])/om0/    # om入 = op[48]</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" ht="24" thickBot="1">
+      <c r="B15" s="237" t="s">
+        <v>402</v>
+      </c>
+      <c r="C15" s="238" t="s">
+        <v>403</v>
+      </c>
+      <c r="D15" s="238"/>
+      <c r="E15" s="238"/>
+      <c r="F15" s="238"/>
+      <c r="G15" s="238"/>
+      <c r="H15" s="238"/>
+      <c r="I15" s="238"/>
+      <c r="J15" s="238"/>
+      <c r="K15" s="238" t="s">
+        <v>404</v>
+      </c>
+      <c r="L15" s="238"/>
+      <c r="N15" s="239" t="s">
+        <v>474</v>
+      </c>
+      <c r="O15" s="239" t="s">
+        <v>477</v>
+      </c>
+      <c r="P15" s="239" t="str">
+        <f t="shared" si="0"/>
+        <v>irk([48])</v>
+      </c>
+      <c r="Q15" s="239" t="str">
+        <f t="shared" si="1"/>
+        <v>irng0</v>
+      </c>
+      <c r="R15" s="239" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    - derive/irk([48])/irng0/    # irng入 = irk[48]</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" ht="24" thickBot="1">
+      <c r="B16" s="237" t="s">
+        <v>405</v>
+      </c>
+      <c r="C16" s="238" t="s">
+        <v>194</v>
+      </c>
+      <c r="D16" s="238"/>
+      <c r="E16" s="238"/>
+      <c r="F16" s="238"/>
+      <c r="G16" s="238"/>
+      <c r="H16" s="238"/>
+      <c r="I16" s="238"/>
+      <c r="J16" s="238"/>
+      <c r="K16" s="238" t="s">
+        <v>406</v>
+      </c>
+      <c r="L16" s="238"/>
+      <c r="N16" s="239" t="s">
+        <v>475</v>
+      </c>
+      <c r="O16" s="239" t="s">
+        <v>477</v>
+      </c>
+      <c r="P16" s="239" t="str">
+        <f t="shared" si="0"/>
+        <v>irt([48])</v>
+      </c>
+      <c r="Q16" s="239" t="str">
+        <f t="shared" si="1"/>
+        <v>irng0</v>
+      </c>
+      <c r="R16" s="239" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    - derive/irt([48])/irng0/    # irng入 = irt[48]</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19" ht="24" thickBot="1">
+      <c r="B17" s="237" t="s">
+        <v>407</v>
+      </c>
+      <c r="C17" s="238" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="238" t="s">
+        <v>408</v>
+      </c>
+      <c r="E17" s="238" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="238"/>
+      <c r="G17" s="238" t="s">
+        <v>109</v>
+      </c>
+      <c r="H17" s="238" t="s">
+        <v>409</v>
+      </c>
+      <c r="I17" s="238"/>
+      <c r="J17" s="238" t="s">
+        <v>410</v>
+      </c>
+      <c r="K17" s="238" t="s">
+        <v>411</v>
+      </c>
+      <c r="L17" s="238" t="s">
+        <v>412</v>
+      </c>
+      <c r="N17" s="239" t="s">
+        <v>476</v>
+      </c>
+      <c r="O17" s="239" t="s">
+        <v>478</v>
+      </c>
+      <c r="P17" s="239" t="str">
+        <f t="shared" si="0"/>
+        <v>irp([48])</v>
+      </c>
+      <c r="Q17" s="239" t="str">
+        <f t="shared" si="1"/>
+        <v>irm0</v>
+      </c>
+      <c r="R17" s="239" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    - derive/irp([48])/irm0/    # irm入 = irp[48]</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" ht="24" thickBot="1">
+      <c r="B18" s="237" t="s">
+        <v>413</v>
+      </c>
+      <c r="C18" s="238" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="238"/>
+      <c r="E18" s="238" t="s">
+        <v>414</v>
+      </c>
+      <c r="F18" s="238" t="s">
+        <v>415</v>
+      </c>
+      <c r="G18" s="238" t="s">
+        <v>416</v>
+      </c>
+      <c r="H18" s="238" t="s">
+        <v>417</v>
+      </c>
+      <c r="I18" s="238" t="s">
+        <v>418</v>
+      </c>
+      <c r="J18" s="238" t="s">
+        <v>419</v>
+      </c>
+      <c r="K18" s="238" t="s">
+        <v>420</v>
+      </c>
+      <c r="L18" s="238"/>
+      <c r="N18" s="239" t="s">
+        <v>479</v>
+      </c>
+      <c r="O18" s="239" t="s">
+        <v>480</v>
+      </c>
+      <c r="P18" s="239" t="str">
+        <f t="shared" si="0"/>
+        <v>ut([48])</v>
+      </c>
+      <c r="Q18" s="239" t="str">
+        <f t="shared" si="1"/>
+        <v>un0</v>
+      </c>
+      <c r="R18" s="239" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    - derive/ut([48])/un0/    # un入 = ut[48]</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19" ht="24" thickBot="1">
+      <c r="B19" s="237" t="s">
+        <v>421</v>
+      </c>
+      <c r="C19" s="238" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="238"/>
+      <c r="E19" s="238"/>
+      <c r="F19" s="238" t="s">
+        <v>422</v>
+      </c>
+      <c r="G19" s="238"/>
+      <c r="H19" s="238"/>
+      <c r="I19" s="238" t="s">
+        <v>423</v>
+      </c>
+      <c r="J19" s="238"/>
+      <c r="K19" s="238" t="s">
+        <v>424</v>
+      </c>
+      <c r="L19" s="238"/>
+      <c r="N19" s="239" t="s">
+        <v>481</v>
+      </c>
+      <c r="O19" s="239" t="s">
+        <v>482</v>
+      </c>
+      <c r="P19" s="239" t="str">
+        <f t="shared" si="0"/>
+        <v>uat([48])</v>
+      </c>
+      <c r="Q19" s="239" t="str">
+        <f t="shared" si="1"/>
+        <v>uan0</v>
+      </c>
+      <c r="R19" s="239" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    - derive/uat([48])/uan0/    # uan入 = uat[48]</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" ht="24" thickBot="1">
+      <c r="B20" s="237" t="s">
+        <v>425</v>
+      </c>
+      <c r="C20" s="238" t="s">
+        <v>426</v>
+      </c>
+      <c r="D20" s="238" t="s">
+        <v>427</v>
+      </c>
+      <c r="E20" s="238"/>
+      <c r="F20" s="238" t="s">
+        <v>428</v>
+      </c>
+      <c r="G20" s="238" t="s">
+        <v>429</v>
+      </c>
+      <c r="H20" s="238"/>
+      <c r="I20" s="238" t="s">
+        <v>430</v>
+      </c>
+      <c r="J20" s="238"/>
+      <c r="K20" s="238" t="s">
+        <v>431</v>
+      </c>
+      <c r="L20" s="238"/>
+    </row>
+    <row r="21" spans="2:19" ht="24" thickBot="1">
+      <c r="B21" s="237" t="s">
+        <v>432</v>
+      </c>
+      <c r="C21" s="238" t="s">
+        <v>433</v>
+      </c>
+      <c r="D21" s="238" t="s">
+        <v>434</v>
+      </c>
+      <c r="E21" s="238"/>
+      <c r="F21" s="238"/>
+      <c r="G21" s="238"/>
+      <c r="H21" s="238"/>
+      <c r="I21" s="238"/>
+      <c r="J21" s="238"/>
+      <c r="K21" s="238"/>
+      <c r="L21" s="238"/>
+    </row>
+    <row r="22" spans="2:19" ht="24" thickBot="1">
+      <c r="B22" s="237" t="s">
+        <v>435</v>
+      </c>
+      <c r="C22" s="238" t="s">
+        <v>436</v>
+      </c>
+      <c r="D22" s="238"/>
+      <c r="E22" s="238"/>
+      <c r="F22" s="238"/>
+      <c r="G22" s="238"/>
+      <c r="H22" s="238"/>
+      <c r="I22" s="238"/>
+      <c r="J22" s="238"/>
+      <c r="K22" s="238" t="s">
+        <v>437</v>
+      </c>
+      <c r="L22" s="238"/>
+      <c r="N22" s="240" t="s">
+        <v>457</v>
+      </c>
+      <c r="O22" s="240" t="s">
+        <v>458</v>
+      </c>
+      <c r="P22" s="240" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(N22,$P$2)</f>
+        <v>ek([48])</v>
+      </c>
+      <c r="Q22" s="240" t="str">
+        <f>_xlfn.CONCAT(O22,$Q$2)</f>
+        <v>eng0</v>
+      </c>
+      <c r="R22" s="240" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/", P22, "/", Q22, "/    # " &amp; O22, "入 = ", N22, "[48]")</f>
+        <v xml:space="preserve">    - xform/ek([48])/eng0/    # eng入 = ek[48]</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19" ht="24" thickBot="1">
+      <c r="B23" s="237" t="s">
+        <v>438</v>
+      </c>
+      <c r="C23" s="238" t="s">
+        <v>439</v>
+      </c>
+      <c r="D23" s="238"/>
+      <c r="E23" s="238"/>
+      <c r="F23" s="238"/>
+      <c r="G23" s="238"/>
+      <c r="H23" s="238"/>
+      <c r="I23" s="238"/>
+      <c r="J23" s="238"/>
+      <c r="K23" s="238" t="s">
+        <v>440</v>
+      </c>
+      <c r="L23" s="238"/>
+      <c r="N23" s="241" t="s">
+        <v>484</v>
+      </c>
+      <c r="O23" s="239" t="s">
+        <v>483</v>
+      </c>
+      <c r="P23" s="239" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(N23,$P$2)</f>
+        <v>uak([48])</v>
+      </c>
+      <c r="Q23" s="239" t="str">
+        <f>_xlfn.CONCAT(O23,$Q$2)</f>
+        <v>uang0</v>
+      </c>
+      <c r="R23" s="239" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/", P23, "/", Q23, "/    # " &amp; O23, "入 = ", N23, "[48]")</f>
+        <v xml:space="preserve">    - xform/uak([48])/uang0/    # uang入 = uak[48]</v>
+      </c>
+      <c r="S23" s="240"/>
+    </row>
+    <row r="24" spans="2:19" ht="24" thickBot="1">
+      <c r="B24" s="237" t="s">
+        <v>441</v>
+      </c>
+      <c r="C24" s="238" t="s">
+        <v>442</v>
+      </c>
+      <c r="D24" s="238"/>
+      <c r="E24" s="238"/>
+      <c r="F24" s="238"/>
+      <c r="G24" s="238"/>
+      <c r="H24" s="238"/>
+      <c r="I24" s="238"/>
+      <c r="J24" s="238"/>
+      <c r="K24" s="238"/>
+      <c r="L24" s="238"/>
+    </row>
+    <row r="25" spans="2:19" ht="24" thickBot="1">
+      <c r="B25" s="237" t="s">
+        <v>443</v>
+      </c>
+      <c r="C25" s="238"/>
+      <c r="D25" s="238" t="s">
+        <v>444</v>
+      </c>
+      <c r="E25" s="238"/>
+      <c r="F25" s="238"/>
+      <c r="G25" s="238"/>
+      <c r="H25" s="238"/>
+      <c r="I25" s="238"/>
+      <c r="J25" s="238"/>
+      <c r="K25" s="238"/>
+      <c r="L25" s="238"/>
+    </row>
+    <row r="26" spans="2:19" ht="24" thickBot="1">
+      <c r="B26" s="237" t="s">
+        <v>445</v>
+      </c>
+      <c r="C26" s="238" t="s">
+        <v>446</v>
+      </c>
+      <c r="D26" s="238"/>
+      <c r="E26" s="238"/>
+      <c r="F26" s="238"/>
+      <c r="G26" s="238"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="238"/>
+      <c r="J26" s="238"/>
+      <c r="K26" s="238" t="s">
+        <v>447</v>
+      </c>
+      <c r="L26" s="238"/>
+    </row>
+    <row r="27" spans="2:19" ht="24" thickBot="1">
+      <c r="B27" s="237" t="s">
+        <v>448</v>
+      </c>
+      <c r="C27" s="245" t="s">
+        <v>192</v>
+      </c>
+      <c r="D27" s="246"/>
+      <c r="E27" s="245" t="s">
+        <v>449</v>
+      </c>
+      <c r="F27" s="247"/>
+      <c r="G27" s="247"/>
+      <c r="H27" s="247"/>
+      <c r="I27" s="247"/>
+      <c r="J27" s="246"/>
+      <c r="K27" s="245" t="s">
+        <v>450</v>
+      </c>
+      <c r="L27" s="246"/>
+    </row>
+    <row r="28" spans="2:19" ht="24" thickBot="1">
+      <c r="B28" s="237" t="s">
+        <v>451</v>
+      </c>
+      <c r="C28" s="245" t="s">
+        <v>452</v>
+      </c>
+      <c r="D28" s="246"/>
+      <c r="E28" s="245" t="s">
+        <v>449</v>
+      </c>
+      <c r="F28" s="247"/>
+      <c r="G28" s="247"/>
+      <c r="H28" s="247"/>
+      <c r="I28" s="247"/>
+      <c r="J28" s="246"/>
+      <c r="K28" s="245" t="s">
+        <v>453</v>
+      </c>
+      <c r="L28" s="246"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -10014,7 +11466,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE696064-E7AA-4532-A325-42E320CBBB3B}">
   <dimension ref="B2:Z11"/>
   <sheetFormatPr defaultRowHeight="21"/>
@@ -10528,7 +11980,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50EA2289-9B8A-4614-ACA7-AA3E199A79B3}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>

--- a/docs/鍵盤設計規格_方音符號輸入_台語音標編碼.xlsx
+++ b/docs/鍵盤設計規格_方音符號輸入_台語音標編碼.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\rime-tlpa\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{483B5F2C-798F-44C0-86C5-9BFFB7B64E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9719D13D-C8C3-4CFD-A503-E91ADD7DD6CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6D6F034E-466E-416C-B3CC-1F7937B8DE3D}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{6D6F034E-466E-416C-B3CC-1F7937B8DE3D}"/>
   </bookViews>
   <sheets>
     <sheet name="xlit對映工具" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,6 @@
     <definedName name="顯示注音輸入">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -68,7 +67,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -90,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="537">
   <si>
     <t>algebra:</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1055,10 +1054,6 @@
     <t>一</t>
   </si>
   <si>
-    <t>拼音字母</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>p</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1978,6 +1973,80 @@
   </si>
   <si>
     <t>字長</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>按鍵</t>
+  </si>
+  <si>
+    <t>th</t>
+  </si>
+  <si>
+    <t>kh</t>
+  </si>
+  <si>
+    <t>z(ts)</t>
+  </si>
+  <si>
+    <t>c(tsh)</t>
+  </si>
+  <si>
+    <t>j(i)</t>
+  </si>
+  <si>
+    <t>z(i)</t>
+  </si>
+  <si>
+    <t>c(i)</t>
+  </si>
+  <si>
+    <t>s(i)</t>
+  </si>
+  <si>
+    <t>-n</t>
+  </si>
+  <si>
+    <t>-p</t>
+  </si>
+  <si>
+    <t>-t</t>
+  </si>
+  <si>
+    <t>-k</t>
+  </si>
+  <si>
+    <t>-h</t>
+  </si>
+  <si>
+    <t>aⁿ</t>
+  </si>
+  <si>
+    <t>iⁿ</t>
+  </si>
+  <si>
+    <t>uⁿ</t>
+  </si>
+  <si>
+    <t>eⁿ</t>
+  </si>
+  <si>
+    <t>oⁿ</t>
+  </si>
+  <si>
+    <t>aiⁿ</t>
+  </si>
+  <si>
+    <t>auⁿ</t>
+  </si>
+  <si>
+    <t>g</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>台羅拼音</t>
+  </si>
+  <si>
+    <t>台羅拼音</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3181,7 +3250,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="259">
+  <cellXfs count="261">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3771,9 +3840,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="103" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="36" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3827,14 +3893,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="105" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="108" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="108" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="107" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3863,11 +3926,29 @@
     <xf numFmtId="0" fontId="107" fillId="30" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="108" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="108" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4248,38 +4329,119 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="0" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{0C1D783C-B8EF-43B2-A50F-3BE701820E02}">
+  <we:reference id="wa200007447" version="1.1.6.7" store="zh-TW" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200007447" version="1.1.6.7" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14158527-94DC-4FED-8C0E-3D91F976F89A}">
-  <dimension ref="A1:BP62"/>
+  <dimension ref="A1:CH62"/>
   <sheetFormatPr defaultRowHeight="25.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.3984375" style="1" customWidth="1"/>
     <col min="2" max="2" width="4.3984375" style="1" customWidth="1"/>
     <col min="3" max="62" width="3.69921875" style="1" customWidth="1"/>
-    <col min="63" max="64" width="8.796875" style="1"/>
-    <col min="65" max="68" width="10.3984375" style="1" customWidth="1"/>
-    <col min="69" max="16384" width="8.796875" style="1"/>
+    <col min="63" max="63" width="8.796875" style="1"/>
+    <col min="64" max="64" width="8.796875" style="257"/>
+    <col min="65" max="68" width="10.3984375" style="257" customWidth="1"/>
+    <col min="69" max="69" width="8.796875" style="257"/>
+    <col min="70" max="70" width="6.5" style="257" bestFit="1" customWidth="1"/>
+    <col min="71" max="72" width="11.19921875" style="257" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="6.5" style="257" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="11.19921875" style="257" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="8.796875" style="257"/>
+    <col min="76" max="76" width="6.5" style="257" bestFit="1" customWidth="1"/>
+    <col min="77" max="78" width="11.19921875" style="257" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="6.5" style="257" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="11.19921875" style="257" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="8.796875" style="257"/>
+    <col min="82" max="82" width="6.5" style="257" bestFit="1" customWidth="1"/>
+    <col min="83" max="84" width="11.19921875" style="257" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="6.5" style="257" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="11.19921875" style="257" bestFit="1" customWidth="1"/>
+    <col min="87" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68">
-      <c r="BL1" s="222" t="s">
-        <v>291</v>
-      </c>
-      <c r="BM1" s="222" t="str" cm="1">
+    <row r="1" spans="1:86">
+      <c r="BL1" s="256" t="s">
+        <v>290</v>
+      </c>
+      <c r="BM1" s="256" t="str" cm="1">
         <f t="array" ref="BM1:BP1">TRANSPOSE(A3:A6)</f>
-        <v>拼音字母</v>
-      </c>
-      <c r="BN1" s="222" t="str">
+        <v>台羅拼音</v>
+      </c>
+      <c r="BN1" s="256" t="str">
         <v>字典編碼</v>
       </c>
-      <c r="BO1" s="222" t="str">
+      <c r="BO1" s="256" t="str">
         <v>按鍵</v>
       </c>
-      <c r="BP1" s="222" t="str">
+      <c r="BP1" s="256" t="str">
         <v>注音符號</v>
       </c>
+      <c r="BR1" s="256" t="s">
+        <v>188</v>
+      </c>
+      <c r="BS1" s="256" t="s">
+        <v>535</v>
+      </c>
+      <c r="BT1" s="256" t="s">
+        <v>205</v>
+      </c>
+      <c r="BU1" s="256" t="s">
+        <v>513</v>
+      </c>
+      <c r="BV1" s="256" t="s">
+        <v>212</v>
+      </c>
+      <c r="BX1" s="256" t="s">
+        <v>188</v>
+      </c>
+      <c r="BY1" s="256" t="s">
+        <v>535</v>
+      </c>
+      <c r="BZ1" s="256" t="s">
+        <v>205</v>
+      </c>
+      <c r="CA1" s="256" t="s">
+        <v>513</v>
+      </c>
+      <c r="CB1" s="256" t="s">
+        <v>212</v>
+      </c>
+      <c r="CD1" s="256" t="s">
+        <v>188</v>
+      </c>
+      <c r="CE1" s="256" t="s">
+        <v>535</v>
+      </c>
+      <c r="CF1" s="256" t="s">
+        <v>205</v>
+      </c>
+      <c r="CG1" s="256" t="s">
+        <v>513</v>
+      </c>
+      <c r="CH1" s="256" t="s">
+        <v>212</v>
+      </c>
     </row>
-    <row r="2" spans="1:68">
+    <row r="2" spans="1:86">
       <c r="C2" s="3">
         <f xml:space="preserve"> COLUMN() -2</f>
         <v>1</v>
@@ -4520,152 +4682,197 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="BL2" s="221" cm="1">
+      <c r="BL2" s="258" cm="1">
         <f t="array" ref="BL2:BP61" xml:space="preserve"> TRANSPOSE(C2:BJ6)</f>
         <v>1</v>
       </c>
-      <c r="BM2" s="221" t="str">
+      <c r="BM2" s="258" t="str">
         <v>b</v>
       </c>
-      <c r="BN2" s="221" t="str">
+      <c r="BN2" s="258" t="str">
         <v>b</v>
       </c>
-      <c r="BO2" s="221" t="str">
+      <c r="BO2" s="258" t="str">
         <v>!</v>
       </c>
-      <c r="BP2" s="221" t="str">
+      <c r="BP2" s="258" t="str">
         <v>ㆠ</v>
       </c>
+      <c r="BR2" s="258">
+        <v>1</v>
+      </c>
+      <c r="BS2" s="258" t="s">
+        <v>38</v>
+      </c>
+      <c r="BT2" s="258" t="s">
+        <v>38</v>
+      </c>
+      <c r="BU2" s="258" t="s">
+        <v>227</v>
+      </c>
+      <c r="BV2" s="258" t="s">
+        <v>37</v>
+      </c>
+      <c r="BX2" s="258">
+        <v>1</v>
+      </c>
+      <c r="BY2" s="258" t="s">
+        <v>58</v>
+      </c>
+      <c r="BZ2" s="258" t="s">
+        <v>58</v>
+      </c>
+      <c r="CA2" s="258" t="s">
+        <v>223</v>
+      </c>
+      <c r="CB2" s="258" t="s">
+        <v>238</v>
+      </c>
+      <c r="CD2" s="258">
+        <v>1</v>
+      </c>
+      <c r="CE2" s="8">
+        <v>1</v>
+      </c>
+      <c r="CF2" s="8">
+        <v>1</v>
+      </c>
+      <c r="CG2" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="CH2" s="8" t="s">
+        <v>245</v>
+      </c>
     </row>
-    <row r="3" spans="1:68">
+    <row r="3" spans="1:86">
       <c r="A3" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C3" s="217" t="s">
+        <v>247</v>
+      </c>
+      <c r="D3" s="217" t="s">
         <v>246</v>
       </c>
-      <c r="C3" s="217" t="s">
+      <c r="E3" s="217" t="s">
         <v>248</v>
       </c>
-      <c r="D3" s="217" t="s">
-        <v>247</v>
-      </c>
-      <c r="E3" s="217" t="s">
+      <c r="F3" s="217" t="s">
         <v>249</v>
       </c>
-      <c r="F3" s="217" t="s">
+      <c r="G3" s="217" t="s">
         <v>250</v>
-      </c>
-      <c r="G3" s="217" t="s">
-        <v>251</v>
       </c>
       <c r="H3" s="217" t="s">
         <v>96</v>
       </c>
       <c r="I3" s="217" t="s">
+        <v>251</v>
+      </c>
+      <c r="J3" s="217" t="s">
         <v>252</v>
       </c>
-      <c r="J3" s="217" t="s">
+      <c r="K3" s="217" t="s">
+        <v>534</v>
+      </c>
+      <c r="L3" s="217" t="s">
+        <v>283</v>
+      </c>
+      <c r="M3" s="217" t="s">
+        <v>284</v>
+      </c>
+      <c r="N3" s="217" t="s">
         <v>253</v>
       </c>
-      <c r="K3" s="217" t="s">
-        <v>81</v>
-      </c>
-      <c r="L3" s="217" t="s">
-        <v>284</v>
-      </c>
-      <c r="M3" s="217" t="s">
-        <v>285</v>
-      </c>
-      <c r="N3" s="217" t="s">
+      <c r="O3" s="217" t="s">
         <v>254</v>
       </c>
-      <c r="O3" s="217" t="s">
+      <c r="P3" s="217" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q3" s="217" t="s">
+        <v>292</v>
+      </c>
+      <c r="R3" s="217" t="s">
         <v>255</v>
       </c>
-      <c r="P3" s="217" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q3" s="217" t="s">
-        <v>293</v>
-      </c>
-      <c r="R3" s="217" t="s">
+      <c r="S3" s="217" t="s">
         <v>256</v>
       </c>
-      <c r="S3" s="217" t="s">
+      <c r="T3" s="217" t="s">
         <v>257</v>
       </c>
-      <c r="T3" s="217" t="s">
+      <c r="U3" s="217" t="s">
         <v>258</v>
       </c>
-      <c r="U3" s="217" t="s">
+      <c r="V3" s="217" t="s">
         <v>259</v>
       </c>
-      <c r="V3" s="217" t="s">
+      <c r="W3" s="217" t="s">
         <v>260</v>
       </c>
-      <c r="W3" s="217" t="s">
+      <c r="X3" s="217" t="s">
         <v>261</v>
       </c>
-      <c r="X3" s="217" t="s">
+      <c r="Y3" s="217" t="s">
         <v>262</v>
       </c>
-      <c r="Y3" s="217" t="s">
+      <c r="Z3" s="217" t="s">
         <v>263</v>
       </c>
-      <c r="Z3" s="217" t="s">
+      <c r="AA3" s="217" t="s">
         <v>264</v>
       </c>
-      <c r="AA3" s="217" t="s">
+      <c r="AB3" s="217" t="s">
         <v>265</v>
       </c>
-      <c r="AB3" s="217" t="s">
+      <c r="AC3" s="217" t="s">
         <v>266</v>
       </c>
-      <c r="AC3" s="217" t="s">
+      <c r="AD3" s="217" t="s">
         <v>267</v>
       </c>
-      <c r="AD3" s="217" t="s">
+      <c r="AE3" s="218" t="s">
         <v>268</v>
-      </c>
-      <c r="AE3" s="218" t="s">
-        <v>269</v>
       </c>
       <c r="AF3" s="218" t="s">
         <v>111</v>
       </c>
       <c r="AG3" s="218" t="s">
+        <v>269</v>
+      </c>
+      <c r="AH3" s="219" t="s">
         <v>270</v>
       </c>
-      <c r="AH3" s="219" t="s">
+      <c r="AI3" s="219" t="s">
         <v>271</v>
       </c>
-      <c r="AI3" s="219" t="s">
+      <c r="AJ3" s="219" t="s">
         <v>272</v>
       </c>
-      <c r="AJ3" s="219" t="s">
+      <c r="AK3" s="219" t="s">
         <v>273</v>
       </c>
-      <c r="AK3" s="219" t="s">
+      <c r="AL3" s="217" t="s">
         <v>274</v>
       </c>
-      <c r="AL3" s="217" t="s">
+      <c r="AM3" s="217" t="s">
         <v>275</v>
       </c>
-      <c r="AM3" s="217" t="s">
+      <c r="AN3" s="217" t="s">
         <v>276</v>
       </c>
-      <c r="AN3" s="217" t="s">
+      <c r="AO3" s="217" t="s">
         <v>277</v>
       </c>
-      <c r="AO3" s="217" t="s">
+      <c r="AP3" s="217" t="s">
         <v>278</v>
       </c>
-      <c r="AP3" s="217" t="s">
+      <c r="AQ3" s="217" t="s">
         <v>279</v>
       </c>
-      <c r="AQ3" s="217" t="s">
+      <c r="AR3" s="217" t="s">
         <v>280</v>
-      </c>
-      <c r="AR3" s="217" t="s">
-        <v>281</v>
       </c>
       <c r="AS3" s="217" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+207F",4))))</f>
@@ -4726,23 +4933,68 @@
         <v>226</v>
       </c>
       <c r="BJ3" s="217"/>
-      <c r="BL3" s="221">
+      <c r="BL3" s="258">
         <v>2</v>
       </c>
-      <c r="BM3" s="221" t="str">
+      <c r="BM3" s="258" t="str">
         <v>p</v>
       </c>
-      <c r="BN3" s="221" t="str">
+      <c r="BN3" s="258" t="str">
         <v>p</v>
       </c>
-      <c r="BO3" s="221" t="str">
+      <c r="BO3" s="258" t="str">
         <v>1</v>
       </c>
-      <c r="BP3" s="221" t="str">
+      <c r="BP3" s="258" t="str">
         <v>ㄅ</v>
       </c>
+      <c r="BR3" s="258">
+        <v>2</v>
+      </c>
+      <c r="BS3" s="258" t="s">
+        <v>45</v>
+      </c>
+      <c r="BT3" s="258" t="s">
+        <v>45</v>
+      </c>
+      <c r="BU3" s="258" t="s">
+        <v>225</v>
+      </c>
+      <c r="BV3" s="258" t="s">
+        <v>44</v>
+      </c>
+      <c r="BX3" s="258">
+        <v>2</v>
+      </c>
+      <c r="BY3" s="258" t="s">
+        <v>105</v>
+      </c>
+      <c r="BZ3" s="258" t="s">
+        <v>105</v>
+      </c>
+      <c r="CA3" s="258" t="s">
+        <v>142</v>
+      </c>
+      <c r="CB3" s="258" t="s">
+        <v>104</v>
+      </c>
+      <c r="CD3" s="258">
+        <v>2</v>
+      </c>
+      <c r="CE3" s="8">
+        <v>7</v>
+      </c>
+      <c r="CF3" s="8">
+        <v>7</v>
+      </c>
+      <c r="CG3" s="8">
+        <v>5</v>
+      </c>
+      <c r="CH3" s="8" t="s">
+        <v>240</v>
+      </c>
     </row>
-    <row r="4" spans="1:68">
+    <row r="4" spans="1:86">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -4774,7 +5026,7 @@
         <v>98</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>119</v>
@@ -4924,23 +5176,68 @@
         <v>226</v>
       </c>
       <c r="BJ4" s="5"/>
-      <c r="BL4" s="221">
+      <c r="BL4" s="258">
         <v>3</v>
       </c>
-      <c r="BM4" s="221" t="str">
+      <c r="BM4" s="258" t="str">
         <v>ph</v>
       </c>
-      <c r="BN4" s="223" t="str">
+      <c r="BN4" s="259" t="str">
         <v>P</v>
       </c>
-      <c r="BO4" s="221" t="str">
+      <c r="BO4" s="258" t="str">
         <v>q</v>
       </c>
-      <c r="BP4" s="221" t="str">
+      <c r="BP4" s="258" t="str">
         <v>ㄆ</v>
       </c>
+      <c r="BR4" s="258">
+        <v>3</v>
+      </c>
+      <c r="BS4" s="258" t="s">
+        <v>94</v>
+      </c>
+      <c r="BT4" s="258" t="s">
+        <v>77</v>
+      </c>
+      <c r="BU4" s="258" t="s">
+        <v>195</v>
+      </c>
+      <c r="BV4" s="258" t="s">
+        <v>93</v>
+      </c>
+      <c r="BX4" s="258">
+        <v>3</v>
+      </c>
+      <c r="BY4" s="258" t="s">
+        <v>126</v>
+      </c>
+      <c r="BZ4" s="258" t="s">
+        <v>199</v>
+      </c>
+      <c r="CA4" s="258" t="s">
+        <v>119</v>
+      </c>
+      <c r="CB4" s="258" t="s">
+        <v>125</v>
+      </c>
+      <c r="CD4" s="258">
+        <v>3</v>
+      </c>
+      <c r="CE4" s="8">
+        <v>3</v>
+      </c>
+      <c r="CF4" s="8">
+        <v>3</v>
+      </c>
+      <c r="CG4" s="8">
+        <v>3</v>
+      </c>
+      <c r="CH4" s="8" t="s">
+        <v>241</v>
+      </c>
     </row>
-    <row r="5" spans="1:68">
+    <row r="5" spans="1:86">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -5092,7 +5389,7 @@
         <v>120</v>
       </c>
       <c r="AZ5" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BA5" s="6">
         <v>5</v>
@@ -5122,23 +5419,68 @@
         <v>226</v>
       </c>
       <c r="BJ5" s="6"/>
-      <c r="BL5" s="221">
+      <c r="BL5" s="258">
         <v>4</v>
       </c>
-      <c r="BM5" s="221" t="str">
+      <c r="BM5" s="258" t="str">
         <v>m</v>
       </c>
-      <c r="BN5" s="221" t="str">
+      <c r="BN5" s="258" t="str">
         <v>m</v>
       </c>
-      <c r="BO5" s="221" t="str">
+      <c r="BO5" s="258" t="str">
         <v>a</v>
       </c>
-      <c r="BP5" s="221" t="str">
+      <c r="BP5" s="258" t="str">
         <v>ㄇ</v>
       </c>
+      <c r="BR5" s="258">
+        <v>4</v>
+      </c>
+      <c r="BS5" s="258" t="s">
+        <v>192</v>
+      </c>
+      <c r="BT5" s="258" t="s">
+        <v>192</v>
+      </c>
+      <c r="BU5" s="258" t="s">
+        <v>58</v>
+      </c>
+      <c r="BV5" s="258" t="s">
+        <v>129</v>
+      </c>
+      <c r="BX5" s="258">
+        <v>4</v>
+      </c>
+      <c r="BY5" s="258" t="s">
+        <v>142</v>
+      </c>
+      <c r="BZ5" s="258" t="s">
+        <v>142</v>
+      </c>
+      <c r="CA5" s="258" t="s">
+        <v>191</v>
+      </c>
+      <c r="CB5" s="258" t="s">
+        <v>141</v>
+      </c>
+      <c r="CD5" s="258">
+        <v>4</v>
+      </c>
+      <c r="CE5" s="8">
+        <v>2</v>
+      </c>
+      <c r="CF5" s="8">
+        <v>2</v>
+      </c>
+      <c r="CG5" s="8">
+        <v>4</v>
+      </c>
+      <c r="CH5" s="8" t="s">
+        <v>242</v>
+      </c>
     </row>
-    <row r="6" spans="1:68">
+    <row r="6" spans="1:86">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -5320,348 +5662,663 @@
         <v>226</v>
       </c>
       <c r="BJ6" s="8"/>
-      <c r="BL6" s="221">
+      <c r="BL6" s="258">
         <v>5</v>
       </c>
-      <c r="BM6" s="221" t="str">
+      <c r="BM6" s="258" t="str">
         <v>n</v>
       </c>
-      <c r="BN6" s="221" t="str">
+      <c r="BN6" s="258" t="str">
         <v>n</v>
       </c>
-      <c r="BO6" s="221" t="str">
+      <c r="BO6" s="258" t="str">
         <v>s</v>
       </c>
-      <c r="BP6" s="221" t="str">
+      <c r="BP6" s="258" t="str">
         <v>ㄋ</v>
       </c>
+      <c r="BR6" s="258">
+        <v>5</v>
+      </c>
+      <c r="BS6" s="258" t="s">
+        <v>193</v>
+      </c>
+      <c r="BT6" s="258" t="s">
+        <v>193</v>
+      </c>
+      <c r="BU6" s="258" t="s">
+        <v>179</v>
+      </c>
+      <c r="BV6" s="258" t="s">
+        <v>131</v>
+      </c>
+      <c r="BX6" s="258">
+        <v>5</v>
+      </c>
+      <c r="BY6" s="258" t="s">
+        <v>183</v>
+      </c>
+      <c r="BZ6" s="258" t="s">
+        <v>183</v>
+      </c>
+      <c r="CA6" s="258" t="s">
+        <v>228</v>
+      </c>
+      <c r="CB6" s="258" t="s">
+        <v>182</v>
+      </c>
+      <c r="CD6" s="258">
+        <v>5</v>
+      </c>
+      <c r="CE6" s="8">
+        <v>5</v>
+      </c>
+      <c r="CF6" s="8">
+        <v>5</v>
+      </c>
+      <c r="CG6" s="8">
+        <v>6</v>
+      </c>
+      <c r="CH6" s="8" t="s">
+        <v>243</v>
+      </c>
     </row>
-    <row r="7" spans="1:68">
-      <c r="C7" s="257"/>
-      <c r="D7" s="257"/>
-      <c r="E7" s="257"/>
-      <c r="F7" s="257"/>
-      <c r="G7" s="257"/>
-      <c r="H7" s="257"/>
-      <c r="I7" s="257"/>
-      <c r="J7" s="257"/>
-      <c r="K7" s="257"/>
-      <c r="L7" s="257"/>
-      <c r="M7" s="257"/>
-      <c r="N7" s="257"/>
-      <c r="O7" s="257"/>
-      <c r="P7" s="257"/>
-      <c r="Q7" s="257"/>
-      <c r="R7" s="257"/>
-      <c r="S7" s="257"/>
-      <c r="T7" s="257"/>
-      <c r="U7" s="257"/>
-      <c r="V7" s="257"/>
-      <c r="W7" s="257"/>
-      <c r="X7" s="257"/>
-      <c r="Y7" s="257"/>
-      <c r="Z7" s="257"/>
-      <c r="AA7" s="257"/>
-      <c r="AB7" s="257"/>
-      <c r="AC7" s="257"/>
-      <c r="AD7" s="257"/>
-      <c r="AE7" s="257"/>
-      <c r="AF7" s="257"/>
-      <c r="AG7" s="257"/>
-      <c r="AH7" s="257"/>
-      <c r="AI7" s="257"/>
-      <c r="AJ7" s="257"/>
-      <c r="AK7" s="257"/>
-      <c r="AL7" s="257"/>
-      <c r="AM7" s="257"/>
-      <c r="AN7" s="257"/>
-      <c r="AO7" s="257"/>
-      <c r="AP7" s="257"/>
-      <c r="AQ7" s="257"/>
-      <c r="AR7" s="257"/>
-      <c r="AS7" s="257"/>
-      <c r="AT7" s="257"/>
-      <c r="AU7" s="257"/>
-      <c r="AV7" s="257"/>
-      <c r="AW7" s="257"/>
-      <c r="AX7" s="257"/>
-      <c r="AY7" s="257"/>
-      <c r="AZ7" s="257"/>
-      <c r="BA7" s="257"/>
-      <c r="BB7" s="257"/>
-      <c r="BC7" s="257"/>
-      <c r="BD7" s="257"/>
-      <c r="BE7" s="257"/>
-      <c r="BF7" s="257"/>
-      <c r="BG7" s="257"/>
-      <c r="BH7" s="257"/>
-      <c r="BI7" s="257"/>
-      <c r="BJ7" s="257"/>
-      <c r="BL7" s="221">
+    <row r="7" spans="1:86">
+      <c r="C7" s="242"/>
+      <c r="D7" s="242"/>
+      <c r="E7" s="242"/>
+      <c r="F7" s="242"/>
+      <c r="G7" s="242"/>
+      <c r="H7" s="242"/>
+      <c r="I7" s="242"/>
+      <c r="J7" s="242"/>
+      <c r="K7" s="242"/>
+      <c r="L7" s="242"/>
+      <c r="M7" s="242"/>
+      <c r="N7" s="242"/>
+      <c r="O7" s="242"/>
+      <c r="P7" s="242"/>
+      <c r="Q7" s="242"/>
+      <c r="R7" s="242"/>
+      <c r="S7" s="242"/>
+      <c r="T7" s="242"/>
+      <c r="U7" s="242"/>
+      <c r="V7" s="242"/>
+      <c r="W7" s="242"/>
+      <c r="X7" s="242"/>
+      <c r="Y7" s="242"/>
+      <c r="Z7" s="242"/>
+      <c r="AA7" s="242"/>
+      <c r="AB7" s="242"/>
+      <c r="AC7" s="242"/>
+      <c r="AD7" s="242"/>
+      <c r="AE7" s="242"/>
+      <c r="AF7" s="242"/>
+      <c r="AG7" s="242"/>
+      <c r="AH7" s="242"/>
+      <c r="AI7" s="242"/>
+      <c r="AJ7" s="242"/>
+      <c r="AK7" s="242"/>
+      <c r="AL7" s="242"/>
+      <c r="AM7" s="242"/>
+      <c r="AN7" s="242"/>
+      <c r="AO7" s="242"/>
+      <c r="AP7" s="242"/>
+      <c r="AQ7" s="242"/>
+      <c r="AR7" s="242"/>
+      <c r="AS7" s="242"/>
+      <c r="AT7" s="242"/>
+      <c r="AU7" s="242"/>
+      <c r="AV7" s="242"/>
+      <c r="AW7" s="242"/>
+      <c r="AX7" s="242"/>
+      <c r="AY7" s="242"/>
+      <c r="AZ7" s="242"/>
+      <c r="BA7" s="242"/>
+      <c r="BB7" s="242"/>
+      <c r="BC7" s="242"/>
+      <c r="BD7" s="242"/>
+      <c r="BE7" s="242"/>
+      <c r="BF7" s="242"/>
+      <c r="BG7" s="242"/>
+      <c r="BH7" s="242"/>
+      <c r="BI7" s="242"/>
+      <c r="BJ7" s="242"/>
+      <c r="BL7" s="258">
         <v>6</v>
       </c>
-      <c r="BM7" s="221" t="str">
+      <c r="BM7" s="258" t="str">
         <v>t</v>
       </c>
-      <c r="BN7" s="221" t="str">
+      <c r="BN7" s="258" t="str">
         <v>t</v>
       </c>
-      <c r="BO7" s="221" t="str">
+      <c r="BO7" s="258" t="str">
         <v>2</v>
       </c>
-      <c r="BP7" s="221" t="str">
+      <c r="BP7" s="258" t="str">
         <v>ㄉ</v>
       </c>
+      <c r="BR7" s="258">
+        <v>6</v>
+      </c>
+      <c r="BS7" s="258" t="s">
+        <v>197</v>
+      </c>
+      <c r="BT7" s="258" t="s">
+        <v>197</v>
+      </c>
+      <c r="BU7" s="258" t="s">
+        <v>224</v>
+      </c>
+      <c r="BV7" s="258" t="s">
+        <v>46</v>
+      </c>
+      <c r="BX7" s="258">
+        <v>6</v>
+      </c>
+      <c r="BY7" s="258" t="s">
+        <v>107</v>
+      </c>
+      <c r="BZ7" s="258" t="s">
+        <v>76</v>
+      </c>
+      <c r="CA7" s="258" t="s">
+        <v>105</v>
+      </c>
+      <c r="CB7" s="258" t="s">
+        <v>106</v>
+      </c>
+      <c r="CD7" s="258">
+        <v>6</v>
+      </c>
+      <c r="CE7" s="8">
+        <v>8</v>
+      </c>
+      <c r="CF7" s="8">
+        <v>8</v>
+      </c>
+      <c r="CG7" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="CH7" s="8" t="s">
+        <v>239</v>
+      </c>
     </row>
-    <row r="8" spans="1:68">
-      <c r="C8" s="258" t="str">
+    <row r="8" spans="1:86">
+      <c r="C8" s="243" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("""", C5:AY5, AZ5:BH5, """")</f>
         <v>"!1qas2wxEedGYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7N"</v>
       </c>
-      <c r="D8" s="257"/>
-      <c r="E8" s="257"/>
-      <c r="F8" s="257"/>
-      <c r="G8" s="257"/>
-      <c r="H8" s="257"/>
-      <c r="I8" s="257"/>
-      <c r="J8" s="257"/>
-      <c r="K8" s="257"/>
-      <c r="L8" s="257"/>
-      <c r="M8" s="257"/>
-      <c r="N8" s="257"/>
-      <c r="O8" s="257"/>
-      <c r="P8" s="257"/>
-      <c r="Q8" s="257"/>
-      <c r="R8" s="257"/>
-      <c r="S8" s="257"/>
-      <c r="T8" s="257"/>
-      <c r="U8" s="257"/>
-      <c r="V8" s="257"/>
-      <c r="W8" s="257"/>
-      <c r="X8" s="257"/>
-      <c r="Y8" s="257"/>
-      <c r="Z8" s="257"/>
-      <c r="AA8" s="257"/>
-      <c r="AB8" s="257"/>
-      <c r="AC8" s="257"/>
-      <c r="AD8" s="257"/>
-      <c r="AE8" s="257"/>
-      <c r="AF8" s="257"/>
-      <c r="AG8" s="257"/>
-      <c r="AH8" s="257"/>
-      <c r="AI8" s="257"/>
-      <c r="AJ8" s="257"/>
-      <c r="AK8" s="257"/>
-      <c r="AL8" s="257"/>
-      <c r="AM8" s="257"/>
-      <c r="AN8" s="257"/>
-      <c r="AO8" s="257"/>
-      <c r="AP8" s="257"/>
-      <c r="AQ8" s="257"/>
-      <c r="AR8" s="257"/>
-      <c r="AS8" s="257"/>
-      <c r="AT8" s="257"/>
-      <c r="AU8" s="257"/>
-      <c r="AV8" s="257"/>
-      <c r="AW8" s="257"/>
-      <c r="AX8" s="257"/>
-      <c r="AY8" s="257"/>
-      <c r="AZ8" s="257"/>
-      <c r="BA8" s="257"/>
-      <c r="BB8" s="257"/>
-      <c r="BC8" s="257"/>
-      <c r="BD8" s="257"/>
-      <c r="BE8" s="257"/>
-      <c r="BF8" s="257"/>
-      <c r="BG8" s="257"/>
-      <c r="BH8" s="257"/>
-      <c r="BI8" s="257"/>
-      <c r="BJ8" s="257"/>
-      <c r="BL8" s="221">
+      <c r="D8" s="242"/>
+      <c r="E8" s="242"/>
+      <c r="F8" s="242"/>
+      <c r="G8" s="242"/>
+      <c r="H8" s="242"/>
+      <c r="I8" s="242"/>
+      <c r="J8" s="242"/>
+      <c r="K8" s="242"/>
+      <c r="L8" s="242"/>
+      <c r="M8" s="242"/>
+      <c r="N8" s="242"/>
+      <c r="O8" s="242"/>
+      <c r="P8" s="242"/>
+      <c r="Q8" s="242"/>
+      <c r="R8" s="242"/>
+      <c r="S8" s="242"/>
+      <c r="T8" s="242"/>
+      <c r="U8" s="242"/>
+      <c r="V8" s="242"/>
+      <c r="W8" s="242"/>
+      <c r="X8" s="242"/>
+      <c r="Y8" s="242"/>
+      <c r="Z8" s="242"/>
+      <c r="AA8" s="242"/>
+      <c r="AB8" s="242"/>
+      <c r="AC8" s="242"/>
+      <c r="AD8" s="242"/>
+      <c r="AE8" s="242"/>
+      <c r="AF8" s="242"/>
+      <c r="AG8" s="242"/>
+      <c r="AH8" s="242"/>
+      <c r="AI8" s="242"/>
+      <c r="AJ8" s="242"/>
+      <c r="AK8" s="242"/>
+      <c r="AL8" s="242"/>
+      <c r="AM8" s="242"/>
+      <c r="AN8" s="242"/>
+      <c r="AO8" s="242"/>
+      <c r="AP8" s="242"/>
+      <c r="AQ8" s="242"/>
+      <c r="AR8" s="242"/>
+      <c r="AS8" s="242"/>
+      <c r="AT8" s="242"/>
+      <c r="AU8" s="242"/>
+      <c r="AV8" s="242"/>
+      <c r="AW8" s="242"/>
+      <c r="AX8" s="242"/>
+      <c r="AY8" s="242"/>
+      <c r="AZ8" s="242"/>
+      <c r="BA8" s="242"/>
+      <c r="BB8" s="242"/>
+      <c r="BC8" s="242"/>
+      <c r="BD8" s="242"/>
+      <c r="BE8" s="242"/>
+      <c r="BF8" s="242"/>
+      <c r="BG8" s="242"/>
+      <c r="BH8" s="242"/>
+      <c r="BI8" s="242"/>
+      <c r="BJ8" s="242"/>
+      <c r="BL8" s="258">
         <v>7</v>
       </c>
-      <c r="BM8" s="221" t="str">
+      <c r="BM8" s="258" t="str">
         <v>th</v>
       </c>
-      <c r="BN8" s="221" t="str">
+      <c r="BN8" s="258" t="str">
         <v>T</v>
       </c>
-      <c r="BO8" s="221" t="str">
+      <c r="BO8" s="258" t="str">
         <v>w</v>
       </c>
-      <c r="BP8" s="221" t="str">
+      <c r="BP8" s="258" t="str">
         <v>ㄊ</v>
       </c>
+      <c r="BR8" s="258">
+        <v>7</v>
+      </c>
+      <c r="BS8" s="258" t="s">
+        <v>514</v>
+      </c>
+      <c r="BT8" s="258" t="s">
+        <v>72</v>
+      </c>
+      <c r="BU8" s="258" t="s">
+        <v>199</v>
+      </c>
+      <c r="BV8" s="258" t="s">
+        <v>95</v>
+      </c>
+      <c r="BX8" s="258">
+        <v>7</v>
+      </c>
+      <c r="BY8" s="258" t="s">
+        <v>194</v>
+      </c>
+      <c r="BZ8" s="258" t="s">
+        <v>10</v>
+      </c>
+      <c r="CA8" s="258" t="s">
+        <v>134</v>
+      </c>
+      <c r="CB8" s="258" t="s">
+        <v>143</v>
+      </c>
+      <c r="CD8" s="258">
+        <v>7</v>
+      </c>
+      <c r="CE8" s="8">
+        <v>4</v>
+      </c>
+      <c r="CF8" s="8">
+        <v>4</v>
+      </c>
+      <c r="CG8" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="CH8" s="8" t="s">
+        <v>244</v>
+      </c>
     </row>
-    <row r="9" spans="1:68">
+    <row r="9" spans="1:86">
       <c r="C9" s="1" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("""",C5:AY5, """")</f>
         <v>"!1qas2wxEedGYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L"</v>
       </c>
-      <c r="D9" s="257"/>
-      <c r="E9" s="257"/>
-      <c r="F9" s="257"/>
-      <c r="G9" s="257"/>
-      <c r="H9" s="257"/>
-      <c r="I9" s="257"/>
-      <c r="J9" s="257"/>
-      <c r="K9" s="257"/>
-      <c r="L9" s="257"/>
-      <c r="M9" s="257"/>
-      <c r="N9" s="257"/>
-      <c r="O9" s="257"/>
-      <c r="P9" s="257"/>
-      <c r="Q9" s="257"/>
-      <c r="R9" s="257"/>
-      <c r="S9" s="257"/>
-      <c r="T9" s="257"/>
-      <c r="U9" s="257"/>
-      <c r="V9" s="257"/>
-      <c r="W9" s="257"/>
-      <c r="X9" s="257"/>
-      <c r="Y9" s="257"/>
-      <c r="Z9" s="257"/>
-      <c r="AA9" s="257"/>
-      <c r="AB9" s="257"/>
-      <c r="AC9" s="257"/>
-      <c r="AD9" s="257"/>
-      <c r="AE9" s="257"/>
-      <c r="AF9" s="257"/>
-      <c r="AG9" s="257"/>
-      <c r="AH9" s="257"/>
-      <c r="AI9" s="257"/>
-      <c r="AJ9" s="257"/>
-      <c r="AK9" s="257"/>
-      <c r="AL9" s="257"/>
-      <c r="AM9" s="257"/>
-      <c r="AN9" s="257"/>
-      <c r="AO9" s="257"/>
-      <c r="AP9" s="257"/>
-      <c r="AQ9" s="257"/>
-      <c r="AR9" s="257"/>
-      <c r="AS9" s="257"/>
-      <c r="AT9" s="257"/>
-      <c r="AU9" s="257"/>
-      <c r="AV9" s="257"/>
-      <c r="AW9" s="257"/>
-      <c r="AX9" s="257"/>
-      <c r="AY9" s="257"/>
-      <c r="AZ9" s="257"/>
-      <c r="BA9" s="257"/>
-      <c r="BB9" s="257"/>
-      <c r="BC9" s="257"/>
-      <c r="BD9" s="257"/>
-      <c r="BE9" s="257"/>
-      <c r="BF9" s="257"/>
-      <c r="BG9" s="257"/>
-      <c r="BH9" s="257"/>
-      <c r="BI9" s="257"/>
-      <c r="BJ9" s="257"/>
-      <c r="BL9" s="221">
+      <c r="D9" s="242"/>
+      <c r="E9" s="242"/>
+      <c r="F9" s="242"/>
+      <c r="G9" s="242"/>
+      <c r="H9" s="242"/>
+      <c r="I9" s="242"/>
+      <c r="J9" s="242"/>
+      <c r="K9" s="242"/>
+      <c r="L9" s="242"/>
+      <c r="M9" s="242"/>
+      <c r="N9" s="242"/>
+      <c r="O9" s="242"/>
+      <c r="P9" s="242"/>
+      <c r="Q9" s="242"/>
+      <c r="R9" s="242"/>
+      <c r="S9" s="242"/>
+      <c r="T9" s="242"/>
+      <c r="U9" s="242"/>
+      <c r="V9" s="242"/>
+      <c r="W9" s="242"/>
+      <c r="X9" s="242"/>
+      <c r="Y9" s="242"/>
+      <c r="Z9" s="242"/>
+      <c r="AA9" s="242"/>
+      <c r="AB9" s="242"/>
+      <c r="AC9" s="242"/>
+      <c r="AD9" s="242"/>
+      <c r="AE9" s="242"/>
+      <c r="AF9" s="242"/>
+      <c r="AG9" s="242"/>
+      <c r="AH9" s="242"/>
+      <c r="AI9" s="242"/>
+      <c r="AJ9" s="242"/>
+      <c r="AK9" s="242"/>
+      <c r="AL9" s="242"/>
+      <c r="AM9" s="242"/>
+      <c r="AN9" s="242"/>
+      <c r="AO9" s="242"/>
+      <c r="AP9" s="242"/>
+      <c r="AQ9" s="242"/>
+      <c r="AR9" s="242"/>
+      <c r="AS9" s="242"/>
+      <c r="AT9" s="242"/>
+      <c r="AU9" s="242"/>
+      <c r="AV9" s="242"/>
+      <c r="AW9" s="242"/>
+      <c r="AX9" s="242"/>
+      <c r="AY9" s="242"/>
+      <c r="AZ9" s="242"/>
+      <c r="BA9" s="242"/>
+      <c r="BB9" s="242"/>
+      <c r="BC9" s="242"/>
+      <c r="BD9" s="242"/>
+      <c r="BE9" s="242"/>
+      <c r="BF9" s="242"/>
+      <c r="BG9" s="242"/>
+      <c r="BH9" s="242"/>
+      <c r="BI9" s="242"/>
+      <c r="BJ9" s="242"/>
+      <c r="BL9" s="258">
         <v>8</v>
       </c>
-      <c r="BM9" s="221" t="str">
+      <c r="BM9" s="258" t="str">
         <v>l</v>
       </c>
-      <c r="BN9" s="221" t="str">
+      <c r="BN9" s="258" t="str">
         <v>l</v>
       </c>
-      <c r="BO9" s="221" t="str">
+      <c r="BO9" s="258" t="str">
         <v>x</v>
       </c>
-      <c r="BP9" s="221" t="str">
+      <c r="BP9" s="258" t="str">
         <v>ㄌ</v>
       </c>
+      <c r="BR9" s="258">
+        <v>8</v>
+      </c>
+      <c r="BS9" s="258" t="s">
+        <v>171</v>
+      </c>
+      <c r="BT9" s="258" t="s">
+        <v>171</v>
+      </c>
+      <c r="BU9" s="258" t="s">
+        <v>200</v>
+      </c>
+      <c r="BV9" s="258" t="s">
+        <v>170</v>
+      </c>
+      <c r="BX9" s="258">
+        <v>8</v>
+      </c>
+      <c r="BY9" s="258" t="s">
+        <v>181</v>
+      </c>
+      <c r="BZ9" s="258" t="s">
+        <v>155</v>
+      </c>
+      <c r="CA9" s="258" t="s">
+        <v>192</v>
+      </c>
+      <c r="CB9" s="258" t="s">
+        <v>180</v>
+      </c>
+      <c r="CD9" s="258">
+        <v>8</v>
+      </c>
+      <c r="CE9" s="8">
+        <v>0</v>
+      </c>
+      <c r="CF9" s="8">
+        <v>0</v>
+      </c>
+      <c r="CG9" s="8">
+        <v>7</v>
+      </c>
+      <c r="CH9" s="8" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="10" spans="1:68">
+    <row r="10" spans="1:86">
       <c r="AR10" s="220" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AS10" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AV10" s="1" t="str">
         <f xml:space="preserve"> _xlfn.UNICHAR(HEX2DEC(RIGHT("U+207F",4)))</f>
         <v>ⁿ</v>
       </c>
-      <c r="BL10" s="221">
+      <c r="BL10" s="258">
         <v>9</v>
       </c>
-      <c r="BM10" s="221" t="str">
+      <c r="BM10" s="258" t="str">
+        <v>g</v>
+      </c>
+      <c r="BN10" s="258" t="str">
+        <v>g</v>
+      </c>
+      <c r="BO10" s="258" t="str">
+        <v>E</v>
+      </c>
+      <c r="BP10" s="258" t="str">
         <v>ㆣ</v>
       </c>
-      <c r="BN10" s="221" t="str">
-        <v>g</v>
-      </c>
-      <c r="BO10" s="221" t="str">
-        <v>E</v>
-      </c>
-      <c r="BP10" s="221" t="str">
-        <v>ㆣ</v>
+      <c r="BR10" s="258">
+        <v>9</v>
+      </c>
+      <c r="BS10" s="258" t="s">
+        <v>81</v>
+      </c>
+      <c r="BT10" s="258" t="s">
+        <v>98</v>
+      </c>
+      <c r="BU10" s="258" t="s">
+        <v>70</v>
+      </c>
+      <c r="BV10" s="258" t="s">
+        <v>81</v>
+      </c>
+      <c r="BX10" s="258">
+        <v>9</v>
+      </c>
+      <c r="BY10" s="258" t="s">
+        <v>522</v>
+      </c>
+      <c r="BZ10" s="258" t="s">
+        <v>154</v>
+      </c>
+      <c r="CA10" s="258" t="s">
+        <v>45</v>
+      </c>
+      <c r="CB10" s="258" t="s">
+        <v>110</v>
+      </c>
+      <c r="CD10" s="258">
+        <v>9</v>
+      </c>
+      <c r="CE10" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="CF10" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="CG10" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="CH10" s="8" t="s">
+        <v>184</v>
       </c>
     </row>
-    <row r="11" spans="1:68">
+    <row r="11" spans="1:86">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="BL11" s="221">
+      <c r="BL11" s="258">
         <v>10</v>
       </c>
-      <c r="BM11" s="221" t="str">
+      <c r="BM11" s="258" t="str">
         <v>k</v>
       </c>
-      <c r="BN11" s="223" t="str">
+      <c r="BN11" s="259" t="str">
         <v>k</v>
       </c>
-      <c r="BO11" s="221" t="str">
+      <c r="BO11" s="258" t="str">
         <v>e</v>
       </c>
-      <c r="BP11" s="221" t="str">
+      <c r="BP11" s="258" t="str">
         <v>ㄍ</v>
       </c>
+      <c r="BR11" s="258">
+        <v>10</v>
+      </c>
+      <c r="BS11" s="258" t="s">
+        <v>134</v>
+      </c>
+      <c r="BT11" s="258" t="s">
+        <v>134</v>
+      </c>
+      <c r="BU11" s="258" t="s">
+        <v>183</v>
+      </c>
+      <c r="BV11" s="258" t="s">
+        <v>97</v>
+      </c>
+      <c r="BX11" s="258">
+        <v>10</v>
+      </c>
+      <c r="BY11" s="258" t="s">
+        <v>187</v>
+      </c>
+      <c r="BZ11" s="258" t="s">
+        <v>116</v>
+      </c>
+      <c r="CA11" s="258" t="s">
+        <v>229</v>
+      </c>
+      <c r="CB11" s="258" t="s">
+        <v>186</v>
+      </c>
     </row>
-    <row r="12" spans="1:68" outlineLevel="1">
+    <row r="12" spans="1:86" outlineLevel="1">
       <c r="B12" s="1" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - xlit|", C4:BH4, "|", C5:BH5, "|")</f>
         <v xml:space="preserve">    - xlit|bpPmntTlgkKŋjzcshJZCSaiwueOəMNGRFQVIUY@AWHdfqrvxy17325840L|!1qas2wxEedGYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7N|</v>
       </c>
-      <c r="BL12" s="221">
+      <c r="BL12" s="258">
         <v>11</v>
       </c>
-      <c r="BM12" s="221" t="str">
+      <c r="BM12" s="258" t="str">
         <v>kh</v>
       </c>
-      <c r="BN12" s="221" t="str">
+      <c r="BN12" s="258" t="str">
         <v>K</v>
       </c>
-      <c r="BO12" s="221" t="str">
+      <c r="BO12" s="258" t="str">
         <v>d</v>
       </c>
-      <c r="BP12" s="221" t="str">
+      <c r="BP12" s="258" t="str">
         <v>ㄎ</v>
       </c>
+      <c r="BR12" s="258">
+        <v>11</v>
+      </c>
+      <c r="BS12" s="258" t="s">
+        <v>515</v>
+      </c>
+      <c r="BT12" s="258" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU12" s="258" t="s">
+        <v>189</v>
+      </c>
+      <c r="BV12" s="258" t="s">
+        <v>133</v>
+      </c>
+      <c r="BX12" s="258">
+        <v>11</v>
+      </c>
+      <c r="BY12" s="258" t="s">
+        <v>523</v>
+      </c>
+      <c r="BZ12" s="258" t="s">
+        <v>71</v>
+      </c>
+      <c r="CA12" s="258" t="s">
+        <v>38</v>
+      </c>
+      <c r="CB12" s="258" t="s">
+        <v>176</v>
+      </c>
     </row>
-    <row r="13" spans="1:68" outlineLevel="1">
+    <row r="13" spans="1:86" outlineLevel="1">
       <c r="B13" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="BL13" s="221">
+        <v>285</v>
+      </c>
+      <c r="BL13" s="258">
         <v>12</v>
       </c>
-      <c r="BM13" s="221" t="str">
+      <c r="BM13" s="258" t="str">
         <v>ng</v>
       </c>
-      <c r="BN13" s="221" t="str">
+      <c r="BN13" s="258" t="str">
         <v>ŋ</v>
       </c>
-      <c r="BO13" s="221" t="str">
+      <c r="BO13" s="258" t="str">
         <v>G</v>
       </c>
-      <c r="BP13" s="221" t="str">
+      <c r="BP13" s="258" t="str">
         <v>ㄫ</v>
       </c>
+      <c r="BR13" s="258">
+        <v>12</v>
+      </c>
+      <c r="BS13" s="258" t="s">
+        <v>451</v>
+      </c>
+      <c r="BT13" s="258" t="s">
+        <v>221</v>
+      </c>
+      <c r="BU13" s="258" t="s">
+        <v>116</v>
+      </c>
+      <c r="BV13" s="258" t="s">
+        <v>159</v>
+      </c>
+      <c r="BX13" s="258">
+        <v>12</v>
+      </c>
+      <c r="BY13" s="258" t="s">
+        <v>524</v>
+      </c>
+      <c r="BZ13" s="258" t="s">
+        <v>115</v>
+      </c>
+      <c r="CA13" s="258" t="s">
+        <v>197</v>
+      </c>
+      <c r="CB13" s="258" t="s">
+        <v>100</v>
+      </c>
     </row>
-    <row r="14" spans="1:68" outlineLevel="1">
+    <row r="14" spans="1:86" outlineLevel="1">
       <c r="A14" s="1" t="s">
         <v>1</v>
       </c>
@@ -5669,23 +6326,53 @@
         <f xml:space="preserve"> SEARCH("|", $B$12)</f>
         <v>11</v>
       </c>
-      <c r="BL14" s="221">
+      <c r="BL14" s="258">
         <v>13</v>
       </c>
-      <c r="BM14" s="221" t="str">
+      <c r="BM14" s="258" t="str">
         <v>j</v>
       </c>
-      <c r="BN14" s="221" t="str">
+      <c r="BN14" s="258" t="str">
         <v>j</v>
       </c>
-      <c r="BO14" s="221" t="str">
+      <c r="BO14" s="258" t="str">
         <v>Y</v>
       </c>
-      <c r="BP14" s="221" t="str">
+      <c r="BP14" s="258" t="str">
         <v>ㆡ</v>
       </c>
+      <c r="BR14" s="258">
+        <v>13</v>
+      </c>
+      <c r="BS14" s="258" t="s">
+        <v>191</v>
+      </c>
+      <c r="BT14" s="258" t="s">
+        <v>191</v>
+      </c>
+      <c r="BU14" s="258" t="s">
+        <v>73</v>
+      </c>
+      <c r="BV14" s="258" t="s">
+        <v>85</v>
+      </c>
+      <c r="BX14" s="258">
+        <v>13</v>
+      </c>
+      <c r="BY14" s="258" t="s">
+        <v>525</v>
+      </c>
+      <c r="BZ14" s="258" t="s">
+        <v>68</v>
+      </c>
+      <c r="CA14" s="258" t="s">
+        <v>98</v>
+      </c>
+      <c r="CB14" s="258" t="s">
+        <v>137</v>
+      </c>
     </row>
-    <row r="15" spans="1:68" outlineLevel="1">
+    <row r="15" spans="1:86" outlineLevel="1">
       <c r="A15" s="1" t="s">
         <v>2</v>
       </c>
@@ -5693,23 +6380,53 @@
         <f xml:space="preserve"> SEARCH("|", $B$12, B14+1)</f>
         <v>70</v>
       </c>
-      <c r="BL15" s="221">
+      <c r="BL15" s="258">
         <v>14</v>
       </c>
-      <c r="BM15" s="221" t="str">
+      <c r="BM15" s="258" t="str">
         <v>z(ts)</v>
       </c>
-      <c r="BN15" s="223" t="str">
+      <c r="BN15" s="259" t="str">
         <v>z</v>
       </c>
-      <c r="BO15" s="221" t="str">
+      <c r="BO15" s="258" t="str">
         <v>y</v>
       </c>
-      <c r="BP15" s="221" t="str">
+      <c r="BP15" s="258" t="str">
         <v>ㄗ</v>
       </c>
+      <c r="BR15" s="258">
+        <v>14</v>
+      </c>
+      <c r="BS15" s="258" t="s">
+        <v>516</v>
+      </c>
+      <c r="BT15" s="258" t="s">
+        <v>103</v>
+      </c>
+      <c r="BU15" s="258" t="s">
+        <v>201</v>
+      </c>
+      <c r="BV15" s="258" t="s">
+        <v>102</v>
+      </c>
+      <c r="BX15" s="258">
+        <v>14</v>
+      </c>
+      <c r="BY15" s="258" t="s">
+        <v>526</v>
+      </c>
+      <c r="BZ15" s="258" t="s">
+        <v>152</v>
+      </c>
+      <c r="CA15" s="258" t="s">
+        <v>103</v>
+      </c>
+      <c r="CB15" s="258" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="16" spans="1:68" outlineLevel="1">
+    <row r="16" spans="1:86" outlineLevel="1">
       <c r="A16" s="1" t="s">
         <v>3</v>
       </c>
@@ -5717,40 +6434,100 @@
         <f xml:space="preserve"> SEARCH("|", $B$12, B15+1)</f>
         <v>129</v>
       </c>
-      <c r="BL16" s="221">
+      <c r="BL16" s="258">
         <v>15</v>
       </c>
-      <c r="BM16" s="221" t="str">
+      <c r="BM16" s="258" t="str">
         <v>c(tsh)</v>
       </c>
-      <c r="BN16" s="223" t="str">
+      <c r="BN16" s="259" t="str">
         <v>c</v>
       </c>
-      <c r="BO16" s="221" t="str">
+      <c r="BO16" s="258" t="str">
         <v>h</v>
       </c>
-      <c r="BP16" s="221" t="str">
+      <c r="BP16" s="258" t="str">
         <v>ㄘ</v>
       </c>
+      <c r="BR16" s="258">
+        <v>15</v>
+      </c>
+      <c r="BS16" s="258" t="s">
+        <v>517</v>
+      </c>
+      <c r="BT16" s="258" t="s">
+        <v>140</v>
+      </c>
+      <c r="BU16" s="258" t="s">
+        <v>173</v>
+      </c>
+      <c r="BV16" s="258" t="s">
+        <v>139</v>
+      </c>
+      <c r="BX16" s="258">
+        <v>15</v>
+      </c>
+      <c r="BY16" s="258" t="s">
+        <v>60</v>
+      </c>
+      <c r="BZ16" s="258" t="s">
+        <v>75</v>
+      </c>
+      <c r="CA16" s="258" t="s">
+        <v>230</v>
+      </c>
+      <c r="CB16" s="258" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="17" spans="1:68" outlineLevel="1">
-      <c r="BL17" s="221">
+    <row r="17" spans="1:80" outlineLevel="1">
+      <c r="BL17" s="258">
         <v>16</v>
       </c>
-      <c r="BM17" s="221" t="str">
+      <c r="BM17" s="258" t="str">
         <v>s</v>
       </c>
-      <c r="BN17" s="223" t="str">
+      <c r="BN17" s="259" t="str">
         <v>s</v>
       </c>
-      <c r="BO17" s="221" t="str">
+      <c r="BO17" s="258" t="str">
         <v>n</v>
       </c>
-      <c r="BP17" s="221" t="str">
+      <c r="BP17" s="258" t="str">
         <v>ㄙ</v>
       </c>
+      <c r="BR17" s="258">
+        <v>16</v>
+      </c>
+      <c r="BS17" s="258" t="s">
+        <v>179</v>
+      </c>
+      <c r="BT17" s="258" t="s">
+        <v>179</v>
+      </c>
+      <c r="BU17" s="258" t="s">
+        <v>193</v>
+      </c>
+      <c r="BV17" s="258" t="s">
+        <v>178</v>
+      </c>
+      <c r="BX17" s="258">
+        <v>16</v>
+      </c>
+      <c r="BY17" s="258" t="s">
+        <v>146</v>
+      </c>
+      <c r="BZ17" s="258" t="s">
+        <v>74</v>
+      </c>
+      <c r="CA17" s="258" t="s">
+        <v>171</v>
+      </c>
+      <c r="CB17" s="258" t="s">
+        <v>145</v>
+      </c>
     </row>
-    <row r="18" spans="1:68" outlineLevel="1">
+    <row r="18" spans="1:80" outlineLevel="1">
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
@@ -5762,23 +6539,53 @@
         <f xml:space="preserve"> MID($B$12,B14+1, (B15-B14-1))</f>
         <v>bpPmntTlgkKŋjzcshJZCSaiwueOəMNGRFQVIUY@AWHdfqrvxy17325840L</v>
       </c>
-      <c r="BL18" s="221">
+      <c r="BL18" s="258">
         <v>17</v>
       </c>
-      <c r="BM18" s="221" t="str">
+      <c r="BM18" s="258" t="str">
         <v>h</v>
       </c>
-      <c r="BN18" s="223" t="str">
+      <c r="BN18" s="259" t="str">
         <v>h</v>
       </c>
-      <c r="BO18" s="221" t="str">
+      <c r="BO18" s="258" t="str">
         <v>c</v>
       </c>
-      <c r="BP18" s="221" t="str">
+      <c r="BP18" s="258" t="str">
         <v>ㄏ</v>
       </c>
+      <c r="BR18" s="258">
+        <v>17</v>
+      </c>
+      <c r="BS18" s="258" t="s">
+        <v>173</v>
+      </c>
+      <c r="BT18" s="258" t="s">
+        <v>173</v>
+      </c>
+      <c r="BU18" s="258" t="s">
+        <v>140</v>
+      </c>
+      <c r="BV18" s="258" t="s">
+        <v>172</v>
+      </c>
+      <c r="BX18" s="258">
+        <v>17</v>
+      </c>
+      <c r="BY18" s="258" t="s">
+        <v>162</v>
+      </c>
+      <c r="BZ18" s="258" t="s">
+        <v>73</v>
+      </c>
+      <c r="CA18" s="258" t="s">
+        <v>155</v>
+      </c>
+      <c r="CB18" s="258" t="s">
+        <v>161</v>
+      </c>
     </row>
-    <row r="19" spans="1:68" outlineLevel="1">
+    <row r="19" spans="1:80" outlineLevel="1">
       <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
@@ -5790,40 +6597,100 @@
         <f xml:space="preserve"> MID($B$12,B15+1, (B16-B15-1))</f>
         <v>!1qas2wxEedGYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7N</v>
       </c>
-      <c r="BL19" s="221">
+      <c r="BL19" s="258">
         <v>18</v>
       </c>
-      <c r="BM19" s="221" t="str">
+      <c r="BM19" s="258" t="str">
         <v>j(i)</v>
       </c>
-      <c r="BN19" s="223" t="str">
+      <c r="BN19" s="259" t="str">
         <v>J</v>
       </c>
-      <c r="BO19" s="221" t="str">
+      <c r="BO19" s="258" t="str">
         <v>R</v>
       </c>
-      <c r="BP19" s="221" t="str">
+      <c r="BP19" s="258" t="str">
         <v>ㆢ</v>
       </c>
+      <c r="BR19" s="258">
+        <v>18</v>
+      </c>
+      <c r="BS19" s="258" t="s">
+        <v>518</v>
+      </c>
+      <c r="BT19" s="258" t="s">
+        <v>118</v>
+      </c>
+      <c r="BU19" s="258" t="s">
+        <v>71</v>
+      </c>
+      <c r="BV19" s="258" t="s">
+        <v>83</v>
+      </c>
+      <c r="BX19" s="258">
+        <v>18</v>
+      </c>
+      <c r="BY19" s="258" t="s">
+        <v>62</v>
+      </c>
+      <c r="BZ19" s="258" t="s">
+        <v>222</v>
+      </c>
+      <c r="CA19" s="258" t="s">
+        <v>231</v>
+      </c>
+      <c r="CB19" s="258" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="20" spans="1:68">
-      <c r="BL20" s="221">
+    <row r="20" spans="1:80">
+      <c r="BL20" s="258">
         <v>19</v>
       </c>
-      <c r="BM20" s="221" t="str">
+      <c r="BM20" s="258" t="str">
         <v>z(i)</v>
       </c>
-      <c r="BN20" s="223" t="str">
+      <c r="BN20" s="259" t="str">
         <v>Z</v>
       </c>
-      <c r="BO20" s="221" t="str">
+      <c r="BO20" s="258" t="str">
         <v>r</v>
       </c>
-      <c r="BP20" s="221" t="str">
+      <c r="BP20" s="258" t="str">
         <v>ㄐ</v>
       </c>
+      <c r="BR20" s="258">
+        <v>19</v>
+      </c>
+      <c r="BS20" s="258" t="s">
+        <v>519</v>
+      </c>
+      <c r="BT20" s="258" t="s">
+        <v>149</v>
+      </c>
+      <c r="BU20" s="258" t="s">
+        <v>196</v>
+      </c>
+      <c r="BV20" s="258" t="s">
+        <v>99</v>
+      </c>
+      <c r="BX20" s="258">
+        <v>19</v>
+      </c>
+      <c r="BY20" s="258" t="s">
+        <v>148</v>
+      </c>
+      <c r="BZ20" s="258" t="s">
+        <v>112</v>
+      </c>
+      <c r="CA20" s="258" t="s">
+        <v>232</v>
+      </c>
+      <c r="CB20" s="258" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="21" spans="1:68">
+    <row r="21" spans="1:80">
       <c r="C21" s="3">
         <f xml:space="preserve"> COLUMN() -2</f>
         <v>1</v>
@@ -6064,23 +6931,53 @@
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="BL21" s="221">
+      <c r="BL21" s="258">
         <v>20</v>
       </c>
-      <c r="BM21" s="221" t="str">
+      <c r="BM21" s="258" t="str">
         <v>c(i)</v>
       </c>
-      <c r="BN21" s="223" t="str">
+      <c r="BN21" s="259" t="str">
         <v>C</v>
       </c>
-      <c r="BO21" s="221" t="str">
+      <c r="BO21" s="258" t="str">
         <v>f</v>
       </c>
-      <c r="BP21" s="221" t="str">
+      <c r="BP21" s="258" t="str">
         <v>ㄑ</v>
       </c>
+      <c r="BR21" s="258">
+        <v>20</v>
+      </c>
+      <c r="BS21" s="258" t="s">
+        <v>520</v>
+      </c>
+      <c r="BT21" s="258" t="s">
+        <v>151</v>
+      </c>
+      <c r="BU21" s="258" t="s">
+        <v>190</v>
+      </c>
+      <c r="BV21" s="258" t="s">
+        <v>135</v>
+      </c>
+      <c r="BX21" s="258">
+        <v>20</v>
+      </c>
+      <c r="BY21" s="258" t="s">
+        <v>92</v>
+      </c>
+      <c r="BZ21" s="258" t="s">
+        <v>69</v>
+      </c>
+      <c r="CA21" s="258" t="s">
+        <v>76</v>
+      </c>
+      <c r="CB21" s="258" t="s">
+        <v>91</v>
+      </c>
     </row>
-    <row r="22" spans="1:68">
+    <row r="22" spans="1:80">
       <c r="A22" s="4" t="s">
         <v>4</v>
       </c>
@@ -6324,23 +7221,53 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="BL22" s="221">
+      <c r="BL22" s="258">
         <v>21</v>
       </c>
-      <c r="BM22" s="221" t="str">
+      <c r="BM22" s="258" t="str">
         <v>s(i)</v>
       </c>
-      <c r="BN22" s="223" t="str">
+      <c r="BN22" s="259" t="str">
         <v>S</v>
       </c>
-      <c r="BO22" s="221" t="str">
+      <c r="BO22" s="258" t="str">
         <v>v</v>
       </c>
-      <c r="BP22" s="221" t="str">
+      <c r="BP22" s="258" t="str">
         <v>ㄒ</v>
       </c>
+      <c r="BR22" s="258">
+        <v>21</v>
+      </c>
+      <c r="BS22" s="258" t="s">
+        <v>521</v>
+      </c>
+      <c r="BT22" s="258" t="s">
+        <v>113</v>
+      </c>
+      <c r="BU22" s="258" t="s">
+        <v>198</v>
+      </c>
+      <c r="BV22" s="258" t="s">
+        <v>174</v>
+      </c>
+      <c r="BX22" s="258">
+        <v>21</v>
+      </c>
+      <c r="BY22" s="258" t="s">
+        <v>109</v>
+      </c>
+      <c r="BZ22" s="258" t="s">
+        <v>117</v>
+      </c>
+      <c r="CA22" s="258" t="s">
+        <v>194</v>
+      </c>
+      <c r="CB22" s="258" t="s">
+        <v>108</v>
+      </c>
     </row>
-    <row r="23" spans="1:68">
+    <row r="23" spans="1:80">
       <c r="A23" s="1" t="s">
         <v>5</v>
       </c>
@@ -6584,115 +7511,205 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="BL23" s="221">
+      <c r="BL23" s="258">
         <v>22</v>
       </c>
-      <c r="BM23" s="221" t="str">
+      <c r="BM23" s="258" t="str">
         <v>a</v>
       </c>
-      <c r="BN23" s="223" t="str">
+      <c r="BN23" s="259" t="str">
         <v>a</v>
       </c>
-      <c r="BO23" s="221" t="str">
+      <c r="BO23" s="258" t="str">
         <v>8</v>
       </c>
-      <c r="BP23" s="221" t="str">
+      <c r="BP23" s="258" t="str">
         <v>ㄚ</v>
       </c>
+      <c r="BX23" s="258">
+        <v>22</v>
+      </c>
+      <c r="BY23" s="258" t="s">
+        <v>527</v>
+      </c>
+      <c r="BZ23" s="258" t="s">
+        <v>189</v>
+      </c>
+      <c r="CA23" s="258" t="s">
+        <v>233</v>
+      </c>
+      <c r="CB23" s="258" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="24" spans="1:68">
-      <c r="BL24" s="221">
+    <row r="24" spans="1:80">
+      <c r="BL24" s="258">
         <v>23</v>
       </c>
-      <c r="BM24" s="221" t="str">
+      <c r="BM24" s="258" t="str">
         <v>i</v>
       </c>
-      <c r="BN24" s="223" t="str">
+      <c r="BN24" s="259" t="str">
         <v>i</v>
       </c>
-      <c r="BO24" s="221" t="str">
+      <c r="BO24" s="258" t="str">
         <v>u</v>
       </c>
-      <c r="BP24" s="221" t="str">
+      <c r="BP24" s="258" t="str">
         <v>ㄧ</v>
       </c>
+      <c r="BX24" s="258">
+        <v>23</v>
+      </c>
+      <c r="BY24" s="258" t="s">
+        <v>528</v>
+      </c>
+      <c r="BZ24" s="258" t="s">
+        <v>190</v>
+      </c>
+      <c r="CA24" s="258" t="s">
+        <v>74</v>
+      </c>
+      <c r="CB24" s="258" t="s">
+        <v>87</v>
+      </c>
     </row>
-    <row r="25" spans="1:68">
-      <c r="BL25" s="221">
+    <row r="25" spans="1:80">
+      <c r="BL25" s="258">
         <v>24</v>
       </c>
-      <c r="BM25" s="221" t="str">
+      <c r="BM25" s="258" t="str">
         <v>ir</v>
       </c>
-      <c r="BN25" s="223" t="str">
+      <c r="BN25" s="259" t="str">
         <v>w</v>
       </c>
-      <c r="BO25" s="221" t="str">
+      <c r="BO25" s="258" t="str">
         <v>K</v>
       </c>
-      <c r="BP25" s="221" t="str">
+      <c r="BP25" s="258" t="str">
         <v>ㆨ</v>
       </c>
+      <c r="BX25" s="258">
+        <v>24</v>
+      </c>
+      <c r="BY25" s="258" t="s">
+        <v>529</v>
+      </c>
+      <c r="BZ25" s="258" t="s">
+        <v>195</v>
+      </c>
+      <c r="CA25" s="258" t="s">
+        <v>118</v>
+      </c>
+      <c r="CB25" s="258" t="s">
+        <v>123</v>
+      </c>
     </row>
-    <row r="26" spans="1:68">
+    <row r="26" spans="1:80">
       <c r="A26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="BL26" s="221">
+      <c r="BL26" s="258">
         <v>25</v>
       </c>
-      <c r="BM26" s="221" t="str">
+      <c r="BM26" s="258" t="str">
         <v>u</v>
       </c>
-      <c r="BN26" s="221" t="str">
+      <c r="BN26" s="258" t="str">
         <v>u</v>
       </c>
-      <c r="BO26" s="221" t="str">
+      <c r="BO26" s="258" t="str">
         <v>j</v>
       </c>
-      <c r="BP26" s="221" t="str">
+      <c r="BP26" s="258" t="str">
         <v>ㄨ</v>
       </c>
+      <c r="BX26" s="258">
+        <v>25</v>
+      </c>
+      <c r="BY26" s="258" t="s">
+        <v>530</v>
+      </c>
+      <c r="BZ26" s="258" t="s">
+        <v>196</v>
+      </c>
+      <c r="CA26" s="258" t="s">
+        <v>234</v>
+      </c>
+      <c r="CB26" s="258" t="s">
+        <v>163</v>
+      </c>
     </row>
-    <row r="27" spans="1:68" outlineLevel="1">
+    <row r="27" spans="1:80" outlineLevel="1">
       <c r="B27" s="1" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - xlit|", C5:BH5, "|", C6:BH6, "|")</f>
         <v xml:space="preserve">    - xlit|!1qas2wxEedGYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7N|ㆠㄅㄆㄇㄋㄉㄊㄌㆣㄍㄎㄫㆡㄗㄘㄙㄏㆢㄐㄑㄒㄚㄧㆨㄨㆤㆦㄜㆬㄣㆭㆴㆵㆻㆷㄞㄠㆰㄢㄤㆱㆲㆩㆪㆫㆥㆧㆮㆯ一七三二五八四入ㄥ|</v>
       </c>
-      <c r="BL27" s="221">
+      <c r="BL27" s="258">
         <v>26</v>
       </c>
-      <c r="BM27" s="221" t="str">
+      <c r="BM27" s="258" t="str">
         <v>e</v>
       </c>
-      <c r="BN27" s="221" t="str">
+      <c r="BN27" s="258" t="str">
         <v>e</v>
       </c>
-      <c r="BO27" s="221" t="str">
+      <c r="BO27" s="258" t="str">
         <v>,</v>
       </c>
-      <c r="BP27" s="221" t="str">
+      <c r="BP27" s="258" t="str">
         <v>ㆤ</v>
       </c>
+      <c r="BX27" s="258">
+        <v>26</v>
+      </c>
+      <c r="BY27" s="258" t="s">
+        <v>531</v>
+      </c>
+      <c r="BZ27" s="258" t="s">
+        <v>198</v>
+      </c>
+      <c r="CA27" s="258" t="s">
+        <v>75</v>
+      </c>
+      <c r="CB27" s="258" t="s">
+        <v>89</v>
+      </c>
     </row>
-    <row r="28" spans="1:68" outlineLevel="1">
-      <c r="BL28" s="221">
+    <row r="28" spans="1:80" outlineLevel="1">
+      <c r="BL28" s="258">
         <v>27</v>
       </c>
-      <c r="BM28" s="221" t="str">
+      <c r="BM28" s="258" t="str">
         <v>oo</v>
       </c>
-      <c r="BN28" s="221" t="str">
+      <c r="BN28" s="258" t="str">
         <v>O</v>
       </c>
-      <c r="BO28" s="221" t="str">
+      <c r="BO28" s="258" t="str">
         <v>i</v>
       </c>
-      <c r="BP28" s="221" t="str">
+      <c r="BP28" s="258" t="str">
         <v>ㆦ</v>
       </c>
+      <c r="BX28" s="258">
+        <v>27</v>
+      </c>
+      <c r="BY28" s="258" t="s">
+        <v>532</v>
+      </c>
+      <c r="BZ28" s="258" t="s">
+        <v>200</v>
+      </c>
+      <c r="CA28" s="258" t="s">
+        <v>235</v>
+      </c>
+      <c r="CB28" s="258" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="29" spans="1:68" outlineLevel="1">
+    <row r="29" spans="1:80" outlineLevel="1">
       <c r="A29" s="1" t="s">
         <v>1</v>
       </c>
@@ -6700,23 +7717,38 @@
         <f xml:space="preserve"> SEARCH("|", $B$27)</f>
         <v>11</v>
       </c>
-      <c r="BL29" s="221">
+      <c r="BL29" s="258">
         <v>28</v>
       </c>
-      <c r="BM29" s="221" t="str">
+      <c r="BM29" s="258" t="str">
         <v>o</v>
       </c>
-      <c r="BN29" s="221" t="str">
+      <c r="BN29" s="258" t="str">
         <v>ə</v>
       </c>
-      <c r="BO29" s="221" t="str">
+      <c r="BO29" s="258" t="str">
         <v>k</v>
       </c>
-      <c r="BP29" s="221" t="str">
+      <c r="BP29" s="258" t="str">
         <v>ㄜ</v>
       </c>
+      <c r="BX29" s="258">
+        <v>28</v>
+      </c>
+      <c r="BY29" s="258" t="s">
+        <v>533</v>
+      </c>
+      <c r="BZ29" s="258" t="s">
+        <v>201</v>
+      </c>
+      <c r="CA29" s="258" t="s">
+        <v>120</v>
+      </c>
+      <c r="CB29" s="258" t="s">
+        <v>127</v>
+      </c>
     </row>
-    <row r="30" spans="1:68" outlineLevel="1">
+    <row r="30" spans="1:80" outlineLevel="1">
       <c r="A30" s="1" t="s">
         <v>2</v>
       </c>
@@ -6724,23 +7756,23 @@
         <f xml:space="preserve"> SEARCH("|", $B$27, B29+1)</f>
         <v>70</v>
       </c>
-      <c r="BL30" s="221">
+      <c r="BL30" s="258">
         <v>29</v>
       </c>
-      <c r="BM30" s="221" t="str">
+      <c r="BM30" s="258" t="str">
         <v>-m</v>
       </c>
-      <c r="BN30" s="221" t="str">
+      <c r="BN30" s="258" t="str">
         <v>M</v>
       </c>
-      <c r="BO30" s="221" t="str">
+      <c r="BO30" s="258" t="str">
         <v>m</v>
       </c>
-      <c r="BP30" s="221" t="str">
+      <c r="BP30" s="258" t="str">
         <v>ㆬ</v>
       </c>
     </row>
-    <row r="31" spans="1:68" outlineLevel="1">
+    <row r="31" spans="1:80" outlineLevel="1">
       <c r="A31" s="1" t="s">
         <v>3</v>
       </c>
@@ -6748,36 +7780,36 @@
         <f xml:space="preserve"> SEARCH("|", $B$27, B30+1)</f>
         <v>129</v>
       </c>
-      <c r="BL31" s="221">
+      <c r="BL31" s="258">
         <v>30</v>
       </c>
-      <c r="BM31" s="221" t="str">
+      <c r="BM31" s="258" t="str">
         <v>-n</v>
       </c>
-      <c r="BN31" s="221" t="str">
+      <c r="BN31" s="258" t="str">
         <v>N</v>
       </c>
-      <c r="BO31" s="221" t="str">
+      <c r="BO31" s="258" t="str">
         <v>p</v>
       </c>
-      <c r="BP31" s="221" t="str">
+      <c r="BP31" s="258" t="str">
         <v>ㄣ</v>
       </c>
     </row>
-    <row r="32" spans="1:68" outlineLevel="1">
-      <c r="BL32" s="221">
+    <row r="32" spans="1:80" outlineLevel="1">
+      <c r="BL32" s="258">
         <v>31</v>
       </c>
-      <c r="BM32" s="221" t="str">
+      <c r="BM32" s="258" t="str">
         <v>-ng</v>
       </c>
-      <c r="BN32" s="221" t="str">
+      <c r="BN32" s="258" t="str">
         <v>G</v>
       </c>
-      <c r="BO32" s="221" t="str">
+      <c r="BO32" s="258" t="str">
         <v>/</v>
       </c>
-      <c r="BP32" s="221" t="str">
+      <c r="BP32" s="258" t="str">
         <v>ㆭ</v>
       </c>
     </row>
@@ -6793,19 +7825,19 @@
         <f xml:space="preserve"> MID($B$27,B29+1, (B30-B29-1))</f>
         <v>!1qas2wxEedGYyhncRrfv8uKj,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7N</v>
       </c>
-      <c r="BL33" s="221">
+      <c r="BL33" s="258">
         <v>32</v>
       </c>
-      <c r="BM33" s="221" t="str">
+      <c r="BM33" s="258" t="str">
         <v>-p</v>
       </c>
-      <c r="BN33" s="221" t="str">
+      <c r="BN33" s="258" t="str">
         <v>R</v>
       </c>
-      <c r="BO33" s="221" t="str">
+      <c r="BO33" s="258" t="str">
         <v>b</v>
       </c>
-      <c r="BP33" s="221" t="str">
+      <c r="BP33" s="258" t="str">
         <v>ㆴ</v>
       </c>
     </row>
@@ -6821,36 +7853,36 @@
         <f xml:space="preserve"> MID($B$27,B30+1, (B31-B30-1))</f>
         <v>ㆠㄅㄆㄇㄋㄉㄊㄌㆣㄍㄎㄫㆡㄗㄘㄙㄏㆢㄐㄑㄒㄚㄧㆨㄨㆤㆦㄜㆬㄣㆭㆴㆵㆻㆷㄞㄠㆰㄢㄤㆱㆲㆩㆪㆫㆥㆧㆮㆯ一七三二五八四入ㄥ</v>
       </c>
-      <c r="BL34" s="221">
+      <c r="BL34" s="258">
         <v>33</v>
       </c>
-      <c r="BM34" s="221" t="str">
+      <c r="BM34" s="258" t="str">
         <v>-t</v>
       </c>
-      <c r="BN34" s="221" t="str">
+      <c r="BN34" s="258" t="str">
         <v>F</v>
       </c>
-      <c r="BO34" s="221" t="str">
+      <c r="BO34" s="258" t="str">
         <v>t</v>
       </c>
-      <c r="BP34" s="221" t="str">
+      <c r="BP34" s="258" t="str">
         <v>ㆵ</v>
       </c>
     </row>
     <row r="35" spans="1:68">
-      <c r="BL35" s="221">
+      <c r="BL35" s="258">
         <v>34</v>
       </c>
-      <c r="BM35" s="221" t="str">
+      <c r="BM35" s="258" t="str">
         <v>-k</v>
       </c>
-      <c r="BN35" s="221" t="str">
+      <c r="BN35" s="258" t="str">
         <v>Q</v>
       </c>
-      <c r="BO35" s="221" t="str">
+      <c r="BO35" s="258" t="str">
         <v>g</v>
       </c>
-      <c r="BP35" s="221" t="str">
+      <c r="BP35" s="258" t="str">
         <v>ㆻ</v>
       </c>
     </row>
@@ -7095,19 +8127,19 @@
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="BL36" s="221">
+      <c r="BL36" s="258">
         <v>35</v>
       </c>
-      <c r="BM36" s="221" t="str">
+      <c r="BM36" s="258" t="str">
         <v>-h</v>
       </c>
-      <c r="BN36" s="221" t="str">
+      <c r="BN36" s="258" t="str">
         <v>V</v>
       </c>
-      <c r="BO36" s="221" t="str">
+      <c r="BO36" s="258" t="str">
         <v>z</v>
       </c>
-      <c r="BP36" s="221" t="str">
+      <c r="BP36" s="258" t="str">
         <v>ㆷ</v>
       </c>
     </row>
@@ -7355,19 +8387,19 @@
         <f xml:space="preserve"> _xlfn.XLOOKUP(BJ38, $C$23:$BJ$23,$C$22:$BJ$22, "")</f>
         <v/>
       </c>
-      <c r="BL37" s="221">
+      <c r="BL37" s="258">
         <v>36</v>
       </c>
-      <c r="BM37" s="221" t="str">
+      <c r="BM37" s="258" t="str">
         <v>ai</v>
       </c>
-      <c r="BN37" s="221" t="str">
+      <c r="BN37" s="258" t="str">
         <v>I</v>
       </c>
-      <c r="BO37" s="221" t="str">
+      <c r="BO37" s="258" t="str">
         <v>9</v>
       </c>
-      <c r="BP37" s="221" t="str">
+      <c r="BP37" s="258" t="str">
         <v>ㄞ</v>
       </c>
     </row>
@@ -7615,19 +8647,19 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BL38" s="221">
+      <c r="BL38" s="258">
         <v>37</v>
       </c>
-      <c r="BM38" s="221" t="str">
+      <c r="BM38" s="258" t="str">
         <v>au</v>
       </c>
-      <c r="BN38" s="221" t="str">
+      <c r="BN38" s="258" t="str">
         <v>U</v>
       </c>
-      <c r="BO38" s="221" t="str">
+      <c r="BO38" s="258" t="str">
         <v>l</v>
       </c>
-      <c r="BP38" s="221" t="str">
+      <c r="BP38" s="258" t="str">
         <v>ㄠ</v>
       </c>
     </row>
@@ -7875,402 +8907,402 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="BL39" s="221">
+      <c r="BL39" s="258">
         <v>38</v>
       </c>
-      <c r="BM39" s="221" t="str">
+      <c r="BM39" s="258" t="str">
         <v>am</v>
       </c>
-      <c r="BN39" s="221" t="str">
+      <c r="BN39" s="258" t="str">
         <v>Y</v>
       </c>
-      <c r="BO39" s="221" t="str">
+      <c r="BO39" s="258" t="str">
         <v>M</v>
       </c>
-      <c r="BP39" s="221" t="str">
+      <c r="BP39" s="258" t="str">
         <v>ㆰ</v>
       </c>
     </row>
     <row r="40" spans="1:68">
-      <c r="BL40" s="221">
+      <c r="BL40" s="258">
         <v>39</v>
       </c>
-      <c r="BM40" s="221" t="str">
+      <c r="BM40" s="258" t="str">
         <v>an</v>
       </c>
-      <c r="BN40" s="223" t="str">
+      <c r="BN40" s="259" t="str">
         <v>@</v>
       </c>
-      <c r="BO40" s="221" t="str">
+      <c r="BO40" s="258" t="str">
         <v>0</v>
       </c>
-      <c r="BP40" s="221" t="str">
+      <c r="BP40" s="258" t="str">
         <v>ㄢ</v>
       </c>
     </row>
     <row r="41" spans="1:68">
-      <c r="BL41" s="221">
+      <c r="BL41" s="258">
         <v>40</v>
       </c>
-      <c r="BM41" s="221" t="str">
+      <c r="BM41" s="258" t="str">
         <v>ang</v>
       </c>
-      <c r="BN41" s="223" t="str">
+      <c r="BN41" s="259" t="str">
         <v>A</v>
       </c>
-      <c r="BO41" s="221" t="str">
+      <c r="BO41" s="258" t="str">
         <v>;</v>
       </c>
-      <c r="BP41" s="221" t="str">
+      <c r="BP41" s="258" t="str">
         <v>ㄤ</v>
       </c>
     </row>
     <row r="42" spans="1:68">
-      <c r="BL42" s="221">
+      <c r="BL42" s="258">
         <v>41</v>
       </c>
-      <c r="BM42" s="221" t="str">
+      <c r="BM42" s="258" t="str">
         <v>om</v>
       </c>
-      <c r="BN42" s="223" t="str">
+      <c r="BN42" s="259" t="str">
         <v>W</v>
       </c>
-      <c r="BO42" s="221" t="str">
+      <c r="BO42" s="258" t="str">
         <v>O</v>
       </c>
-      <c r="BP42" s="221" t="str">
+      <c r="BP42" s="258" t="str">
         <v>ㆱ</v>
       </c>
     </row>
     <row r="43" spans="1:68">
-      <c r="BL43" s="221">
+      <c r="BL43" s="258">
         <v>42</v>
       </c>
-      <c r="BM43" s="221" t="str">
+      <c r="BM43" s="258" t="str">
         <v>ong</v>
       </c>
-      <c r="BN43" s="223" t="str">
+      <c r="BN43" s="259" t="str">
         <v>H</v>
       </c>
-      <c r="BO43" s="221" t="str">
+      <c r="BO43" s="258" t="str">
         <v>o</v>
       </c>
-      <c r="BP43" s="221" t="str">
+      <c r="BP43" s="258" t="str">
         <v>ㆲ</v>
       </c>
     </row>
     <row r="44" spans="1:68">
-      <c r="BL44" s="221">
+      <c r="BL44" s="258">
         <v>43</v>
       </c>
-      <c r="BM44" s="221" t="str">
+      <c r="BM44" s="258" t="str">
         <v>aⁿ</v>
       </c>
-      <c r="BN44" s="223" t="str">
+      <c r="BN44" s="259" t="str">
         <v>d</v>
       </c>
-      <c r="BO44" s="221" t="str">
+      <c r="BO44" s="258" t="str">
         <v>*</v>
       </c>
-      <c r="BP44" s="221" t="str">
+      <c r="BP44" s="258" t="str">
         <v>ㆩ</v>
       </c>
     </row>
     <row r="45" spans="1:68">
-      <c r="BL45" s="221">
+      <c r="BL45" s="258">
         <v>44</v>
       </c>
-      <c r="BM45" s="221" t="str">
+      <c r="BM45" s="258" t="str">
         <v>iⁿ</v>
       </c>
-      <c r="BN45" s="223" t="str">
+      <c r="BN45" s="259" t="str">
         <v>f</v>
       </c>
-      <c r="BO45" s="221" t="str">
+      <c r="BO45" s="258" t="str">
         <v>U</v>
       </c>
-      <c r="BP45" s="221" t="str">
+      <c r="BP45" s="258" t="str">
         <v>ㆪ</v>
       </c>
     </row>
     <row r="46" spans="1:68">
-      <c r="BL46" s="221">
+      <c r="BL46" s="258">
         <v>45</v>
       </c>
-      <c r="BM46" s="221" t="str">
+      <c r="BM46" s="258" t="str">
         <v>uⁿ</v>
       </c>
-      <c r="BN46" s="223" t="str">
+      <c r="BN46" s="259" t="str">
         <v>q</v>
       </c>
-      <c r="BO46" s="221" t="str">
+      <c r="BO46" s="258" t="str">
         <v>J</v>
       </c>
-      <c r="BP46" s="221" t="str">
+      <c r="BP46" s="258" t="str">
         <v>ㆫ</v>
       </c>
     </row>
     <row r="47" spans="1:68">
-      <c r="BL47" s="221">
+      <c r="BL47" s="258">
         <v>46</v>
       </c>
-      <c r="BM47" s="221" t="str">
+      <c r="BM47" s="258" t="str">
         <v>eⁿ</v>
       </c>
-      <c r="BN47" s="223" t="str">
+      <c r="BN47" s="259" t="str">
         <v>r</v>
       </c>
-      <c r="BO47" s="221" t="str">
+      <c r="BO47" s="258" t="str">
         <v>&lt;</v>
       </c>
-      <c r="BP47" s="221" t="str">
+      <c r="BP47" s="258" t="str">
         <v>ㆥ</v>
       </c>
     </row>
     <row r="48" spans="1:68">
-      <c r="BL48" s="221">
+      <c r="BL48" s="258">
         <v>47</v>
       </c>
-      <c r="BM48" s="221" t="str">
+      <c r="BM48" s="258" t="str">
         <v>oⁿ</v>
       </c>
-      <c r="BN48" s="223" t="str">
+      <c r="BN48" s="259" t="str">
         <v>v</v>
       </c>
-      <c r="BO48" s="221" t="str">
+      <c r="BO48" s="258" t="str">
         <v>I</v>
       </c>
-      <c r="BP48" s="221" t="str">
+      <c r="BP48" s="258" t="str">
         <v>ㆧ</v>
       </c>
     </row>
     <row r="49" spans="64:68">
-      <c r="BL49" s="221">
+      <c r="BL49" s="258">
         <v>48</v>
       </c>
-      <c r="BM49" s="221" t="str">
+      <c r="BM49" s="258" t="str">
         <v>aiⁿ</v>
       </c>
-      <c r="BN49" s="223" t="str">
+      <c r="BN49" s="259" t="str">
         <v>x</v>
       </c>
-      <c r="BO49" s="221" t="str">
+      <c r="BO49" s="258" t="str">
         <v>(</v>
       </c>
-      <c r="BP49" s="221" t="str">
+      <c r="BP49" s="258" t="str">
         <v>ㆮ</v>
       </c>
     </row>
     <row r="50" spans="64:68">
-      <c r="BL50" s="221">
+      <c r="BL50" s="258">
         <v>49</v>
       </c>
-      <c r="BM50" s="221" t="str">
+      <c r="BM50" s="258" t="str">
         <v>auⁿ</v>
       </c>
-      <c r="BN50" s="223" t="str">
+      <c r="BN50" s="259" t="str">
         <v>y</v>
       </c>
-      <c r="BO50" s="221" t="str">
+      <c r="BO50" s="258" t="str">
         <v>L</v>
       </c>
-      <c r="BP50" s="221" t="str">
+      <c r="BP50" s="258" t="str">
         <v>ㆯ</v>
       </c>
     </row>
     <row r="51" spans="64:68">
-      <c r="BL51" s="221">
+      <c r="BL51" s="258">
         <v>50</v>
       </c>
-      <c r="BM51" s="221">
+      <c r="BM51" s="258">
         <v>1</v>
       </c>
-      <c r="BN51" s="223">
+      <c r="BN51" s="259">
         <v>1</v>
       </c>
-      <c r="BO51" s="221" t="str">
+      <c r="BO51" s="258" t="str">
         <v>:</v>
       </c>
-      <c r="BP51" s="221" t="str">
+      <c r="BP51" s="258" t="str">
         <v>一</v>
       </c>
     </row>
     <row r="52" spans="64:68">
-      <c r="BL52" s="221">
+      <c r="BL52" s="258">
         <v>51</v>
       </c>
-      <c r="BM52" s="221">
+      <c r="BM52" s="258">
         <v>7</v>
       </c>
-      <c r="BN52" s="223">
+      <c r="BN52" s="259">
         <v>7</v>
       </c>
-      <c r="BO52" s="221">
+      <c r="BO52" s="258">
         <v>5</v>
       </c>
-      <c r="BP52" s="221" t="str">
+      <c r="BP52" s="258" t="str">
         <v>七</v>
       </c>
     </row>
     <row r="53" spans="64:68">
-      <c r="BL53" s="221">
+      <c r="BL53" s="258">
         <v>52</v>
       </c>
-      <c r="BM53" s="221">
+      <c r="BM53" s="258">
         <v>3</v>
       </c>
-      <c r="BN53" s="223">
+      <c r="BN53" s="259">
         <v>3</v>
       </c>
-      <c r="BO53" s="221">
+      <c r="BO53" s="258">
         <v>3</v>
       </c>
-      <c r="BP53" s="221" t="str">
+      <c r="BP53" s="258" t="str">
         <v>三</v>
       </c>
     </row>
     <row r="54" spans="64:68">
-      <c r="BL54" s="221">
+      <c r="BL54" s="258">
         <v>53</v>
       </c>
-      <c r="BM54" s="221">
+      <c r="BM54" s="258">
         <v>2</v>
       </c>
-      <c r="BN54" s="221">
+      <c r="BN54" s="258">
         <v>2</v>
       </c>
-      <c r="BO54" s="221">
+      <c r="BO54" s="258">
         <v>4</v>
       </c>
-      <c r="BP54" s="221" t="str">
+      <c r="BP54" s="258" t="str">
         <v>二</v>
       </c>
     </row>
     <row r="55" spans="64:68">
-      <c r="BL55" s="221">
+      <c r="BL55" s="258">
         <v>54</v>
       </c>
-      <c r="BM55" s="221">
+      <c r="BM55" s="258">
         <v>5</v>
       </c>
-      <c r="BN55" s="221">
+      <c r="BN55" s="258">
         <v>5</v>
       </c>
-      <c r="BO55" s="221">
+      <c r="BO55" s="258">
         <v>6</v>
       </c>
-      <c r="BP55" s="221" t="str">
+      <c r="BP55" s="258" t="str">
         <v>五</v>
       </c>
     </row>
     <row r="56" spans="64:68">
-      <c r="BL56" s="221">
+      <c r="BL56" s="258">
         <v>55</v>
       </c>
-      <c r="BM56" s="221">
+      <c r="BM56" s="258">
         <v>8</v>
       </c>
-      <c r="BN56" s="221">
+      <c r="BN56" s="258">
         <v>8</v>
       </c>
-      <c r="BO56" s="221" t="str">
+      <c r="BO56" s="258" t="str">
         <v>]</v>
       </c>
-      <c r="BP56" s="221" t="str">
+      <c r="BP56" s="258" t="str">
         <v>八</v>
       </c>
     </row>
     <row r="57" spans="64:68">
-      <c r="BL57" s="221">
+      <c r="BL57" s="258">
         <v>56</v>
       </c>
-      <c r="BM57" s="221">
+      <c r="BM57" s="258">
         <v>4</v>
       </c>
-      <c r="BN57" s="221">
+      <c r="BN57" s="258">
         <v>4</v>
       </c>
-      <c r="BO57" s="221" t="str">
+      <c r="BO57" s="258" t="str">
         <v>[</v>
       </c>
-      <c r="BP57" s="221" t="str">
+      <c r="BP57" s="258" t="str">
         <v>四</v>
       </c>
     </row>
     <row r="58" spans="64:68">
-      <c r="BL58" s="221">
+      <c r="BL58" s="258">
         <v>57</v>
       </c>
-      <c r="BM58" s="221">
+      <c r="BM58" s="258">
         <v>0</v>
       </c>
-      <c r="BN58" s="221">
+      <c r="BN58" s="258">
         <v>0</v>
       </c>
-      <c r="BO58" s="221">
+      <c r="BO58" s="258">
         <v>7</v>
       </c>
-      <c r="BP58" s="221" t="str">
+      <c r="BP58" s="258" t="str">
         <v>入</v>
       </c>
     </row>
     <row r="59" spans="64:68">
-      <c r="BL59" s="221">
+      <c r="BL59" s="258">
         <v>58</v>
       </c>
-      <c r="BM59" s="221" t="str">
+      <c r="BM59" s="258" t="str">
         <v>L</v>
       </c>
-      <c r="BN59" s="221" t="str">
+      <c r="BN59" s="258" t="str">
         <v>L</v>
       </c>
-      <c r="BO59" s="221" t="str">
+      <c r="BO59" s="258" t="str">
         <v>N</v>
       </c>
-      <c r="BP59" s="221" t="str">
+      <c r="BP59" s="258" t="str">
         <v>ㄥ</v>
       </c>
     </row>
     <row r="60" spans="64:68">
-      <c r="BL60" s="221">
+      <c r="BL60" s="258">
         <v>59</v>
       </c>
-      <c r="BM60" s="221" t="str">
+      <c r="BM60" s="260" t="str">
         <v/>
       </c>
-      <c r="BN60" s="221" t="str">
+      <c r="BN60" s="260" t="str">
         <v/>
       </c>
-      <c r="BO60" s="221" t="str">
+      <c r="BO60" s="260" t="str">
         <v/>
       </c>
-      <c r="BP60" s="221" t="str">
+      <c r="BP60" s="260" t="str">
         <v/>
       </c>
     </row>
     <row r="61" spans="64:68">
-      <c r="BL61" s="221">
+      <c r="BL61" s="258">
         <v>60</v>
       </c>
-      <c r="BM61" s="221">
+      <c r="BM61" s="260">
         <v>0</v>
       </c>
-      <c r="BN61" s="221">
+      <c r="BN61" s="260">
         <v>0</v>
       </c>
-      <c r="BO61" s="221">
+      <c r="BO61" s="260">
         <v>0</v>
       </c>
-      <c r="BP61" s="221">
+      <c r="BP61" s="260">
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="64:68">
-      <c r="BL62" s="221"/>
-      <c r="BM62" s="221"/>
-      <c r="BN62" s="221"/>
-      <c r="BO62" s="221"/>
-      <c r="BP62" s="221"/>
+      <c r="BL62" s="258"/>
+      <c r="BM62" s="258"/>
+      <c r="BN62" s="258"/>
+      <c r="BO62" s="258"/>
+      <c r="BP62" s="258"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -8281,1016 +9313,1016 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92A2CFCB-5854-4835-8802-8D34ADF19BD0}">
   <dimension ref="B1:Y28"/>
-  <sheetFormatPr defaultRowHeight="21.75"/>
+  <sheetFormatPr defaultRowHeight="21"/>
   <cols>
-    <col min="15" max="16" width="8.796875" style="239"/>
-    <col min="17" max="18" width="15" style="239" customWidth="1"/>
-    <col min="19" max="19" width="47.296875" style="239" customWidth="1"/>
-    <col min="20" max="25" width="8.796875" style="239"/>
+    <col min="15" max="16" width="8.796875" style="236"/>
+    <col min="17" max="18" width="15" style="236" customWidth="1"/>
+    <col min="19" max="19" width="47.296875" style="236" customWidth="1"/>
+    <col min="20" max="25" width="8.796875" style="236"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="22.5" thickBot="1"/>
+    <row r="1" spans="2:19" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:19" ht="24" thickBot="1">
-      <c r="B2" s="248" t="s">
+      <c r="B2" s="244" t="s">
+        <v>332</v>
+      </c>
+      <c r="C2" s="246" t="s">
         <v>333</v>
       </c>
-      <c r="C2" s="250" t="s">
+      <c r="D2" s="247"/>
+      <c r="E2" s="250" t="s">
         <v>334</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="254" t="s">
+      <c r="F2" s="251"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="250" t="s">
         <v>335</v>
       </c>
-      <c r="F2" s="255"/>
-      <c r="G2" s="256"/>
-      <c r="H2" s="254" t="s">
-        <v>336</v>
-      </c>
-      <c r="I2" s="255"/>
-      <c r="J2" s="255"/>
-      <c r="K2" s="255"/>
-      <c r="L2" s="256"/>
-      <c r="O2" s="239" t="s">
+      <c r="I2" s="251"/>
+      <c r="J2" s="251"/>
+      <c r="K2" s="251"/>
+      <c r="L2" s="252"/>
+      <c r="O2" s="236" t="s">
+        <v>484</v>
+      </c>
+      <c r="P2" s="236" t="s">
         <v>485</v>
       </c>
-      <c r="P2" s="239" t="s">
+      <c r="Q2" s="239">
+        <v>0</v>
+      </c>
+      <c r="R2" s="239" t="s">
         <v>486</v>
-      </c>
-      <c r="Q2" s="242">
-        <v>0</v>
-      </c>
-      <c r="R2" s="242" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="3" spans="2:19" ht="24" thickBot="1">
-      <c r="B3" s="249"/>
-      <c r="C3" s="252"/>
-      <c r="D3" s="253"/>
-      <c r="E3" s="237" t="s">
+      <c r="B3" s="245"/>
+      <c r="C3" s="248"/>
+      <c r="D3" s="249"/>
+      <c r="E3" s="234" t="s">
+        <v>336</v>
+      </c>
+      <c r="F3" s="234" t="s">
         <v>337</v>
       </c>
-      <c r="F3" s="237" t="s">
+      <c r="G3" s="234" t="s">
         <v>338</v>
       </c>
-      <c r="G3" s="237" t="s">
+      <c r="H3" s="234" t="s">
         <v>339</v>
       </c>
-      <c r="H3" s="237" t="s">
+      <c r="I3" s="234" t="s">
         <v>340</v>
       </c>
-      <c r="I3" s="237" t="s">
+      <c r="J3" s="234" t="s">
         <v>341</v>
       </c>
-      <c r="J3" s="237" t="s">
+      <c r="K3" s="250" t="s">
         <v>342</v>
       </c>
-      <c r="K3" s="254" t="s">
-        <v>343</v>
-      </c>
-      <c r="L3" s="256"/>
-      <c r="O3" s="239" t="s">
-        <v>279</v>
-      </c>
-      <c r="P3" s="239" t="s">
-        <v>455</v>
-      </c>
-      <c r="Q3" s="239" t="str">
+      <c r="L3" s="252"/>
+      <c r="O3" s="236" t="s">
+        <v>278</v>
+      </c>
+      <c r="P3" s="236" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q3" s="236" t="str">
         <f t="shared" ref="Q3:Q19" si="0">_xlfn.CONCAT(O3,$Q$2)</f>
         <v>ang0</v>
       </c>
-      <c r="R3" s="239" t="str">
+      <c r="R3" s="236" t="str">
         <f t="shared" ref="R3:R19" si="1" xml:space="preserve"> _xlfn.CONCAT(P3,$R$2)</f>
         <v>ak[48]</v>
       </c>
-      <c r="S3" s="239" t="str">
+      <c r="S3" s="236" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - derive/", Q3, "/", R3, "/    # " &amp; R3, "入 = ", P3, "[48]")</f>
         <v xml:space="preserve">    - derive/ang0/ak[48]/    # ak[48]入 = ak[48]</v>
       </c>
     </row>
     <row r="4" spans="2:19" ht="24" thickBot="1">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="234" t="s">
+        <v>343</v>
+      </c>
+      <c r="C4" s="235" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="235" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="235" t="s">
+        <v>162</v>
+      </c>
+      <c r="F4" s="235" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="235" t="s">
+        <v>148</v>
+      </c>
+      <c r="H4" s="235" t="s">
         <v>344</v>
       </c>
-      <c r="C4" s="238" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="238" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="238" t="s">
-        <v>162</v>
-      </c>
-      <c r="F4" s="238" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" s="238" t="s">
-        <v>148</v>
-      </c>
-      <c r="H4" s="238" t="s">
+      <c r="I4" s="235" t="s">
         <v>345</v>
       </c>
-      <c r="I4" s="238" t="s">
+      <c r="J4" s="235" t="s">
         <v>346</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="K4" s="235" t="s">
         <v>347</v>
       </c>
-      <c r="K4" s="238" t="s">
+      <c r="L4" s="235" t="s">
         <v>348</v>
       </c>
-      <c r="L4" s="238" t="s">
-        <v>349</v>
-      </c>
-      <c r="O4" s="239" t="s">
-        <v>278</v>
-      </c>
-      <c r="P4" s="239" t="s">
-        <v>456</v>
-      </c>
-      <c r="Q4" s="239" t="str">
+      <c r="O4" s="236" t="s">
+        <v>277</v>
+      </c>
+      <c r="P4" s="236" t="s">
+        <v>455</v>
+      </c>
+      <c r="Q4" s="236" t="str">
         <f t="shared" si="0"/>
         <v>an0</v>
       </c>
-      <c r="R4" s="239" t="str">
+      <c r="R4" s="236" t="str">
         <f t="shared" si="1"/>
         <v>at[48]</v>
       </c>
-      <c r="S4" s="239" t="str">
+      <c r="S4" s="236" t="str">
         <f t="shared" ref="S4:S19" si="2" xml:space="preserve"> _xlfn.CONCAT("    - derive/", Q4, "/", R4, "/    # " &amp; R4, "入 = ", P4, "[48]")</f>
         <v xml:space="preserve">    - derive/an0/at[48]/    # at[48]入 = at[48]</v>
       </c>
     </row>
     <row r="5" spans="2:19" ht="24" thickBot="1">
-      <c r="B5" s="237" t="s">
+      <c r="B5" s="234" t="s">
+        <v>349</v>
+      </c>
+      <c r="C5" s="235" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="235" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="235"/>
+      <c r="F5" s="235"/>
+      <c r="G5" s="235"/>
+      <c r="H5" s="235"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="235"/>
+      <c r="K5" s="235" t="s">
         <v>350</v>
       </c>
-      <c r="C5" s="238" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="238" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="238"/>
-      <c r="F5" s="238"/>
-      <c r="G5" s="238"/>
-      <c r="H5" s="238"/>
-      <c r="I5" s="238"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="238" t="s">
+      <c r="L5" s="235" t="s">
         <v>351</v>
       </c>
-      <c r="L5" s="238" t="s">
-        <v>352</v>
-      </c>
-      <c r="O5" s="239" t="s">
-        <v>277</v>
-      </c>
-      <c r="P5" s="239" t="s">
-        <v>454</v>
-      </c>
-      <c r="Q5" s="239" t="str">
+      <c r="O5" s="236" t="s">
+        <v>276</v>
+      </c>
+      <c r="P5" s="236" t="s">
+        <v>453</v>
+      </c>
+      <c r="Q5" s="236" t="str">
         <f t="shared" si="0"/>
         <v>am0</v>
       </c>
-      <c r="R5" s="239" t="str">
+      <c r="R5" s="236" t="str">
         <f t="shared" si="1"/>
         <v>ap[48]</v>
       </c>
-      <c r="S5" s="239" t="str">
+      <c r="S5" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/am0/ap[48]/    # ap[48]入 = ap[48]</v>
       </c>
     </row>
     <row r="6" spans="2:19" ht="24" thickBot="1">
-      <c r="B6" s="237" t="s">
+      <c r="B6" s="234" t="s">
+        <v>352</v>
+      </c>
+      <c r="C6" s="235" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="235"/>
+      <c r="E6" s="235"/>
+      <c r="F6" s="235"/>
+      <c r="G6" s="235"/>
+      <c r="H6" s="235"/>
+      <c r="I6" s="235"/>
+      <c r="J6" s="235"/>
+      <c r="K6" s="235" t="s">
         <v>353</v>
       </c>
-      <c r="C6" s="238" t="s">
-        <v>146</v>
-      </c>
-      <c r="D6" s="238"/>
-      <c r="E6" s="238"/>
-      <c r="F6" s="238"/>
-      <c r="G6" s="238"/>
-      <c r="H6" s="238"/>
-      <c r="I6" s="238"/>
-      <c r="J6" s="238"/>
-      <c r="K6" s="238" t="s">
+      <c r="L6" s="235" t="s">
         <v>354</v>
       </c>
-      <c r="L6" s="238" t="s">
-        <v>355</v>
-      </c>
-      <c r="O6" s="239" t="s">
-        <v>462</v>
-      </c>
-      <c r="P6" s="239" t="s">
-        <v>459</v>
-      </c>
-      <c r="Q6" s="239" t="str">
+      <c r="O6" s="236" t="s">
+        <v>461</v>
+      </c>
+      <c r="P6" s="236" t="s">
+        <v>458</v>
+      </c>
+      <c r="Q6" s="236" t="str">
         <f t="shared" si="0"/>
         <v>ing0</v>
       </c>
-      <c r="R6" s="239" t="str">
+      <c r="R6" s="236" t="str">
         <f t="shared" si="1"/>
         <v>ik[48]</v>
       </c>
-      <c r="S6" s="239" t="str">
+      <c r="S6" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/ing0/ik[48]/    # ik[48]入 = ik[48]</v>
       </c>
     </row>
     <row r="7" spans="2:19" ht="24" thickBot="1">
-      <c r="B7" s="237" t="s">
+      <c r="B7" s="234" t="s">
+        <v>355</v>
+      </c>
+      <c r="C7" s="235" t="s">
         <v>356</v>
       </c>
-      <c r="C7" s="238" t="s">
+      <c r="D7" s="235"/>
+      <c r="E7" s="235"/>
+      <c r="F7" s="235"/>
+      <c r="G7" s="235" t="s">
         <v>357</v>
       </c>
-      <c r="D7" s="238"/>
-      <c r="E7" s="238"/>
-      <c r="F7" s="238"/>
-      <c r="G7" s="238" t="s">
+      <c r="H7" s="235"/>
+      <c r="I7" s="235"/>
+      <c r="J7" s="235" t="s">
         <v>358</v>
       </c>
-      <c r="H7" s="238"/>
-      <c r="I7" s="238"/>
-      <c r="J7" s="238" t="s">
+      <c r="K7" s="235" t="s">
         <v>359</v>
       </c>
-      <c r="K7" s="238" t="s">
-        <v>360</v>
-      </c>
-      <c r="L7" s="238"/>
-      <c r="O7" s="239" t="s">
-        <v>462</v>
-      </c>
-      <c r="P7" s="239" t="s">
-        <v>460</v>
-      </c>
-      <c r="Q7" s="239" t="str">
+      <c r="L7" s="235"/>
+      <c r="O7" s="236" t="s">
+        <v>461</v>
+      </c>
+      <c r="P7" s="236" t="s">
+        <v>459</v>
+      </c>
+      <c r="Q7" s="236" t="str">
         <f t="shared" si="0"/>
         <v>ing0</v>
       </c>
-      <c r="R7" s="239" t="str">
+      <c r="R7" s="236" t="str">
         <f t="shared" si="1"/>
         <v>it[48]</v>
       </c>
-      <c r="S7" s="239" t="str">
+      <c r="S7" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/ing0/it[48]/    # it[48]入 = it[48]</v>
       </c>
     </row>
     <row r="8" spans="2:19" ht="24" thickBot="1">
-      <c r="B8" s="237" t="s">
+      <c r="B8" s="234" t="s">
+        <v>360</v>
+      </c>
+      <c r="C8" s="235" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="235" t="s">
+        <v>164</v>
+      </c>
+      <c r="E8" s="235"/>
+      <c r="F8" s="235"/>
+      <c r="G8" s="235"/>
+      <c r="H8" s="235"/>
+      <c r="I8" s="235"/>
+      <c r="J8" s="235"/>
+      <c r="K8" s="235" t="s">
         <v>361</v>
       </c>
-      <c r="C8" s="238" t="s">
-        <v>183</v>
-      </c>
-      <c r="D8" s="238" t="s">
-        <v>164</v>
-      </c>
-      <c r="E8" s="238"/>
-      <c r="F8" s="238"/>
-      <c r="G8" s="238"/>
-      <c r="H8" s="238"/>
-      <c r="I8" s="238"/>
-      <c r="J8" s="238"/>
-      <c r="K8" s="238" t="s">
+      <c r="L8" s="235" t="s">
         <v>362</v>
       </c>
-      <c r="L8" s="238" t="s">
-        <v>363</v>
-      </c>
-      <c r="O8" s="239" t="s">
-        <v>463</v>
-      </c>
-      <c r="P8" s="239" t="s">
-        <v>461</v>
-      </c>
-      <c r="Q8" s="239" t="str">
+      <c r="O8" s="236" t="s">
+        <v>462</v>
+      </c>
+      <c r="P8" s="236" t="s">
+        <v>460</v>
+      </c>
+      <c r="Q8" s="236" t="str">
         <f t="shared" si="0"/>
         <v>im0</v>
       </c>
-      <c r="R8" s="239" t="str">
+      <c r="R8" s="236" t="str">
         <f t="shared" si="1"/>
         <v>ip[48]</v>
       </c>
-      <c r="S8" s="239" t="str">
+      <c r="S8" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/im0/ip[48]/    # ip[48]入 = ip[48]</v>
       </c>
     </row>
     <row r="9" spans="2:19" ht="24" thickBot="1">
-      <c r="B9" s="237" t="s">
+      <c r="B9" s="234" t="s">
+        <v>363</v>
+      </c>
+      <c r="C9" s="235" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="235" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="235" t="s">
         <v>364</v>
       </c>
-      <c r="C9" s="238" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9" s="238" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="238" t="s">
+      <c r="F9" s="235" t="s">
         <v>365</v>
       </c>
-      <c r="F9" s="238" t="s">
+      <c r="G9" s="235" t="s">
         <v>366</v>
       </c>
-      <c r="G9" s="238" t="s">
+      <c r="H9" s="235" t="s">
         <v>367</v>
       </c>
-      <c r="H9" s="238" t="s">
+      <c r="I9" s="235" t="s">
         <v>368</v>
       </c>
-      <c r="I9" s="238" t="s">
+      <c r="J9" s="235" t="s">
         <v>369</v>
       </c>
-      <c r="J9" s="238" t="s">
+      <c r="K9" s="235" t="s">
         <v>370</v>
       </c>
-      <c r="K9" s="238" t="s">
+      <c r="L9" s="235" t="s">
         <v>371</v>
       </c>
-      <c r="L9" s="238" t="s">
-        <v>372</v>
-      </c>
-      <c r="O9" s="239" t="s">
-        <v>465</v>
-      </c>
-      <c r="P9" s="239" t="s">
+      <c r="O9" s="236" t="s">
         <v>464</v>
       </c>
-      <c r="Q9" s="239" t="str">
+      <c r="P9" s="236" t="s">
+        <v>463</v>
+      </c>
+      <c r="Q9" s="236" t="str">
         <f t="shared" si="0"/>
         <v>iang0</v>
       </c>
-      <c r="R9" s="239" t="str">
+      <c r="R9" s="236" t="str">
         <f t="shared" si="1"/>
         <v>iak[48]</v>
       </c>
-      <c r="S9" s="239" t="str">
+      <c r="S9" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/iang0/iak[48]/    # iak[48]入 = iak[48]</v>
       </c>
     </row>
     <row r="10" spans="2:19" ht="24" thickBot="1">
-      <c r="B10" s="237" t="s">
+      <c r="B10" s="234" t="s">
+        <v>372</v>
+      </c>
+      <c r="C10" s="235" t="s">
         <v>373</v>
       </c>
-      <c r="C10" s="238" t="s">
+      <c r="D10" s="235" t="s">
         <v>374</v>
       </c>
-      <c r="D10" s="238" t="s">
+      <c r="E10" s="235" t="s">
         <v>375</v>
       </c>
-      <c r="E10" s="238" t="s">
+      <c r="F10" s="235" t="s">
         <v>376</v>
       </c>
-      <c r="F10" s="238" t="s">
+      <c r="G10" s="235" t="s">
         <v>377</v>
       </c>
-      <c r="G10" s="238" t="s">
+      <c r="H10" s="235" t="s">
         <v>378</v>
       </c>
-      <c r="H10" s="238" t="s">
+      <c r="I10" s="235" t="s">
         <v>379</v>
       </c>
-      <c r="I10" s="238" t="s">
+      <c r="J10" s="235" t="s">
         <v>380</v>
       </c>
-      <c r="J10" s="238" t="s">
+      <c r="K10" s="235" t="s">
         <v>381</v>
       </c>
-      <c r="K10" s="238" t="s">
+      <c r="L10" s="235" t="s">
         <v>382</v>
       </c>
-      <c r="L10" s="238" t="s">
-        <v>383</v>
-      </c>
-      <c r="O10" s="239" t="s">
-        <v>468</v>
-      </c>
-      <c r="P10" s="239" t="s">
-        <v>466</v>
-      </c>
-      <c r="Q10" s="239" t="str">
+      <c r="O10" s="236" t="s">
+        <v>467</v>
+      </c>
+      <c r="P10" s="236" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q10" s="236" t="str">
         <f t="shared" si="0"/>
         <v>ian0</v>
       </c>
-      <c r="R10" s="239" t="str">
+      <c r="R10" s="236" t="str">
         <f t="shared" si="1"/>
         <v>iat[48]</v>
       </c>
-      <c r="S10" s="239" t="str">
+      <c r="S10" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/ian0/iat[48]/    # iat[48]入 = iat[48]</v>
       </c>
     </row>
     <row r="11" spans="2:19" ht="24" thickBot="1">
-      <c r="B11" s="237" t="s">
+      <c r="B11" s="234" t="s">
+        <v>383</v>
+      </c>
+      <c r="C11" s="235" t="s">
         <v>384</v>
       </c>
-      <c r="C11" s="238" t="s">
+      <c r="D11" s="235" t="s">
         <v>385</v>
       </c>
-      <c r="D11" s="238" t="s">
+      <c r="E11" s="235"/>
+      <c r="F11" s="235"/>
+      <c r="G11" s="235"/>
+      <c r="H11" s="235"/>
+      <c r="I11" s="235"/>
+      <c r="J11" s="235"/>
+      <c r="K11" s="235" t="s">
         <v>386</v>
       </c>
-      <c r="E11" s="238"/>
-      <c r="F11" s="238"/>
-      <c r="G11" s="238"/>
-      <c r="H11" s="238"/>
-      <c r="I11" s="238"/>
-      <c r="J11" s="238"/>
-      <c r="K11" s="238" t="s">
-        <v>387</v>
-      </c>
-      <c r="L11" s="238"/>
-      <c r="O11" s="239" t="s">
-        <v>469</v>
-      </c>
-      <c r="P11" s="239" t="s">
-        <v>467</v>
-      </c>
-      <c r="Q11" s="239" t="str">
+      <c r="L11" s="235"/>
+      <c r="O11" s="236" t="s">
+        <v>468</v>
+      </c>
+      <c r="P11" s="236" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q11" s="236" t="str">
         <f t="shared" si="0"/>
         <v>iam0</v>
       </c>
-      <c r="R11" s="239" t="str">
+      <c r="R11" s="236" t="str">
         <f t="shared" si="1"/>
         <v>iap[48]</v>
       </c>
-      <c r="S11" s="239" t="str">
+      <c r="S11" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/iam0/iap[48]/    # iap[48]入 = iap[48]</v>
       </c>
     </row>
     <row r="12" spans="2:19" ht="24" thickBot="1">
-      <c r="B12" s="237" t="s">
+      <c r="B12" s="234" t="s">
+        <v>387</v>
+      </c>
+      <c r="C12" s="235" t="s">
         <v>388</v>
       </c>
-      <c r="C12" s="238" t="s">
+      <c r="D12" s="235"/>
+      <c r="E12" s="235"/>
+      <c r="F12" s="235"/>
+      <c r="G12" s="235"/>
+      <c r="H12" s="235"/>
+      <c r="I12" s="235"/>
+      <c r="J12" s="235"/>
+      <c r="K12" s="235" t="s">
         <v>389</v>
       </c>
-      <c r="D12" s="238"/>
-      <c r="E12" s="238"/>
-      <c r="F12" s="238"/>
-      <c r="G12" s="238"/>
-      <c r="H12" s="238"/>
-      <c r="I12" s="238"/>
-      <c r="J12" s="238"/>
-      <c r="K12" s="238" t="s">
-        <v>390</v>
-      </c>
-      <c r="L12" s="238"/>
-      <c r="O12" s="239" t="s">
-        <v>471</v>
-      </c>
-      <c r="P12" s="239" t="s">
+      <c r="L12" s="235"/>
+      <c r="O12" s="236" t="s">
         <v>470</v>
       </c>
-      <c r="Q12" s="239" t="str">
+      <c r="P12" s="236" t="s">
+        <v>469</v>
+      </c>
+      <c r="Q12" s="236" t="str">
         <f t="shared" si="0"/>
         <v>iong0</v>
       </c>
-      <c r="R12" s="239" t="str">
+      <c r="R12" s="236" t="str">
         <f t="shared" si="1"/>
         <v>iok[48]</v>
       </c>
-      <c r="S12" s="239" t="str">
+      <c r="S12" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/iong0/iok[48]/    # iok[48]入 = iok[48]</v>
       </c>
     </row>
     <row r="13" spans="2:19" ht="24" thickBot="1">
-      <c r="B13" s="237" t="s">
+      <c r="B13" s="234" t="s">
+        <v>390</v>
+      </c>
+      <c r="C13" s="235" t="s">
         <v>391</v>
       </c>
-      <c r="C13" s="238" t="s">
+      <c r="D13" s="235" t="s">
         <v>392</v>
       </c>
-      <c r="D13" s="238" t="s">
+      <c r="E13" s="235"/>
+      <c r="F13" s="235"/>
+      <c r="G13" s="235" t="s">
         <v>393</v>
       </c>
-      <c r="E13" s="238"/>
-      <c r="F13" s="238"/>
-      <c r="G13" s="238" t="s">
+      <c r="H13" s="235"/>
+      <c r="I13" s="235"/>
+      <c r="J13" s="235" t="s">
         <v>394</v>
       </c>
-      <c r="H13" s="238"/>
-      <c r="I13" s="238"/>
-      <c r="J13" s="238" t="s">
+      <c r="K13" s="235" t="s">
         <v>395</v>
       </c>
-      <c r="K13" s="238" t="s">
-        <v>396</v>
-      </c>
-      <c r="L13" s="238"/>
-      <c r="O13" s="239" t="s">
-        <v>281</v>
-      </c>
-      <c r="P13" s="239" t="s">
-        <v>472</v>
-      </c>
-      <c r="Q13" s="239" t="str">
+      <c r="L13" s="235"/>
+      <c r="O13" s="236" t="s">
+        <v>280</v>
+      </c>
+      <c r="P13" s="236" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q13" s="236" t="str">
         <f t="shared" si="0"/>
         <v>ong0</v>
       </c>
-      <c r="R13" s="239" t="str">
+      <c r="R13" s="236" t="str">
         <f t="shared" si="1"/>
         <v>ok[48]</v>
       </c>
-      <c r="S13" s="239" t="str">
+      <c r="S13" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/ong0/ok[48]/    # ok[48]入 = ok[48]</v>
       </c>
     </row>
     <row r="14" spans="2:19" ht="24" thickBot="1">
-      <c r="B14" s="237" t="s">
+      <c r="B14" s="234" t="s">
+        <v>396</v>
+      </c>
+      <c r="C14" s="235" t="s">
         <v>397</v>
       </c>
-      <c r="C14" s="238" t="s">
+      <c r="D14" s="235" t="s">
         <v>398</v>
       </c>
-      <c r="D14" s="238" t="s">
+      <c r="E14" s="235"/>
+      <c r="F14" s="235"/>
+      <c r="G14" s="235"/>
+      <c r="H14" s="235"/>
+      <c r="I14" s="235"/>
+      <c r="J14" s="235"/>
+      <c r="K14" s="235" t="s">
         <v>399</v>
       </c>
-      <c r="E14" s="238"/>
-      <c r="F14" s="238"/>
-      <c r="G14" s="238"/>
-      <c r="H14" s="238"/>
-      <c r="I14" s="238"/>
-      <c r="J14" s="238"/>
-      <c r="K14" s="238" t="s">
+      <c r="L14" s="235" t="s">
         <v>400</v>
       </c>
-      <c r="L14" s="238" t="s">
-        <v>401</v>
-      </c>
-      <c r="O14" s="239" t="s">
-        <v>280</v>
-      </c>
-      <c r="P14" s="239" t="s">
-        <v>473</v>
-      </c>
-      <c r="Q14" s="239" t="str">
+      <c r="O14" s="236" t="s">
+        <v>279</v>
+      </c>
+      <c r="P14" s="236" t="s">
+        <v>472</v>
+      </c>
+      <c r="Q14" s="236" t="str">
         <f t="shared" si="0"/>
         <v>om0</v>
       </c>
-      <c r="R14" s="239" t="str">
+      <c r="R14" s="236" t="str">
         <f t="shared" si="1"/>
         <v>op[48]</v>
       </c>
-      <c r="S14" s="239" t="str">
+      <c r="S14" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/om0/op[48]/    # op[48]入 = op[48]</v>
       </c>
     </row>
     <row r="15" spans="2:19" ht="24" thickBot="1">
-      <c r="B15" s="237" t="s">
+      <c r="B15" s="234" t="s">
+        <v>401</v>
+      </c>
+      <c r="C15" s="235" t="s">
         <v>402</v>
       </c>
-      <c r="C15" s="238" t="s">
+      <c r="D15" s="235"/>
+      <c r="E15" s="235"/>
+      <c r="F15" s="235"/>
+      <c r="G15" s="235"/>
+      <c r="H15" s="235"/>
+      <c r="I15" s="235"/>
+      <c r="J15" s="235"/>
+      <c r="K15" s="235" t="s">
         <v>403</v>
       </c>
-      <c r="D15" s="238"/>
-      <c r="E15" s="238"/>
-      <c r="F15" s="238"/>
-      <c r="G15" s="238"/>
-      <c r="H15" s="238"/>
-      <c r="I15" s="238"/>
-      <c r="J15" s="238"/>
-      <c r="K15" s="238" t="s">
-        <v>404</v>
-      </c>
-      <c r="L15" s="238"/>
-      <c r="O15" s="239" t="s">
-        <v>477</v>
-      </c>
-      <c r="P15" s="239" t="s">
-        <v>474</v>
-      </c>
-      <c r="Q15" s="239" t="str">
+      <c r="L15" s="235"/>
+      <c r="O15" s="236" t="s">
+        <v>476</v>
+      </c>
+      <c r="P15" s="236" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q15" s="236" t="str">
         <f t="shared" si="0"/>
         <v>irng0</v>
       </c>
-      <c r="R15" s="239" t="str">
+      <c r="R15" s="236" t="str">
         <f t="shared" si="1"/>
         <v>irk[48]</v>
       </c>
-      <c r="S15" s="239" t="str">
+      <c r="S15" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/irng0/irk[48]/    # irk[48]入 = irk[48]</v>
       </c>
     </row>
     <row r="16" spans="2:19" ht="24" thickBot="1">
-      <c r="B16" s="237" t="s">
+      <c r="B16" s="234" t="s">
+        <v>404</v>
+      </c>
+      <c r="C16" s="235" t="s">
+        <v>194</v>
+      </c>
+      <c r="D16" s="235"/>
+      <c r="E16" s="235"/>
+      <c r="F16" s="235"/>
+      <c r="G16" s="235"/>
+      <c r="H16" s="235"/>
+      <c r="I16" s="235"/>
+      <c r="J16" s="235"/>
+      <c r="K16" s="235" t="s">
         <v>405</v>
       </c>
-      <c r="C16" s="238" t="s">
-        <v>194</v>
-      </c>
-      <c r="D16" s="238"/>
-      <c r="E16" s="238"/>
-      <c r="F16" s="238"/>
-      <c r="G16" s="238"/>
-      <c r="H16" s="238"/>
-      <c r="I16" s="238"/>
-      <c r="J16" s="238"/>
-      <c r="K16" s="238" t="s">
-        <v>406</v>
-      </c>
-      <c r="L16" s="238"/>
-      <c r="O16" s="239" t="s">
-        <v>477</v>
-      </c>
-      <c r="P16" s="239" t="s">
-        <v>475</v>
-      </c>
-      <c r="Q16" s="239" t="str">
+      <c r="L16" s="235"/>
+      <c r="O16" s="236" t="s">
+        <v>476</v>
+      </c>
+      <c r="P16" s="236" t="s">
+        <v>474</v>
+      </c>
+      <c r="Q16" s="236" t="str">
         <f t="shared" si="0"/>
         <v>irng0</v>
       </c>
-      <c r="R16" s="239" t="str">
+      <c r="R16" s="236" t="str">
         <f t="shared" si="1"/>
         <v>irt[48]</v>
       </c>
-      <c r="S16" s="239" t="str">
+      <c r="S16" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/irng0/irt[48]/    # irt[48]入 = irt[48]</v>
       </c>
     </row>
     <row r="17" spans="2:20" ht="24" thickBot="1">
-      <c r="B17" s="237" t="s">
+      <c r="B17" s="234" t="s">
+        <v>406</v>
+      </c>
+      <c r="C17" s="235" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="235" t="s">
         <v>407</v>
       </c>
-      <c r="C17" s="238" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" s="238" t="s">
+      <c r="E17" s="235" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="235"/>
+      <c r="G17" s="235" t="s">
+        <v>109</v>
+      </c>
+      <c r="H17" s="235" t="s">
         <v>408</v>
       </c>
-      <c r="E17" s="238" t="s">
-        <v>92</v>
-      </c>
-      <c r="F17" s="238"/>
-      <c r="G17" s="238" t="s">
-        <v>109</v>
-      </c>
-      <c r="H17" s="238" t="s">
+      <c r="I17" s="235"/>
+      <c r="J17" s="235" t="s">
         <v>409</v>
       </c>
-      <c r="I17" s="238"/>
-      <c r="J17" s="238" t="s">
+      <c r="K17" s="235" t="s">
         <v>410</v>
       </c>
-      <c r="K17" s="238" t="s">
+      <c r="L17" s="235" t="s">
         <v>411</v>
       </c>
-      <c r="L17" s="238" t="s">
-        <v>412</v>
-      </c>
-      <c r="O17" s="239" t="s">
-        <v>478</v>
-      </c>
-      <c r="P17" s="239" t="s">
-        <v>476</v>
-      </c>
-      <c r="Q17" s="239" t="str">
+      <c r="O17" s="236" t="s">
+        <v>477</v>
+      </c>
+      <c r="P17" s="236" t="s">
+        <v>475</v>
+      </c>
+      <c r="Q17" s="236" t="str">
         <f t="shared" si="0"/>
         <v>irm0</v>
       </c>
-      <c r="R17" s="239" t="str">
+      <c r="R17" s="236" t="str">
         <f t="shared" si="1"/>
         <v>irp[48]</v>
       </c>
-      <c r="S17" s="239" t="str">
+      <c r="S17" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/irm0/irp[48]/    # irp[48]入 = irp[48]</v>
       </c>
     </row>
     <row r="18" spans="2:20" ht="24" thickBot="1">
-      <c r="B18" s="237" t="s">
+      <c r="B18" s="234" t="s">
+        <v>412</v>
+      </c>
+      <c r="C18" s="235" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="235"/>
+      <c r="E18" s="235" t="s">
         <v>413</v>
       </c>
-      <c r="C18" s="238" t="s">
-        <v>126</v>
-      </c>
-      <c r="D18" s="238"/>
-      <c r="E18" s="238" t="s">
+      <c r="F18" s="235" t="s">
         <v>414</v>
       </c>
-      <c r="F18" s="238" t="s">
+      <c r="G18" s="235" t="s">
         <v>415</v>
       </c>
-      <c r="G18" s="238" t="s">
+      <c r="H18" s="235" t="s">
         <v>416</v>
       </c>
-      <c r="H18" s="238" t="s">
+      <c r="I18" s="235" t="s">
         <v>417</v>
       </c>
-      <c r="I18" s="238" t="s">
+      <c r="J18" s="235" t="s">
         <v>418</v>
       </c>
-      <c r="J18" s="238" t="s">
+      <c r="K18" s="235" t="s">
         <v>419</v>
       </c>
-      <c r="K18" s="238" t="s">
-        <v>420</v>
-      </c>
-      <c r="L18" s="238"/>
-      <c r="O18" s="239" t="s">
-        <v>480</v>
-      </c>
-      <c r="P18" s="239" t="s">
+      <c r="L18" s="235"/>
+      <c r="O18" s="236" t="s">
         <v>479</v>
       </c>
-      <c r="Q18" s="239" t="str">
+      <c r="P18" s="236" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q18" s="236" t="str">
         <f t="shared" si="0"/>
         <v>un0</v>
       </c>
-      <c r="R18" s="239" t="str">
+      <c r="R18" s="236" t="str">
         <f t="shared" si="1"/>
         <v>ut[48]</v>
       </c>
-      <c r="S18" s="239" t="str">
+      <c r="S18" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/un0/ut[48]/    # ut[48]入 = ut[48]</v>
       </c>
     </row>
     <row r="19" spans="2:20" ht="24" thickBot="1">
-      <c r="B19" s="237" t="s">
+      <c r="B19" s="234" t="s">
+        <v>420</v>
+      </c>
+      <c r="C19" s="235" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="235"/>
+      <c r="E19" s="235"/>
+      <c r="F19" s="235" t="s">
         <v>421</v>
       </c>
-      <c r="C19" s="238" t="s">
-        <v>142</v>
-      </c>
-      <c r="D19" s="238"/>
-      <c r="E19" s="238"/>
-      <c r="F19" s="238" t="s">
+      <c r="G19" s="235"/>
+      <c r="H19" s="235"/>
+      <c r="I19" s="235" t="s">
         <v>422</v>
       </c>
-      <c r="G19" s="238"/>
-      <c r="H19" s="238"/>
-      <c r="I19" s="238" t="s">
+      <c r="J19" s="235"/>
+      <c r="K19" s="235" t="s">
         <v>423</v>
       </c>
-      <c r="J19" s="238"/>
-      <c r="K19" s="238" t="s">
-        <v>424</v>
-      </c>
-      <c r="L19" s="238"/>
-      <c r="O19" s="239" t="s">
-        <v>482</v>
-      </c>
-      <c r="P19" s="239" t="s">
+      <c r="L19" s="235"/>
+      <c r="O19" s="236" t="s">
         <v>481</v>
       </c>
-      <c r="Q19" s="239" t="str">
+      <c r="P19" s="236" t="s">
+        <v>480</v>
+      </c>
+      <c r="Q19" s="236" t="str">
         <f t="shared" si="0"/>
         <v>uan0</v>
       </c>
-      <c r="R19" s="239" t="str">
+      <c r="R19" s="236" t="str">
         <f t="shared" si="1"/>
         <v>uat[48]</v>
       </c>
-      <c r="S19" s="239" t="str">
+      <c r="S19" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/uan0/uat[48]/    # uat[48]入 = uat[48]</v>
       </c>
     </row>
     <row r="20" spans="2:20" ht="24" thickBot="1">
-      <c r="B20" s="237" t="s">
+      <c r="B20" s="234" t="s">
+        <v>424</v>
+      </c>
+      <c r="C20" s="235" t="s">
         <v>425</v>
       </c>
-      <c r="C20" s="238" t="s">
+      <c r="D20" s="235" t="s">
         <v>426</v>
       </c>
-      <c r="D20" s="238" t="s">
+      <c r="E20" s="235"/>
+      <c r="F20" s="235" t="s">
         <v>427</v>
       </c>
-      <c r="E20" s="238"/>
-      <c r="F20" s="238" t="s">
+      <c r="G20" s="235" t="s">
         <v>428</v>
       </c>
-      <c r="G20" s="238" t="s">
+      <c r="H20" s="235"/>
+      <c r="I20" s="235" t="s">
         <v>429</v>
       </c>
-      <c r="H20" s="238"/>
-      <c r="I20" s="238" t="s">
+      <c r="J20" s="235"/>
+      <c r="K20" s="235" t="s">
         <v>430</v>
       </c>
-      <c r="J20" s="238"/>
-      <c r="K20" s="238" t="s">
-        <v>431</v>
-      </c>
-      <c r="L20" s="238"/>
+      <c r="L20" s="235"/>
     </row>
     <row r="21" spans="2:20" ht="24" thickBot="1">
-      <c r="B21" s="237" t="s">
+      <c r="B21" s="234" t="s">
+        <v>431</v>
+      </c>
+      <c r="C21" s="235" t="s">
         <v>432</v>
       </c>
-      <c r="C21" s="238" t="s">
+      <c r="D21" s="235" t="s">
         <v>433</v>
       </c>
-      <c r="D21" s="238" t="s">
-        <v>434</v>
-      </c>
-      <c r="E21" s="238"/>
-      <c r="F21" s="238"/>
-      <c r="G21" s="238"/>
-      <c r="H21" s="238"/>
-      <c r="I21" s="238"/>
-      <c r="J21" s="238"/>
-      <c r="K21" s="238"/>
-      <c r="L21" s="238"/>
+      <c r="E21" s="235"/>
+      <c r="F21" s="235"/>
+      <c r="G21" s="235"/>
+      <c r="H21" s="235"/>
+      <c r="I21" s="235"/>
+      <c r="J21" s="235"/>
+      <c r="K21" s="235"/>
+      <c r="L21" s="235"/>
     </row>
     <row r="22" spans="2:20" ht="24" thickBot="1">
-      <c r="B22" s="237" t="s">
+      <c r="B22" s="234" t="s">
+        <v>434</v>
+      </c>
+      <c r="C22" s="235" t="s">
         <v>435</v>
       </c>
-      <c r="C22" s="238" t="s">
+      <c r="D22" s="235"/>
+      <c r="E22" s="235"/>
+      <c r="F22" s="235"/>
+      <c r="G22" s="235"/>
+      <c r="H22" s="235"/>
+      <c r="I22" s="235"/>
+      <c r="J22" s="235"/>
+      <c r="K22" s="235" t="s">
         <v>436</v>
       </c>
-      <c r="D22" s="238"/>
-      <c r="E22" s="238"/>
-      <c r="F22" s="238"/>
-      <c r="G22" s="238"/>
-      <c r="H22" s="238"/>
-      <c r="I22" s="238"/>
-      <c r="J22" s="238"/>
-      <c r="K22" s="238" t="s">
-        <v>437</v>
-      </c>
-      <c r="L22" s="238"/>
-      <c r="O22" s="240" t="s">
-        <v>458</v>
-      </c>
-      <c r="P22" s="240" t="s">
+      <c r="L22" s="235"/>
+      <c r="O22" s="237" t="s">
         <v>457</v>
       </c>
-      <c r="Q22" s="240" t="str">
+      <c r="P22" s="237" t="s">
+        <v>456</v>
+      </c>
+      <c r="Q22" s="237" t="str">
         <f>_xlfn.CONCAT(O22,$Q$2)</f>
         <v>eng0</v>
       </c>
-      <c r="R22" s="240" t="str">
+      <c r="R22" s="237" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(P22,$R$2)</f>
         <v>ek[48]</v>
       </c>
-      <c r="S22" s="240" t="str">
+      <c r="S22" s="237" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - xform/", R22, "/", Q22, "/    # " &amp; O22, "入 = ", P22, "[48]")</f>
         <v xml:space="preserve">    - xform/ek[48]/eng0/    # eng入 = ek[48]</v>
       </c>
     </row>
     <row r="23" spans="2:20" ht="24" thickBot="1">
-      <c r="B23" s="237" t="s">
+      <c r="B23" s="234" t="s">
+        <v>437</v>
+      </c>
+      <c r="C23" s="235" t="s">
         <v>438</v>
       </c>
-      <c r="C23" s="238" t="s">
+      <c r="D23" s="235"/>
+      <c r="E23" s="235"/>
+      <c r="F23" s="235"/>
+      <c r="G23" s="235"/>
+      <c r="H23" s="235"/>
+      <c r="I23" s="235"/>
+      <c r="J23" s="235"/>
+      <c r="K23" s="235" t="s">
         <v>439</v>
       </c>
-      <c r="D23" s="238"/>
-      <c r="E23" s="238"/>
-      <c r="F23" s="238"/>
-      <c r="G23" s="238"/>
-      <c r="H23" s="238"/>
-      <c r="I23" s="238"/>
-      <c r="J23" s="238"/>
-      <c r="K23" s="238" t="s">
-        <v>440</v>
-      </c>
-      <c r="L23" s="238"/>
-      <c r="O23" s="239" t="s">
+      <c r="L23" s="235"/>
+      <c r="O23" s="236" t="s">
+        <v>482</v>
+      </c>
+      <c r="P23" s="238" t="s">
         <v>483</v>
       </c>
-      <c r="P23" s="241" t="s">
-        <v>484</v>
-      </c>
-      <c r="Q23" s="239" t="str">
+      <c r="Q23" s="236" t="str">
         <f>_xlfn.CONCAT(O23,$Q$2)</f>
         <v>uang0</v>
       </c>
-      <c r="R23" s="239" t="str">
+      <c r="R23" s="236" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(P23,$R$2)</f>
         <v>uak[48]</v>
       </c>
-      <c r="S23" s="239" t="str">
+      <c r="S23" s="236" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - xform/", R23, "/", Q23, "/    # " &amp; O23, "入 = ", P23, "[48]")</f>
         <v xml:space="preserve">    - xform/uak[48]/uang0/    # uang入 = uak[48]</v>
       </c>
-      <c r="T23" s="240"/>
+      <c r="T23" s="237"/>
     </row>
     <row r="24" spans="2:20" ht="24" thickBot="1">
-      <c r="B24" s="237" t="s">
+      <c r="B24" s="234" t="s">
+        <v>440</v>
+      </c>
+      <c r="C24" s="235" t="s">
         <v>441</v>
       </c>
-      <c r="C24" s="238" t="s">
-        <v>442</v>
-      </c>
-      <c r="D24" s="238"/>
-      <c r="E24" s="238"/>
-      <c r="F24" s="238"/>
-      <c r="G24" s="238"/>
-      <c r="H24" s="238"/>
-      <c r="I24" s="238"/>
-      <c r="J24" s="238"/>
-      <c r="K24" s="238"/>
-      <c r="L24" s="238"/>
+      <c r="D24" s="235"/>
+      <c r="E24" s="235"/>
+      <c r="F24" s="235"/>
+      <c r="G24" s="235"/>
+      <c r="H24" s="235"/>
+      <c r="I24" s="235"/>
+      <c r="J24" s="235"/>
+      <c r="K24" s="235"/>
+      <c r="L24" s="235"/>
     </row>
     <row r="25" spans="2:20" ht="24" thickBot="1">
-      <c r="B25" s="237" t="s">
+      <c r="B25" s="234" t="s">
+        <v>442</v>
+      </c>
+      <c r="C25" s="235"/>
+      <c r="D25" s="235" t="s">
         <v>443</v>
       </c>
-      <c r="C25" s="238"/>
-      <c r="D25" s="238" t="s">
-        <v>444</v>
-      </c>
-      <c r="E25" s="238"/>
-      <c r="F25" s="238"/>
-      <c r="G25" s="238"/>
-      <c r="H25" s="238"/>
-      <c r="I25" s="238"/>
-      <c r="J25" s="238"/>
-      <c r="K25" s="238"/>
-      <c r="L25" s="238"/>
+      <c r="E25" s="235"/>
+      <c r="F25" s="235"/>
+      <c r="G25" s="235"/>
+      <c r="H25" s="235"/>
+      <c r="I25" s="235"/>
+      <c r="J25" s="235"/>
+      <c r="K25" s="235"/>
+      <c r="L25" s="235"/>
     </row>
     <row r="26" spans="2:20" ht="24" thickBot="1">
-      <c r="B26" s="237" t="s">
+      <c r="B26" s="234" t="s">
+        <v>444</v>
+      </c>
+      <c r="C26" s="235" t="s">
         <v>445</v>
       </c>
-      <c r="C26" s="238" t="s">
+      <c r="D26" s="235"/>
+      <c r="E26" s="235"/>
+      <c r="F26" s="235"/>
+      <c r="G26" s="235"/>
+      <c r="H26" s="235"/>
+      <c r="I26" s="235"/>
+      <c r="J26" s="235"/>
+      <c r="K26" s="235" t="s">
         <v>446</v>
       </c>
-      <c r="D26" s="238"/>
-      <c r="E26" s="238"/>
-      <c r="F26" s="238"/>
-      <c r="G26" s="238"/>
-      <c r="H26" s="238"/>
-      <c r="I26" s="238"/>
-      <c r="J26" s="238"/>
-      <c r="K26" s="238" t="s">
-        <v>447</v>
-      </c>
-      <c r="L26" s="238"/>
+      <c r="L26" s="235"/>
     </row>
     <row r="27" spans="2:20" ht="24" thickBot="1">
-      <c r="B27" s="237" t="s">
+      <c r="B27" s="234" t="s">
+        <v>447</v>
+      </c>
+      <c r="C27" s="253" t="s">
+        <v>192</v>
+      </c>
+      <c r="D27" s="254"/>
+      <c r="E27" s="253" t="s">
         <v>448</v>
       </c>
-      <c r="C27" s="245" t="s">
-        <v>192</v>
-      </c>
-      <c r="D27" s="246"/>
-      <c r="E27" s="245" t="s">
+      <c r="F27" s="255"/>
+      <c r="G27" s="255"/>
+      <c r="H27" s="255"/>
+      <c r="I27" s="255"/>
+      <c r="J27" s="254"/>
+      <c r="K27" s="253" t="s">
         <v>449</v>
       </c>
-      <c r="F27" s="247"/>
-      <c r="G27" s="247"/>
-      <c r="H27" s="247"/>
-      <c r="I27" s="247"/>
-      <c r="J27" s="246"/>
-      <c r="K27" s="245" t="s">
-        <v>450</v>
-      </c>
-      <c r="L27" s="246"/>
+      <c r="L27" s="254"/>
     </row>
     <row r="28" spans="2:20" ht="24" thickBot="1">
-      <c r="B28" s="237" t="s">
+      <c r="B28" s="234" t="s">
+        <v>450</v>
+      </c>
+      <c r="C28" s="253" t="s">
         <v>451</v>
       </c>
-      <c r="C28" s="245" t="s">
+      <c r="D28" s="254"/>
+      <c r="E28" s="253" t="s">
+        <v>448</v>
+      </c>
+      <c r="F28" s="255"/>
+      <c r="G28" s="255"/>
+      <c r="H28" s="255"/>
+      <c r="I28" s="255"/>
+      <c r="J28" s="254"/>
+      <c r="K28" s="253" t="s">
         <v>452</v>
       </c>
-      <c r="D28" s="246"/>
-      <c r="E28" s="245" t="s">
-        <v>449</v>
-      </c>
-      <c r="F28" s="247"/>
-      <c r="G28" s="247"/>
-      <c r="H28" s="247"/>
-      <c r="I28" s="247"/>
-      <c r="J28" s="246"/>
-      <c r="K28" s="245" t="s">
-        <v>453</v>
-      </c>
-      <c r="L28" s="246"/>
+      <c r="L28" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:D3"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="K3:L3"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="E27:J27"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:J28"/>
     <mergeCell ref="K28:L28"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9300,120 +10332,120 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A576E6A5-6E98-4E7F-8993-972F5CA6ECFB}">
   <dimension ref="B1:Z28"/>
-  <sheetFormatPr defaultRowHeight="21.75"/>
+  <sheetFormatPr defaultRowHeight="21"/>
   <cols>
     <col min="1" max="1" width="2.8984375" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="17" width="7.796875" style="239" customWidth="1"/>
-    <col min="18" max="19" width="14.69921875" style="239" customWidth="1"/>
-    <col min="20" max="20" width="65.09765625" style="239" customWidth="1"/>
-    <col min="21" max="26" width="8.796875" style="239"/>
+    <col min="16" max="17" width="7.796875" style="236" customWidth="1"/>
+    <col min="18" max="19" width="14.69921875" style="236" customWidth="1"/>
+    <col min="20" max="20" width="65.09765625" style="236" customWidth="1"/>
+    <col min="21" max="26" width="8.796875" style="236"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="22.5" thickBot="1"/>
+    <row r="1" spans="2:20" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:20" ht="24" thickBot="1">
-      <c r="B2" s="248" t="s">
+      <c r="B2" s="244" t="s">
+        <v>332</v>
+      </c>
+      <c r="C2" s="246" t="s">
         <v>333</v>
       </c>
-      <c r="C2" s="250" t="s">
+      <c r="D2" s="247"/>
+      <c r="E2" s="250" t="s">
         <v>334</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="254" t="s">
+      <c r="F2" s="251"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="250" t="s">
         <v>335</v>
       </c>
-      <c r="F2" s="255"/>
-      <c r="G2" s="256"/>
-      <c r="H2" s="254" t="s">
-        <v>336</v>
-      </c>
-      <c r="I2" s="255"/>
-      <c r="J2" s="255"/>
-      <c r="K2" s="255"/>
-      <c r="L2" s="256"/>
+      <c r="I2" s="251"/>
+      <c r="J2" s="251"/>
+      <c r="K2" s="251"/>
+      <c r="L2" s="252"/>
     </row>
     <row r="3" spans="2:20" ht="24" thickBot="1">
-      <c r="B3" s="249"/>
-      <c r="C3" s="252"/>
-      <c r="D3" s="253"/>
-      <c r="E3" s="237" t="s">
+      <c r="B3" s="245"/>
+      <c r="C3" s="248"/>
+      <c r="D3" s="249"/>
+      <c r="E3" s="234" t="s">
+        <v>336</v>
+      </c>
+      <c r="F3" s="234" t="s">
         <v>337</v>
       </c>
-      <c r="F3" s="237" t="s">
+      <c r="G3" s="234" t="s">
         <v>338</v>
       </c>
-      <c r="G3" s="237" t="s">
+      <c r="H3" s="234" t="s">
         <v>339</v>
       </c>
-      <c r="H3" s="237" t="s">
+      <c r="I3" s="234" t="s">
         <v>340</v>
       </c>
-      <c r="I3" s="237" t="s">
+      <c r="J3" s="234" t="s">
         <v>341</v>
       </c>
-      <c r="J3" s="237" t="s">
+      <c r="K3" s="250" t="s">
         <v>342</v>
       </c>
-      <c r="K3" s="254" t="s">
-        <v>343</v>
-      </c>
-      <c r="L3" s="256"/>
-      <c r="N3" s="243" t="s">
-        <v>510</v>
-      </c>
-      <c r="O3" s="243" t="s">
-        <v>513</v>
-      </c>
-      <c r="P3" s="244" t="s">
+      <c r="L3" s="252"/>
+      <c r="N3" s="240" t="s">
+        <v>509</v>
+      </c>
+      <c r="O3" s="240" t="s">
+        <v>512</v>
+      </c>
+      <c r="P3" s="241" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q3" s="241" t="s">
+        <v>504</v>
+      </c>
+      <c r="R3" s="241" t="s">
         <v>506</v>
       </c>
-      <c r="Q3" s="244" t="s">
-        <v>505</v>
-      </c>
-      <c r="R3" s="244" t="s">
-        <v>507</v>
-      </c>
-      <c r="S3" s="244" t="str">
+      <c r="S3" s="241" t="str">
         <f xml:space="preserve"> "$1"</f>
         <v>$1</v>
       </c>
-      <c r="T3" s="244" t="s">
-        <v>512</v>
+      <c r="T3" s="241" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="4" spans="2:20" ht="24" thickBot="1">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="234" t="s">
+        <v>343</v>
+      </c>
+      <c r="C4" s="235" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="235" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="235" t="s">
+        <v>162</v>
+      </c>
+      <c r="F4" s="235" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="235" t="s">
+        <v>148</v>
+      </c>
+      <c r="H4" s="235" t="s">
         <v>344</v>
       </c>
-      <c r="C4" s="238" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="238" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="238" t="s">
-        <v>162</v>
-      </c>
-      <c r="F4" s="238" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" s="238" t="s">
-        <v>148</v>
-      </c>
-      <c r="H4" s="238" t="s">
+      <c r="I4" s="235" t="s">
         <v>345</v>
       </c>
-      <c r="I4" s="238" t="s">
+      <c r="J4" s="235" t="s">
         <v>346</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="K4" s="235" t="s">
         <v>347</v>
       </c>
-      <c r="K4" s="238" t="s">
+      <c r="L4" s="235" t="s">
         <v>348</v>
-      </c>
-      <c r="L4" s="238" t="s">
-        <v>349</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -9422,46 +10454,46 @@
         <f t="shared" ref="O4:O20" si="0" xml:space="preserve"> LEN(P4)</f>
         <v>4</v>
       </c>
-      <c r="P4" s="239" t="s">
-        <v>465</v>
-      </c>
-      <c r="Q4" s="239" t="s">
-        <v>490</v>
-      </c>
-      <c r="R4" s="239" t="str">
+      <c r="P4" s="236" t="s">
+        <v>464</v>
+      </c>
+      <c r="Q4" s="236" t="s">
+        <v>489</v>
+      </c>
+      <c r="R4" s="236" t="str">
         <f>_xlfn.CONCAT(P4,$R$3)</f>
         <v>iang([12357])</v>
       </c>
-      <c r="S4" s="239" t="str">
+      <c r="S4" s="236" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(Q4,$S$3)</f>
         <v>iaG$1</v>
       </c>
-      <c r="T4" s="239" t="str">
+      <c r="T4" s="236" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - derive/", R4, "/", S4, "/    # " &amp; Q4, "入 = ", P4, "[48]")</f>
         <v xml:space="preserve">    - derive/iang([12357])/iaG$1/    # iaG入 = iang[48]</v>
       </c>
     </row>
     <row r="5" spans="2:20" ht="24" thickBot="1">
-      <c r="B5" s="237" t="s">
+      <c r="B5" s="234" t="s">
+        <v>349</v>
+      </c>
+      <c r="C5" s="235" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="235" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="235"/>
+      <c r="F5" s="235"/>
+      <c r="G5" s="235"/>
+      <c r="H5" s="235"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="235"/>
+      <c r="K5" s="235" t="s">
         <v>350</v>
       </c>
-      <c r="C5" s="238" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="238" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="238"/>
-      <c r="F5" s="238"/>
-      <c r="G5" s="238"/>
-      <c r="H5" s="238"/>
-      <c r="I5" s="238"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="238" t="s">
+      <c r="L5" s="235" t="s">
         <v>351</v>
-      </c>
-      <c r="L5" s="238" t="s">
-        <v>352</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -9470,44 +10502,44 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="P5" s="239" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q5" s="239" t="s">
-        <v>491</v>
-      </c>
-      <c r="R5" s="239" t="str">
+      <c r="P5" s="236" t="s">
+        <v>470</v>
+      </c>
+      <c r="Q5" s="236" t="s">
+        <v>490</v>
+      </c>
+      <c r="R5" s="236" t="str">
         <f t="shared" ref="R5:R20" si="1">_xlfn.CONCAT(P5,$R$3)</f>
         <v>iong([12357])</v>
       </c>
-      <c r="S5" s="239" t="str">
+      <c r="S5" s="236" t="str">
         <f t="shared" ref="S5:S20" si="2" xml:space="preserve"> _xlfn.CONCAT(Q5,$S$3)</f>
         <v>ioG$1</v>
       </c>
-      <c r="T5" s="239" t="str">
+      <c r="T5" s="236" t="str">
         <f t="shared" ref="T5:T20" si="3" xml:space="preserve"> _xlfn.CONCAT("    - derive/", R5, "/", S5, "/    # " &amp; Q5, "入 = ", P5, "[48]")</f>
         <v xml:space="preserve">    - derive/iong([12357])/ioG$1/    # ioG入 = iong[48]</v>
       </c>
     </row>
     <row r="6" spans="2:20" ht="24" thickBot="1">
-      <c r="B6" s="237" t="s">
+      <c r="B6" s="234" t="s">
+        <v>352</v>
+      </c>
+      <c r="C6" s="235" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="235"/>
+      <c r="E6" s="235"/>
+      <c r="F6" s="235"/>
+      <c r="G6" s="235"/>
+      <c r="H6" s="235"/>
+      <c r="I6" s="235"/>
+      <c r="J6" s="235"/>
+      <c r="K6" s="235" t="s">
         <v>353</v>
       </c>
-      <c r="C6" s="238" t="s">
-        <v>146</v>
-      </c>
-      <c r="D6" s="238"/>
-      <c r="E6" s="238"/>
-      <c r="F6" s="238"/>
-      <c r="G6" s="238"/>
-      <c r="H6" s="238"/>
-      <c r="I6" s="238"/>
-      <c r="J6" s="238"/>
-      <c r="K6" s="238" t="s">
+      <c r="L6" s="235" t="s">
         <v>354</v>
-      </c>
-      <c r="L6" s="238" t="s">
-        <v>355</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -9516,47 +10548,47 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="P6" s="239" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q6" s="239" t="s">
-        <v>493</v>
-      </c>
-      <c r="R6" s="239" t="str">
+      <c r="P6" s="236" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q6" s="236" t="s">
+        <v>492</v>
+      </c>
+      <c r="R6" s="236" t="str">
         <f t="shared" si="1"/>
         <v>irng([12357])</v>
       </c>
-      <c r="S6" s="239" t="str">
+      <c r="S6" s="236" t="str">
         <f t="shared" si="2"/>
         <v>irG$1</v>
       </c>
-      <c r="T6" s="239" t="str">
+      <c r="T6" s="236" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    - derive/irng([12357])/irG$1/    # irG入 = irng[48]</v>
       </c>
     </row>
     <row r="7" spans="2:20" ht="24" thickBot="1">
-      <c r="B7" s="237" t="s">
+      <c r="B7" s="234" t="s">
+        <v>355</v>
+      </c>
+      <c r="C7" s="235" t="s">
         <v>356</v>
       </c>
-      <c r="C7" s="238" t="s">
+      <c r="D7" s="235"/>
+      <c r="E7" s="235"/>
+      <c r="F7" s="235"/>
+      <c r="G7" s="235" t="s">
         <v>357</v>
       </c>
-      <c r="D7" s="238"/>
-      <c r="E7" s="238"/>
-      <c r="F7" s="238"/>
-      <c r="G7" s="238" t="s">
+      <c r="H7" s="235"/>
+      <c r="I7" s="235"/>
+      <c r="J7" s="235" t="s">
         <v>358</v>
       </c>
-      <c r="H7" s="238"/>
-      <c r="I7" s="238"/>
-      <c r="J7" s="238" t="s">
+      <c r="K7" s="235" t="s">
         <v>359</v>
       </c>
-      <c r="K7" s="238" t="s">
-        <v>360</v>
-      </c>
-      <c r="L7" s="238"/>
+      <c r="L7" s="235"/>
       <c r="N7">
         <v>1</v>
       </c>
@@ -9564,46 +10596,46 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P7" s="239" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q7" s="239" t="s">
-        <v>488</v>
-      </c>
-      <c r="R7" s="239" t="str">
+      <c r="P7" s="236" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q7" s="236" t="s">
+        <v>487</v>
+      </c>
+      <c r="R7" s="236" t="str">
         <f t="shared" si="1"/>
         <v>ang([12357])</v>
       </c>
-      <c r="S7" s="239" t="str">
+      <c r="S7" s="236" t="str">
         <f t="shared" si="2"/>
         <v>aG$1</v>
       </c>
-      <c r="T7" s="239" t="str">
+      <c r="T7" s="236" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    - derive/ang([12357])/aG$1/    # aG入 = ang[48]</v>
       </c>
     </row>
     <row r="8" spans="2:20" ht="24" thickBot="1">
-      <c r="B8" s="237" t="s">
+      <c r="B8" s="234" t="s">
+        <v>360</v>
+      </c>
+      <c r="C8" s="235" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="235" t="s">
+        <v>164</v>
+      </c>
+      <c r="E8" s="235"/>
+      <c r="F8" s="235"/>
+      <c r="G8" s="235"/>
+      <c r="H8" s="235"/>
+      <c r="I8" s="235"/>
+      <c r="J8" s="235"/>
+      <c r="K8" s="235" t="s">
         <v>361</v>
       </c>
-      <c r="C8" s="238" t="s">
-        <v>183</v>
-      </c>
-      <c r="D8" s="238" t="s">
-        <v>164</v>
-      </c>
-      <c r="E8" s="238"/>
-      <c r="F8" s="238"/>
-      <c r="G8" s="238"/>
-      <c r="H8" s="238"/>
-      <c r="I8" s="238"/>
-      <c r="J8" s="238"/>
-      <c r="K8" s="238" t="s">
+      <c r="L8" s="235" t="s">
         <v>362</v>
-      </c>
-      <c r="L8" s="238" t="s">
-        <v>363</v>
       </c>
       <c r="N8">
         <v>1</v>
@@ -9612,58 +10644,58 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P8" s="239" t="s">
-        <v>462</v>
-      </c>
-      <c r="Q8" s="239" t="s">
-        <v>489</v>
-      </c>
-      <c r="R8" s="239" t="str">
+      <c r="P8" s="236" t="s">
+        <v>461</v>
+      </c>
+      <c r="Q8" s="236" t="s">
+        <v>488</v>
+      </c>
+      <c r="R8" s="236" t="str">
         <f t="shared" si="1"/>
         <v>ing([12357])</v>
       </c>
-      <c r="S8" s="239" t="str">
+      <c r="S8" s="236" t="str">
         <f t="shared" si="2"/>
         <v>iG$1</v>
       </c>
-      <c r="T8" s="239" t="str">
+      <c r="T8" s="236" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    - derive/ing([12357])/iG$1/    # iG入 = ing[48]</v>
       </c>
     </row>
     <row r="9" spans="2:20" ht="24" thickBot="1">
-      <c r="B9" s="237" t="s">
+      <c r="B9" s="234" t="s">
+        <v>363</v>
+      </c>
+      <c r="C9" s="235" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="235" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="235" t="s">
         <v>364</v>
       </c>
-      <c r="C9" s="238" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9" s="238" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="238" t="s">
+      <c r="F9" s="235" t="s">
         <v>365</v>
       </c>
-      <c r="F9" s="238" t="s">
+      <c r="G9" s="235" t="s">
         <v>366</v>
       </c>
-      <c r="G9" s="238" t="s">
+      <c r="H9" s="235" t="s">
         <v>367</v>
       </c>
-      <c r="H9" s="238" t="s">
+      <c r="I9" s="235" t="s">
         <v>368</v>
       </c>
-      <c r="I9" s="238" t="s">
+      <c r="J9" s="235" t="s">
         <v>369</v>
       </c>
-      <c r="J9" s="238" t="s">
+      <c r="K9" s="235" t="s">
         <v>370</v>
       </c>
-      <c r="K9" s="238" t="s">
+      <c r="L9" s="235" t="s">
         <v>371</v>
-      </c>
-      <c r="L9" s="238" t="s">
-        <v>372</v>
       </c>
       <c r="N9">
         <v>1</v>
@@ -9672,58 +10704,58 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P9" s="239" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q9" s="239" t="s">
-        <v>492</v>
-      </c>
-      <c r="R9" s="239" t="str">
+      <c r="P9" s="236" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q9" s="236" t="s">
+        <v>491</v>
+      </c>
+      <c r="R9" s="236" t="str">
         <f t="shared" si="1"/>
         <v>ong([12357])</v>
       </c>
-      <c r="S9" s="239" t="str">
+      <c r="S9" s="236" t="str">
         <f t="shared" si="2"/>
         <v>oG$1</v>
       </c>
-      <c r="T9" s="239" t="str">
+      <c r="T9" s="236" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    - derive/ong([12357])/oG$1/    # oG入 = ong[48]</v>
       </c>
     </row>
     <row r="10" spans="2:20" ht="24" thickBot="1">
-      <c r="B10" s="237" t="s">
+      <c r="B10" s="234" t="s">
+        <v>372</v>
+      </c>
+      <c r="C10" s="235" t="s">
         <v>373</v>
       </c>
-      <c r="C10" s="238" t="s">
+      <c r="D10" s="235" t="s">
         <v>374</v>
       </c>
-      <c r="D10" s="238" t="s">
+      <c r="E10" s="235" t="s">
         <v>375</v>
       </c>
-      <c r="E10" s="238" t="s">
+      <c r="F10" s="235" t="s">
         <v>376</v>
       </c>
-      <c r="F10" s="238" t="s">
+      <c r="G10" s="235" t="s">
         <v>377</v>
       </c>
-      <c r="G10" s="238" t="s">
+      <c r="H10" s="235" t="s">
         <v>378</v>
       </c>
-      <c r="H10" s="238" t="s">
+      <c r="I10" s="235" t="s">
         <v>379</v>
       </c>
-      <c r="I10" s="238" t="s">
+      <c r="J10" s="235" t="s">
         <v>380</v>
       </c>
-      <c r="J10" s="238" t="s">
+      <c r="K10" s="235" t="s">
         <v>381</v>
       </c>
-      <c r="K10" s="238" t="s">
+      <c r="L10" s="235" t="s">
         <v>382</v>
-      </c>
-      <c r="L10" s="238" t="s">
-        <v>383</v>
       </c>
       <c r="N10">
         <v>2</v>
@@ -9732,45 +10764,45 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P10" s="239" t="s">
-        <v>468</v>
-      </c>
-      <c r="Q10" s="239" t="s">
-        <v>497</v>
-      </c>
-      <c r="R10" s="239" t="str">
+      <c r="P10" s="236" t="s">
+        <v>467</v>
+      </c>
+      <c r="Q10" s="236" t="s">
+        <v>496</v>
+      </c>
+      <c r="R10" s="236" t="str">
         <f t="shared" si="1"/>
         <v>ian([12357])</v>
       </c>
-      <c r="S10" s="239" t="str">
+      <c r="S10" s="236" t="str">
         <f t="shared" si="2"/>
         <v>iaN$1</v>
       </c>
-      <c r="T10" s="239" t="str">
+      <c r="T10" s="236" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    - derive/ian([12357])/iaN$1/    # iaN入 = ian[48]</v>
       </c>
     </row>
     <row r="11" spans="2:20" ht="24" thickBot="1">
-      <c r="B11" s="237" t="s">
+      <c r="B11" s="234" t="s">
+        <v>383</v>
+      </c>
+      <c r="C11" s="235" t="s">
         <v>384</v>
       </c>
-      <c r="C11" s="238" t="s">
+      <c r="D11" s="235" t="s">
         <v>385</v>
       </c>
-      <c r="D11" s="238" t="s">
+      <c r="E11" s="235"/>
+      <c r="F11" s="235"/>
+      <c r="G11" s="235"/>
+      <c r="H11" s="235"/>
+      <c r="I11" s="235"/>
+      <c r="J11" s="235"/>
+      <c r="K11" s="235" t="s">
         <v>386</v>
       </c>
-      <c r="E11" s="238"/>
-      <c r="F11" s="238"/>
-      <c r="G11" s="238"/>
-      <c r="H11" s="238"/>
-      <c r="I11" s="238"/>
-      <c r="J11" s="238"/>
-      <c r="K11" s="238" t="s">
-        <v>387</v>
-      </c>
-      <c r="L11" s="238"/>
+      <c r="L11" s="235"/>
       <c r="N11">
         <v>2</v>
       </c>
@@ -9778,43 +10810,43 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P11" s="239" t="s">
-        <v>511</v>
-      </c>
-      <c r="Q11" s="239" t="s">
-        <v>493</v>
-      </c>
-      <c r="R11" s="239" t="str">
+      <c r="P11" s="236" t="s">
+        <v>510</v>
+      </c>
+      <c r="Q11" s="236" t="s">
+        <v>492</v>
+      </c>
+      <c r="R11" s="236" t="str">
         <f t="shared" si="1"/>
         <v>irn([12357])</v>
       </c>
-      <c r="S11" s="239" t="str">
+      <c r="S11" s="236" t="str">
         <f t="shared" si="2"/>
         <v>irG$1</v>
       </c>
-      <c r="T11" s="239" t="str">
+      <c r="T11" s="236" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    - derive/irn([12357])/irG$1/    # irG入 = irn[48]</v>
       </c>
     </row>
     <row r="12" spans="2:20" ht="24" thickBot="1">
-      <c r="B12" s="237" t="s">
+      <c r="B12" s="234" t="s">
+        <v>387</v>
+      </c>
+      <c r="C12" s="235" t="s">
         <v>388</v>
       </c>
-      <c r="C12" s="238" t="s">
+      <c r="D12" s="235"/>
+      <c r="E12" s="235"/>
+      <c r="F12" s="235"/>
+      <c r="G12" s="235"/>
+      <c r="H12" s="235"/>
+      <c r="I12" s="235"/>
+      <c r="J12" s="235"/>
+      <c r="K12" s="235" t="s">
         <v>389</v>
       </c>
-      <c r="D12" s="238"/>
-      <c r="E12" s="238"/>
-      <c r="F12" s="238"/>
-      <c r="G12" s="238"/>
-      <c r="H12" s="238"/>
-      <c r="I12" s="238"/>
-      <c r="J12" s="238"/>
-      <c r="K12" s="238" t="s">
-        <v>390</v>
-      </c>
-      <c r="L12" s="238"/>
+      <c r="L12" s="235"/>
       <c r="N12">
         <v>2</v>
       </c>
@@ -9822,49 +10854,49 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P12" s="239" t="s">
-        <v>482</v>
-      </c>
-      <c r="Q12" s="239" t="s">
-        <v>499</v>
-      </c>
-      <c r="R12" s="239" t="str">
+      <c r="P12" s="236" t="s">
+        <v>481</v>
+      </c>
+      <c r="Q12" s="236" t="s">
+        <v>498</v>
+      </c>
+      <c r="R12" s="236" t="str">
         <f t="shared" si="1"/>
         <v>uan([12357])</v>
       </c>
-      <c r="S12" s="239" t="str">
+      <c r="S12" s="236" t="str">
         <f t="shared" si="2"/>
         <v>uaN$1</v>
       </c>
-      <c r="T12" s="239" t="str">
+      <c r="T12" s="236" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    - derive/uan([12357])/uaN$1/    # uaN入 = uan[48]</v>
       </c>
     </row>
     <row r="13" spans="2:20" ht="24" thickBot="1">
-      <c r="B13" s="237" t="s">
+      <c r="B13" s="234" t="s">
+        <v>390</v>
+      </c>
+      <c r="C13" s="235" t="s">
         <v>391</v>
       </c>
-      <c r="C13" s="238" t="s">
+      <c r="D13" s="235" t="s">
         <v>392</v>
       </c>
-      <c r="D13" s="238" t="s">
+      <c r="E13" s="235"/>
+      <c r="F13" s="235"/>
+      <c r="G13" s="235" t="s">
         <v>393</v>
       </c>
-      <c r="E13" s="238"/>
-      <c r="F13" s="238"/>
-      <c r="G13" s="238" t="s">
+      <c r="H13" s="235"/>
+      <c r="I13" s="235"/>
+      <c r="J13" s="235" t="s">
         <v>394</v>
       </c>
-      <c r="H13" s="238"/>
-      <c r="I13" s="238"/>
-      <c r="J13" s="238" t="s">
+      <c r="K13" s="235" t="s">
         <v>395</v>
       </c>
-      <c r="K13" s="238" t="s">
-        <v>396</v>
-      </c>
-      <c r="L13" s="238"/>
+      <c r="L13" s="235"/>
       <c r="N13">
         <v>2</v>
       </c>
@@ -9872,46 +10904,46 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="P13" s="239" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q13" s="239" t="s">
-        <v>496</v>
-      </c>
-      <c r="R13" s="239" t="str">
+      <c r="P13" s="236" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q13" s="236" t="s">
+        <v>495</v>
+      </c>
+      <c r="R13" s="236" t="str">
         <f t="shared" si="1"/>
         <v>an([12357])</v>
       </c>
-      <c r="S13" s="239" t="str">
+      <c r="S13" s="236" t="str">
         <f t="shared" si="2"/>
         <v>aN$1</v>
       </c>
-      <c r="T13" s="239" t="str">
+      <c r="T13" s="236" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    - derive/an([12357])/aN$1/    # aN入 = an[48]</v>
       </c>
     </row>
     <row r="14" spans="2:20" ht="24" thickBot="1">
-      <c r="B14" s="237" t="s">
+      <c r="B14" s="234" t="s">
+        <v>396</v>
+      </c>
+      <c r="C14" s="235" t="s">
         <v>397</v>
       </c>
-      <c r="C14" s="238" t="s">
+      <c r="D14" s="235" t="s">
         <v>398</v>
       </c>
-      <c r="D14" s="238" t="s">
+      <c r="E14" s="235"/>
+      <c r="F14" s="235"/>
+      <c r="G14" s="235"/>
+      <c r="H14" s="235"/>
+      <c r="I14" s="235"/>
+      <c r="J14" s="235"/>
+      <c r="K14" s="235" t="s">
         <v>399</v>
       </c>
-      <c r="E14" s="238"/>
-      <c r="F14" s="238"/>
-      <c r="G14" s="238"/>
-      <c r="H14" s="238"/>
-      <c r="I14" s="238"/>
-      <c r="J14" s="238"/>
-      <c r="K14" s="238" t="s">
+      <c r="L14" s="235" t="s">
         <v>400</v>
-      </c>
-      <c r="L14" s="238" t="s">
-        <v>401</v>
       </c>
       <c r="N14">
         <v>2</v>
@@ -9920,43 +10952,43 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="P14" s="239" t="s">
+      <c r="P14" s="236" t="s">
+        <v>507</v>
+      </c>
+      <c r="Q14" s="236" t="s">
         <v>508</v>
       </c>
-      <c r="Q14" s="239" t="s">
-        <v>509</v>
-      </c>
-      <c r="R14" s="239" t="str">
+      <c r="R14" s="236" t="str">
         <f t="shared" si="1"/>
         <v>in([12357])</v>
       </c>
-      <c r="S14" s="239" t="str">
+      <c r="S14" s="236" t="str">
         <f t="shared" si="2"/>
         <v>iN$1</v>
       </c>
-      <c r="T14" s="239" t="str">
+      <c r="T14" s="236" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    - derive/in([12357])/iN$1/    # iN入 = in[48]</v>
       </c>
     </row>
     <row r="15" spans="2:20" ht="24" thickBot="1">
-      <c r="B15" s="237" t="s">
+      <c r="B15" s="234" t="s">
+        <v>401</v>
+      </c>
+      <c r="C15" s="235" t="s">
         <v>402</v>
       </c>
-      <c r="C15" s="238" t="s">
+      <c r="D15" s="235"/>
+      <c r="E15" s="235"/>
+      <c r="F15" s="235"/>
+      <c r="G15" s="235"/>
+      <c r="H15" s="235"/>
+      <c r="I15" s="235"/>
+      <c r="J15" s="235"/>
+      <c r="K15" s="235" t="s">
         <v>403</v>
       </c>
-      <c r="D15" s="238"/>
-      <c r="E15" s="238"/>
-      <c r="F15" s="238"/>
-      <c r="G15" s="238"/>
-      <c r="H15" s="238"/>
-      <c r="I15" s="238"/>
-      <c r="J15" s="238"/>
-      <c r="K15" s="238" t="s">
-        <v>404</v>
-      </c>
-      <c r="L15" s="238"/>
+      <c r="L15" s="235"/>
       <c r="N15">
         <v>2</v>
       </c>
@@ -9964,43 +10996,43 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="P15" s="239" t="s">
-        <v>480</v>
-      </c>
-      <c r="Q15" s="239" t="s">
-        <v>498</v>
-      </c>
-      <c r="R15" s="239" t="str">
+      <c r="P15" s="236" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q15" s="236" t="s">
+        <v>497</v>
+      </c>
+      <c r="R15" s="236" t="str">
         <f t="shared" si="1"/>
         <v>un([12357])</v>
       </c>
-      <c r="S15" s="239" t="str">
+      <c r="S15" s="236" t="str">
         <f t="shared" si="2"/>
         <v>uN$1</v>
       </c>
-      <c r="T15" s="239" t="str">
+      <c r="T15" s="236" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    - derive/un([12357])/uN$1/    # uN入 = un[48]</v>
       </c>
     </row>
     <row r="16" spans="2:20" ht="24" thickBot="1">
-      <c r="B16" s="237" t="s">
+      <c r="B16" s="234" t="s">
+        <v>404</v>
+      </c>
+      <c r="C16" s="235" t="s">
+        <v>194</v>
+      </c>
+      <c r="D16" s="235"/>
+      <c r="E16" s="235"/>
+      <c r="F16" s="235"/>
+      <c r="G16" s="235"/>
+      <c r="H16" s="235"/>
+      <c r="I16" s="235"/>
+      <c r="J16" s="235"/>
+      <c r="K16" s="235" t="s">
         <v>405</v>
       </c>
-      <c r="C16" s="238" t="s">
-        <v>194</v>
-      </c>
-      <c r="D16" s="238"/>
-      <c r="E16" s="238"/>
-      <c r="F16" s="238"/>
-      <c r="G16" s="238"/>
-      <c r="H16" s="238"/>
-      <c r="I16" s="238"/>
-      <c r="J16" s="238"/>
-      <c r="K16" s="238" t="s">
-        <v>406</v>
-      </c>
-      <c r="L16" s="238"/>
+      <c r="L16" s="235"/>
       <c r="N16">
         <v>3</v>
       </c>
@@ -10008,54 +11040,54 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P16" s="239" t="s">
-        <v>469</v>
-      </c>
-      <c r="Q16" s="239" t="s">
-        <v>502</v>
-      </c>
-      <c r="R16" s="239" t="str">
+      <c r="P16" s="236" t="s">
+        <v>468</v>
+      </c>
+      <c r="Q16" s="236" t="s">
+        <v>501</v>
+      </c>
+      <c r="R16" s="236" t="str">
         <f t="shared" si="1"/>
         <v>iam([12357])</v>
       </c>
-      <c r="S16" s="239" t="str">
+      <c r="S16" s="236" t="str">
         <f t="shared" si="2"/>
         <v>iaM$1</v>
       </c>
-      <c r="T16" s="239" t="str">
+      <c r="T16" s="236" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    - derive/iam([12357])/iaM$1/    # iaM入 = iam[48]</v>
       </c>
     </row>
     <row r="17" spans="2:21" ht="24" thickBot="1">
-      <c r="B17" s="237" t="s">
+      <c r="B17" s="234" t="s">
+        <v>406</v>
+      </c>
+      <c r="C17" s="235" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="235" t="s">
         <v>407</v>
       </c>
-      <c r="C17" s="238" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" s="238" t="s">
+      <c r="E17" s="235" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="235"/>
+      <c r="G17" s="235" t="s">
+        <v>109</v>
+      </c>
+      <c r="H17" s="235" t="s">
         <v>408</v>
       </c>
-      <c r="E17" s="238" t="s">
-        <v>92</v>
-      </c>
-      <c r="F17" s="238"/>
-      <c r="G17" s="238" t="s">
-        <v>109</v>
-      </c>
-      <c r="H17" s="238" t="s">
+      <c r="I17" s="235"/>
+      <c r="J17" s="235" t="s">
         <v>409</v>
       </c>
-      <c r="I17" s="238"/>
-      <c r="J17" s="238" t="s">
+      <c r="K17" s="235" t="s">
         <v>410</v>
       </c>
-      <c r="K17" s="238" t="s">
+      <c r="L17" s="235" t="s">
         <v>411</v>
-      </c>
-      <c r="L17" s="238" t="s">
-        <v>412</v>
       </c>
       <c r="N17">
         <v>3</v>
@@ -10064,55 +11096,55 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P17" s="239" t="s">
-        <v>478</v>
-      </c>
-      <c r="Q17" s="239" t="s">
-        <v>504</v>
-      </c>
-      <c r="R17" s="239" t="str">
+      <c r="P17" s="236" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q17" s="236" t="s">
+        <v>503</v>
+      </c>
+      <c r="R17" s="236" t="str">
         <f t="shared" si="1"/>
         <v>irm([12357])</v>
       </c>
-      <c r="S17" s="239" t="str">
+      <c r="S17" s="236" t="str">
         <f t="shared" si="2"/>
         <v>irM$1</v>
       </c>
-      <c r="T17" s="239" t="str">
+      <c r="T17" s="236" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    - derive/irm([12357])/irM$1/    # irM入 = irm[48]</v>
       </c>
     </row>
     <row r="18" spans="2:21" ht="24" thickBot="1">
-      <c r="B18" s="237" t="s">
+      <c r="B18" s="234" t="s">
+        <v>412</v>
+      </c>
+      <c r="C18" s="235" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="235"/>
+      <c r="E18" s="235" t="s">
         <v>413</v>
       </c>
-      <c r="C18" s="238" t="s">
-        <v>126</v>
-      </c>
-      <c r="D18" s="238"/>
-      <c r="E18" s="238" t="s">
+      <c r="F18" s="235" t="s">
         <v>414</v>
       </c>
-      <c r="F18" s="238" t="s">
+      <c r="G18" s="235" t="s">
         <v>415</v>
       </c>
-      <c r="G18" s="238" t="s">
+      <c r="H18" s="235" t="s">
         <v>416</v>
       </c>
-      <c r="H18" s="238" t="s">
+      <c r="I18" s="235" t="s">
         <v>417</v>
       </c>
-      <c r="I18" s="238" t="s">
+      <c r="J18" s="235" t="s">
         <v>418</v>
       </c>
-      <c r="J18" s="238" t="s">
+      <c r="K18" s="235" t="s">
         <v>419</v>
       </c>
-      <c r="K18" s="238" t="s">
-        <v>420</v>
-      </c>
-      <c r="L18" s="238"/>
+      <c r="L18" s="235"/>
       <c r="N18">
         <v>3</v>
       </c>
@@ -10120,47 +11152,47 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="P18" s="239" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q18" s="239" t="s">
-        <v>500</v>
-      </c>
-      <c r="R18" s="239" t="str">
+      <c r="P18" s="236" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q18" s="236" t="s">
+        <v>499</v>
+      </c>
+      <c r="R18" s="236" t="str">
         <f t="shared" si="1"/>
         <v>am([12357])</v>
       </c>
-      <c r="S18" s="239" t="str">
+      <c r="S18" s="236" t="str">
         <f t="shared" si="2"/>
         <v>aM$1</v>
       </c>
-      <c r="T18" s="239" t="str">
+      <c r="T18" s="236" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    - derive/am([12357])/aM$1/    # aM入 = am[48]</v>
       </c>
     </row>
     <row r="19" spans="2:21" ht="24" thickBot="1">
-      <c r="B19" s="237" t="s">
+      <c r="B19" s="234" t="s">
+        <v>420</v>
+      </c>
+      <c r="C19" s="235" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="235"/>
+      <c r="E19" s="235"/>
+      <c r="F19" s="235" t="s">
         <v>421</v>
       </c>
-      <c r="C19" s="238" t="s">
-        <v>142</v>
-      </c>
-      <c r="D19" s="238"/>
-      <c r="E19" s="238"/>
-      <c r="F19" s="238" t="s">
+      <c r="G19" s="235"/>
+      <c r="H19" s="235"/>
+      <c r="I19" s="235" t="s">
         <v>422</v>
       </c>
-      <c r="G19" s="238"/>
-      <c r="H19" s="238"/>
-      <c r="I19" s="238" t="s">
+      <c r="J19" s="235"/>
+      <c r="K19" s="235" t="s">
         <v>423</v>
       </c>
-      <c r="J19" s="238"/>
-      <c r="K19" s="238" t="s">
-        <v>424</v>
-      </c>
-      <c r="L19" s="238"/>
+      <c r="L19" s="235"/>
       <c r="N19">
         <v>3</v>
       </c>
@@ -10168,51 +11200,51 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="P19" s="239" t="s">
-        <v>463</v>
-      </c>
-      <c r="Q19" s="239" t="s">
-        <v>501</v>
-      </c>
-      <c r="R19" s="239" t="str">
+      <c r="P19" s="236" t="s">
+        <v>462</v>
+      </c>
+      <c r="Q19" s="236" t="s">
+        <v>500</v>
+      </c>
+      <c r="R19" s="236" t="str">
         <f t="shared" si="1"/>
         <v>im([12357])</v>
       </c>
-      <c r="S19" s="239" t="str">
+      <c r="S19" s="236" t="str">
         <f t="shared" si="2"/>
         <v>iM$1</v>
       </c>
-      <c r="T19" s="239" t="str">
+      <c r="T19" s="236" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    - derive/im([12357])/iM$1/    # iM入 = im[48]</v>
       </c>
     </row>
     <row r="20" spans="2:21" ht="24" thickBot="1">
-      <c r="B20" s="237" t="s">
+      <c r="B20" s="234" t="s">
+        <v>424</v>
+      </c>
+      <c r="C20" s="235" t="s">
         <v>425</v>
       </c>
-      <c r="C20" s="238" t="s">
+      <c r="D20" s="235" t="s">
         <v>426</v>
       </c>
-      <c r="D20" s="238" t="s">
+      <c r="E20" s="235"/>
+      <c r="F20" s="235" t="s">
         <v>427</v>
       </c>
-      <c r="E20" s="238"/>
-      <c r="F20" s="238" t="s">
+      <c r="G20" s="235" t="s">
         <v>428</v>
       </c>
-      <c r="G20" s="238" t="s">
+      <c r="H20" s="235"/>
+      <c r="I20" s="235" t="s">
         <v>429</v>
       </c>
-      <c r="H20" s="238"/>
-      <c r="I20" s="238" t="s">
+      <c r="J20" s="235"/>
+      <c r="K20" s="235" t="s">
         <v>430</v>
       </c>
-      <c r="J20" s="238"/>
-      <c r="K20" s="238" t="s">
-        <v>431</v>
-      </c>
-      <c r="L20" s="238"/>
+      <c r="L20" s="235"/>
       <c r="N20">
         <v>3</v>
       </c>
@@ -10220,213 +11252,213 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="P20" s="239" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q20" s="239" t="s">
-        <v>503</v>
-      </c>
-      <c r="R20" s="239" t="str">
+      <c r="P20" s="236" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q20" s="236" t="s">
+        <v>502</v>
+      </c>
+      <c r="R20" s="236" t="str">
         <f t="shared" si="1"/>
         <v>om([12357])</v>
       </c>
-      <c r="S20" s="239" t="str">
+      <c r="S20" s="236" t="str">
         <f t="shared" si="2"/>
         <v>oM$1</v>
       </c>
-      <c r="T20" s="239" t="str">
+      <c r="T20" s="236" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    - derive/om([12357])/oM$1/    # oM入 = om[48]</v>
       </c>
     </row>
     <row r="21" spans="2:21" ht="24" thickBot="1">
-      <c r="B21" s="237" t="s">
+      <c r="B21" s="234" t="s">
+        <v>431</v>
+      </c>
+      <c r="C21" s="235" t="s">
         <v>432</v>
       </c>
-      <c r="C21" s="238" t="s">
+      <c r="D21" s="235" t="s">
         <v>433</v>
       </c>
-      <c r="D21" s="238" t="s">
-        <v>434</v>
-      </c>
-      <c r="E21" s="238"/>
-      <c r="F21" s="238"/>
-      <c r="G21" s="238"/>
-      <c r="H21" s="238"/>
-      <c r="I21" s="238"/>
-      <c r="J21" s="238"/>
-      <c r="K21" s="238"/>
-      <c r="L21" s="238"/>
+      <c r="E21" s="235"/>
+      <c r="F21" s="235"/>
+      <c r="G21" s="235"/>
+      <c r="H21" s="235"/>
+      <c r="I21" s="235"/>
+      <c r="J21" s="235"/>
+      <c r="K21" s="235"/>
+      <c r="L21" s="235"/>
     </row>
     <row r="22" spans="2:21" ht="24" thickBot="1">
-      <c r="B22" s="237" t="s">
+      <c r="B22" s="234" t="s">
+        <v>434</v>
+      </c>
+      <c r="C22" s="235" t="s">
         <v>435</v>
       </c>
-      <c r="C22" s="238" t="s">
+      <c r="D22" s="235"/>
+      <c r="E22" s="235"/>
+      <c r="F22" s="235"/>
+      <c r="G22" s="235"/>
+      <c r="H22" s="235"/>
+      <c r="I22" s="235"/>
+      <c r="J22" s="235"/>
+      <c r="K22" s="235" t="s">
         <v>436</v>
       </c>
-      <c r="D22" s="238"/>
-      <c r="E22" s="238"/>
-      <c r="F22" s="238"/>
-      <c r="G22" s="238"/>
-      <c r="H22" s="238"/>
-      <c r="I22" s="238"/>
-      <c r="J22" s="238"/>
-      <c r="K22" s="238" t="s">
-        <v>437</v>
-      </c>
-      <c r="L22" s="238"/>
-      <c r="P22" s="240" t="s">
-        <v>457</v>
-      </c>
-      <c r="Q22" s="240" t="s">
-        <v>494</v>
-      </c>
-      <c r="R22" s="240" t="str">
+      <c r="L22" s="235"/>
+      <c r="P22" s="237" t="s">
+        <v>456</v>
+      </c>
+      <c r="Q22" s="237" t="s">
+        <v>493</v>
+      </c>
+      <c r="R22" s="237" t="str">
         <f>_xlfn.CONCAT(Q22,$R$3)</f>
         <v>eG([12357])</v>
       </c>
-      <c r="S22" s="240" t="str">
+      <c r="S22" s="237" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(P22,$S$3)</f>
         <v>ek$1</v>
       </c>
-      <c r="T22" s="240" t="str">
+      <c r="T22" s="237" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - xform/", S22, "/", R22, "/    # " &amp; Q22, "入 = ", P22, "[48]")</f>
         <v xml:space="preserve">    - xform/ek$1/eG([12357])/    # eG入 = ek[48]</v>
       </c>
     </row>
     <row r="23" spans="2:21" ht="24" thickBot="1">
-      <c r="B23" s="237" t="s">
+      <c r="B23" s="234" t="s">
+        <v>437</v>
+      </c>
+      <c r="C23" s="235" t="s">
         <v>438</v>
       </c>
-      <c r="C23" s="238" t="s">
+      <c r="D23" s="235"/>
+      <c r="E23" s="235"/>
+      <c r="F23" s="235"/>
+      <c r="G23" s="235"/>
+      <c r="H23" s="235"/>
+      <c r="I23" s="235"/>
+      <c r="J23" s="235"/>
+      <c r="K23" s="235" t="s">
         <v>439</v>
       </c>
-      <c r="D23" s="238"/>
-      <c r="E23" s="238"/>
-      <c r="F23" s="238"/>
-      <c r="G23" s="238"/>
-      <c r="H23" s="238"/>
-      <c r="I23" s="238"/>
-      <c r="J23" s="238"/>
-      <c r="K23" s="238" t="s">
-        <v>440</v>
-      </c>
-      <c r="L23" s="238"/>
-      <c r="P23" s="241" t="s">
-        <v>484</v>
-      </c>
-      <c r="Q23" s="239" t="s">
-        <v>495</v>
-      </c>
-      <c r="R23" s="239" t="str">
+      <c r="L23" s="235"/>
+      <c r="P23" s="238" t="s">
+        <v>483</v>
+      </c>
+      <c r="Q23" s="236" t="s">
+        <v>494</v>
+      </c>
+      <c r="R23" s="236" t="str">
         <f>_xlfn.CONCAT(Q23,$R$3)</f>
         <v>uaG([12357])</v>
       </c>
-      <c r="S23" s="239" t="str">
+      <c r="S23" s="236" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(P23,$S$3)</f>
         <v>uak$1</v>
       </c>
-      <c r="T23" s="239" t="str">
+      <c r="T23" s="236" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - xform/", S23, "/", R23, "/    # " &amp; Q23, "入 = ", P23, "[48]")</f>
         <v xml:space="preserve">    - xform/uak$1/uaG([12357])/    # uaG入 = uak[48]</v>
       </c>
-      <c r="U23" s="240"/>
+      <c r="U23" s="237"/>
     </row>
     <row r="24" spans="2:21" ht="24" thickBot="1">
-      <c r="B24" s="237" t="s">
+      <c r="B24" s="234" t="s">
+        <v>440</v>
+      </c>
+      <c r="C24" s="235" t="s">
         <v>441</v>
       </c>
-      <c r="C24" s="238" t="s">
-        <v>442</v>
-      </c>
-      <c r="D24" s="238"/>
-      <c r="E24" s="238"/>
-      <c r="F24" s="238"/>
-      <c r="G24" s="238"/>
-      <c r="H24" s="238"/>
-      <c r="I24" s="238"/>
-      <c r="J24" s="238"/>
-      <c r="K24" s="238"/>
-      <c r="L24" s="238"/>
+      <c r="D24" s="235"/>
+      <c r="E24" s="235"/>
+      <c r="F24" s="235"/>
+      <c r="G24" s="235"/>
+      <c r="H24" s="235"/>
+      <c r="I24" s="235"/>
+      <c r="J24" s="235"/>
+      <c r="K24" s="235"/>
+      <c r="L24" s="235"/>
     </row>
     <row r="25" spans="2:21" ht="24" thickBot="1">
-      <c r="B25" s="237" t="s">
+      <c r="B25" s="234" t="s">
+        <v>442</v>
+      </c>
+      <c r="C25" s="235"/>
+      <c r="D25" s="235" t="s">
         <v>443</v>
       </c>
-      <c r="C25" s="238"/>
-      <c r="D25" s="238" t="s">
-        <v>444</v>
-      </c>
-      <c r="E25" s="238"/>
-      <c r="F25" s="238"/>
-      <c r="G25" s="238"/>
-      <c r="H25" s="238"/>
-      <c r="I25" s="238"/>
-      <c r="J25" s="238"/>
-      <c r="K25" s="238"/>
-      <c r="L25" s="238"/>
+      <c r="E25" s="235"/>
+      <c r="F25" s="235"/>
+      <c r="G25" s="235"/>
+      <c r="H25" s="235"/>
+      <c r="I25" s="235"/>
+      <c r="J25" s="235"/>
+      <c r="K25" s="235"/>
+      <c r="L25" s="235"/>
     </row>
     <row r="26" spans="2:21" ht="24" thickBot="1">
-      <c r="B26" s="237" t="s">
+      <c r="B26" s="234" t="s">
+        <v>444</v>
+      </c>
+      <c r="C26" s="235" t="s">
         <v>445</v>
       </c>
-      <c r="C26" s="238" t="s">
+      <c r="D26" s="235"/>
+      <c r="E26" s="235"/>
+      <c r="F26" s="235"/>
+      <c r="G26" s="235"/>
+      <c r="H26" s="235"/>
+      <c r="I26" s="235"/>
+      <c r="J26" s="235"/>
+      <c r="K26" s="235" t="s">
         <v>446</v>
       </c>
-      <c r="D26" s="238"/>
-      <c r="E26" s="238"/>
-      <c r="F26" s="238"/>
-      <c r="G26" s="238"/>
-      <c r="H26" s="238"/>
-      <c r="I26" s="238"/>
-      <c r="J26" s="238"/>
-      <c r="K26" s="238" t="s">
-        <v>447</v>
-      </c>
-      <c r="L26" s="238"/>
+      <c r="L26" s="235"/>
     </row>
     <row r="27" spans="2:21" ht="24" thickBot="1">
-      <c r="B27" s="237" t="s">
+      <c r="B27" s="234" t="s">
+        <v>447</v>
+      </c>
+      <c r="C27" s="253" t="s">
+        <v>192</v>
+      </c>
+      <c r="D27" s="254"/>
+      <c r="E27" s="253" t="s">
         <v>448</v>
       </c>
-      <c r="C27" s="245" t="s">
-        <v>192</v>
-      </c>
-      <c r="D27" s="246"/>
-      <c r="E27" s="245" t="s">
+      <c r="F27" s="255"/>
+      <c r="G27" s="255"/>
+      <c r="H27" s="255"/>
+      <c r="I27" s="255"/>
+      <c r="J27" s="254"/>
+      <c r="K27" s="253" t="s">
         <v>449</v>
       </c>
-      <c r="F27" s="247"/>
-      <c r="G27" s="247"/>
-      <c r="H27" s="247"/>
-      <c r="I27" s="247"/>
-      <c r="J27" s="246"/>
-      <c r="K27" s="245" t="s">
-        <v>450</v>
-      </c>
-      <c r="L27" s="246"/>
+      <c r="L27" s="254"/>
     </row>
     <row r="28" spans="2:21" ht="24" thickBot="1">
-      <c r="B28" s="237" t="s">
+      <c r="B28" s="234" t="s">
+        <v>450</v>
+      </c>
+      <c r="C28" s="253" t="s">
         <v>451</v>
       </c>
-      <c r="C28" s="245" t="s">
+      <c r="D28" s="254"/>
+      <c r="E28" s="253" t="s">
+        <v>448</v>
+      </c>
+      <c r="F28" s="255"/>
+      <c r="G28" s="255"/>
+      <c r="H28" s="255"/>
+      <c r="I28" s="255"/>
+      <c r="J28" s="254"/>
+      <c r="K28" s="253" t="s">
         <v>452</v>
       </c>
-      <c r="D28" s="246"/>
-      <c r="E28" s="245" t="s">
-        <v>449</v>
-      </c>
-      <c r="F28" s="247"/>
-      <c r="G28" s="247"/>
-      <c r="H28" s="247"/>
-      <c r="I28" s="247"/>
-      <c r="J28" s="246"/>
-      <c r="K28" s="245" t="s">
-        <v>453</v>
-      </c>
-      <c r="L28" s="246"/>
+      <c r="L28" s="254"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N4:T20">
@@ -10454,998 +11486,998 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ED0EFA4-32E9-4AEC-A6ED-2DBF7A08ED31}">
   <dimension ref="B1:X28"/>
-  <sheetFormatPr defaultRowHeight="21.75"/>
+  <sheetFormatPr defaultRowHeight="21"/>
   <cols>
     <col min="1" max="1" width="2.8984375" customWidth="1"/>
-    <col min="14" max="15" width="6.8984375" style="239" customWidth="1"/>
-    <col min="16" max="17" width="13.09765625" style="239" customWidth="1"/>
-    <col min="18" max="18" width="47.296875" style="239" customWidth="1"/>
-    <col min="19" max="24" width="8.796875" style="239"/>
+    <col min="14" max="15" width="6.8984375" style="236" customWidth="1"/>
+    <col min="16" max="17" width="13.09765625" style="236" customWidth="1"/>
+    <col min="18" max="18" width="47.296875" style="236" customWidth="1"/>
+    <col min="19" max="24" width="8.796875" style="236"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="22.5" thickBot="1"/>
+    <row r="1" spans="2:18" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:18" ht="24" thickBot="1">
-      <c r="B2" s="248" t="s">
+      <c r="B2" s="244" t="s">
+        <v>332</v>
+      </c>
+      <c r="C2" s="246" t="s">
         <v>333</v>
       </c>
-      <c r="C2" s="250" t="s">
+      <c r="D2" s="247"/>
+      <c r="E2" s="250" t="s">
         <v>334</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="254" t="s">
+      <c r="F2" s="251"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="250" t="s">
         <v>335</v>
       </c>
-      <c r="F2" s="255"/>
-      <c r="G2" s="256"/>
-      <c r="H2" s="254" t="s">
-        <v>336</v>
-      </c>
-      <c r="I2" s="255"/>
-      <c r="J2" s="255"/>
-      <c r="K2" s="255"/>
-      <c r="L2" s="256"/>
-      <c r="P2" s="239" t="str">
+      <c r="I2" s="251"/>
+      <c r="J2" s="251"/>
+      <c r="K2" s="251"/>
+      <c r="L2" s="252"/>
+      <c r="P2" s="236" t="str">
         <f xml:space="preserve"> "([48])"</f>
         <v>([48])</v>
       </c>
-      <c r="Q2" s="239">
+      <c r="Q2" s="236">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="2:18" ht="24" thickBot="1">
-      <c r="B3" s="249"/>
-      <c r="C3" s="252"/>
-      <c r="D3" s="253"/>
-      <c r="E3" s="237" t="s">
+      <c r="B3" s="245"/>
+      <c r="C3" s="248"/>
+      <c r="D3" s="249"/>
+      <c r="E3" s="234" t="s">
+        <v>336</v>
+      </c>
+      <c r="F3" s="234" t="s">
         <v>337</v>
       </c>
-      <c r="F3" s="237" t="s">
+      <c r="G3" s="234" t="s">
         <v>338</v>
       </c>
-      <c r="G3" s="237" t="s">
+      <c r="H3" s="234" t="s">
         <v>339</v>
       </c>
-      <c r="H3" s="237" t="s">
+      <c r="I3" s="234" t="s">
         <v>340</v>
       </c>
-      <c r="I3" s="237" t="s">
+      <c r="J3" s="234" t="s">
         <v>341</v>
       </c>
-      <c r="J3" s="237" t="s">
+      <c r="K3" s="250" t="s">
         <v>342</v>
       </c>
-      <c r="K3" s="254" t="s">
-        <v>343</v>
-      </c>
-      <c r="L3" s="256"/>
-      <c r="N3" s="239" t="s">
-        <v>455</v>
-      </c>
-      <c r="O3" s="239" t="s">
-        <v>279</v>
-      </c>
-      <c r="P3" s="239" t="str">
+      <c r="L3" s="252"/>
+      <c r="N3" s="236" t="s">
+        <v>454</v>
+      </c>
+      <c r="O3" s="236" t="s">
+        <v>278</v>
+      </c>
+      <c r="P3" s="236" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(N3,$P$2)</f>
         <v>ak([48])</v>
       </c>
-      <c r="Q3" s="239" t="str">
+      <c r="Q3" s="236" t="str">
         <f>_xlfn.CONCAT(O3,$Q$2)</f>
         <v>ang0</v>
       </c>
-      <c r="R3" s="239" t="str">
+      <c r="R3" s="236" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - derive/", P3, "/", Q3, "/    # " &amp; O3, "入 = ", N3, "[48]")</f>
         <v xml:space="preserve">    - derive/ak([48])/ang0/    # ang入 = ak[48]</v>
       </c>
     </row>
     <row r="4" spans="2:18" ht="24" thickBot="1">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="234" t="s">
+        <v>343</v>
+      </c>
+      <c r="C4" s="235" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="235" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="235" t="s">
+        <v>162</v>
+      </c>
+      <c r="F4" s="235" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="235" t="s">
+        <v>148</v>
+      </c>
+      <c r="H4" s="235" t="s">
         <v>344</v>
       </c>
-      <c r="C4" s="238" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="238" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="238" t="s">
-        <v>162</v>
-      </c>
-      <c r="F4" s="238" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" s="238" t="s">
-        <v>148</v>
-      </c>
-      <c r="H4" s="238" t="s">
+      <c r="I4" s="235" t="s">
         <v>345</v>
       </c>
-      <c r="I4" s="238" t="s">
+      <c r="J4" s="235" t="s">
         <v>346</v>
       </c>
-      <c r="J4" s="238" t="s">
+      <c r="K4" s="235" t="s">
         <v>347</v>
       </c>
-      <c r="K4" s="238" t="s">
+      <c r="L4" s="235" t="s">
         <v>348</v>
       </c>
-      <c r="L4" s="238" t="s">
-        <v>349</v>
-      </c>
-      <c r="N4" s="239" t="s">
-        <v>456</v>
-      </c>
-      <c r="O4" s="239" t="s">
-        <v>278</v>
-      </c>
-      <c r="P4" s="239" t="str">
+      <c r="N4" s="236" t="s">
+        <v>455</v>
+      </c>
+      <c r="O4" s="236" t="s">
+        <v>277</v>
+      </c>
+      <c r="P4" s="236" t="str">
         <f t="shared" ref="P4:P19" si="0" xml:space="preserve"> _xlfn.CONCAT(N4,$P$2)</f>
         <v>at([48])</v>
       </c>
-      <c r="Q4" s="239" t="str">
+      <c r="Q4" s="236" t="str">
         <f t="shared" ref="Q4:Q19" si="1">_xlfn.CONCAT(O4,$Q$2)</f>
         <v>an0</v>
       </c>
-      <c r="R4" s="239" t="str">
+      <c r="R4" s="236" t="str">
         <f t="shared" ref="R4:R19" si="2" xml:space="preserve"> _xlfn.CONCAT("    - derive/", P4, "/", Q4, "/    # " &amp; O4, "入 = ", N4, "[48]")</f>
         <v xml:space="preserve">    - derive/at([48])/an0/    # an入 = at[48]</v>
       </c>
     </row>
     <row r="5" spans="2:18" ht="24" thickBot="1">
-      <c r="B5" s="237" t="s">
+      <c r="B5" s="234" t="s">
+        <v>349</v>
+      </c>
+      <c r="C5" s="235" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="235" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="235"/>
+      <c r="F5" s="235"/>
+      <c r="G5" s="235"/>
+      <c r="H5" s="235"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="235"/>
+      <c r="K5" s="235" t="s">
         <v>350</v>
       </c>
-      <c r="C5" s="238" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="238" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="238"/>
-      <c r="F5" s="238"/>
-      <c r="G5" s="238"/>
-      <c r="H5" s="238"/>
-      <c r="I5" s="238"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="238" t="s">
+      <c r="L5" s="235" t="s">
         <v>351</v>
       </c>
-      <c r="L5" s="238" t="s">
-        <v>352</v>
-      </c>
-      <c r="N5" s="239" t="s">
-        <v>454</v>
-      </c>
-      <c r="O5" s="239" t="s">
-        <v>277</v>
-      </c>
-      <c r="P5" s="239" t="str">
+      <c r="N5" s="236" t="s">
+        <v>453</v>
+      </c>
+      <c r="O5" s="236" t="s">
+        <v>276</v>
+      </c>
+      <c r="P5" s="236" t="str">
         <f t="shared" si="0"/>
         <v>ap([48])</v>
       </c>
-      <c r="Q5" s="239" t="str">
+      <c r="Q5" s="236" t="str">
         <f t="shared" si="1"/>
         <v>am0</v>
       </c>
-      <c r="R5" s="239" t="str">
+      <c r="R5" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/ap([48])/am0/    # am入 = ap[48]</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="24" thickBot="1">
-      <c r="B6" s="237" t="s">
+      <c r="B6" s="234" t="s">
+        <v>352</v>
+      </c>
+      <c r="C6" s="235" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="235"/>
+      <c r="E6" s="235"/>
+      <c r="F6" s="235"/>
+      <c r="G6" s="235"/>
+      <c r="H6" s="235"/>
+      <c r="I6" s="235"/>
+      <c r="J6" s="235"/>
+      <c r="K6" s="235" t="s">
         <v>353</v>
       </c>
-      <c r="C6" s="238" t="s">
-        <v>146</v>
-      </c>
-      <c r="D6" s="238"/>
-      <c r="E6" s="238"/>
-      <c r="F6" s="238"/>
-      <c r="G6" s="238"/>
-      <c r="H6" s="238"/>
-      <c r="I6" s="238"/>
-      <c r="J6" s="238"/>
-      <c r="K6" s="238" t="s">
+      <c r="L6" s="235" t="s">
         <v>354</v>
       </c>
-      <c r="L6" s="238" t="s">
-        <v>355</v>
-      </c>
-      <c r="N6" s="239" t="s">
-        <v>459</v>
-      </c>
-      <c r="O6" s="239" t="s">
-        <v>462</v>
-      </c>
-      <c r="P6" s="239" t="str">
+      <c r="N6" s="236" t="s">
+        <v>458</v>
+      </c>
+      <c r="O6" s="236" t="s">
+        <v>461</v>
+      </c>
+      <c r="P6" s="236" t="str">
         <f t="shared" si="0"/>
         <v>ik([48])</v>
       </c>
-      <c r="Q6" s="239" t="str">
+      <c r="Q6" s="236" t="str">
         <f t="shared" si="1"/>
         <v>ing0</v>
       </c>
-      <c r="R6" s="239" t="str">
+      <c r="R6" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/ik([48])/ing0/    # ing入 = ik[48]</v>
       </c>
     </row>
     <row r="7" spans="2:18" ht="24" thickBot="1">
-      <c r="B7" s="237" t="s">
+      <c r="B7" s="234" t="s">
+        <v>355</v>
+      </c>
+      <c r="C7" s="235" t="s">
         <v>356</v>
       </c>
-      <c r="C7" s="238" t="s">
+      <c r="D7" s="235"/>
+      <c r="E7" s="235"/>
+      <c r="F7" s="235"/>
+      <c r="G7" s="235" t="s">
         <v>357</v>
       </c>
-      <c r="D7" s="238"/>
-      <c r="E7" s="238"/>
-      <c r="F7" s="238"/>
-      <c r="G7" s="238" t="s">
+      <c r="H7" s="235"/>
+      <c r="I7" s="235"/>
+      <c r="J7" s="235" t="s">
         <v>358</v>
       </c>
-      <c r="H7" s="238"/>
-      <c r="I7" s="238"/>
-      <c r="J7" s="238" t="s">
+      <c r="K7" s="235" t="s">
         <v>359</v>
       </c>
-      <c r="K7" s="238" t="s">
-        <v>360</v>
-      </c>
-      <c r="L7" s="238"/>
-      <c r="N7" s="239" t="s">
-        <v>460</v>
-      </c>
-      <c r="O7" s="239" t="s">
-        <v>462</v>
-      </c>
-      <c r="P7" s="239" t="str">
+      <c r="L7" s="235"/>
+      <c r="N7" s="236" t="s">
+        <v>459</v>
+      </c>
+      <c r="O7" s="236" t="s">
+        <v>461</v>
+      </c>
+      <c r="P7" s="236" t="str">
         <f t="shared" si="0"/>
         <v>it([48])</v>
       </c>
-      <c r="Q7" s="239" t="str">
+      <c r="Q7" s="236" t="str">
         <f t="shared" si="1"/>
         <v>ing0</v>
       </c>
-      <c r="R7" s="239" t="str">
+      <c r="R7" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/it([48])/ing0/    # ing入 = it[48]</v>
       </c>
     </row>
     <row r="8" spans="2:18" ht="24" thickBot="1">
-      <c r="B8" s="237" t="s">
+      <c r="B8" s="234" t="s">
+        <v>360</v>
+      </c>
+      <c r="C8" s="235" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="235" t="s">
+        <v>164</v>
+      </c>
+      <c r="E8" s="235"/>
+      <c r="F8" s="235"/>
+      <c r="G8" s="235"/>
+      <c r="H8" s="235"/>
+      <c r="I8" s="235"/>
+      <c r="J8" s="235"/>
+      <c r="K8" s="235" t="s">
         <v>361</v>
       </c>
-      <c r="C8" s="238" t="s">
-        <v>183</v>
-      </c>
-      <c r="D8" s="238" t="s">
-        <v>164</v>
-      </c>
-      <c r="E8" s="238"/>
-      <c r="F8" s="238"/>
-      <c r="G8" s="238"/>
-      <c r="H8" s="238"/>
-      <c r="I8" s="238"/>
-      <c r="J8" s="238"/>
-      <c r="K8" s="238" t="s">
+      <c r="L8" s="235" t="s">
         <v>362</v>
       </c>
-      <c r="L8" s="238" t="s">
-        <v>363</v>
-      </c>
-      <c r="N8" s="239" t="s">
-        <v>461</v>
-      </c>
-      <c r="O8" s="239" t="s">
-        <v>463</v>
-      </c>
-      <c r="P8" s="239" t="str">
+      <c r="N8" s="236" t="s">
+        <v>460</v>
+      </c>
+      <c r="O8" s="236" t="s">
+        <v>462</v>
+      </c>
+      <c r="P8" s="236" t="str">
         <f t="shared" si="0"/>
         <v>ip([48])</v>
       </c>
-      <c r="Q8" s="239" t="str">
+      <c r="Q8" s="236" t="str">
         <f t="shared" si="1"/>
         <v>im0</v>
       </c>
-      <c r="R8" s="239" t="str">
+      <c r="R8" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/ip([48])/im0/    # im入 = ip[48]</v>
       </c>
     </row>
     <row r="9" spans="2:18" ht="24" thickBot="1">
-      <c r="B9" s="237" t="s">
+      <c r="B9" s="234" t="s">
+        <v>363</v>
+      </c>
+      <c r="C9" s="235" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="235" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="235" t="s">
         <v>364</v>
       </c>
-      <c r="C9" s="238" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9" s="238" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="238" t="s">
+      <c r="F9" s="235" t="s">
         <v>365</v>
       </c>
-      <c r="F9" s="238" t="s">
+      <c r="G9" s="235" t="s">
         <v>366</v>
       </c>
-      <c r="G9" s="238" t="s">
+      <c r="H9" s="235" t="s">
         <v>367</v>
       </c>
-      <c r="H9" s="238" t="s">
+      <c r="I9" s="235" t="s">
         <v>368</v>
       </c>
-      <c r="I9" s="238" t="s">
+      <c r="J9" s="235" t="s">
         <v>369</v>
       </c>
-      <c r="J9" s="238" t="s">
+      <c r="K9" s="235" t="s">
         <v>370</v>
       </c>
-      <c r="K9" s="238" t="s">
+      <c r="L9" s="235" t="s">
         <v>371</v>
       </c>
-      <c r="L9" s="238" t="s">
-        <v>372</v>
-      </c>
-      <c r="N9" s="239" t="s">
+      <c r="N9" s="236" t="s">
+        <v>463</v>
+      </c>
+      <c r="O9" s="236" t="s">
         <v>464</v>
       </c>
-      <c r="O9" s="239" t="s">
-        <v>465</v>
-      </c>
-      <c r="P9" s="239" t="str">
+      <c r="P9" s="236" t="str">
         <f t="shared" si="0"/>
         <v>iak([48])</v>
       </c>
-      <c r="Q9" s="239" t="str">
+      <c r="Q9" s="236" t="str">
         <f t="shared" si="1"/>
         <v>iang0</v>
       </c>
-      <c r="R9" s="239" t="str">
+      <c r="R9" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/iak([48])/iang0/    # iang入 = iak[48]</v>
       </c>
     </row>
     <row r="10" spans="2:18" ht="24" thickBot="1">
-      <c r="B10" s="237" t="s">
+      <c r="B10" s="234" t="s">
+        <v>372</v>
+      </c>
+      <c r="C10" s="235" t="s">
         <v>373</v>
       </c>
-      <c r="C10" s="238" t="s">
+      <c r="D10" s="235" t="s">
         <v>374</v>
       </c>
-      <c r="D10" s="238" t="s">
+      <c r="E10" s="235" t="s">
         <v>375</v>
       </c>
-      <c r="E10" s="238" t="s">
+      <c r="F10" s="235" t="s">
         <v>376</v>
       </c>
-      <c r="F10" s="238" t="s">
+      <c r="G10" s="235" t="s">
         <v>377</v>
       </c>
-      <c r="G10" s="238" t="s">
+      <c r="H10" s="235" t="s">
         <v>378</v>
       </c>
-      <c r="H10" s="238" t="s">
+      <c r="I10" s="235" t="s">
         <v>379</v>
       </c>
-      <c r="I10" s="238" t="s">
+      <c r="J10" s="235" t="s">
         <v>380</v>
       </c>
-      <c r="J10" s="238" t="s">
+      <c r="K10" s="235" t="s">
         <v>381</v>
       </c>
-      <c r="K10" s="238" t="s">
+      <c r="L10" s="235" t="s">
         <v>382</v>
       </c>
-      <c r="L10" s="238" t="s">
-        <v>383</v>
-      </c>
-      <c r="N10" s="239" t="s">
-        <v>466</v>
-      </c>
-      <c r="O10" s="239" t="s">
-        <v>468</v>
-      </c>
-      <c r="P10" s="239" t="str">
+      <c r="N10" s="236" t="s">
+        <v>465</v>
+      </c>
+      <c r="O10" s="236" t="s">
+        <v>467</v>
+      </c>
+      <c r="P10" s="236" t="str">
         <f t="shared" si="0"/>
         <v>iat([48])</v>
       </c>
-      <c r="Q10" s="239" t="str">
+      <c r="Q10" s="236" t="str">
         <f t="shared" si="1"/>
         <v>ian0</v>
       </c>
-      <c r="R10" s="239" t="str">
+      <c r="R10" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/iat([48])/ian0/    # ian入 = iat[48]</v>
       </c>
     </row>
     <row r="11" spans="2:18" ht="24" thickBot="1">
-      <c r="B11" s="237" t="s">
+      <c r="B11" s="234" t="s">
+        <v>383</v>
+      </c>
+      <c r="C11" s="235" t="s">
         <v>384</v>
       </c>
-      <c r="C11" s="238" t="s">
+      <c r="D11" s="235" t="s">
         <v>385</v>
       </c>
-      <c r="D11" s="238" t="s">
+      <c r="E11" s="235"/>
+      <c r="F11" s="235"/>
+      <c r="G11" s="235"/>
+      <c r="H11" s="235"/>
+      <c r="I11" s="235"/>
+      <c r="J11" s="235"/>
+      <c r="K11" s="235" t="s">
         <v>386</v>
       </c>
-      <c r="E11" s="238"/>
-      <c r="F11" s="238"/>
-      <c r="G11" s="238"/>
-      <c r="H11" s="238"/>
-      <c r="I11" s="238"/>
-      <c r="J11" s="238"/>
-      <c r="K11" s="238" t="s">
-        <v>387</v>
-      </c>
-      <c r="L11" s="238"/>
-      <c r="N11" s="239" t="s">
-        <v>467</v>
-      </c>
-      <c r="O11" s="239" t="s">
-        <v>469</v>
-      </c>
-      <c r="P11" s="239" t="str">
+      <c r="L11" s="235"/>
+      <c r="N11" s="236" t="s">
+        <v>466</v>
+      </c>
+      <c r="O11" s="236" t="s">
+        <v>468</v>
+      </c>
+      <c r="P11" s="236" t="str">
         <f t="shared" si="0"/>
         <v>iap([48])</v>
       </c>
-      <c r="Q11" s="239" t="str">
+      <c r="Q11" s="236" t="str">
         <f t="shared" si="1"/>
         <v>iam0</v>
       </c>
-      <c r="R11" s="239" t="str">
+      <c r="R11" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/iap([48])/iam0/    # iam入 = iap[48]</v>
       </c>
     </row>
     <row r="12" spans="2:18" ht="24" thickBot="1">
-      <c r="B12" s="237" t="s">
+      <c r="B12" s="234" t="s">
+        <v>387</v>
+      </c>
+      <c r="C12" s="235" t="s">
         <v>388</v>
       </c>
-      <c r="C12" s="238" t="s">
+      <c r="D12" s="235"/>
+      <c r="E12" s="235"/>
+      <c r="F12" s="235"/>
+      <c r="G12" s="235"/>
+      <c r="H12" s="235"/>
+      <c r="I12" s="235"/>
+      <c r="J12" s="235"/>
+      <c r="K12" s="235" t="s">
         <v>389</v>
       </c>
-      <c r="D12" s="238"/>
-      <c r="E12" s="238"/>
-      <c r="F12" s="238"/>
-      <c r="G12" s="238"/>
-      <c r="H12" s="238"/>
-      <c r="I12" s="238"/>
-      <c r="J12" s="238"/>
-      <c r="K12" s="238" t="s">
-        <v>390</v>
-      </c>
-      <c r="L12" s="238"/>
-      <c r="N12" s="239" t="s">
+      <c r="L12" s="235"/>
+      <c r="N12" s="236" t="s">
+        <v>469</v>
+      </c>
+      <c r="O12" s="236" t="s">
         <v>470</v>
       </c>
-      <c r="O12" s="239" t="s">
-        <v>471</v>
-      </c>
-      <c r="P12" s="239" t="str">
+      <c r="P12" s="236" t="str">
         <f t="shared" si="0"/>
         <v>iok([48])</v>
       </c>
-      <c r="Q12" s="239" t="str">
+      <c r="Q12" s="236" t="str">
         <f t="shared" si="1"/>
         <v>iong0</v>
       </c>
-      <c r="R12" s="239" t="str">
+      <c r="R12" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/iok([48])/iong0/    # iong入 = iok[48]</v>
       </c>
     </row>
     <row r="13" spans="2:18" ht="24" thickBot="1">
-      <c r="B13" s="237" t="s">
+      <c r="B13" s="234" t="s">
+        <v>390</v>
+      </c>
+      <c r="C13" s="235" t="s">
         <v>391</v>
       </c>
-      <c r="C13" s="238" t="s">
+      <c r="D13" s="235" t="s">
         <v>392</v>
       </c>
-      <c r="D13" s="238" t="s">
+      <c r="E13" s="235"/>
+      <c r="F13" s="235"/>
+      <c r="G13" s="235" t="s">
         <v>393</v>
       </c>
-      <c r="E13" s="238"/>
-      <c r="F13" s="238"/>
-      <c r="G13" s="238" t="s">
+      <c r="H13" s="235"/>
+      <c r="I13" s="235"/>
+      <c r="J13" s="235" t="s">
         <v>394</v>
       </c>
-      <c r="H13" s="238"/>
-      <c r="I13" s="238"/>
-      <c r="J13" s="238" t="s">
+      <c r="K13" s="235" t="s">
         <v>395</v>
       </c>
-      <c r="K13" s="238" t="s">
-        <v>396</v>
-      </c>
-      <c r="L13" s="238"/>
-      <c r="N13" s="239" t="s">
-        <v>472</v>
-      </c>
-      <c r="O13" s="239" t="s">
-        <v>281</v>
-      </c>
-      <c r="P13" s="239" t="str">
+      <c r="L13" s="235"/>
+      <c r="N13" s="236" t="s">
+        <v>471</v>
+      </c>
+      <c r="O13" s="236" t="s">
+        <v>280</v>
+      </c>
+      <c r="P13" s="236" t="str">
         <f t="shared" si="0"/>
         <v>ok([48])</v>
       </c>
-      <c r="Q13" s="239" t="str">
+      <c r="Q13" s="236" t="str">
         <f t="shared" si="1"/>
         <v>ong0</v>
       </c>
-      <c r="R13" s="239" t="str">
+      <c r="R13" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/ok([48])/ong0/    # ong入 = ok[48]</v>
       </c>
     </row>
     <row r="14" spans="2:18" ht="24" thickBot="1">
-      <c r="B14" s="237" t="s">
+      <c r="B14" s="234" t="s">
+        <v>396</v>
+      </c>
+      <c r="C14" s="235" t="s">
         <v>397</v>
       </c>
-      <c r="C14" s="238" t="s">
+      <c r="D14" s="235" t="s">
         <v>398</v>
       </c>
-      <c r="D14" s="238" t="s">
+      <c r="E14" s="235"/>
+      <c r="F14" s="235"/>
+      <c r="G14" s="235"/>
+      <c r="H14" s="235"/>
+      <c r="I14" s="235"/>
+      <c r="J14" s="235"/>
+      <c r="K14" s="235" t="s">
         <v>399</v>
       </c>
-      <c r="E14" s="238"/>
-      <c r="F14" s="238"/>
-      <c r="G14" s="238"/>
-      <c r="H14" s="238"/>
-      <c r="I14" s="238"/>
-      <c r="J14" s="238"/>
-      <c r="K14" s="238" t="s">
+      <c r="L14" s="235" t="s">
         <v>400</v>
       </c>
-      <c r="L14" s="238" t="s">
-        <v>401</v>
-      </c>
-      <c r="N14" s="239" t="s">
-        <v>473</v>
-      </c>
-      <c r="O14" s="239" t="s">
-        <v>280</v>
-      </c>
-      <c r="P14" s="239" t="str">
+      <c r="N14" s="236" t="s">
+        <v>472</v>
+      </c>
+      <c r="O14" s="236" t="s">
+        <v>279</v>
+      </c>
+      <c r="P14" s="236" t="str">
         <f t="shared" si="0"/>
         <v>op([48])</v>
       </c>
-      <c r="Q14" s="239" t="str">
+      <c r="Q14" s="236" t="str">
         <f t="shared" si="1"/>
         <v>om0</v>
       </c>
-      <c r="R14" s="239" t="str">
+      <c r="R14" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/op([48])/om0/    # om入 = op[48]</v>
       </c>
     </row>
     <row r="15" spans="2:18" ht="24" thickBot="1">
-      <c r="B15" s="237" t="s">
+      <c r="B15" s="234" t="s">
+        <v>401</v>
+      </c>
+      <c r="C15" s="235" t="s">
         <v>402</v>
       </c>
-      <c r="C15" s="238" t="s">
+      <c r="D15" s="235"/>
+      <c r="E15" s="235"/>
+      <c r="F15" s="235"/>
+      <c r="G15" s="235"/>
+      <c r="H15" s="235"/>
+      <c r="I15" s="235"/>
+      <c r="J15" s="235"/>
+      <c r="K15" s="235" t="s">
         <v>403</v>
       </c>
-      <c r="D15" s="238"/>
-      <c r="E15" s="238"/>
-      <c r="F15" s="238"/>
-      <c r="G15" s="238"/>
-      <c r="H15" s="238"/>
-      <c r="I15" s="238"/>
-      <c r="J15" s="238"/>
-      <c r="K15" s="238" t="s">
-        <v>404</v>
-      </c>
-      <c r="L15" s="238"/>
-      <c r="N15" s="239" t="s">
-        <v>474</v>
-      </c>
-      <c r="O15" s="239" t="s">
-        <v>477</v>
-      </c>
-      <c r="P15" s="239" t="str">
+      <c r="L15" s="235"/>
+      <c r="N15" s="236" t="s">
+        <v>473</v>
+      </c>
+      <c r="O15" s="236" t="s">
+        <v>476</v>
+      </c>
+      <c r="P15" s="236" t="str">
         <f t="shared" si="0"/>
         <v>irk([48])</v>
       </c>
-      <c r="Q15" s="239" t="str">
+      <c r="Q15" s="236" t="str">
         <f t="shared" si="1"/>
         <v>irng0</v>
       </c>
-      <c r="R15" s="239" t="str">
+      <c r="R15" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/irk([48])/irng0/    # irng入 = irk[48]</v>
       </c>
     </row>
     <row r="16" spans="2:18" ht="24" thickBot="1">
-      <c r="B16" s="237" t="s">
+      <c r="B16" s="234" t="s">
+        <v>404</v>
+      </c>
+      <c r="C16" s="235" t="s">
+        <v>194</v>
+      </c>
+      <c r="D16" s="235"/>
+      <c r="E16" s="235"/>
+      <c r="F16" s="235"/>
+      <c r="G16" s="235"/>
+      <c r="H16" s="235"/>
+      <c r="I16" s="235"/>
+      <c r="J16" s="235"/>
+      <c r="K16" s="235" t="s">
         <v>405</v>
       </c>
-      <c r="C16" s="238" t="s">
-        <v>194</v>
-      </c>
-      <c r="D16" s="238"/>
-      <c r="E16" s="238"/>
-      <c r="F16" s="238"/>
-      <c r="G16" s="238"/>
-      <c r="H16" s="238"/>
-      <c r="I16" s="238"/>
-      <c r="J16" s="238"/>
-      <c r="K16" s="238" t="s">
-        <v>406</v>
-      </c>
-      <c r="L16" s="238"/>
-      <c r="N16" s="239" t="s">
-        <v>475</v>
-      </c>
-      <c r="O16" s="239" t="s">
-        <v>477</v>
-      </c>
-      <c r="P16" s="239" t="str">
+      <c r="L16" s="235"/>
+      <c r="N16" s="236" t="s">
+        <v>474</v>
+      </c>
+      <c r="O16" s="236" t="s">
+        <v>476</v>
+      </c>
+      <c r="P16" s="236" t="str">
         <f t="shared" si="0"/>
         <v>irt([48])</v>
       </c>
-      <c r="Q16" s="239" t="str">
+      <c r="Q16" s="236" t="str">
         <f t="shared" si="1"/>
         <v>irng0</v>
       </c>
-      <c r="R16" s="239" t="str">
+      <c r="R16" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/irt([48])/irng0/    # irng入 = irt[48]</v>
       </c>
     </row>
     <row r="17" spans="2:19" ht="24" thickBot="1">
-      <c r="B17" s="237" t="s">
+      <c r="B17" s="234" t="s">
+        <v>406</v>
+      </c>
+      <c r="C17" s="235" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="235" t="s">
         <v>407</v>
       </c>
-      <c r="C17" s="238" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" s="238" t="s">
+      <c r="E17" s="235" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="235"/>
+      <c r="G17" s="235" t="s">
+        <v>109</v>
+      </c>
+      <c r="H17" s="235" t="s">
         <v>408</v>
       </c>
-      <c r="E17" s="238" t="s">
-        <v>92</v>
-      </c>
-      <c r="F17" s="238"/>
-      <c r="G17" s="238" t="s">
-        <v>109</v>
-      </c>
-      <c r="H17" s="238" t="s">
+      <c r="I17" s="235"/>
+      <c r="J17" s="235" t="s">
         <v>409</v>
       </c>
-      <c r="I17" s="238"/>
-      <c r="J17" s="238" t="s">
+      <c r="K17" s="235" t="s">
         <v>410</v>
       </c>
-      <c r="K17" s="238" t="s">
+      <c r="L17" s="235" t="s">
         <v>411</v>
       </c>
-      <c r="L17" s="238" t="s">
-        <v>412</v>
-      </c>
-      <c r="N17" s="239" t="s">
-        <v>476</v>
-      </c>
-      <c r="O17" s="239" t="s">
-        <v>478</v>
-      </c>
-      <c r="P17" s="239" t="str">
+      <c r="N17" s="236" t="s">
+        <v>475</v>
+      </c>
+      <c r="O17" s="236" t="s">
+        <v>477</v>
+      </c>
+      <c r="P17" s="236" t="str">
         <f t="shared" si="0"/>
         <v>irp([48])</v>
       </c>
-      <c r="Q17" s="239" t="str">
+      <c r="Q17" s="236" t="str">
         <f t="shared" si="1"/>
         <v>irm0</v>
       </c>
-      <c r="R17" s="239" t="str">
+      <c r="R17" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/irp([48])/irm0/    # irm入 = irp[48]</v>
       </c>
     </row>
     <row r="18" spans="2:19" ht="24" thickBot="1">
-      <c r="B18" s="237" t="s">
+      <c r="B18" s="234" t="s">
+        <v>412</v>
+      </c>
+      <c r="C18" s="235" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="235"/>
+      <c r="E18" s="235" t="s">
         <v>413</v>
       </c>
-      <c r="C18" s="238" t="s">
-        <v>126</v>
-      </c>
-      <c r="D18" s="238"/>
-      <c r="E18" s="238" t="s">
+      <c r="F18" s="235" t="s">
         <v>414</v>
       </c>
-      <c r="F18" s="238" t="s">
+      <c r="G18" s="235" t="s">
         <v>415</v>
       </c>
-      <c r="G18" s="238" t="s">
+      <c r="H18" s="235" t="s">
         <v>416</v>
       </c>
-      <c r="H18" s="238" t="s">
+      <c r="I18" s="235" t="s">
         <v>417</v>
       </c>
-      <c r="I18" s="238" t="s">
+      <c r="J18" s="235" t="s">
         <v>418</v>
       </c>
-      <c r="J18" s="238" t="s">
+      <c r="K18" s="235" t="s">
         <v>419</v>
       </c>
-      <c r="K18" s="238" t="s">
-        <v>420</v>
-      </c>
-      <c r="L18" s="238"/>
-      <c r="N18" s="239" t="s">
+      <c r="L18" s="235"/>
+      <c r="N18" s="236" t="s">
+        <v>478</v>
+      </c>
+      <c r="O18" s="236" t="s">
         <v>479</v>
       </c>
-      <c r="O18" s="239" t="s">
-        <v>480</v>
-      </c>
-      <c r="P18" s="239" t="str">
+      <c r="P18" s="236" t="str">
         <f t="shared" si="0"/>
         <v>ut([48])</v>
       </c>
-      <c r="Q18" s="239" t="str">
+      <c r="Q18" s="236" t="str">
         <f t="shared" si="1"/>
         <v>un0</v>
       </c>
-      <c r="R18" s="239" t="str">
+      <c r="R18" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/ut([48])/un0/    # un入 = ut[48]</v>
       </c>
     </row>
     <row r="19" spans="2:19" ht="24" thickBot="1">
-      <c r="B19" s="237" t="s">
+      <c r="B19" s="234" t="s">
+        <v>420</v>
+      </c>
+      <c r="C19" s="235" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="235"/>
+      <c r="E19" s="235"/>
+      <c r="F19" s="235" t="s">
         <v>421</v>
       </c>
-      <c r="C19" s="238" t="s">
-        <v>142</v>
-      </c>
-      <c r="D19" s="238"/>
-      <c r="E19" s="238"/>
-      <c r="F19" s="238" t="s">
+      <c r="G19" s="235"/>
+      <c r="H19" s="235"/>
+      <c r="I19" s="235" t="s">
         <v>422</v>
       </c>
-      <c r="G19" s="238"/>
-      <c r="H19" s="238"/>
-      <c r="I19" s="238" t="s">
+      <c r="J19" s="235"/>
+      <c r="K19" s="235" t="s">
         <v>423</v>
       </c>
-      <c r="J19" s="238"/>
-      <c r="K19" s="238" t="s">
-        <v>424</v>
-      </c>
-      <c r="L19" s="238"/>
-      <c r="N19" s="239" t="s">
+      <c r="L19" s="235"/>
+      <c r="N19" s="236" t="s">
+        <v>480</v>
+      </c>
+      <c r="O19" s="236" t="s">
         <v>481</v>
       </c>
-      <c r="O19" s="239" t="s">
-        <v>482</v>
-      </c>
-      <c r="P19" s="239" t="str">
+      <c r="P19" s="236" t="str">
         <f t="shared" si="0"/>
         <v>uat([48])</v>
       </c>
-      <c r="Q19" s="239" t="str">
+      <c r="Q19" s="236" t="str">
         <f t="shared" si="1"/>
         <v>uan0</v>
       </c>
-      <c r="R19" s="239" t="str">
+      <c r="R19" s="236" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    - derive/uat([48])/uan0/    # uan入 = uat[48]</v>
       </c>
     </row>
     <row r="20" spans="2:19" ht="24" thickBot="1">
-      <c r="B20" s="237" t="s">
+      <c r="B20" s="234" t="s">
+        <v>424</v>
+      </c>
+      <c r="C20" s="235" t="s">
         <v>425</v>
       </c>
-      <c r="C20" s="238" t="s">
+      <c r="D20" s="235" t="s">
         <v>426</v>
       </c>
-      <c r="D20" s="238" t="s">
+      <c r="E20" s="235"/>
+      <c r="F20" s="235" t="s">
         <v>427</v>
       </c>
-      <c r="E20" s="238"/>
-      <c r="F20" s="238" t="s">
+      <c r="G20" s="235" t="s">
         <v>428</v>
       </c>
-      <c r="G20" s="238" t="s">
+      <c r="H20" s="235"/>
+      <c r="I20" s="235" t="s">
         <v>429</v>
       </c>
-      <c r="H20" s="238"/>
-      <c r="I20" s="238" t="s">
+      <c r="J20" s="235"/>
+      <c r="K20" s="235" t="s">
         <v>430</v>
       </c>
-      <c r="J20" s="238"/>
-      <c r="K20" s="238" t="s">
-        <v>431</v>
-      </c>
-      <c r="L20" s="238"/>
+      <c r="L20" s="235"/>
     </row>
     <row r="21" spans="2:19" ht="24" thickBot="1">
-      <c r="B21" s="237" t="s">
+      <c r="B21" s="234" t="s">
+        <v>431</v>
+      </c>
+      <c r="C21" s="235" t="s">
         <v>432</v>
       </c>
-      <c r="C21" s="238" t="s">
+      <c r="D21" s="235" t="s">
         <v>433</v>
       </c>
-      <c r="D21" s="238" t="s">
-        <v>434</v>
-      </c>
-      <c r="E21" s="238"/>
-      <c r="F21" s="238"/>
-      <c r="G21" s="238"/>
-      <c r="H21" s="238"/>
-      <c r="I21" s="238"/>
-      <c r="J21" s="238"/>
-      <c r="K21" s="238"/>
-      <c r="L21" s="238"/>
+      <c r="E21" s="235"/>
+      <c r="F21" s="235"/>
+      <c r="G21" s="235"/>
+      <c r="H21" s="235"/>
+      <c r="I21" s="235"/>
+      <c r="J21" s="235"/>
+      <c r="K21" s="235"/>
+      <c r="L21" s="235"/>
     </row>
     <row r="22" spans="2:19" ht="24" thickBot="1">
-      <c r="B22" s="237" t="s">
+      <c r="B22" s="234" t="s">
+        <v>434</v>
+      </c>
+      <c r="C22" s="235" t="s">
         <v>435</v>
       </c>
-      <c r="C22" s="238" t="s">
+      <c r="D22" s="235"/>
+      <c r="E22" s="235"/>
+      <c r="F22" s="235"/>
+      <c r="G22" s="235"/>
+      <c r="H22" s="235"/>
+      <c r="I22" s="235"/>
+      <c r="J22" s="235"/>
+      <c r="K22" s="235" t="s">
         <v>436</v>
       </c>
-      <c r="D22" s="238"/>
-      <c r="E22" s="238"/>
-      <c r="F22" s="238"/>
-      <c r="G22" s="238"/>
-      <c r="H22" s="238"/>
-      <c r="I22" s="238"/>
-      <c r="J22" s="238"/>
-      <c r="K22" s="238" t="s">
-        <v>437</v>
-      </c>
-      <c r="L22" s="238"/>
-      <c r="N22" s="240" t="s">
+      <c r="L22" s="235"/>
+      <c r="N22" s="237" t="s">
+        <v>456</v>
+      </c>
+      <c r="O22" s="237" t="s">
         <v>457</v>
       </c>
-      <c r="O22" s="240" t="s">
-        <v>458</v>
-      </c>
-      <c r="P22" s="240" t="str">
+      <c r="P22" s="237" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(N22,$P$2)</f>
         <v>ek([48])</v>
       </c>
-      <c r="Q22" s="240" t="str">
+      <c r="Q22" s="237" t="str">
         <f>_xlfn.CONCAT(O22,$Q$2)</f>
         <v>eng0</v>
       </c>
-      <c r="R22" s="240" t="str">
+      <c r="R22" s="237" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - xform/", P22, "/", Q22, "/    # " &amp; O22, "入 = ", N22, "[48]")</f>
         <v xml:space="preserve">    - xform/ek([48])/eng0/    # eng入 = ek[48]</v>
       </c>
     </row>
     <row r="23" spans="2:19" ht="24" thickBot="1">
-      <c r="B23" s="237" t="s">
+      <c r="B23" s="234" t="s">
+        <v>437</v>
+      </c>
+      <c r="C23" s="235" t="s">
         <v>438</v>
       </c>
-      <c r="C23" s="238" t="s">
+      <c r="D23" s="235"/>
+      <c r="E23" s="235"/>
+      <c r="F23" s="235"/>
+      <c r="G23" s="235"/>
+      <c r="H23" s="235"/>
+      <c r="I23" s="235"/>
+      <c r="J23" s="235"/>
+      <c r="K23" s="235" t="s">
         <v>439</v>
       </c>
-      <c r="D23" s="238"/>
-      <c r="E23" s="238"/>
-      <c r="F23" s="238"/>
-      <c r="G23" s="238"/>
-      <c r="H23" s="238"/>
-      <c r="I23" s="238"/>
-      <c r="J23" s="238"/>
-      <c r="K23" s="238" t="s">
-        <v>440</v>
-      </c>
-      <c r="L23" s="238"/>
-      <c r="N23" s="241" t="s">
-        <v>484</v>
-      </c>
-      <c r="O23" s="239" t="s">
+      <c r="L23" s="235"/>
+      <c r="N23" s="238" t="s">
         <v>483</v>
       </c>
-      <c r="P23" s="239" t="str">
+      <c r="O23" s="236" t="s">
+        <v>482</v>
+      </c>
+      <c r="P23" s="236" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT(N23,$P$2)</f>
         <v>uak([48])</v>
       </c>
-      <c r="Q23" s="239" t="str">
+      <c r="Q23" s="236" t="str">
         <f>_xlfn.CONCAT(O23,$Q$2)</f>
         <v>uang0</v>
       </c>
-      <c r="R23" s="239" t="str">
+      <c r="R23" s="236" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - xform/", P23, "/", Q23, "/    # " &amp; O23, "入 = ", N23, "[48]")</f>
         <v xml:space="preserve">    - xform/uak([48])/uang0/    # uang入 = uak[48]</v>
       </c>
-      <c r="S23" s="240"/>
+      <c r="S23" s="237"/>
     </row>
     <row r="24" spans="2:19" ht="24" thickBot="1">
-      <c r="B24" s="237" t="s">
+      <c r="B24" s="234" t="s">
+        <v>440</v>
+      </c>
+      <c r="C24" s="235" t="s">
         <v>441</v>
       </c>
-      <c r="C24" s="238" t="s">
-        <v>442</v>
-      </c>
-      <c r="D24" s="238"/>
-      <c r="E24" s="238"/>
-      <c r="F24" s="238"/>
-      <c r="G24" s="238"/>
-      <c r="H24" s="238"/>
-      <c r="I24" s="238"/>
-      <c r="J24" s="238"/>
-      <c r="K24" s="238"/>
-      <c r="L24" s="238"/>
+      <c r="D24" s="235"/>
+      <c r="E24" s="235"/>
+      <c r="F24" s="235"/>
+      <c r="G24" s="235"/>
+      <c r="H24" s="235"/>
+      <c r="I24" s="235"/>
+      <c r="J24" s="235"/>
+      <c r="K24" s="235"/>
+      <c r="L24" s="235"/>
     </row>
     <row r="25" spans="2:19" ht="24" thickBot="1">
-      <c r="B25" s="237" t="s">
+      <c r="B25" s="234" t="s">
+        <v>442</v>
+      </c>
+      <c r="C25" s="235"/>
+      <c r="D25" s="235" t="s">
         <v>443</v>
       </c>
-      <c r="C25" s="238"/>
-      <c r="D25" s="238" t="s">
-        <v>444</v>
-      </c>
-      <c r="E25" s="238"/>
-      <c r="F25" s="238"/>
-      <c r="G25" s="238"/>
-      <c r="H25" s="238"/>
-      <c r="I25" s="238"/>
-      <c r="J25" s="238"/>
-      <c r="K25" s="238"/>
-      <c r="L25" s="238"/>
+      <c r="E25" s="235"/>
+      <c r="F25" s="235"/>
+      <c r="G25" s="235"/>
+      <c r="H25" s="235"/>
+      <c r="I25" s="235"/>
+      <c r="J25" s="235"/>
+      <c r="K25" s="235"/>
+      <c r="L25" s="235"/>
     </row>
     <row r="26" spans="2:19" ht="24" thickBot="1">
-      <c r="B26" s="237" t="s">
+      <c r="B26" s="234" t="s">
+        <v>444</v>
+      </c>
+      <c r="C26" s="235" t="s">
         <v>445</v>
       </c>
-      <c r="C26" s="238" t="s">
+      <c r="D26" s="235"/>
+      <c r="E26" s="235"/>
+      <c r="F26" s="235"/>
+      <c r="G26" s="235"/>
+      <c r="H26" s="235"/>
+      <c r="I26" s="235"/>
+      <c r="J26" s="235"/>
+      <c r="K26" s="235" t="s">
         <v>446</v>
       </c>
-      <c r="D26" s="238"/>
-      <c r="E26" s="238"/>
-      <c r="F26" s="238"/>
-      <c r="G26" s="238"/>
-      <c r="H26" s="238"/>
-      <c r="I26" s="238"/>
-      <c r="J26" s="238"/>
-      <c r="K26" s="238" t="s">
-        <v>447</v>
-      </c>
-      <c r="L26" s="238"/>
+      <c r="L26" s="235"/>
     </row>
     <row r="27" spans="2:19" ht="24" thickBot="1">
-      <c r="B27" s="237" t="s">
+      <c r="B27" s="234" t="s">
+        <v>447</v>
+      </c>
+      <c r="C27" s="253" t="s">
+        <v>192</v>
+      </c>
+      <c r="D27" s="254"/>
+      <c r="E27" s="253" t="s">
         <v>448</v>
       </c>
-      <c r="C27" s="245" t="s">
-        <v>192</v>
-      </c>
-      <c r="D27" s="246"/>
-      <c r="E27" s="245" t="s">
+      <c r="F27" s="255"/>
+      <c r="G27" s="255"/>
+      <c r="H27" s="255"/>
+      <c r="I27" s="255"/>
+      <c r="J27" s="254"/>
+      <c r="K27" s="253" t="s">
         <v>449</v>
       </c>
-      <c r="F27" s="247"/>
-      <c r="G27" s="247"/>
-      <c r="H27" s="247"/>
-      <c r="I27" s="247"/>
-      <c r="J27" s="246"/>
-      <c r="K27" s="245" t="s">
-        <v>450</v>
-      </c>
-      <c r="L27" s="246"/>
+      <c r="L27" s="254"/>
     </row>
     <row r="28" spans="2:19" ht="24" thickBot="1">
-      <c r="B28" s="237" t="s">
+      <c r="B28" s="234" t="s">
+        <v>450</v>
+      </c>
+      <c r="C28" s="253" t="s">
         <v>451</v>
       </c>
-      <c r="C28" s="245" t="s">
+      <c r="D28" s="254"/>
+      <c r="E28" s="253" t="s">
+        <v>448</v>
+      </c>
+      <c r="F28" s="255"/>
+      <c r="G28" s="255"/>
+      <c r="H28" s="255"/>
+      <c r="I28" s="255"/>
+      <c r="J28" s="254"/>
+      <c r="K28" s="253" t="s">
         <v>452</v>
       </c>
-      <c r="D28" s="246"/>
-      <c r="E28" s="245" t="s">
-        <v>449</v>
-      </c>
-      <c r="F28" s="247"/>
-      <c r="G28" s="247"/>
-      <c r="H28" s="247"/>
-      <c r="I28" s="247"/>
-      <c r="J28" s="246"/>
-      <c r="K28" s="245" t="s">
-        <v>453</v>
-      </c>
-      <c r="L28" s="246"/>
+      <c r="L28" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -11479,107 +12511,107 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:26">
-      <c r="B2" s="234" t="s">
+      <c r="B2" s="231" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="D2" s="231" t="s">
+        <v>299</v>
+      </c>
+      <c r="E2" s="231" t="s">
         <v>313</v>
       </c>
-      <c r="C2" s="234" t="s">
-        <v>321</v>
-      </c>
-      <c r="D2" s="234" t="s">
-        <v>300</v>
-      </c>
-      <c r="E2" s="234" t="s">
-        <v>314</v>
-      </c>
-      <c r="F2" s="234" t="s">
+      <c r="F2" s="231" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="234" t="s">
+      <c r="G2" s="231" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="234" t="s">
+      <c r="I2" s="231" t="s">
+        <v>312</v>
+      </c>
+      <c r="J2" s="231" t="s">
+        <v>320</v>
+      </c>
+      <c r="K2" s="231" t="s">
+        <v>299</v>
+      </c>
+      <c r="L2" s="231" t="s">
         <v>313</v>
       </c>
-      <c r="J2" s="234" t="s">
-        <v>321</v>
-      </c>
-      <c r="K2" s="234" t="s">
-        <v>300</v>
-      </c>
-      <c r="L2" s="234" t="s">
-        <v>314</v>
-      </c>
-      <c r="M2" s="234" t="s">
+      <c r="M2" s="231" t="s">
         <v>66</v>
       </c>
-      <c r="N2" s="234" t="s">
+      <c r="N2" s="231" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="2:26" ht="32.25">
-      <c r="B3" s="224" t="s">
-        <v>305</v>
-      </c>
-      <c r="C3" s="224" t="s">
-        <v>322</v>
-      </c>
-      <c r="D3" s="225">
+      <c r="B3" s="221" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" s="221" t="s">
+        <v>321</v>
+      </c>
+      <c r="D3" s="222">
         <v>1</v>
       </c>
-      <c r="E3" s="226" t="s">
-        <v>302</v>
-      </c>
-      <c r="F3" s="227" t="s">
-        <v>295</v>
-      </c>
-      <c r="G3" s="224" t="s">
-        <v>297</v>
-      </c>
-      <c r="I3" s="224" t="s">
-        <v>305</v>
-      </c>
-      <c r="J3" s="224" t="s">
-        <v>322</v>
-      </c>
-      <c r="K3" s="225">
+      <c r="E3" s="223" t="s">
+        <v>301</v>
+      </c>
+      <c r="F3" s="224" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="221" t="s">
+        <v>296</v>
+      </c>
+      <c r="I3" s="221" t="s">
+        <v>304</v>
+      </c>
+      <c r="J3" s="221" t="s">
+        <v>321</v>
+      </c>
+      <c r="K3" s="222">
         <v>1</v>
       </c>
-      <c r="L3" s="226" t="s">
-        <v>302</v>
-      </c>
-      <c r="M3" s="227" t="s">
-        <v>295</v>
-      </c>
-      <c r="N3" s="224" t="s">
-        <v>297</v>
-      </c>
-      <c r="P3" s="235" cm="1">
+      <c r="L3" s="223" t="s">
+        <v>301</v>
+      </c>
+      <c r="M3" s="224" t="s">
+        <v>294</v>
+      </c>
+      <c r="N3" s="221" t="s">
+        <v>296</v>
+      </c>
+      <c r="P3" s="232" cm="1">
         <f t="array" ref="P3:W3" xml:space="preserve"> TRANSPOSE(K3:K10)</f>
         <v>1</v>
       </c>
-      <c r="Q3" s="235">
+      <c r="Q3" s="232">
         <v>7</v>
       </c>
-      <c r="R3" s="235">
+      <c r="R3" s="232">
         <v>3</v>
       </c>
-      <c r="S3" s="235">
+      <c r="S3" s="232">
         <v>2</v>
       </c>
-      <c r="T3" s="235">
+      <c r="T3" s="232">
         <v>5</v>
       </c>
-      <c r="U3" s="235">
+      <c r="U3" s="232">
         <v>8</v>
       </c>
-      <c r="V3" s="235">
+      <c r="V3" s="232">
         <v>4</v>
       </c>
-      <c r="W3" s="235">
+      <c r="W3" s="232">
         <v>0</v>
       </c>
-      <c r="X3" s="235" t="s">
-        <v>331</v>
+      <c r="X3" s="232" t="s">
+        <v>330</v>
       </c>
       <c r="Z3" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - xform/", L3, "/", M3, "/")</f>
@@ -11587,68 +12619,68 @@
       </c>
     </row>
     <row r="4" spans="2:26" ht="32.25">
-      <c r="B4" s="224" t="s">
-        <v>306</v>
-      </c>
-      <c r="C4" s="224" t="s">
-        <v>323</v>
-      </c>
-      <c r="D4" s="225">
+      <c r="B4" s="221" t="s">
+        <v>305</v>
+      </c>
+      <c r="C4" s="221" t="s">
+        <v>322</v>
+      </c>
+      <c r="D4" s="222">
         <v>2</v>
       </c>
-      <c r="E4" s="226" t="s">
-        <v>315</v>
-      </c>
-      <c r="F4" s="227" t="s">
+      <c r="E4" s="223" t="s">
+        <v>314</v>
+      </c>
+      <c r="F4" s="224" t="s">
         <v>49</v>
       </c>
-      <c r="G4" s="224">
+      <c r="G4" s="221">
         <v>4</v>
       </c>
-      <c r="I4" s="229" t="s">
-        <v>311</v>
-      </c>
-      <c r="J4" s="229" t="s">
-        <v>330</v>
-      </c>
-      <c r="K4" s="230">
+      <c r="I4" s="226" t="s">
+        <v>310</v>
+      </c>
+      <c r="J4" s="226" t="s">
+        <v>329</v>
+      </c>
+      <c r="K4" s="227">
         <v>7</v>
       </c>
-      <c r="L4" s="233" t="s">
-        <v>318</v>
-      </c>
-      <c r="M4" s="232" t="s">
+      <c r="L4" s="230" t="s">
+        <v>317</v>
+      </c>
+      <c r="M4" s="229" t="s">
         <v>51</v>
       </c>
-      <c r="N4" s="229">
+      <c r="N4" s="226">
         <v>5</v>
       </c>
-      <c r="P4" s="235" t="str" cm="1">
+      <c r="P4" s="232" t="str" cm="1">
         <f t="array" ref="P4:W4" xml:space="preserve"> TRANSPOSE(N3:N10)</f>
         <v>:</v>
       </c>
-      <c r="Q4" s="235">
+      <c r="Q4" s="232">
         <v>5</v>
       </c>
-      <c r="R4" s="235">
+      <c r="R4" s="232">
         <v>3</v>
       </c>
-      <c r="S4" s="235">
+      <c r="S4" s="232">
         <v>4</v>
       </c>
-      <c r="T4" s="235">
+      <c r="T4" s="232">
         <v>6</v>
       </c>
-      <c r="U4" s="235" t="str">
+      <c r="U4" s="232" t="str">
         <v>]</v>
       </c>
-      <c r="V4" s="235" t="str">
+      <c r="V4" s="232" t="str">
         <v>[</v>
       </c>
-      <c r="W4" s="235">
+      <c r="W4" s="232">
         <v>7</v>
       </c>
-      <c r="X4" s="235" t="s">
+      <c r="X4" s="232" t="s">
         <v>5</v>
       </c>
       <c r="Z4" t="str">
@@ -11657,69 +12689,69 @@
       </c>
     </row>
     <row r="5" spans="2:26" ht="32.25">
-      <c r="B5" s="224" t="s">
-        <v>307</v>
-      </c>
-      <c r="C5" s="224" t="s">
-        <v>324</v>
-      </c>
-      <c r="D5" s="225">
+      <c r="B5" s="221" t="s">
+        <v>306</v>
+      </c>
+      <c r="C5" s="221" t="s">
+        <v>323</v>
+      </c>
+      <c r="D5" s="222">
         <v>3</v>
       </c>
-      <c r="E5" s="228" t="s">
-        <v>316</v>
-      </c>
-      <c r="F5" s="227" t="s">
+      <c r="E5" s="225" t="s">
+        <v>315</v>
+      </c>
+      <c r="F5" s="224" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="224">
+      <c r="G5" s="221">
         <v>3</v>
       </c>
-      <c r="I5" s="224" t="s">
-        <v>307</v>
-      </c>
-      <c r="J5" s="224" t="s">
-        <v>324</v>
-      </c>
-      <c r="K5" s="225">
+      <c r="I5" s="221" t="s">
+        <v>306</v>
+      </c>
+      <c r="J5" s="221" t="s">
+        <v>323</v>
+      </c>
+      <c r="K5" s="222">
         <v>3</v>
       </c>
-      <c r="L5" s="228" t="s">
-        <v>316</v>
-      </c>
-      <c r="M5" s="227" t="s">
+      <c r="L5" s="225" t="s">
+        <v>315</v>
+      </c>
+      <c r="M5" s="224" t="s">
         <v>47</v>
       </c>
-      <c r="N5" s="224">
+      <c r="N5" s="221">
         <v>3</v>
       </c>
-      <c r="P5" s="236" t="str" cm="1">
+      <c r="P5" s="233" t="str" cm="1">
         <f t="array" ref="P5:W5" xml:space="preserve"> TRANSPOSE(L3:L10)</f>
         <v>一</v>
       </c>
-      <c r="Q5" s="236" t="str">
+      <c r="Q5" s="233" t="str">
         <v>七</v>
       </c>
-      <c r="R5" s="236" t="str">
+      <c r="R5" s="233" t="str">
         <v>三</v>
       </c>
-      <c r="S5" s="236" t="str">
+      <c r="S5" s="233" t="str">
         <v>二</v>
       </c>
-      <c r="T5" s="236" t="str">
+      <c r="T5" s="233" t="str">
         <v>五</v>
       </c>
-      <c r="U5" s="235" t="str">
+      <c r="U5" s="232" t="str">
         <v>八</v>
       </c>
-      <c r="V5" s="236" t="str">
+      <c r="V5" s="233" t="str">
         <v>四</v>
       </c>
-      <c r="W5" s="236" t="str">
+      <c r="W5" s="233" t="str">
         <v>入</v>
       </c>
-      <c r="X5" s="235" t="s">
-        <v>332</v>
+      <c r="X5" s="232" t="s">
+        <v>331</v>
       </c>
       <c r="Z5" t="str">
         <f t="shared" si="0"/>
@@ -11727,64 +12759,64 @@
       </c>
     </row>
     <row r="6" spans="2:26" ht="32.25">
-      <c r="B6" s="224" t="s">
-        <v>308</v>
-      </c>
-      <c r="C6" s="224" t="s">
-        <v>325</v>
-      </c>
-      <c r="D6" s="225">
+      <c r="B6" s="221" t="s">
+        <v>307</v>
+      </c>
+      <c r="C6" s="221" t="s">
+        <v>324</v>
+      </c>
+      <c r="D6" s="222">
         <v>4</v>
       </c>
-      <c r="E6" s="228" t="s">
-        <v>303</v>
-      </c>
-      <c r="F6" s="227" t="s">
+      <c r="E6" s="225" t="s">
+        <v>302</v>
+      </c>
+      <c r="F6" s="224" t="s">
+        <v>294</v>
+      </c>
+      <c r="G6" s="221" t="s">
+        <v>318</v>
+      </c>
+      <c r="I6" s="221" t="s">
+        <v>305</v>
+      </c>
+      <c r="J6" s="221" t="s">
+        <v>322</v>
+      </c>
+      <c r="K6" s="222">
+        <v>2</v>
+      </c>
+      <c r="L6" s="223" t="s">
+        <v>314</v>
+      </c>
+      <c r="M6" s="224" t="s">
+        <v>49</v>
+      </c>
+      <c r="N6" s="221">
+        <v>4</v>
+      </c>
+      <c r="P6" s="233" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q6" s="233" t="s">
+        <v>51</v>
+      </c>
+      <c r="R6" s="233" t="s">
+        <v>47</v>
+      </c>
+      <c r="S6" s="233" t="s">
+        <v>49</v>
+      </c>
+      <c r="T6" s="233" t="s">
+        <v>53</v>
+      </c>
+      <c r="U6" s="232" t="s">
         <v>295</v>
       </c>
-      <c r="G6" s="224" t="s">
-        <v>319</v>
-      </c>
-      <c r="I6" s="224" t="s">
-        <v>306</v>
-      </c>
-      <c r="J6" s="224" t="s">
-        <v>323</v>
-      </c>
-      <c r="K6" s="225">
-        <v>2</v>
-      </c>
-      <c r="L6" s="226" t="s">
-        <v>315</v>
-      </c>
-      <c r="M6" s="227" t="s">
-        <v>49</v>
-      </c>
-      <c r="N6" s="224">
-        <v>4</v>
-      </c>
-      <c r="P6" s="236" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q6" s="236" t="s">
-        <v>51</v>
-      </c>
-      <c r="R6" s="236" t="s">
-        <v>47</v>
-      </c>
-      <c r="S6" s="236" t="s">
-        <v>49</v>
-      </c>
-      <c r="T6" s="236" t="s">
-        <v>53</v>
-      </c>
-      <c r="U6" s="235" t="s">
-        <v>296</v>
-      </c>
-      <c r="V6" s="236" t="s">
-        <v>295</v>
-      </c>
-      <c r="W6" s="236" t="s">
+      <c r="V6" s="233" t="s">
+        <v>294</v>
+      </c>
+      <c r="W6" s="233" t="s">
         <v>63</v>
       </c>
       <c r="Z6" t="str">
@@ -11793,40 +12825,40 @@
       </c>
     </row>
     <row r="7" spans="2:26" ht="32.25">
-      <c r="B7" s="229" t="s">
-        <v>309</v>
-      </c>
-      <c r="C7" s="229" t="s">
-        <v>328</v>
-      </c>
-      <c r="D7" s="230">
+      <c r="B7" s="226" t="s">
+        <v>308</v>
+      </c>
+      <c r="C7" s="226" t="s">
+        <v>327</v>
+      </c>
+      <c r="D7" s="227">
         <v>5</v>
       </c>
-      <c r="E7" s="231" t="s">
-        <v>304</v>
-      </c>
-      <c r="F7" s="232" t="s">
+      <c r="E7" s="228" t="s">
+        <v>303</v>
+      </c>
+      <c r="F7" s="229" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="229">
+      <c r="G7" s="226">
         <v>6</v>
       </c>
-      <c r="I7" s="229" t="s">
-        <v>309</v>
-      </c>
-      <c r="J7" s="229" t="s">
-        <v>328</v>
-      </c>
-      <c r="K7" s="230">
+      <c r="I7" s="226" t="s">
+        <v>308</v>
+      </c>
+      <c r="J7" s="226" t="s">
+        <v>327</v>
+      </c>
+      <c r="K7" s="227">
         <v>5</v>
       </c>
-      <c r="L7" s="231" t="s">
-        <v>304</v>
-      </c>
-      <c r="M7" s="232" t="s">
+      <c r="L7" s="228" t="s">
+        <v>303</v>
+      </c>
+      <c r="M7" s="229" t="s">
         <v>53</v>
       </c>
-      <c r="N7" s="229">
+      <c r="N7" s="226">
         <v>6</v>
       </c>
       <c r="Z7" t="str">
@@ -11835,39 +12867,39 @@
       </c>
     </row>
     <row r="8" spans="2:26" ht="32.25">
-      <c r="B8" s="229" t="s">
-        <v>310</v>
-      </c>
-      <c r="C8" s="229" t="s">
-        <v>329</v>
-      </c>
-      <c r="D8" s="230">
+      <c r="B8" s="226" t="s">
+        <v>309</v>
+      </c>
+      <c r="C8" s="226" t="s">
+        <v>328</v>
+      </c>
+      <c r="D8" s="227">
         <v>6</v>
       </c>
-      <c r="E8" s="231" t="s">
-        <v>317</v>
-      </c>
-      <c r="F8" s="232" t="s">
+      <c r="E8" s="228" t="s">
+        <v>316</v>
+      </c>
+      <c r="F8" s="229" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="229"/>
-      <c r="I8" s="229" t="s">
-        <v>312</v>
-      </c>
-      <c r="J8" s="229" t="s">
-        <v>326</v>
-      </c>
-      <c r="K8" s="230">
+      <c r="G8" s="226"/>
+      <c r="I8" s="226" t="s">
+        <v>311</v>
+      </c>
+      <c r="J8" s="226" t="s">
+        <v>325</v>
+      </c>
+      <c r="K8" s="227">
         <v>8</v>
       </c>
-      <c r="L8" s="231" t="s">
-        <v>301</v>
-      </c>
-      <c r="M8" s="232" t="s">
-        <v>296</v>
-      </c>
-      <c r="N8" s="229" t="s">
-        <v>298</v>
+      <c r="L8" s="228" t="s">
+        <v>300</v>
+      </c>
+      <c r="M8" s="229" t="s">
+        <v>295</v>
+      </c>
+      <c r="N8" s="226" t="s">
+        <v>297</v>
       </c>
       <c r="Z8" t="str">
         <f t="shared" si="0"/>
@@ -11875,41 +12907,41 @@
       </c>
     </row>
     <row r="9" spans="2:26" ht="32.25">
-      <c r="B9" s="229" t="s">
-        <v>311</v>
-      </c>
-      <c r="C9" s="229" t="s">
-        <v>330</v>
-      </c>
-      <c r="D9" s="230">
+      <c r="B9" s="226" t="s">
+        <v>310</v>
+      </c>
+      <c r="C9" s="226" t="s">
+        <v>329</v>
+      </c>
+      <c r="D9" s="227">
         <v>7</v>
       </c>
-      <c r="E9" s="233" t="s">
+      <c r="E9" s="230" t="s">
+        <v>317</v>
+      </c>
+      <c r="F9" s="229" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="226">
+        <v>5</v>
+      </c>
+      <c r="I9" s="221" t="s">
+        <v>307</v>
+      </c>
+      <c r="J9" s="221" t="s">
+        <v>324</v>
+      </c>
+      <c r="K9" s="222">
+        <v>4</v>
+      </c>
+      <c r="L9" s="225" t="s">
+        <v>302</v>
+      </c>
+      <c r="M9" s="224" t="s">
+        <v>294</v>
+      </c>
+      <c r="N9" s="221" t="s">
         <v>318</v>
-      </c>
-      <c r="F9" s="232" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="229">
-        <v>5</v>
-      </c>
-      <c r="I9" s="224" t="s">
-        <v>308</v>
-      </c>
-      <c r="J9" s="224" t="s">
-        <v>325</v>
-      </c>
-      <c r="K9" s="225">
-        <v>4</v>
-      </c>
-      <c r="L9" s="228" t="s">
-        <v>303</v>
-      </c>
-      <c r="M9" s="227" t="s">
-        <v>295</v>
-      </c>
-      <c r="N9" s="224" t="s">
-        <v>319</v>
       </c>
       <c r="Z9" t="str">
         <f t="shared" si="0"/>
@@ -11917,60 +12949,60 @@
       </c>
     </row>
     <row r="10" spans="2:26" ht="32.25">
-      <c r="B10" s="229" t="s">
-        <v>312</v>
-      </c>
-      <c r="C10" s="229" t="s">
+      <c r="B10" s="226" t="s">
+        <v>311</v>
+      </c>
+      <c r="C10" s="226" t="s">
+        <v>325</v>
+      </c>
+      <c r="D10" s="227">
+        <v>8</v>
+      </c>
+      <c r="E10" s="228" t="s">
+        <v>300</v>
+      </c>
+      <c r="F10" s="229" t="s">
+        <v>295</v>
+      </c>
+      <c r="G10" s="226" t="s">
+        <v>297</v>
+      </c>
+      <c r="I10" s="226" t="s">
+        <v>319</v>
+      </c>
+      <c r="J10" s="226" t="s">
         <v>326</v>
       </c>
-      <c r="D10" s="230">
-        <v>8</v>
-      </c>
-      <c r="E10" s="231" t="s">
-        <v>301</v>
-      </c>
-      <c r="F10" s="232" t="s">
-        <v>296</v>
-      </c>
-      <c r="G10" s="229" t="s">
+      <c r="K10" s="227">
+        <v>0</v>
+      </c>
+      <c r="L10" s="229" t="s">
         <v>298</v>
       </c>
-      <c r="I10" s="229" t="s">
-        <v>320</v>
-      </c>
-      <c r="J10" s="229" t="s">
-        <v>327</v>
-      </c>
-      <c r="K10" s="230">
-        <v>0</v>
-      </c>
-      <c r="L10" s="232" t="s">
-        <v>299</v>
-      </c>
-      <c r="M10" s="232" t="s">
-        <v>299</v>
-      </c>
-      <c r="N10" s="229">
+      <c r="M10" s="229" t="s">
+        <v>298</v>
+      </c>
+      <c r="N10" s="226">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="2:26" ht="32.25">
-      <c r="B11" s="229" t="s">
-        <v>320</v>
-      </c>
-      <c r="C11" s="229" t="s">
-        <v>327</v>
-      </c>
-      <c r="D11" s="230">
+      <c r="B11" s="226" t="s">
+        <v>319</v>
+      </c>
+      <c r="C11" s="226" t="s">
+        <v>326</v>
+      </c>
+      <c r="D11" s="227">
         <v>0</v>
       </c>
-      <c r="E11" s="231" t="s">
-        <v>301</v>
-      </c>
-      <c r="F11" s="232" t="s">
-        <v>299</v>
-      </c>
-      <c r="G11" s="229">
+      <c r="E11" s="228" t="s">
+        <v>300</v>
+      </c>
+      <c r="F11" s="229" t="s">
+        <v>298</v>
+      </c>
+      <c r="G11" s="226">
         <v>7</v>
       </c>
     </row>
@@ -12080,7 +13112,7 @@
         <v>19</v>
       </c>
       <c r="CA1" s="84" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="CH1" s="17" t="s">
         <v>19</v>
@@ -12095,7 +13127,7 @@
         <v>19</v>
       </c>
       <c r="CR1" s="84" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="CS1" s="19"/>
       <c r="CZ1" s="17" t="s">
@@ -12395,7 +13427,7 @@
       <c r="AV4" s="62"/>
       <c r="BN4" s="80"/>
       <c r="BO4" s="84" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="BP4" s="81" t="s">
         <v>4</v>
@@ -12416,7 +13448,7 @@
       <c r="BW4" s="61"/>
       <c r="BX4" s="80"/>
       <c r="BY4" s="84" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="BZ4" s="86" t="s">
         <v>4</v>
@@ -12435,7 +13467,7 @@
       </c>
       <c r="CG4" s="80"/>
       <c r="CH4" s="84" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="CI4" s="86" t="s">
         <v>4</v>
@@ -12454,7 +13486,7 @@
       </c>
       <c r="CP4" s="80"/>
       <c r="CQ4" s="84" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="CR4" s="86" t="s">
         <v>4</v>
@@ -12473,7 +13505,7 @@
       </c>
       <c r="CY4" s="80"/>
       <c r="CZ4" s="84" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="DA4" s="86" t="s">
         <v>4</v>
@@ -12584,7 +13616,7 @@
         <v>ㆠ</v>
       </c>
       <c r="BS5" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT5" s="95">
         <f t="shared" ref="BT5:BT36" si="0" xml:space="preserve"> LEN(BO5)</f>
@@ -12782,7 +13814,7 @@
         <v>ㄅ</v>
       </c>
       <c r="BS6" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT6" s="95">
         <f t="shared" si="0"/>
@@ -12991,7 +14023,7 @@
         <v>ㄆ</v>
       </c>
       <c r="BS7" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT7" s="95">
         <f t="shared" si="0"/>
@@ -13168,7 +14200,7 @@
         <v>ㄇ</v>
       </c>
       <c r="BS8" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT8" s="95">
         <f t="shared" si="0"/>
@@ -13338,7 +14370,7 @@
         <v>ㄋ</v>
       </c>
       <c r="BS9" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT9" s="95">
         <f t="shared" si="0"/>
@@ -13535,7 +14567,7 @@
         <v>ㄉ</v>
       </c>
       <c r="BS10" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT10" s="95">
         <f t="shared" si="0"/>
@@ -13710,7 +14742,7 @@
         <v>ㄊ</v>
       </c>
       <c r="BS11" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT11" s="95">
         <f t="shared" si="0"/>
@@ -13886,7 +14918,7 @@
         <v>ㄌ</v>
       </c>
       <c r="BS12" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT12" s="95">
         <f t="shared" si="0"/>
@@ -13894,7 +14926,7 @@
       </c>
       <c r="BV12" s="96" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    "x": { commit: "ㄌ" }  # /ㆣ/ ==&gt; l</v>
+        <v xml:space="preserve">    "x": { commit: "ㄌ" }  # /g/ ==&gt; l</v>
       </c>
       <c r="BW12" s="97"/>
       <c r="BX12" s="91">
@@ -14073,7 +15105,7 @@
         <v>9</v>
       </c>
       <c r="BO13" s="93" t="str">
-        <v>ㆣ</v>
+        <v>g</v>
       </c>
       <c r="BP13" s="92" t="str">
         <v>g</v>
@@ -14085,7 +15117,7 @@
         <v>ㆣ</v>
       </c>
       <c r="BS13" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT13" s="95">
         <f t="shared" si="0"/>
@@ -14194,7 +15226,7 @@
         <v>ㄍ</v>
       </c>
       <c r="BS14" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT14" s="95">
         <f t="shared" si="0"/>
@@ -14363,7 +15395,7 @@
         <v>ㄎ</v>
       </c>
       <c r="BS15" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT15" s="95">
         <f t="shared" si="0"/>
@@ -14716,7 +15748,7 @@
         <v>ㄫ</v>
       </c>
       <c r="BS16" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT16" s="95">
         <f t="shared" si="0"/>
@@ -14809,7 +15841,7 @@
     <row r="17" spans="1:111" s="128" customFormat="1" ht="45" customHeight="1">
       <c r="A17" s="129"/>
       <c r="B17" s="140" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C17" s="141"/>
       <c r="D17" s="142" t="str">
@@ -14846,7 +15878,7 @@
       </c>
       <c r="L17" s="142" t="str">
         <f>xlit對映工具!K3</f>
-        <v>ㆣ</v>
+        <v>g</v>
       </c>
       <c r="M17" s="142" t="str">
         <f>xlit對映工具!L3</f>
@@ -15063,7 +16095,7 @@
         <v>ㆡ</v>
       </c>
       <c r="BS17" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT17" s="95">
         <f t="shared" si="0"/>
@@ -15409,7 +16441,7 @@
         <v>ㄗ</v>
       </c>
       <c r="BS18" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT18" s="95">
         <f t="shared" si="0"/>
@@ -15756,7 +16788,7 @@
         <v>ㄘ</v>
       </c>
       <c r="BS19" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT19" s="95">
         <f t="shared" si="0"/>
@@ -16103,7 +17135,7 @@
         <v>ㄙ</v>
       </c>
       <c r="BS20" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT20" s="95">
         <f t="shared" si="0"/>
@@ -16199,7 +17231,7 @@
         <v>ㄏ</v>
       </c>
       <c r="BS21" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT21" s="95">
         <f t="shared" si="0"/>
@@ -16244,7 +17276,7 @@
         <v>17</v>
       </c>
       <c r="CQ21" s="100" t="str">
-        <v>ㆣ</v>
+        <v>g</v>
       </c>
       <c r="CR21" s="98" t="str">
         <v>g</v>
@@ -16263,7 +17295,7 @@
       </c>
       <c r="CX21" s="103" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - xform/^", CR21, "/", CR21, "/", "      # ", CT21, " [", CQ21, "]" )</f>
-        <v xml:space="preserve">    - xform/^g/g/      # ㆣ [ㆣ]</v>
+        <v xml:space="preserve">    - xform/^g/g/      # ㆣ [g]</v>
       </c>
       <c r="CY21" s="91">
         <f t="shared" si="9"/>
@@ -16452,7 +17484,7 @@
         <v>ㆢ</v>
       </c>
       <c r="BS22" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT22" s="95">
         <f t="shared" si="0"/>
@@ -16761,7 +17793,7 @@
         <v>ㄐ</v>
       </c>
       <c r="BS23" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT23" s="95">
         <f t="shared" si="0"/>
@@ -17077,7 +18109,7 @@
         <v>ㄑ</v>
       </c>
       <c r="BS24" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT24" s="95">
         <f t="shared" si="0"/>
@@ -17199,7 +18231,7 @@
         <v>ㄒ</v>
       </c>
       <c r="BS25" s="94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT25" s="95">
         <f t="shared" si="0"/>
@@ -18119,7 +19151,7 @@
         <v>ㄜ</v>
       </c>
       <c r="BS32" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BT32" s="95">
         <f t="shared" si="0"/>
@@ -19160,7 +20192,7 @@
         <v>ㄞ</v>
       </c>
       <c r="BS40" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BT40" s="95">
         <f t="shared" si="18"/>
@@ -19324,7 +20356,7 @@
         <v>ㄠ</v>
       </c>
       <c r="BS41" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BT41" s="95">
         <f t="shared" si="18"/>
@@ -19484,7 +20516,7 @@
         <v>ㆰ</v>
       </c>
       <c r="BS42" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BT42" s="95">
         <f t="shared" si="18"/>
@@ -19631,7 +20663,7 @@
         <v>ㄢ</v>
       </c>
       <c r="BS43" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BT43" s="95">
         <f t="shared" si="18"/>
@@ -19716,7 +20748,7 @@
         <v>ㄤ</v>
       </c>
       <c r="BS44" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BT44" s="95">
         <f t="shared" si="18"/>
@@ -19791,7 +20823,7 @@
         <v>ㆱ</v>
       </c>
       <c r="BS45" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BT45" s="95">
         <f t="shared" si="18"/>
@@ -20048,7 +21080,7 @@
         <v>ㆲ</v>
       </c>
       <c r="BS46" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BT46" s="95">
         <f t="shared" si="18"/>
@@ -20365,7 +21397,7 @@
         <v>ㆩ</v>
       </c>
       <c r="BS47" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BT47" s="95">
         <f t="shared" si="18"/>
@@ -20681,7 +21713,7 @@
         <v>ㆪ</v>
       </c>
       <c r="BS48" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BT48" s="95">
         <f t="shared" si="18"/>
@@ -20764,7 +21796,7 @@
         <v>ㆫ</v>
       </c>
       <c r="BS49" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BT49" s="95">
         <f t="shared" si="18"/>
@@ -20900,7 +21932,7 @@
         <v>ㆥ</v>
       </c>
       <c r="BS50" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BT50" s="95">
         <f t="shared" si="18"/>
@@ -21039,7 +22071,7 @@
         <v>ㆧ</v>
       </c>
       <c r="BS51" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BT51" s="95">
         <f t="shared" si="18"/>
@@ -21177,7 +22209,7 @@
         <v>ㆮ</v>
       </c>
       <c r="BS52" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BT52" s="95">
         <f t="shared" si="18"/>
@@ -21322,7 +22354,7 @@
         <v>ㆯ</v>
       </c>
       <c r="BS53" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BT53" s="95">
         <f t="shared" si="18"/>
@@ -21467,7 +22499,7 @@
         <v>一</v>
       </c>
       <c r="BS54" s="94" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BT54" s="95">
         <f t="shared" si="18"/>
@@ -21606,7 +22638,7 @@
         <v>七</v>
       </c>
       <c r="BS55" s="94" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BT55" s="95">
         <f t="shared" si="18"/>
@@ -21745,7 +22777,7 @@
         <v>三</v>
       </c>
       <c r="BS56" s="94" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BT56" s="95">
         <f t="shared" si="18"/>
@@ -21821,7 +22853,7 @@
         <v>二</v>
       </c>
       <c r="BS57" s="94" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BT57" s="95">
         <f t="shared" si="18"/>
@@ -22073,7 +23105,7 @@
         <v>五</v>
       </c>
       <c r="BS58" s="94" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BT58" s="95">
         <f t="shared" si="18"/>
@@ -22385,7 +23417,7 @@
         <v>八</v>
       </c>
       <c r="BS59" s="94" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BT59" s="95">
         <f t="shared" si="18"/>
@@ -22697,7 +23729,7 @@
         <v>四</v>
       </c>
       <c r="BS60" s="94" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BT60" s="95">
         <f t="shared" si="18"/>
